--- a/data/france/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_selected.xlsx
@@ -523,23 +523,23 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2NocJFqd</t>
+          <t>zkPwWhT1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.04771034243138896</v>
+        <v>0.4975062325299829</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.6819257482875246</v>
+        <v>-1.426790339990133</v>
       </c>
       <c r="D2" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.3625183199394366</v>
+        <v>-0.9637244445914727</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.313225889958726</v>
+        <v>0.912254593610711</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -547,46 +547,46 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>-0.7879773515073688</v>
+        <v>0.3640557484013769</v>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>0.003698636191251414</v>
+        <v>-1.533832187047692</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.819703804861894</v>
+        <v>-0.2253645584913285</v>
       </c>
       <c r="P2" t="n">
-        <v>1.52381337741282</v>
+        <v>0.8346556279095972</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>-2.141032525081042</v>
+        <v>-0.08291111572906798</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9280512712835256</v>
+        <v>-0.5173131307527259</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>M5VGwpVA</t>
+          <t>2NocJFqd</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.7733859245982853</v>
+        <v>-0.04771034243138896</v>
       </c>
       <c r="C3" t="n">
-        <v>1.16664331141238</v>
+        <v>-0.6819257482875246</v>
       </c>
       <c r="D3" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.4827595448698438</v>
+        <v>-0.3625183199394366</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02206240018293621</v>
+        <v>-1.313225889958726</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -594,46 +594,46 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>0.01747659284595973</v>
+        <v>-0.8172765186092259</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>1.203876309128134</v>
+        <v>-0.1058061752262227</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3182801206980313</v>
+        <v>-1.805568477789886</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.3727279152224804</v>
+        <v>1.594987921870995</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>0.1398101616904921</v>
+        <v>-2.128768053049062</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2233300200720767</v>
+        <v>-0.9448536522253775</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>zkPwWhT1</t>
+          <t>M5VGwpVA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4975062325299829</v>
+        <v>-0.7733859245982853</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.426790339990133</v>
+        <v>1.16664331141238</v>
       </c>
       <c r="D4" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.9637244445914727</v>
+        <v>-0.4827595448698438</v>
       </c>
       <c r="F4" t="n">
-        <v>0.912254593610711</v>
+        <v>0.02206240018293621</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -641,24 +641,24 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>0.3506936338275363</v>
+        <v>0.01453286390417468</v>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>-1.510720973424865</v>
+        <v>1.228798783258803</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2063250582212901</v>
+        <v>0.3161859981688425</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8524774529504762</v>
+        <v>-0.4335840705604416</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>-0.07950524125449066</v>
+        <v>0.1135514601068885</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3435610360987559</v>
+        <v>-0.2354619640975041</v>
       </c>
     </row>
     <row r="5">
@@ -688,46 +688,46 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>0.1562604235505738</v>
+        <v>0.1221844637013675</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>-1.69190583136871</v>
+        <v>-1.710959350996687</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.01744960318108858</v>
+        <v>0.02872579858746359</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2558118088057086</v>
+        <v>0.2568964028780106</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>0.1547627093041108</v>
+        <v>0.07866951043858801</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3755432431186783</v>
+        <v>-0.3904874366614428</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>jqSiuc6F</t>
+          <t>ripawyyS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.468913228763976</v>
+        <v>-0.3894305901184459</v>
       </c>
       <c r="C6" t="n">
-        <v>1.324315378269136</v>
+        <v>0.3728460093059502</v>
       </c>
       <c r="D6" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1184465797821922</v>
+        <v>0.5994114795038209</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4671584968968236</v>
+        <v>-0.4230336965309512</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -735,46 +735,46 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>-0.4463210421262403</v>
+        <v>-0.9179928736953989</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>0.5711089222829272</v>
+        <v>1.098376265262096</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5010332776414956</v>
+        <v>-1.436165263641459</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9744616073713748</v>
+        <v>-0.2455161464675775</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
-        <v>-1.025806407101098</v>
+        <v>-2.024959240410921</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3259533119565321</v>
+        <v>-0.8056131572393376</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>ripawyyS</t>
+          <t>fHYrsJy3</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.3894305901184459</v>
+        <v>-1.522098826833972</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3728460093059502</v>
+        <v>0.329350266724776</v>
       </c>
       <c r="D7" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5994114795038209</v>
+        <v>0.3589290296430066</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4230336965309512</v>
+        <v>0.912254593610711</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -782,46 +782,46 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>-0.8648036532239175</v>
+        <v>1.402110551865392</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>1.120870003711796</v>
+        <v>-0.5607430644966563</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.445824403807327</v>
+        <v>1.399402288228303</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.2343696826820265</v>
+        <v>0.1737048639198659</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="n">
-        <v>-1.993763548507826</v>
+        <v>1.360700955803058</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8087022755812063</v>
+        <v>0.9090606609744523</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>fHYrsJy3</t>
+          <t>jqSiuc6F</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-1.522098826833972</v>
+        <v>1.468913228763976</v>
       </c>
       <c r="C8" t="n">
-        <v>0.329350266724776</v>
+        <v>1.324315378269136</v>
       </c>
       <c r="D8" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3589290296430066</v>
+        <v>0.1184465797821922</v>
       </c>
       <c r="F8" t="n">
-        <v>0.912254593610711</v>
+        <v>0.4671584968968236</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -829,46 +829,46 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>1.338978145815176</v>
+        <v>-0.4824454509960153</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>-0.5722389018497528</v>
+        <v>0.7004664426238867</v>
       </c>
       <c r="O8" t="n">
-        <v>1.412828469262016</v>
+        <v>-0.4844945523192761</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3482982959670741</v>
+        <v>1.00182528572968</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="n">
-        <v>1.372937248667634</v>
+        <v>-1.032356165778305</v>
       </c>
       <c r="S8" t="n">
-        <v>0.820525674177228</v>
+        <v>-0.310075895981842</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>SOLVXEbk</t>
+          <t>0js8u60b</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.9576844851486082</v>
+        <v>-0.8924120782870355</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.937463235951923</v>
+        <v>0.008569165188616109</v>
       </c>
       <c r="D9" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.08396566952188</v>
+        <v>-0.6030007698002511</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4230336965309512</v>
+        <v>0.4671584968968236</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
@@ -876,46 +876,46 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>-4.675514704813494</v>
+        <v>-0.7551852950700919</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>0.4571694629792017</v>
+        <v>-0.3690623047528029</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.926591745231298</v>
+        <v>-0.5293369142153455</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.663995461390644</v>
+        <v>-1.270940530605603</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="n">
-        <v>-2.165405228850827</v>
+        <v>-1.050138506447088</v>
       </c>
       <c r="S9" t="n">
-        <v>-3.020482976480897</v>
+        <v>-0.3088796499096527</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>0js8u60b</t>
+          <t>SOLVXEbk</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.8924120782870355</v>
+        <v>-0.9576844851486082</v>
       </c>
       <c r="C10" t="n">
-        <v>0.008569165188616109</v>
+        <v>-0.937463235951923</v>
       </c>
       <c r="D10" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6030007698002511</v>
+        <v>-1.08396566952188</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4671584968968236</v>
+        <v>-0.4230336965309512</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -923,24 +923,24 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>-0.7402572120286448</v>
+        <v>-4.075043717723233</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>-0.2686079151586224</v>
+        <v>0.4917721836097538</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5042702675409887</v>
+        <v>-2.03523770146395</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.355221391018643</v>
+        <v>-0.8173674620757966</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="n">
-        <v>-1.016486953456587</v>
+        <v>-2.038799267889349</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3249279581803695</v>
+        <v>-2.853209703459063</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_selected.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:S19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,23 +523,23 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2NocJFqd</t>
+          <t>OCd990al</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.04771034243138896</v>
+        <v>-0.6543597709095351</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.6819257482875246</v>
+        <v>-0.915715364661336</v>
       </c>
       <c r="D2" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.3625183199394366</v>
+        <v>-0.001794645148215033</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.313225889958726</v>
+        <v>0.02206240018293621</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -547,43 +547,43 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>-0.7879773515073688</v>
+        <v>0.3419648435880835</v>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>0.003698636191251414</v>
+        <v>0.1933340829330602</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.819703804861894</v>
+        <v>0.4245149566036423</v>
       </c>
       <c r="P2" t="n">
-        <v>1.52381337741282</v>
+        <v>-0.7876917886056025</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>-2.141032525081042</v>
+        <v>0.7351614954009811</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9280512712835256</v>
+        <v>0.5364718719604549</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>M5VGwpVA</t>
+          <t>ObHze1pe</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.7733859245982853</v>
+        <v>1.591778935797525</v>
       </c>
       <c r="C3" t="n">
-        <v>1.16664331141238</v>
+        <v>-0.3992034215098922</v>
       </c>
       <c r="D3" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.4827595448698438</v>
+        <v>-0.1220358700786222</v>
       </c>
       <c r="F3" t="n">
         <v>0.02206240018293621</v>
@@ -594,43 +594,43 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>0.01747659284595973</v>
+        <v>0.1806675135830825</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>1.203876309128134</v>
+        <v>0.3849278080810776</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3182801206980313</v>
+        <v>0.857055965007039</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.3727279152224804</v>
+        <v>-0.1537086733489567</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>0.1398101616904921</v>
+        <v>1.094657212953319</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2233300200720767</v>
+        <v>0.3600901767075884</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>zkPwWhT1</t>
+          <t>pSpI7vU0</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4975062325299829</v>
+        <v>-1.487542846730787</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.426790339990133</v>
+        <v>-1.459412146926014</v>
       </c>
       <c r="D4" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.9637244445914727</v>
+        <v>0.7196527044342281</v>
       </c>
       <c r="F4" t="n">
         <v>0.912254593610711</v>
@@ -641,46 +641,46 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>0.3506936338275363</v>
+        <v>-0.6554067251275755</v>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>-1.510720973424865</v>
+        <v>1.461757464290529</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2063250582212901</v>
+        <v>-0.02384714750775555</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8524774529504762</v>
+        <v>-0.8140645510685339</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>-0.07950524125449066</v>
+        <v>-0.1362501345797233</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3435610360987559</v>
+        <v>0.6556859855552013</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6ehlLyFq</t>
+          <t>xrJSdNFr</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.3932701434632443</v>
+        <v>1.123353427732121</v>
       </c>
       <c r="C5" t="n">
-        <v>1.617911640692062</v>
+        <v>0.5305180761627067</v>
       </c>
       <c r="D5" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1220358700786222</v>
+        <v>-0.7232419947306583</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02206240018293621</v>
+        <v>-0.4230336965309512</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -688,46 +688,46 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>0.1562604235505738</v>
+        <v>-0.8905272753361968</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>-1.69190583136871</v>
+        <v>-1.142964521741115</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.01744960318108858</v>
+        <v>-0.9972110049924313</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2558118088057086</v>
+        <v>0.4277535919358421</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>0.1547627093041108</v>
+        <v>-0.8688364518414375</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3755432431186783</v>
+        <v>-0.4044964548946376</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>jqSiuc6F</t>
+          <t>hhlQ5IbD</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.468913228763976</v>
+        <v>0.01756206443018372</v>
       </c>
       <c r="C6" t="n">
-        <v>1.324315378269136</v>
+        <v>1.509172284239127</v>
       </c>
       <c r="D6" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1184465797821922</v>
+        <v>0.4791702545734138</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4671584968968236</v>
+        <v>1.357350690324598</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -735,46 +735,46 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>-0.4463210421262403</v>
+        <v>0.8119040904601154</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>0.5711089222829272</v>
+        <v>0.6057457510659012</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5010332776414956</v>
+        <v>0.6029636446883671</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9744616073713748</v>
+        <v>0.1273258119710973</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
-        <v>-1.025806407101098</v>
+        <v>1.368822461879895</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3259533119565321</v>
+        <v>0.4481997630770287</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>ripawyyS</t>
+          <t>CKcVGr7E</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.3894305901184459</v>
+        <v>1.280775114868855</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3728460093059502</v>
+        <v>-0.05123748086049844</v>
       </c>
       <c r="D7" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5994114795038209</v>
+        <v>-0.1220358700786222</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4230336965309512</v>
+        <v>0.02206240018293621</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -782,46 +782,46 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>-0.8648036532239175</v>
+        <v>0.8919184860440471</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>1.120870003711796</v>
+        <v>-1.153961460538749</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.445824403807327</v>
+        <v>1.687223723945966</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.2343696826820265</v>
+        <v>-0.7110525995287366</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="n">
-        <v>-1.993763548507826</v>
+        <v>2.007695807315457</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8087022755812063</v>
+        <v>0.4879457832178255</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>fHYrsJy3</t>
+          <t>8nivFMyR</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-1.522098826833972</v>
+        <v>0.351603205427644</v>
       </c>
       <c r="C8" t="n">
-        <v>0.329350266724776</v>
+        <v>-0.4100773571551857</v>
       </c>
       <c r="D8" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3589290296430066</v>
+        <v>0.8398939293646354</v>
       </c>
       <c r="F8" t="n">
-        <v>0.912254593610711</v>
+        <v>0.02206240018293621</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -829,46 +829,46 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>1.338978145815176</v>
+        <v>0.6090610000222243</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>-0.5722389018497528</v>
+        <v>0.1414661683902286</v>
       </c>
       <c r="O8" t="n">
-        <v>1.412828469262016</v>
+        <v>0.4805850873226022</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3482982959670741</v>
+        <v>0.1119644841597436</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="n">
-        <v>1.372937248667634</v>
+        <v>0.7852438765669333</v>
       </c>
       <c r="S8" t="n">
-        <v>0.820525674177228</v>
+        <v>0.7752158972854832</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>SOLVXEbk</t>
+          <t>ppvl45N8</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.9576844851486082</v>
+        <v>-0.9116098450110275</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.937463235951923</v>
+        <v>-0.7852281369178133</v>
       </c>
       <c r="D9" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.08396566952188</v>
+        <v>1.681582503877486</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4230336965309512</v>
+        <v>2.692638980466261</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
@@ -876,46 +876,46 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>-4.675514704813494</v>
+        <v>3.888230036795427</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>0.4571694629792017</v>
+        <v>-0.1895746214276763</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.926591745231298</v>
+        <v>1.703166802291295</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.663995461390644</v>
+        <v>0.8026594335692504</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="n">
-        <v>-2.165405228850827</v>
+        <v>1.591591805975201</v>
       </c>
       <c r="S9" t="n">
-        <v>-3.020482976480897</v>
+        <v>2.339344196835786</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>0js8u60b</t>
+          <t>KQAqguF7</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.8924120782870355</v>
+        <v>0.3247263320140552</v>
       </c>
       <c r="C10" t="n">
-        <v>0.008569165188616109</v>
+        <v>-0.9755220107104505</v>
       </c>
       <c r="D10" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6030007698002511</v>
+        <v>0.2386878047125994</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4671584968968236</v>
+        <v>-0.4230336965309512</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -923,24 +923,447 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>-0.7402572120286448</v>
+        <v>-0.06011127555681518</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>-0.2686079151586224</v>
+        <v>0.07240774502748468</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5042702675409887</v>
+        <v>-0.2766915016816837</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.355221391018643</v>
+        <v>-0.2344852991873433</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="n">
-        <v>-1.016486953456587</v>
+        <v>-0.07182453274973141</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3249279581803695</v>
+        <v>-0.01519862997692718</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>zkPwWhT1</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.4975062325299829</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-1.426790339990133</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.3314773970536329</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-0.9637244445914727</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.912254593610711</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>0.3640557484013769</v>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="n">
+        <v>-1.533832187047692</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-0.2253645584913285</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.8346556279095972</v>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="n">
+        <v>-0.08291111572906798</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-0.5173131307527259</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>6ehlLyFq</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>-0.3932701434632443</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.617911640692062</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.3314773970536329</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-0.1220358700786222</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.02206240018293621</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>0.1221844637013675</v>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="n">
+        <v>-1.710959350996687</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.02872579858746359</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.2568964028780106</v>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="n">
+        <v>0.07866951043858801</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-0.3904874366614428</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>M5VGwpVA</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>-0.7733859245982853</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1.16664331141238</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.3314773970536329</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.4827595448698438</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.02206240018293621</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>0.01453286390417468</v>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="n">
+        <v>1.228798783258803</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.3161859981688425</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0.4335840705604416</v>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="n">
+        <v>0.1135514601068885</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-0.2354619640975041</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>2NocJFqd</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>-0.04771034243138896</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.6819257482875246</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.3314773970536329</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0.3625183199394366</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-1.313225889958726</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="n">
+        <v>-0.8172765186092259</v>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="n">
+        <v>-0.1058061752262227</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-1.805568477789886</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.594987921870995</v>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="n">
+        <v>-2.128768053049062</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-0.9448536522253775</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>ripawyyS</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>-0.3894305901184459</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.3728460093059502</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.3314773970536329</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.5994114795038209</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.4230336965309512</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>-0.9179928736953989</v>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="n">
+        <v>1.098376265262096</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-1.436165263641459</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-0.2455161464675775</v>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="n">
+        <v>-2.024959240410921</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-0.8056131572393376</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>fHYrsJy3</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>-1.522098826833972</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.329350266724776</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.3314773970536329</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.3589290296430066</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.912254593610711</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="n">
+        <v>1.402110551865392</v>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="n">
+        <v>-0.5607430644966563</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.399402288228303</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.1737048639198659</v>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="n">
+        <v>1.360700955803058</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.9090606609744523</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>jqSiuc6F</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.468913228763976</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1.324315378269136</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.3314773970536329</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.1184465797821922</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.4671584968968236</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="n">
+        <v>-0.4824454509960153</v>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="n">
+        <v>0.7004664426238867</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-0.4844945523192761</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.00182528572968</v>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="n">
+        <v>-1.032356165778305</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-0.310075895981842</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>0js8u60b</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>-0.8924120782870355</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.008569165188616109</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.3314773970536329</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.6030007698002511</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.4671584968968236</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="n">
+        <v>-0.7551852950700919</v>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="n">
+        <v>-0.3690623047528029</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-0.5293369142153455</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-1.270940530605603</v>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="n">
+        <v>-1.050138506447088</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-0.3088796499096527</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>SOLVXEbk</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>-0.9576844851486082</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.937463235951923</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.3314773970536329</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-1.08396566952188</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-0.4230336965309512</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="n">
+        <v>-4.075043717723233</v>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="n">
+        <v>0.4917721836097538</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-2.03523770146395</v>
+      </c>
+      <c r="P19" t="n">
+        <v>-0.8173674620757966</v>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="n">
+        <v>-2.038799267889349</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-2.853209703459063</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_selected.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S19"/>
+  <dimension ref="A1:S10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,23 +523,23 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>OCd990al</t>
+          <t>zkPwWhT1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.6543597709095351</v>
+        <v>0.4975062325299829</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.915715364661336</v>
+        <v>-1.426790339990133</v>
       </c>
       <c r="D2" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.001794645148215033</v>
+        <v>-0.9637244445914727</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02206240018293621</v>
+        <v>0.912254593610711</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -547,46 +547,46 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>0.3419648435880835</v>
+        <v>0.3640557484013769</v>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>0.1933340829330602</v>
+        <v>-1.533832187047692</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4245149566036423</v>
+        <v>-0.2253645584913285</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.7876917886056025</v>
+        <v>0.8346556279095972</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>0.7351614954009811</v>
+        <v>-0.08291111572906798</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5364718719604549</v>
+        <v>-0.5173131307527259</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ObHze1pe</t>
+          <t>2NocJFqd</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.591778935797525</v>
+        <v>-0.04771034243138896</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.3992034215098922</v>
+        <v>-0.6819257482875246</v>
       </c>
       <c r="D3" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1220358700786222</v>
+        <v>-0.3625183199394366</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02206240018293621</v>
+        <v>-1.313225889958726</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -594,46 +594,46 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>0.1806675135830825</v>
+        <v>-0.8172765186092259</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>0.3849278080810776</v>
+        <v>-0.1058061752262227</v>
       </c>
       <c r="O3" t="n">
-        <v>0.857055965007039</v>
+        <v>-1.805568477789886</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.1537086733489567</v>
+        <v>1.594987921870995</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>1.094657212953319</v>
+        <v>-2.128768053049062</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3600901767075884</v>
+        <v>-0.9448536522253775</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>pSpI7vU0</t>
+          <t>M5VGwpVA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-1.487542846730787</v>
+        <v>-0.7733859245982853</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.459412146926014</v>
+        <v>1.16664331141238</v>
       </c>
       <c r="D4" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7196527044342281</v>
+        <v>-0.4827595448698438</v>
       </c>
       <c r="F4" t="n">
-        <v>0.912254593610711</v>
+        <v>0.02206240018293621</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -641,46 +641,46 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>-0.6554067251275755</v>
+        <v>0.01453286390417468</v>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>1.461757464290529</v>
+        <v>1.228798783258803</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.02384714750775555</v>
+        <v>0.3161859981688425</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.8140645510685339</v>
+        <v>-0.4335840705604416</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>-0.1362501345797233</v>
+        <v>0.1135514601068885</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6556859855552013</v>
+        <v>-0.2354619640975041</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>xrJSdNFr</t>
+          <t>6ehlLyFq</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.123353427732121</v>
+        <v>-0.3932701434632443</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5305180761627067</v>
+        <v>1.617911640692062</v>
       </c>
       <c r="D5" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7232419947306583</v>
+        <v>-0.1220358700786222</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4230336965309512</v>
+        <v>0.02206240018293621</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -688,46 +688,46 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>-0.8905272753361968</v>
+        <v>0.1221844637013675</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>-1.142964521741115</v>
+        <v>-1.710959350996687</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9972110049924313</v>
+        <v>0.02872579858746359</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4277535919358421</v>
+        <v>0.2568964028780106</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>-0.8688364518414375</v>
+        <v>0.07866951043858801</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4044964548946376</v>
+        <v>-0.3904874366614428</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hhlQ5IbD</t>
+          <t>ripawyyS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01756206443018372</v>
+        <v>-0.3894305901184459</v>
       </c>
       <c r="C6" t="n">
-        <v>1.509172284239127</v>
+        <v>0.3728460093059502</v>
       </c>
       <c r="D6" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4791702545734138</v>
+        <v>0.5994114795038209</v>
       </c>
       <c r="F6" t="n">
-        <v>1.357350690324598</v>
+        <v>-0.4230336965309512</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -735,46 +735,46 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>0.8119040904601154</v>
+        <v>-0.9179928736953989</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>0.6057457510659012</v>
+        <v>1.098376265262096</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6029636446883671</v>
+        <v>-1.436165263641459</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1273258119710973</v>
+        <v>-0.2455161464675775</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
-        <v>1.368822461879895</v>
+        <v>-2.024959240410921</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4481997630770287</v>
+        <v>-0.8056131572393376</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>CKcVGr7E</t>
+          <t>fHYrsJy3</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.280775114868855</v>
+        <v>-1.522098826833972</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.05123748086049844</v>
+        <v>0.329350266724776</v>
       </c>
       <c r="D7" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1220358700786222</v>
+        <v>0.3589290296430066</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02206240018293621</v>
+        <v>0.912254593610711</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -782,46 +782,46 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>0.8919184860440471</v>
+        <v>1.402110551865392</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>-1.153961460538749</v>
+        <v>-0.5607430644966563</v>
       </c>
       <c r="O7" t="n">
-        <v>1.687223723945966</v>
+        <v>1.399402288228303</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.7110525995287366</v>
+        <v>0.1737048639198659</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="n">
-        <v>2.007695807315457</v>
+        <v>1.360700955803058</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4879457832178255</v>
+        <v>0.9090606609744523</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>8nivFMyR</t>
+          <t>jqSiuc6F</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.351603205427644</v>
+        <v>1.468913228763976</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.4100773571551857</v>
+        <v>1.324315378269136</v>
       </c>
       <c r="D8" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8398939293646354</v>
+        <v>0.1184465797821922</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02206240018293621</v>
+        <v>0.4671584968968236</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -829,46 +829,46 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>0.6090610000222243</v>
+        <v>-0.4824454509960153</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>0.1414661683902286</v>
+        <v>0.7004664426238867</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4805850873226022</v>
+        <v>-0.4844945523192761</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1119644841597436</v>
+        <v>1.00182528572968</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="n">
-        <v>0.7852438765669333</v>
+        <v>-1.032356165778305</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7752158972854832</v>
+        <v>-0.310075895981842</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ppvl45N8</t>
+          <t>0js8u60b</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.9116098450110275</v>
+        <v>-0.8924120782870355</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.7852281369178133</v>
+        <v>0.008569165188616109</v>
       </c>
       <c r="D9" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E9" t="n">
-        <v>1.681582503877486</v>
+        <v>-0.6030007698002511</v>
       </c>
       <c r="F9" t="n">
-        <v>2.692638980466261</v>
+        <v>0.4671584968968236</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
@@ -876,43 +876,43 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>3.888230036795427</v>
+        <v>-0.7551852950700919</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>-0.1895746214276763</v>
+        <v>-0.3690623047528029</v>
       </c>
       <c r="O9" t="n">
-        <v>1.703166802291295</v>
+        <v>-0.5293369142153455</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8026594335692504</v>
+        <v>-1.270940530605603</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="n">
-        <v>1.591591805975201</v>
+        <v>-1.050138506447088</v>
       </c>
       <c r="S9" t="n">
-        <v>2.339344196835786</v>
+        <v>-0.3088796499096527</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>KQAqguF7</t>
+          <t>SOLVXEbk</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3247263320140552</v>
+        <v>-0.9576844851486082</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.9755220107104505</v>
+        <v>-0.937463235951923</v>
       </c>
       <c r="D10" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2386878047125994</v>
+        <v>-1.08396566952188</v>
       </c>
       <c r="F10" t="n">
         <v>-0.4230336965309512</v>
@@ -923,446 +923,23 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>-0.06011127555681518</v>
+        <v>-4.075043717723233</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>0.07240774502748468</v>
+        <v>0.4917721836097538</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2766915016816837</v>
+        <v>-2.03523770146395</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.2344852991873433</v>
+        <v>-0.8173674620757966</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="n">
-        <v>-0.07182453274973141</v>
+        <v>-2.038799267889349</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.01519862997692718</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>zkPwWhT1</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0.4975062325299829</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-1.426790339990133</v>
-      </c>
-      <c r="D11" t="n">
-        <v>-0.3314773970536329</v>
-      </c>
-      <c r="E11" t="n">
-        <v>-0.9637244445914727</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.912254593610711</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="n">
-        <v>0.3640557484013769</v>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="n">
-        <v>-1.533832187047692</v>
-      </c>
-      <c r="O11" t="n">
-        <v>-0.2253645584913285</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0.8346556279095972</v>
-      </c>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="n">
-        <v>-0.08291111572906798</v>
-      </c>
-      <c r="S11" t="n">
-        <v>-0.5173131307527259</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>6ehlLyFq</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>-0.3932701434632443</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1.617911640692062</v>
-      </c>
-      <c r="D12" t="n">
-        <v>-0.3314773970536329</v>
-      </c>
-      <c r="E12" t="n">
-        <v>-0.1220358700786222</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.02206240018293621</v>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="n">
-        <v>0.1221844637013675</v>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="n">
-        <v>-1.710959350996687</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.02872579858746359</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0.2568964028780106</v>
-      </c>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="n">
-        <v>0.07866951043858801</v>
-      </c>
-      <c r="S12" t="n">
-        <v>-0.3904874366614428</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>M5VGwpVA</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>-0.7733859245982853</v>
-      </c>
-      <c r="C13" t="n">
-        <v>1.16664331141238</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.3314773970536329</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.4827595448698438</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.02206240018293621</v>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="n">
-        <v>0.01453286390417468</v>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="n">
-        <v>1.228798783258803</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.3161859981688425</v>
-      </c>
-      <c r="P13" t="n">
-        <v>-0.4335840705604416</v>
-      </c>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="n">
-        <v>0.1135514601068885</v>
-      </c>
-      <c r="S13" t="n">
-        <v>-0.2354619640975041</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>2NocJFqd</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>-0.04771034243138896</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-0.6819257482875246</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.3314773970536329</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.3625183199394366</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-1.313225889958726</v>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="n">
-        <v>-0.8172765186092259</v>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="n">
-        <v>-0.1058061752262227</v>
-      </c>
-      <c r="O14" t="n">
-        <v>-1.805568477789886</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.594987921870995</v>
-      </c>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="n">
-        <v>-2.128768053049062</v>
-      </c>
-      <c r="S14" t="n">
-        <v>-0.9448536522253775</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>ripawyyS</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>-0.3894305901184459</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.3728460093059502</v>
-      </c>
-      <c r="D15" t="n">
-        <v>-0.3314773970536329</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.5994114795038209</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-0.4230336965309512</v>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="n">
-        <v>-0.9179928736953989</v>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="n">
-        <v>1.098376265262096</v>
-      </c>
-      <c r="O15" t="n">
-        <v>-1.436165263641459</v>
-      </c>
-      <c r="P15" t="n">
-        <v>-0.2455161464675775</v>
-      </c>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="n">
-        <v>-2.024959240410921</v>
-      </c>
-      <c r="S15" t="n">
-        <v>-0.8056131572393376</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>fHYrsJy3</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>-1.522098826833972</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.329350266724776</v>
-      </c>
-      <c r="D16" t="n">
-        <v>-0.3314773970536329</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.3589290296430066</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.912254593610711</v>
-      </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="n">
-        <v>1.402110551865392</v>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="n">
-        <v>-0.5607430644966563</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.399402288228303</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0.1737048639198659</v>
-      </c>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="n">
-        <v>1.360700955803058</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.9090606609744523</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>jqSiuc6F</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1.468913228763976</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1.324315378269136</v>
-      </c>
-      <c r="D17" t="n">
-        <v>-0.3314773970536329</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.1184465797821922</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.4671584968968236</v>
-      </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="n">
-        <v>-0.4824454509960153</v>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="n">
-        <v>0.7004664426238867</v>
-      </c>
-      <c r="O17" t="n">
-        <v>-0.4844945523192761</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.00182528572968</v>
-      </c>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="n">
-        <v>-1.032356165778305</v>
-      </c>
-      <c r="S17" t="n">
-        <v>-0.310075895981842</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>0js8u60b</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>-0.8924120782870355</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.008569165188616109</v>
-      </c>
-      <c r="D18" t="n">
-        <v>-0.3314773970536329</v>
-      </c>
-      <c r="E18" t="n">
-        <v>-0.6030007698002511</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.4671584968968236</v>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="n">
-        <v>-0.7551852950700919</v>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="n">
-        <v>-0.3690623047528029</v>
-      </c>
-      <c r="O18" t="n">
-        <v>-0.5293369142153455</v>
-      </c>
-      <c r="P18" t="n">
-        <v>-1.270940530605603</v>
-      </c>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="n">
-        <v>-1.050138506447088</v>
-      </c>
-      <c r="S18" t="n">
-        <v>-0.3088796499096527</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>SOLVXEbk</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>-0.9576844851486082</v>
-      </c>
-      <c r="C19" t="n">
-        <v>-0.937463235951923</v>
-      </c>
-      <c r="D19" t="n">
-        <v>-0.3314773970536329</v>
-      </c>
-      <c r="E19" t="n">
-        <v>-1.08396566952188</v>
-      </c>
-      <c r="F19" t="n">
-        <v>-0.4230336965309512</v>
-      </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="n">
-        <v>-4.075043717723233</v>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="n">
-        <v>0.4917721836097538</v>
-      </c>
-      <c r="O19" t="n">
-        <v>-2.03523770146395</v>
-      </c>
-      <c r="P19" t="n">
-        <v>-0.8173674620757966</v>
-      </c>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="n">
-        <v>-2.038799267889349</v>
-      </c>
-      <c r="S19" t="n">
         <v>-2.853209703459063</v>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_selected.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:S18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,23 +523,23 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>zkPwWhT1</t>
+          <t>xrJSdNFr</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4975062325299829</v>
+        <v>1.123353427732121</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.426790339990133</v>
+        <v>0.5305180761627067</v>
       </c>
       <c r="D2" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.9637244445914727</v>
+        <v>-0.7232419947306583</v>
       </c>
       <c r="F2" t="n">
-        <v>0.912254593610711</v>
+        <v>-0.4230336965309512</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -547,46 +547,46 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>0.3640557484013769</v>
+        <v>-0.7660115930786068</v>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>-1.533832187047692</v>
+        <v>-1.045787651161129</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.2253645584913285</v>
+        <v>-1.003966295251164</v>
       </c>
       <c r="P2" t="n">
-        <v>0.8346556279095972</v>
+        <v>0.6344817964525374</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>-0.08291111572906798</v>
+        <v>-0.9050597798729464</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5173131307527259</v>
+        <v>-0.3365571372653608</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2NocJFqd</t>
+          <t>ObHze1pe</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.04771034243138896</v>
+        <v>1.591778935797525</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.6819257482875246</v>
+        <v>-0.3992034215098922</v>
       </c>
       <c r="D3" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.3625183199394366</v>
+        <v>-0.1220358700786222</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.313225889958726</v>
+        <v>0.02206240018293621</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -594,43 +594,43 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>-0.8172765186092259</v>
+        <v>0.1481384419647008</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>-0.1058061752262227</v>
+        <v>0.292130110633695</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.805568477789886</v>
+        <v>0.9561917255387056</v>
       </c>
       <c r="P3" t="n">
-        <v>1.594987921870995</v>
+        <v>0.03660885460768826</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>-2.128768053049062</v>
+        <v>1.157798745178357</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9448536522253775</v>
+        <v>0.325220391774471</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>M5VGwpVA</t>
+          <t>8nivFMyR</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.7733859245982853</v>
+        <v>0.351603205427644</v>
       </c>
       <c r="C4" t="n">
-        <v>1.16664331141238</v>
+        <v>-0.4100773571551857</v>
       </c>
       <c r="D4" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4827595448698438</v>
+        <v>0.8398939293646354</v>
       </c>
       <c r="F4" t="n">
         <v>0.02206240018293621</v>
@@ -641,43 +641,43 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>0.01453286390417468</v>
+        <v>0.4699276141396709</v>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>1.228798783258803</v>
+        <v>0.2150692090272017</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3161859981688425</v>
+        <v>0.501913725282361</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.4335840705604416</v>
+        <v>-0.09573306519164995</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>0.1135514601068885</v>
+        <v>0.6189228094181555</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2354619640975041</v>
+        <v>0.70556173006165</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6ehlLyFq</t>
+          <t>OCd990al</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.3932701434632443</v>
+        <v>-0.6543597709095351</v>
       </c>
       <c r="C5" t="n">
-        <v>1.617911640692062</v>
+        <v>-0.915715364661336</v>
       </c>
       <c r="D5" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1220358700786222</v>
+        <v>-0.001794645148215033</v>
       </c>
       <c r="F5" t="n">
         <v>0.02206240018293621</v>
@@ -688,43 +688,43 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>0.1221844637013675</v>
+        <v>0.3649303242542564</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>-1.710959350996687</v>
+        <v>0.01797113376443251</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02872579858746359</v>
+        <v>0.4311114425705788</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2568964028780106</v>
+        <v>-0.5679254942975149</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>0.07866951043858801</v>
+        <v>0.8821119982479788</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3904874366614428</v>
+        <v>0.5480724198983898</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ripawyyS</t>
+          <t>KQAqguF7</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.3894305901184459</v>
+        <v>0.3247263320140552</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3728460093059502</v>
+        <v>-0.9755220107104505</v>
       </c>
       <c r="D6" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5994114795038209</v>
+        <v>0.2386878047125994</v>
       </c>
       <c r="F6" t="n">
         <v>-0.4230336965309512</v>
@@ -735,46 +735,46 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>-0.9179928736953989</v>
+        <v>-0.03172871811431431</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>1.098376265262096</v>
+        <v>0.02652079000775457</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.436165263641459</v>
+        <v>-0.2986290460383922</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2455161464675775</v>
+        <v>-0.43339266205816</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
-        <v>-2.024959240410921</v>
+        <v>-0.05165501515695082</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8056131572393376</v>
+        <v>-0.01519862997692718</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>fHYrsJy3</t>
+          <t>CKcVGr7E</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-1.522098826833972</v>
+        <v>1.280775114868855</v>
       </c>
       <c r="C7" t="n">
-        <v>0.329350266724776</v>
+        <v>-0.05123748086049844</v>
       </c>
       <c r="D7" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3589290296430066</v>
+        <v>-0.1220358700786222</v>
       </c>
       <c r="F7" t="n">
-        <v>0.912254593610711</v>
+        <v>0.02206240018293621</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -782,46 +782,46 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>1.402110551865392</v>
+        <v>0.7239963788051578</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>-0.5607430644966563</v>
+        <v>-1.303771522828518</v>
       </c>
       <c r="O7" t="n">
-        <v>1.399402288228303</v>
+        <v>1.636113522437384</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1737048639198659</v>
+        <v>-0.625442967160646</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="n">
-        <v>1.360700955803058</v>
+        <v>1.931778623206189</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9090606609744523</v>
+        <v>0.5103510700246302</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jqSiuc6F</t>
+          <t>pSpI7vU0</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.468913228763976</v>
+        <v>-1.487542846730787</v>
       </c>
       <c r="C8" t="n">
-        <v>1.324315378269136</v>
+        <v>-1.459412146926014</v>
       </c>
       <c r="D8" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1184465797821922</v>
+        <v>0.7196527044342281</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4671584968968236</v>
+        <v>0.912254593610711</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -829,46 +829,46 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>-0.4824454509960153</v>
+        <v>-0.6001845623884667</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>0.7004664426238867</v>
+        <v>1.37595746239825</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4844945523192761</v>
+        <v>-0.05320166870626593</v>
       </c>
       <c r="P8" t="n">
-        <v>1.00182528572968</v>
+        <v>-0.7864772281158374</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="n">
-        <v>-1.032356165778305</v>
+        <v>-0.1174928389157254</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.310075895981842</v>
+        <v>0.6021091894674917</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>0js8u60b</t>
+          <t>ppvl45N8</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.8924120782870355</v>
+        <v>-0.9116098450110275</v>
       </c>
       <c r="C9" t="n">
-        <v>0.008569165188616109</v>
+        <v>-0.7852281369178133</v>
       </c>
       <c r="D9" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6030007698002511</v>
+        <v>1.681582503877486</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4671584968968236</v>
+        <v>2.692638980466261</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
@@ -876,46 +876,46 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>-0.7551852950700919</v>
+        <v>3.823864188143704</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>-0.3690623047528029</v>
+        <v>-0.3546133857015877</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5293369142153455</v>
+        <v>1.841704001740234</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.270940530605603</v>
+        <v>0.6802629409281883</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="n">
-        <v>-1.050138506447088</v>
+        <v>1.756074083115175</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3088796499096527</v>
+        <v>2.41628828238018</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>SOLVXEbk</t>
+          <t>zkPwWhT1</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.9576844851486082</v>
+        <v>0.4975062325299829</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.937463235951923</v>
+        <v>-1.426790339990133</v>
       </c>
       <c r="D10" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.08396566952188</v>
+        <v>-0.9637244445914727</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4230336965309512</v>
+        <v>0.912254593610711</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -923,24 +923,400 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>-4.075043717723233</v>
+        <v>0.2778011403590083</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>0.4917721836097538</v>
+        <v>-1.432444367451535</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.03523770146395</v>
+        <v>-0.1914169285454702</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.8173674620757966</v>
+        <v>0.6956523967730938</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="n">
-        <v>-2.038799267889349</v>
+        <v>-0.1664883538575814</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.853209703459063</v>
+        <v>-0.4217535845464235</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>6ehlLyFq</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>-0.3932701434632443</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.617911640692062</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.3314773970536329</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-0.1220358700786222</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.02206240018293621</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>0.1692960007598572</v>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="n">
+        <v>-1.656621535761338</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-0.06582383360528934</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.09941300643103226</v>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="n">
+        <v>0.1224968037170665</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-0.3556176517283254</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>M5VGwpVA</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>-0.7733859245982853</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.16664331141238</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.3314773970536329</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-0.4827595448698438</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.02206240018293621</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>0.04120612100820847</v>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="n">
+        <v>1.170646343620567</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.3010629433039032</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-0.4221893453397607</v>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="n">
+        <v>0.2387764831419047</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-0.201138995774058</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>2NocJFqd</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>-0.04771034243138896</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.6819257482875246</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.3314773970536329</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.3625183199394366</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-1.313225889958726</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>-0.7852199013621108</v>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="n">
+        <v>0.1778725045979098</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-1.76622200958901</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.275643920066095</v>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="n">
+        <v>-2.220613514940311</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-0.9507613386752518</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>ripawyyS</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>-0.3894305901184459</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.3728460093059502</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.3314773970536329</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.5994114795038209</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.4230336965309512</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="n">
+        <v>-0.7934419532529534</v>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="n">
+        <v>1.063233106837157</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-1.462080029940132</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-0.07065272862585056</v>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="n">
+        <v>-1.96560699876566</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-0.7359589900155045</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>fHYrsJy3</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>-1.522098826833972</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.329350266724776</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.3314773970536329</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.3589290296430066</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.912254593610711</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>1.257836596698672</v>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="n">
+        <v>-0.5413114902278765</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.413888246585326</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.3388792921183025</v>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="n">
+        <v>1.316637003421563</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.7024790251142622</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>jqSiuc6F</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.468913228763976</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1.324315378269136</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.3314773970536329</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.1184465797821922</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.4671584968968236</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="n">
+        <v>-0.3508654030271136</v>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="n">
+        <v>0.5471297149881588</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-0.5261093478672345</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.065768971708677</v>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="n">
+        <v>-0.9476160785860009</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-0.4019035651852597</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>0js8u60b</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>-0.8924120782870355</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.008569165188616109</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.3314773970536329</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-0.6030007698002511</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.4671584968968236</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="n">
+        <v>-0.705139156053646</v>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="n">
+        <v>-0.2477901807502743</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-0.5104269877767955</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-1.309148021460257</v>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="n">
+        <v>-1.068380875916484</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-0.2131342262168804</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>SOLVXEbk</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>-0.9576844851486082</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.937463235951923</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.3314773970536329</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-1.08396566952188</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-0.4230336965309512</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="n">
+        <v>-4.014942965405655</v>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="n">
+        <v>0.6286540799889889</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-2.149038078536879</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-0.7679450563159238</v>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="n">
+        <v>-2.203568862779601</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-2.867817189214581</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_selected.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S18"/>
+  <dimension ref="A1:S19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,446 +523,504 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>xrJSdNFr</t>
+          <t>6ZfxDZ5t</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.123353427732121</v>
+        <v>1.280775114868855</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5305180761627067</v>
+        <v>-0.937463235951923</v>
       </c>
       <c r="D2" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.7232419947306583</v>
+        <v>-2.526860368686766</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.4230336965309512</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
+        <v>-2.2034180833865</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-1.940313130496242</v>
+      </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="n">
+        <v>-2.322839734237166</v>
+      </c>
       <c r="L2" t="n">
-        <v>-0.7660115930786068</v>
+        <v>-3.791188403310099</v>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>-1.045787651161129</v>
+        <v>0.06241390935039094</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.003966295251164</v>
+        <v>-1.009148812235373</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6344817964525374</v>
+        <v>-1.120066975937771</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>-0.9050597798729464</v>
+        <v>-1.335734579044827</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3365571372653608</v>
+        <v>-2.497586615359341</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ObHze1pe</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.591778935797525</v>
+        <v>1.468913228763976</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.3992034215098922</v>
+        <v>0.5305180761627067</v>
       </c>
       <c r="D3" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1220358700786222</v>
+        <v>0.4791702545734138</v>
       </c>
       <c r="F3" t="n">
         <v>0.02206240018293621</v>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>-1.08690139601271</v>
+      </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>0.1481384419647008</v>
+        <v>-0.7628195923695251</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>0.292130110633695</v>
+        <v>0.4553699639032255</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9561917255387056</v>
+        <v>-0.344910160723087</v>
       </c>
       <c r="P3" t="n">
-        <v>0.03660885460768826</v>
+        <v>0.7476926128442786</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>1.157798745178357</v>
+        <v>-1.152590823766842</v>
       </c>
       <c r="S3" t="n">
-        <v>0.325220391774471</v>
+        <v>-0.9055083734955436</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>8nivFMyR</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.351603205427644</v>
+        <v>-0.9576844851486082</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.4100773571551857</v>
+        <v>-0.3992034215098922</v>
       </c>
       <c r="D4" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8398939293646354</v>
+        <v>-0.4827595448698438</v>
       </c>
       <c r="F4" t="n">
         <v>0.02206240018293621</v>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>-1.08690139601271</v>
+      </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>0.4699276141396709</v>
+        <v>0.1041679836785226</v>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>0.2150692090272017</v>
+        <v>-0.1899945045454065</v>
       </c>
       <c r="O4" t="n">
-        <v>0.501913725282361</v>
+        <v>0.6323042645621348</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.09573306519164995</v>
+        <v>0.3121830830724476</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>0.6189228094181555</v>
+        <v>0.7987871012142048</v>
       </c>
       <c r="S4" t="n">
-        <v>0.70556173006165</v>
+        <v>-0.01519862997692718</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>OCd990al</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.6543597709095351</v>
+        <v>-0.04771034243138896</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.915715364661336</v>
+        <v>0.3728460093059502</v>
       </c>
       <c r="D5" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.001794645148215033</v>
+        <v>-0.4827595448698438</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02206240018293621</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+        <v>-0.4230336965309512</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0.2334896615291791</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-1.569124830594241</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-0.6125136550637249</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-0.3572502892232755</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.057921702696035</v>
+      </c>
       <c r="L5" t="n">
-        <v>0.3649303242542564</v>
+        <v>-0.8689877292020191</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>0.01797113376443251</v>
+        <v>1.568031410373552</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4311114425705788</v>
+        <v>-1.345102345459794</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.5679254942975149</v>
+        <v>0.6238238645793514</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>0.8821119982479788</v>
+        <v>-2.053368754545011</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5480724198983898</v>
+        <v>-0.6981045704285569</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>KQAqguF7</t>
+          <t>IgtCPCkn</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3247263320140552</v>
+        <v>-1.522098826833972</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.9755220107104505</v>
+        <v>-0.6819257482875246</v>
       </c>
       <c r="D6" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2386878047125994</v>
+        <v>1.200617604155857</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4230336965309512</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+        <v>0.912254593610711</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0.2334896615291791</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.1931863155641903</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.7737629918402692</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.250417846856467</v>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>-0.03172871811431431</v>
+        <v>0.582111690094425</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>0.02652079000775457</v>
+        <v>-1.143815265312986</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2986290460383922</v>
+        <v>-0.06323410207752374</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.43339266205816</v>
+        <v>1.081504216473647</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
-        <v>-0.05165501515695082</v>
+        <v>0.05886543785175675</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.01519862997692718</v>
+        <v>-0.1471634636296043</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>CKcVGr7E</t>
+          <t>tYQyK8JN</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.280775114868855</v>
+        <v>-0.3932701434632443</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.05123748086049844</v>
+        <v>0.008569165188616109</v>
       </c>
       <c r="D7" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1220358700786222</v>
+        <v>-2.767342818547581</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02206240018293621</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+        <v>-0.8681297932448386</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-1.940313130496242</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.4676803642452214</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-1.07460587069839</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-0.6469911932321357</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-0.6794662660060118</v>
+      </c>
       <c r="L7" t="n">
-        <v>0.7239963788051578</v>
+        <v>-0.8194898726967851</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>-1.303771522828518</v>
+        <v>-1.891817829206164</v>
       </c>
       <c r="O7" t="n">
-        <v>1.636113522437384</v>
+        <v>-0.9826254415766533</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.625442967160646</v>
+        <v>-1.018027381339254</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="n">
-        <v>1.931778623206189</v>
+        <v>-1.018636166568021</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5103510700246302</v>
+        <v>-0.6697935064066921</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>pSpI7vU0</t>
+          <t>6FCg7VZH</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-1.487542846730787</v>
+        <v>-0.7733859245982853</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.459412146926014</v>
+        <v>1.617911640692062</v>
       </c>
       <c r="D8" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7196527044342281</v>
+        <v>-0.2422770950090294</v>
       </c>
       <c r="F8" t="n">
-        <v>0.912254593610711</v>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+        <v>-0.4230336965309512</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-0.2334896615291791</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.2473914709754175</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.7737629918402692</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.250417846856467</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-1.515986399084776</v>
+      </c>
       <c r="L8" t="n">
-        <v>-0.6001845623884667</v>
+        <v>0.1343238500150756</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>1.37595746239825</v>
+        <v>-0.7081796698352379</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.05320166870626593</v>
+        <v>0.01795153817480565</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.7864772281158374</v>
+        <v>0.2781703677058301</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="n">
-        <v>-0.1174928389157254</v>
+        <v>0.1349138269196955</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6021091894674917</v>
+        <v>-0.05453524821421407</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ppvl45N8</t>
+          <t>bk9o9i55</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.9116098450110275</v>
+        <v>-0.8924120782870355</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.7852281369178133</v>
+        <v>0.329350266724776</v>
       </c>
       <c r="D9" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E9" t="n">
-        <v>1.681582503877486</v>
+        <v>-0.2422770950090294</v>
       </c>
       <c r="F9" t="n">
-        <v>2.692638980466261</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+        <v>0.02206240018293621</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.2334896615291791</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.4676803642452214</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-0.1504214394290603</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-1.516213905258716</v>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>3.823864188143704</v>
+        <v>0.3248044002730888</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>-0.3546133857015877</v>
+        <v>0.5139271928216256</v>
       </c>
       <c r="O9" t="n">
-        <v>1.841704001740234</v>
+        <v>0.9686151074431053</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6802629409281883</v>
+        <v>-0.2719502417331857</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="n">
-        <v>1.756074083115175</v>
+        <v>0.3474254260879144</v>
       </c>
       <c r="S9" t="n">
-        <v>2.41628828238018</v>
+        <v>0.3742790257911701</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>zkPwWhT1</t>
+          <t>vmgpBDzg</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4975062325299829</v>
+        <v>-1.487542846730787</v>
       </c>
       <c r="C10" t="n">
-        <v>-1.426790339990133</v>
+        <v>1.16664331141238</v>
       </c>
       <c r="D10" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9637244445914727</v>
+        <v>2.403029853459929</v>
       </c>
       <c r="F10" t="n">
         <v>0.912254593610711</v>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>-0.2334896615291791</v>
+      </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="n">
+        <v>0.9792745106971847</v>
+      </c>
       <c r="L10" t="n">
-        <v>0.2778011403590083</v>
+        <v>0.471997890686953</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>-1.432444367451535</v>
+        <v>2.429312726225035</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1914169285454702</v>
+        <v>1.15512575082037</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6956523967730938</v>
+        <v>-1.173437944404851</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="n">
-        <v>-0.1664883538575814</v>
+        <v>1.006811991276203</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4217535845464235</v>
+        <v>0.9178495900452143</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>6ehlLyFq</t>
+          <t>hhlQ5IbD</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.3932701434632443</v>
+        <v>0.01756206443018372</v>
       </c>
       <c r="C11" t="n">
-        <v>1.617911640692062</v>
+        <v>1.509172284239127</v>
       </c>
       <c r="D11" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1220358700786222</v>
+        <v>0.4791702545734138</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02206240018293621</v>
+        <v>1.357350690324598</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
@@ -970,46 +1028,46 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>0.1692960007598572</v>
+        <v>0.8037190555388526</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
-        <v>-1.656621535761338</v>
+        <v>0.6507802736927751</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.06582383360528934</v>
+        <v>0.5962159892513572</v>
       </c>
       <c r="P11" t="n">
-        <v>0.09941300643103226</v>
+        <v>0.1153988204680074</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="n">
-        <v>0.1224968037170665</v>
+        <v>1.387695665392737</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3556176517283254</v>
+        <v>0.5005514816596128</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>M5VGwpVA</t>
+          <t>xrJSdNFr</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.7733859245982853</v>
+        <v>1.123353427732121</v>
       </c>
       <c r="C12" t="n">
-        <v>1.16664331141238</v>
+        <v>0.5305180761627067</v>
       </c>
       <c r="D12" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.4827595448698438</v>
+        <v>-0.7232419947306583</v>
       </c>
       <c r="F12" t="n">
-        <v>0.02206240018293621</v>
+        <v>-0.4230336965309512</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
@@ -1017,46 +1075,46 @@
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>0.04120612100820847</v>
+        <v>-0.8112217896748449</v>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>1.170646343620567</v>
+        <v>-1.179745459553833</v>
       </c>
       <c r="O12" t="n">
-        <v>0.3010629433039032</v>
+        <v>-1.009753490115673</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.4221893453397607</v>
+        <v>0.4007706574176597</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="n">
-        <v>0.2387764831419047</v>
+        <v>-0.9552731792707884</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.201138995774058</v>
+        <v>-0.4914170159881233</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>2NocJFqd</t>
+          <t>8nivFMyR</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.04771034243138896</v>
+        <v>0.351603205427644</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.6819257482875246</v>
+        <v>-0.4100773571551857</v>
       </c>
       <c r="D13" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.3625183199394366</v>
+        <v>0.8398939293646354</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.313225889958726</v>
+        <v>0.02206240018293621</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
@@ -1064,46 +1122,46 @@
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>-0.7852199013621108</v>
+        <v>0.5223580149944398</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
-        <v>0.1778725045979098</v>
+        <v>0.1656711951768826</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.76622200958901</v>
+        <v>0.4537593777237267</v>
       </c>
       <c r="P13" t="n">
-        <v>1.275643920066095</v>
+        <v>-0.05553397489161699</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="n">
-        <v>-2.220613514940311</v>
+        <v>0.7102066415033742</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9507613386752518</v>
+        <v>0.6677073104747026</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>ripawyyS</t>
+          <t>ObHze1pe</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.3894305901184459</v>
+        <v>1.591778935797525</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3728460093059502</v>
+        <v>-0.3992034215098922</v>
       </c>
       <c r="D14" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5994114795038209</v>
+        <v>-0.1220358700786222</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4230336965309512</v>
+        <v>0.02206240018293621</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
@@ -1111,46 +1169,46 @@
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>-0.7934419532529534</v>
+        <v>0.1697346675580974</v>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="n">
-        <v>1.063233106837157</v>
+        <v>0.2239608515202577</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.462080029940132</v>
+        <v>0.9313449617299121</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.07065272862585056</v>
+        <v>0.1053661066916915</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="n">
-        <v>-1.96560699876566</v>
+        <v>1.168202380051884</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7359589900155045</v>
+        <v>0.4066011420144549</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>fHYrsJy3</t>
+          <t>OCd990al</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-1.522098826833972</v>
+        <v>-0.6543597709095351</v>
       </c>
       <c r="C15" t="n">
-        <v>0.329350266724776</v>
+        <v>-0.915715364661336</v>
       </c>
       <c r="D15" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3589290296430066</v>
+        <v>-0.001794645148215033</v>
       </c>
       <c r="F15" t="n">
-        <v>0.912254593610711</v>
+        <v>0.02206240018293621</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
@@ -1158,46 +1216,46 @@
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>1.257836596698672</v>
+        <v>0.3477293639130817</v>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
-        <v>-0.5413114902278765</v>
+        <v>-0.01216165468426112</v>
       </c>
       <c r="O15" t="n">
-        <v>1.413888246585326</v>
+        <v>0.4550786749171127</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3388792921183025</v>
+        <v>-0.456583046150979</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="n">
-        <v>1.316637003421563</v>
+        <v>0.8959298419778611</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7024790251142622</v>
+        <v>0.4652671618902298</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>jqSiuc6F</t>
+          <t>KQAqguF7</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.468913228763976</v>
+        <v>0.3247263320140552</v>
       </c>
       <c r="C16" t="n">
-        <v>1.324315378269136</v>
+        <v>-0.9755220107104505</v>
       </c>
       <c r="D16" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1184465797821922</v>
+        <v>0.2386878047125994</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4671584968968236</v>
+        <v>-0.4230336965309512</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
@@ -1205,46 +1263,46 @@
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>-0.3508654030271136</v>
+        <v>-0.03272576761724501</v>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="n">
-        <v>0.5471297149881588</v>
+        <v>0.03130859750402006</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5261093478672345</v>
+        <v>-0.2838376948125331</v>
       </c>
       <c r="P16" t="n">
-        <v>1.065768971708677</v>
+        <v>-0.2646428603361297</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="n">
-        <v>-0.9476160785860009</v>
+        <v>-0.02544670688870301</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4019035651852597</v>
+        <v>-0.01519862997692718</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>0js8u60b</t>
+          <t>CKcVGr7E</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.8924120782870355</v>
+        <v>1.280775114868855</v>
       </c>
       <c r="C17" t="n">
-        <v>0.008569165188616109</v>
+        <v>-0.05123748086049844</v>
       </c>
       <c r="D17" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6030007698002511</v>
+        <v>-0.1220358700786222</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4671584968968236</v>
+        <v>0.02206240018293621</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
@@ -1252,46 +1310,46 @@
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>-0.705139156053646</v>
+        <v>0.7963715409071193</v>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="n">
-        <v>-0.2477901807502743</v>
+        <v>-1.138757457561532</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5104269877767955</v>
+        <v>1.658992334599374</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.309148021460257</v>
+        <v>-0.7429710774502449</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="n">
-        <v>-1.068380875916484</v>
+        <v>1.887440145217044</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2131342262168804</v>
+        <v>0.5629831856689673</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>SOLVXEbk</t>
+          <t>pSpI7vU0</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.9576844851486082</v>
+        <v>-1.487542846730787</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.937463235951923</v>
+        <v>-1.459412146926014</v>
       </c>
       <c r="D18" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.08396566952188</v>
+        <v>0.7196527044342281</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4230336965309512</v>
+        <v>0.912254593610711</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
@@ -1299,24 +1357,71 @@
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>-4.014942965405655</v>
+        <v>-0.5889686421743903</v>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="n">
-        <v>0.6286540799889889</v>
+        <v>1.365224621207135</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.149038078536879</v>
+        <v>-0.03944899493277701</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7679450563159238</v>
+        <v>-0.9535107592740711</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="n">
-        <v>-2.203568862779601</v>
+        <v>-0.07803965168332798</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.867817189214581</v>
+        <v>0.7328070983632824</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>ppvl45N8</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>-0.9116098450110275</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.7852281369178133</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.3314773970536329</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.681582503877486</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.692638980466261</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="n">
+        <v>4.24374407464747</v>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="n">
+        <v>-0.324712150442819</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.724984679626932</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.6721269439578612</v>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="n">
+        <v>1.838930676538943</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.662908017297287</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_selected.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S18"/>
+  <dimension ref="A1:S19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,58 +523,62 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>xrJSdNFr</t>
+          <t>6ZfxDZ5t</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.123353427732121</v>
+        <v>1.280775114868855</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5305180761627067</v>
+        <v>-0.937463235951923</v>
       </c>
       <c r="D2" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.7232419947306583</v>
+        <v>-2.526860368686766</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.4230336965309512</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
+        <v>-2.2034180833865</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-1.940313130496242</v>
+      </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="n">
+        <v>-2.322839734237166</v>
+      </c>
       <c r="L2" t="n">
-        <v>-0.7660115930786068</v>
+        <v>-3.791188403310099</v>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>-1.045787651161129</v>
+        <v>0.06241390935039094</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.003966295251164</v>
+        <v>-1.009148812235373</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6344817964525374</v>
+        <v>-1.120066975937771</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>-0.9050597798729464</v>
+        <v>-1.335734579044827</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3365571372653608</v>
+        <v>-2.497586615359341</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ObHze1pe</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.591778935797525</v>
+        <v>-0.9576844851486082</v>
       </c>
       <c r="C3" t="n">
         <v>-0.3992034215098922</v>
@@ -583,386 +587,440 @@
         <v>-0.3314773970536329</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1220358700786222</v>
+        <v>-0.4827595448698438</v>
       </c>
       <c r="F3" t="n">
         <v>0.02206240018293621</v>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>-1.08690139601271</v>
+      </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>0.1481384419647008</v>
+        <v>0.1041679836785226</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>0.292130110633695</v>
+        <v>-0.1899945045454065</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9561917255387056</v>
+        <v>0.6323042645621348</v>
       </c>
       <c r="P3" t="n">
-        <v>0.03660885460768826</v>
+        <v>0.3121830830724476</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>1.157798745178357</v>
+        <v>0.7987871012142048</v>
       </c>
       <c r="S3" t="n">
-        <v>0.325220391774471</v>
+        <v>-0.01519862997692718</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>8nivFMyR</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.351603205427644</v>
+        <v>-0.04771034243138896</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.4100773571551857</v>
+        <v>0.3728460093059502</v>
       </c>
       <c r="D4" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8398939293646354</v>
+        <v>-0.4827595448698438</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02206240018293621</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+        <v>-0.4230336965309512</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0.2334896615291791</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-1.569124830594241</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-0.6125136550637249</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-0.3572502892232755</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.057921702696035</v>
+      </c>
       <c r="L4" t="n">
-        <v>0.4699276141396709</v>
+        <v>-0.8689877292020191</v>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>0.2150692090272017</v>
+        <v>1.568031410373552</v>
       </c>
       <c r="O4" t="n">
-        <v>0.501913725282361</v>
+        <v>-1.345102345459794</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.09573306519164995</v>
+        <v>0.6238238645793514</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>0.6189228094181555</v>
+        <v>-2.053368754545011</v>
       </c>
       <c r="S4" t="n">
-        <v>0.70556173006165</v>
+        <v>-0.6981045704285569</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>OCd990al</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.6543597709095351</v>
+        <v>1.468913228763976</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.915715364661336</v>
+        <v>0.5305180761627067</v>
       </c>
       <c r="D5" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.001794645148215033</v>
+        <v>0.4791702545734138</v>
       </c>
       <c r="F5" t="n">
         <v>0.02206240018293621</v>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>-1.08690139601271</v>
+      </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>0.3649303242542564</v>
+        <v>-0.7628195923695251</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>0.01797113376443251</v>
+        <v>0.4553699639032255</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4311114425705788</v>
+        <v>-0.344910160723087</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.5679254942975149</v>
+        <v>0.7476926128442786</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>0.8821119982479788</v>
+        <v>-1.152590823766842</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5480724198983898</v>
+        <v>-0.9055083734955436</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>KQAqguF7</t>
+          <t>IgtCPCkn</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3247263320140552</v>
+        <v>-1.522098826833972</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.9755220107104505</v>
+        <v>-0.6819257482875246</v>
       </c>
       <c r="D6" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2386878047125994</v>
+        <v>1.200617604155857</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4230336965309512</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+        <v>0.912254593610711</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0.2334896615291791</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.1931863155641903</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.7737629918402692</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.250417846856467</v>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>-0.03172871811431431</v>
+        <v>0.582111690094425</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>0.02652079000775457</v>
+        <v>-1.143815265312986</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2986290460383922</v>
+        <v>-0.06323410207752374</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.43339266205816</v>
+        <v>1.081504216473647</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
-        <v>-0.05165501515695082</v>
+        <v>0.05886543785175675</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.01519862997692718</v>
+        <v>-0.1471634636296043</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>CKcVGr7E</t>
+          <t>tYQyK8JN</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.280775114868855</v>
+        <v>-0.3932701434632443</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.05123748086049844</v>
+        <v>0.008569165188616109</v>
       </c>
       <c r="D7" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1220358700786222</v>
+        <v>-2.767342818547581</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02206240018293621</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+        <v>-0.8681297932448386</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-1.940313130496242</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.4676803642452214</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-1.07460587069839</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-0.6469911932321357</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-0.6794662660060118</v>
+      </c>
       <c r="L7" t="n">
-        <v>0.7239963788051578</v>
+        <v>-0.8194898726967851</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>-1.303771522828518</v>
+        <v>-1.891817829206164</v>
       </c>
       <c r="O7" t="n">
-        <v>1.636113522437384</v>
+        <v>-0.9826254415766533</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.625442967160646</v>
+        <v>-1.018027381339254</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="n">
-        <v>1.931778623206189</v>
+        <v>-1.018636166568021</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5103510700246302</v>
+        <v>-0.6697935064066921</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>pSpI7vU0</t>
+          <t>6FCg7VZH</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-1.487542846730787</v>
+        <v>-0.7733859245982853</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.459412146926014</v>
+        <v>1.617911640692062</v>
       </c>
       <c r="D8" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7196527044342281</v>
+        <v>-0.2422770950090294</v>
       </c>
       <c r="F8" t="n">
-        <v>0.912254593610711</v>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+        <v>-0.4230336965309512</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-0.2334896615291791</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.2473914709754175</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.7737629918402692</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.250417846856467</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-1.515986399084776</v>
+      </c>
       <c r="L8" t="n">
-        <v>-0.6001845623884667</v>
+        <v>0.1343238500150756</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>1.37595746239825</v>
+        <v>-0.7081796698352379</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.05320166870626593</v>
+        <v>0.01795153817480565</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.7864772281158374</v>
+        <v>0.2781703677058301</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="n">
-        <v>-0.1174928389157254</v>
+        <v>0.1349138269196955</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6021091894674917</v>
+        <v>-0.05453524821421407</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ppvl45N8</t>
+          <t>bk9o9i55</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.9116098450110275</v>
+        <v>-0.8924120782870355</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.7852281369178133</v>
+        <v>0.329350266724776</v>
       </c>
       <c r="D9" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E9" t="n">
-        <v>1.681582503877486</v>
+        <v>-0.2422770950090294</v>
       </c>
       <c r="F9" t="n">
-        <v>2.692638980466261</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+        <v>0.02206240018293621</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.2334896615291791</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.4676803642452214</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-0.1504214394290603</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-1.516213905258716</v>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>3.823864188143704</v>
+        <v>0.3248044002730888</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>-0.3546133857015877</v>
+        <v>0.5139271928216256</v>
       </c>
       <c r="O9" t="n">
-        <v>1.841704001740234</v>
+        <v>0.9686151074431053</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6802629409281883</v>
+        <v>-0.2719502417331857</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="n">
-        <v>1.756074083115175</v>
+        <v>0.3474254260879144</v>
       </c>
       <c r="S9" t="n">
-        <v>2.41628828238018</v>
+        <v>0.3742790257911701</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>zkPwWhT1</t>
+          <t>vmgpBDzg</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4975062325299829</v>
+        <v>-1.487542846730787</v>
       </c>
       <c r="C10" t="n">
-        <v>-1.426790339990133</v>
+        <v>1.16664331141238</v>
       </c>
       <c r="D10" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9637244445914727</v>
+        <v>2.403029853459929</v>
       </c>
       <c r="F10" t="n">
         <v>0.912254593610711</v>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>-0.2334896615291791</v>
+      </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="n">
+        <v>0.9792745106971847</v>
+      </c>
       <c r="L10" t="n">
-        <v>0.2778011403590083</v>
+        <v>0.471997890686953</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>-1.432444367451535</v>
+        <v>2.429312726225035</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1914169285454702</v>
+        <v>1.15512575082037</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6956523967730938</v>
+        <v>-1.173437944404851</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="n">
-        <v>-0.1664883538575814</v>
+        <v>1.006811991276203</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4217535845464235</v>
+        <v>0.9178495900452143</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>6ehlLyFq</t>
+          <t>hhlQ5IbD</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.3932701434632443</v>
+        <v>0.01756206443018372</v>
       </c>
       <c r="C11" t="n">
-        <v>1.617911640692062</v>
+        <v>1.509172284239127</v>
       </c>
       <c r="D11" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1220358700786222</v>
+        <v>0.4791702545734138</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02206240018293621</v>
+        <v>1.357350690324598</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
@@ -970,46 +1028,46 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>0.1692960007598572</v>
+        <v>0.8037190555388526</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
-        <v>-1.656621535761338</v>
+        <v>0.6507802736927751</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.06582383360528934</v>
+        <v>0.5962159892513572</v>
       </c>
       <c r="P11" t="n">
-        <v>0.09941300643103226</v>
+        <v>0.1153988204680074</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="n">
-        <v>0.1224968037170665</v>
+        <v>1.387695665392737</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3556176517283254</v>
+        <v>0.5005514816596128</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>M5VGwpVA</t>
+          <t>xrJSdNFr</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.7733859245982853</v>
+        <v>1.123353427732121</v>
       </c>
       <c r="C12" t="n">
-        <v>1.16664331141238</v>
+        <v>0.5305180761627067</v>
       </c>
       <c r="D12" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.4827595448698438</v>
+        <v>-0.7232419947306583</v>
       </c>
       <c r="F12" t="n">
-        <v>0.02206240018293621</v>
+        <v>-0.4230336965309512</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
@@ -1017,46 +1075,46 @@
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>0.04120612100820847</v>
+        <v>-0.8112217896748449</v>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>1.170646343620567</v>
+        <v>-1.179745459553833</v>
       </c>
       <c r="O12" t="n">
-        <v>0.3010629433039032</v>
+        <v>-1.009753490115673</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.4221893453397607</v>
+        <v>0.4007706574176597</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="n">
-        <v>0.2387764831419047</v>
+        <v>-0.9552731792707884</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.201138995774058</v>
+        <v>-0.4914170159881233</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>2NocJFqd</t>
+          <t>8nivFMyR</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.04771034243138896</v>
+        <v>0.351603205427644</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.6819257482875246</v>
+        <v>-0.4100773571551857</v>
       </c>
       <c r="D13" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.3625183199394366</v>
+        <v>0.8398939293646354</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.313225889958726</v>
+        <v>0.02206240018293621</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
@@ -1064,46 +1122,46 @@
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>-0.7852199013621108</v>
+        <v>0.5223580149944398</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
-        <v>0.1778725045979098</v>
+        <v>0.1656711951768826</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.76622200958901</v>
+        <v>0.4537593777237267</v>
       </c>
       <c r="P13" t="n">
-        <v>1.275643920066095</v>
+        <v>-0.05553397489161699</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="n">
-        <v>-2.220613514940311</v>
+        <v>0.7102066415033742</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9507613386752518</v>
+        <v>0.6677073104747026</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>ripawyyS</t>
+          <t>ObHze1pe</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.3894305901184459</v>
+        <v>1.591778935797525</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3728460093059502</v>
+        <v>-0.3992034215098922</v>
       </c>
       <c r="D14" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5994114795038209</v>
+        <v>-0.1220358700786222</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4230336965309512</v>
+        <v>0.02206240018293621</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
@@ -1111,46 +1169,46 @@
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>-0.7934419532529534</v>
+        <v>0.1697346675580974</v>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="n">
-        <v>1.063233106837157</v>
+        <v>0.2239608515202577</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.462080029940132</v>
+        <v>0.9313449617299121</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.07065272862585056</v>
+        <v>0.1053661066916915</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="n">
-        <v>-1.96560699876566</v>
+        <v>1.168202380051884</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7359589900155045</v>
+        <v>0.4066011420144549</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>fHYrsJy3</t>
+          <t>OCd990al</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-1.522098826833972</v>
+        <v>-0.6543597709095351</v>
       </c>
       <c r="C15" t="n">
-        <v>0.329350266724776</v>
+        <v>-0.915715364661336</v>
       </c>
       <c r="D15" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3589290296430066</v>
+        <v>-0.001794645148215033</v>
       </c>
       <c r="F15" t="n">
-        <v>0.912254593610711</v>
+        <v>0.02206240018293621</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
@@ -1158,46 +1216,46 @@
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>1.257836596698672</v>
+        <v>0.3477293639130817</v>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
-        <v>-0.5413114902278765</v>
+        <v>-0.01216165468426112</v>
       </c>
       <c r="O15" t="n">
-        <v>1.413888246585326</v>
+        <v>0.4550786749171127</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3388792921183025</v>
+        <v>-0.456583046150979</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="n">
-        <v>1.316637003421563</v>
+        <v>0.8959298419778611</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7024790251142622</v>
+        <v>0.4652671618902298</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>jqSiuc6F</t>
+          <t>KQAqguF7</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.468913228763976</v>
+        <v>0.3247263320140552</v>
       </c>
       <c r="C16" t="n">
-        <v>1.324315378269136</v>
+        <v>-0.9755220107104505</v>
       </c>
       <c r="D16" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1184465797821922</v>
+        <v>0.2386878047125994</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4671584968968236</v>
+        <v>-0.4230336965309512</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
@@ -1205,46 +1263,46 @@
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>-0.3508654030271136</v>
+        <v>-0.03272576761724501</v>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="n">
-        <v>0.5471297149881588</v>
+        <v>0.03130859750402006</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5261093478672345</v>
+        <v>-0.2838376948125331</v>
       </c>
       <c r="P16" t="n">
-        <v>1.065768971708677</v>
+        <v>-0.2646428603361297</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="n">
-        <v>-0.9476160785860009</v>
+        <v>-0.02544670688870301</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4019035651852597</v>
+        <v>-0.01519862997692718</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>0js8u60b</t>
+          <t>CKcVGr7E</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.8924120782870355</v>
+        <v>1.280775114868855</v>
       </c>
       <c r="C17" t="n">
-        <v>0.008569165188616109</v>
+        <v>-0.05123748086049844</v>
       </c>
       <c r="D17" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6030007698002511</v>
+        <v>-0.1220358700786222</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4671584968968236</v>
+        <v>0.02206240018293621</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
@@ -1252,46 +1310,46 @@
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>-0.705139156053646</v>
+        <v>0.7963715409071193</v>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="n">
-        <v>-0.2477901807502743</v>
+        <v>-1.138757457561532</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5104269877767955</v>
+        <v>1.658992334599374</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.309148021460257</v>
+        <v>-0.7429710774502449</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="n">
-        <v>-1.068380875916484</v>
+        <v>1.887440145217044</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2131342262168804</v>
+        <v>0.5629831856689673</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>SOLVXEbk</t>
+          <t>pSpI7vU0</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.9576844851486082</v>
+        <v>-1.487542846730787</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.937463235951923</v>
+        <v>-1.459412146926014</v>
       </c>
       <c r="D18" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.08396566952188</v>
+        <v>0.7196527044342281</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4230336965309512</v>
+        <v>0.912254593610711</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
@@ -1299,24 +1357,71 @@
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>-4.014942965405655</v>
+        <v>-0.5889686421743903</v>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="n">
-        <v>0.6286540799889889</v>
+        <v>1.365224621207135</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.149038078536879</v>
+        <v>-0.03944899493277701</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7679450563159238</v>
+        <v>-0.9535107592740711</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="n">
-        <v>-2.203568862779601</v>
+        <v>-0.07803965168332798</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.867817189214581</v>
+        <v>0.7328070983632824</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>ppvl45N8</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>-0.9116098450110275</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.7852281369178133</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.3314773970536329</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.681582503877486</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.692638980466261</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="n">
+        <v>4.24374407464747</v>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="n">
+        <v>-0.324712150442819</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.724984679626932</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.6721269439578612</v>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="n">
+        <v>1.838930676538943</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.662908017297287</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_selected.xlsx
@@ -1406,7 +1406,9 @@
       <c r="L19" t="n">
         <v>4.24374407464747</v>
       </c>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" t="n">
+        <v>0.9776021629251436</v>
+      </c>
       <c r="N19" t="n">
         <v>-0.324712150442819</v>
       </c>
@@ -1416,7 +1418,9 @@
       <c r="P19" t="n">
         <v>0.6721269439578612</v>
       </c>
-      <c r="Q19" t="inlineStr"/>
+      <c r="Q19" t="n">
+        <v>-0.78428741682084</v>
+      </c>
       <c r="R19" t="n">
         <v>1.838930676538943</v>
       </c>

--- a/data/france/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_selected.xlsx
@@ -425,248 +425,1896 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S4"/>
+  <dimension ref="A1:AP15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>id_team_home</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>id_team_away</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>is_cup</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>h2h_35_segun_loc</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>h2h_35</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>h2h_3_segun_loc</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>h2h_3</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_shots_on_goal_against</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls_against</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>mean_last_match_mean_rat_player_start_home_against</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>mean_last_match_mean_rat_player_start_away_against</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_val_player_sub</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_val_player_miss</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_start</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_start</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_miss</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>is_rival_match</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>KQAqguF7</t>
+          <t>6ZfxDZ5t</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3247263320140552</v>
+        <v>1.638011315230593</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.9755220107104505</v>
+        <v>1.434356868719363</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.3314773970536329</v>
+        <v>-0.8491384558266935</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2386878047125994</v>
+        <v>0.942940809258732</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.4230336965309512</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+        <v>1.374205524096437</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-0.2304341233182217</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-0.1705560731334942</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-3.208047130483493</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-1.802173782774859</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-2.566999137530125</v>
+      </c>
       <c r="L2" t="n">
-        <v>-0.03272576761724501</v>
+        <v>-0.3168419859493746</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.00234596248375403</v>
+        <v>0.02256820770482074</v>
       </c>
       <c r="N2" t="n">
-        <v>0.03130859750402006</v>
+        <v>-0.005351037217539404</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.2838376948125331</v>
+        <v>-0.0382251362397396</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.2646428603361297</v>
-      </c>
-      <c r="Q2" t="inlineStr"/>
+        <v>-0.2905195926144082</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-0.545064442987507</v>
+      </c>
       <c r="R2" t="n">
-        <v>-0.02544670688870301</v>
+        <v>-1.716473638531606</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.01519862997692718</v>
+        <v>-0.8078761484333244</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-2.908456167603774</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-0.5555118250598432</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.576143683664408</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-0.2864663542175895</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="n">
+        <v>-1.426422580272545</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-5.142309059685487</v>
+      </c>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="n">
+        <v>-0.02033440592676761</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>-2.688821830586664</v>
+      </c>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="n">
+        <v>-1.28402057009189</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.4437753571286891</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>-1.007185220929726</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>-1.102517807333721</v>
+      </c>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="n">
+        <v>-1.572739107969445</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>-3.255834176743024</v>
+      </c>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="n">
+        <v>-1.00635301316531</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>-2.082337273419576</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>-0.1244973286161158</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>CKcVGr7E</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.280775114868855</v>
+        <v>1.453818357394956</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.05123748086049844</v>
+        <v>-0.8644088099435222</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.3314773970536329</v>
+        <v>-0.2972647030472513</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1220358700786222</v>
+        <v>0.4167423534753607</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02206240018293621</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+        <v>0.3678697099325769</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-0.2304341233182217</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.2924698004996741</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-0.610951582512485</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-1.007897383813373</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.02375662033231982</v>
+      </c>
       <c r="L3" t="n">
-        <v>0.7963715409071193</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.9772298422088028</v>
-      </c>
-      <c r="N3" t="n">
-        <v>-1.138757457561532</v>
-      </c>
+        <v>-2.009408789391938</v>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>1.658992334599374</v>
+        <v>2.261902640026929</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.7429710774502449</v>
+        <v>-2.616780043755007</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.171122315021479</v>
+        <v>1.139175203184027</v>
       </c>
       <c r="R3" t="n">
-        <v>1.887440145217044</v>
+        <v>-2.469696644960085</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5629831856689673</v>
+        <v>3.509462102463153</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-0.9497785234691912</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3.094443235804783</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-0.5912489864002151</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-2.327504892377828</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.5906327669452608</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.4351681203790291</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.1453562585067054</v>
+      </c>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="n">
+        <v>-0.1808034209530883</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.1055750172136678</v>
+      </c>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="n">
+        <v>0.7706632951592588</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.380493889641392</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.8403976760258079</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.2863938153517505</v>
+      </c>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="n">
+        <v>0.9493481204015384</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>-0.01011206808736213</v>
+      </c>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="n">
+        <v>1.656116824825132</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>-0.01303597738284825</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>-0.1244973286161158</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>pSpI7vU0</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-1.487542846730787</v>
+        <v>1.545914836312775</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.459412146926014</v>
+        <v>1.62756358956753</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.3314773970536329</v>
+        <v>0.6559717790263305</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7196527044342281</v>
+        <v>-1.758211263762574</v>
       </c>
       <c r="F4" t="n">
-        <v>0.912254593610711</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+        <v>0.0135261133960064</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0.2304341233182217</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.2924698004996741</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.6112110282974008</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.5806554141095995</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.02375662033231982</v>
+      </c>
       <c r="L4" t="n">
-        <v>-0.5889686421743903</v>
+        <v>-1.906828983122691</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.01574950827202163</v>
+        <v>0.02256820770482074</v>
       </c>
       <c r="N4" t="n">
-        <v>1.365224621207135</v>
+        <v>-0.005351037217539404</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.03944899493277701</v>
+        <v>1.341851529520262</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.9535107592740711</v>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+        <v>-4.820605734309258</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.139175203184027</v>
+      </c>
       <c r="R4" t="n">
-        <v>-0.07803965168332798</v>
+        <v>-3.976142657817044</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7328070983632824</v>
+        <v>1.985695660970278</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-2.908456167603774</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.051598932700604</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-2.050489823980994</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.2966875138281929</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.7124858346939471</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-0.4952676384776727</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-1.054440375697624</v>
+      </c>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="n">
+        <v>0.4442244939232457</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-0.2685312646682247</v>
+      </c>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="n">
+        <v>-0.420517024063075</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>-0.2248327216689833</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>-0.3174350824225947</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.6972868244958977</v>
+      </c>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="n">
+        <v>-1.369526462055643</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>-1.227290207929787</v>
+      </c>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="n">
+        <v>0.5864711174291231</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>-1.038700048690099</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>-0.1244973286161158</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>SU02594U</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1.453818357394956</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.07008083987312229</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.4943117908384131</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.942940809258732</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3678697099325769</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0.2304341233182217</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.8650948835832468</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-0.610951582512485</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-1.007897383813373</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-0.4943945312401692</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-1.54779966118033</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.02256820770482074</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-0.005351037217539404</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.881825974266928</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-1.025128156132492</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-1.387184266073274</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.2921210452776735</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-0.8078761484333244</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0.9497785234691912</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-0.5555118250598432</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-1.61271757270676</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-0.4322548212290351</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-0.0704319790026163</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-1.840282701808398</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-1.197996221644789</v>
+      </c>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="n">
+        <v>1.453676153582566</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-0.9476989159176191</v>
+      </c>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="n">
+        <v>-1.676547766347071</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.2247715715663637</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-1.925885461729405</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.5441887615623552</v>
+      </c>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="n">
+        <v>-2.409869620944682</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-0.9437401546465152</v>
+      </c>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="n">
+        <v>0.05203568812216311</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-0.695841027977622</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-0.1244973286161158</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>IgtCPCkn</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.453818357394956</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-1.444028972488023</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.5871377853152412</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.03086348590088838</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.7660297989844487</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0.2304341233182217</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.144573295032348</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.527832986404815</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-0.2136209848518865</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.060058923477298</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.9141156892815804</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.02256820770482074</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.005351037217539404</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-0.4982506914930734</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.056262773835412</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.05644971635946939</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.04104670980151362</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-0.299954001269033</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.5192297096317455</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-0.03408967350775372</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-0.007552651367903501</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.754572183942649</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.1485005269621932</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.054047862282065</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.810206431619437</v>
+      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="n">
+        <v>-1.125001227593124</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.1144115718975815</v>
+      </c>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="n">
+        <v>-0.1013099134869722</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-1.353643956390671</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.4921804241906396</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.059277007033653</v>
+      </c>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="n">
+        <v>0.04927919429747567</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-0.2174071509580034</v>
+      </c>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="n">
+        <v>0.7476084298757015</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.2773309485697404</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-0.1244973286161158</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>tYQyK8JN</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.545914836312775</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.2847886473990212</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.1208214733008109</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.1211494013254189</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.74272286449447</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.2304341233182217</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-2.254172504482752</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-3.513587783185964</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-1.007897383813373</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-1.012545682812658</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.4525065610699723</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.02256820770482074</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-0.005351037217539404</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.4218004190135942</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.0767846891446337</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-0.3044587792487164</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-0.9632506321031258</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-1.569759369179762</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-4.867133811738356</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-1.076933976611933</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.576143683664408</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-0.5780432882404807</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.8088096179422681</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>-0.3164962956384968</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-1.132864580927866</v>
+      </c>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="n">
+        <v>-1.828999341403407</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-0.6144068443147668</v>
+      </c>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="n">
+        <v>-1.197863195143588</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-0.6402218220376218</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>-0.08358788706605595</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>-0.9686285048337927</v>
+      </c>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="n">
+        <v>-1.210344559973232</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>-0.9050349641283204</v>
+      </c>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="n">
+        <v>-0.07362496260912958</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>-1.433992904345862</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>-0.1244973286161158</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>6FCg7VZH</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.453818357394956</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.675145083398379</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.77086824928783</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-1.430798891275143</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.05604734498039485</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-0.2304341233182217</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.218521547766011</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-0.3054109298100136</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-0.2136209848518865</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-0.4943945312401692</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-1.086190532968721</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.02256820770482074</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-0.005351037217539404</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.881825974266928</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.199219449730981</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.101597858139189</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.045344051706153</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.985695660970278</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.5192297096317455</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3.615865387356873</v>
+      </c>
+      <c r="V8" t="n">
+        <v>2.910929023793654</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.025629848885421</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-0.0733953318175113</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.563288629369048</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.2212491408708654</v>
+      </c>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="n">
+        <v>-0.6064961694068275</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.06439279314363468</v>
+      </c>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="n">
+        <v>0.04380006566068867</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-0.5090379948501089</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.5746474595745067</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.2609536857990569</v>
+      </c>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="n">
+        <v>0.1705134105305575</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>-0.0329160425745702</v>
+      </c>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="n">
+        <v>-0.4245683917791569</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>-0.4052410627586161</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>-0.1244973286161158</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>bk9o9i55</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.453818357394956</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.7973779067921173</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.4497159320279531</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-1.793291160814799</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.260815573204735</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.2304341233182217</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.1705560731334942</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-0.3054109298100136</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.5806554141095995</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.02375662033231982</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.273145011223942</v>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="n">
+        <v>-0.9582762467464072</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.0767846891446337</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-1.507487097942669</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.5431953807538333</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-0.5539150748511786</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.008899120665391</v>
+      </c>
+      <c r="U9" t="n">
+        <v>4.137287538908963</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-1.174945321432527</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-1.452774090309154</v>
+      </c>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="n">
+        <v>0.2408205750526639</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.4506880041122437</v>
+      </c>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="n">
+        <v>0.5009364830102572</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.3914120755139429</v>
+      </c>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="n">
+        <v>1.1806110474798</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-0.2714151346006083</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.797643729222633</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>-0.2647222525251339</v>
+      </c>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="n">
+        <v>0.41298296911706</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.5223584479427571</v>
+      </c>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="n">
+        <v>0.2535324109266778</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.7163769264948451</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>-0.1244973286161158</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>vmgpBDzg</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.453818357394956</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-1.408542023760809</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.308186214129307</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.03086348590088838</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.74272286449447</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0.2304341233182217</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.8391121054821</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.055536249917173</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.374931813071086</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.060058923477298</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-1.496509758045706</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.02256820770482074</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0.005351037217539404</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.801877084773595</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-0.4129543532007556</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.703112017486166</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-1.214324967579286</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.4619292194774042</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-0.9497785234691912</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.530176781148515</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-2.050489823980994</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-2.91065876042361</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.9853365451258583</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.4294611992885234</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.6579080416419949</v>
+      </c>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="n">
+        <v>2.270430278186216</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.4837074859613015</v>
+      </c>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="n">
+        <v>1.384914855395015</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.6177083277128748</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>-0.09860808063646979</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>-1.064717962066928</v>
+      </c>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="n">
+        <v>1.200902216879667</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1.301339969429545</v>
+      </c>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="n">
+        <v>-0.4618772605239777</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1.949284112087189</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>-0.1244973286161158</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>hhlQ5IbD</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.607312488924654</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.1371117430245272</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.65937860226168</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-1.793291160814799</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.9489932082525525</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.2304341233182217</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.1705560731334942</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.6112110282974008</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.374931813071086</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.578210075049787</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.093783461377912</v>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="n">
+        <v>-2.798378467759743</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.301132295008107</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-3.432332407852994</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.551790064563112</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-0.5539150748511786</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4.926254408934556</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-1.076933976611933</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.576143683664408</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-0.8696202222633719</v>
+      </c>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="n">
+        <v>0.2947720475497861</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.113442820136443</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-0.1098230912000561</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.6334770859766959</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.4204833743722263</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.0326949765739812</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.7266733148718427</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.7847197535738653</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.05945590303603123</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.1007324869851525</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-0.5173603621389383</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.649163918962556</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.6949905841921701</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>-0.1776019725838051</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.002918637068733171</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0.3593473223106401</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1.02311486091306</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>-0.1244973286161158</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>xrJSdNFr</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.453818357394956</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.272694102295386</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.6559717790263305</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.445752667007287</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.0135261133960064</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0.2304341233182217</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.2924698004996741</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-0.9164922352149566</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.5806554141095995</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-0.4943945312401692</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.9654055924162035</v>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="n">
+        <v>0.881825974266928</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-2.616780043755007</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-2.229304089159041</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-1.967547974007765</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.477773513805987</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-1.929117345536482</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.008754629596425</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.451688186212875</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.337726051988432</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.300533567282685</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-0.5958406208672474</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-1.121422642825057</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-0.02644307020855297</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-1.139365606973121</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-0.5482626187779959</v>
+      </c>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="n">
+        <v>-1.230931063036714</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-0.01033444251915991</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>-0.2010529481030272</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0.3699741104019082</v>
+      </c>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="n">
+        <v>-1.135048627375482</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>-0.6611693135725666</v>
+      </c>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="n">
+        <v>-0.370709828862477</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0.724077854098284</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>-1.19642231886209</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>-0.1244973286161158</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>ObHze1pe</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.453818357394956</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1.753739407264292</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.2972647030472513</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.1211494013254189</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.3678697099325769</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.2304341233182217</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.7554956741328426</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-0.1526406034587778</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.5806554141095995</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.02375662033231982</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.1447671422622335</v>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="n">
+        <v>0.881825974266928</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-2.371910522582313</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-0.545064442987507</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-2.469696644960085</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.4619292194774042</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-1.929117345536482</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-1.076933976611933</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-0.8830971539163709</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-2.035927958354937</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.6824967042071594</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.6370348766560953</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.2360919147121103</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.08187651063308733</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.2201074839741273</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.2547454426332818</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.3934247694328797</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.135180420465523</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.7333315263353567</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.017131316306373</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0.09126685725348596</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.9487634617597244</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.388334177126735</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0.5665473087149022</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>-0.6996963436424987</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>-0.328009432756053</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0.5322256961077512</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1.161481925346727</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>-0.1244973286161158</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>8nivFMyR</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.607312488924654</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.4801522473875992</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.3084136677498663</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0.4017885777432169</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.05604734498039485</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0.2304341233182217</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.7554956741328426</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.069522007351108</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.5806554141095995</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.02375662033231982</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.1447671422622335</v>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="n">
+        <v>1.801877084773595</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.5665237314900229</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.34220352187798</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-0.4611019611508061</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.49361780813457</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.008899120665391</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.051598932700604</v>
+      </c>
+      <c r="V14" t="n">
+        <v>2.035384521245187</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.8798413818739753</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.4712689155610916</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.3054089651391695</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.7240761916315998</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.7984235660288179</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.1636546357862854</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.5705879944289084</v>
+      </c>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="n">
+        <v>0.5530251291675776</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.2132841158128733</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.2309265194700102</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>-0.06053858941019961</v>
+      </c>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="n">
+        <v>0.8440855908339702</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0.9235160184717908</v>
+      </c>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="n">
+        <v>1.737622228892209</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0.04976520099344014</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0.5019808013934147</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>-0.1244973286161158</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>OCd990al</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.453818357394956</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.5529122600046407</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.8268405264214634</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-1.489265386362184</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.74272286449447</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0.2304341233182217</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.06095686368308995</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.0001297228924578849</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.5806554141095995</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.02375662033231982</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.5550863673392186</v>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="n">
+        <v>-2.798378467759743</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.8113932526627176</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-0.7856701067262976</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.04104670980151362</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-1.06183722201547</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.02956029859809994</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-5.248311189028649</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-0.007552651367903501</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-0.5780432882404807</v>
+      </c>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="n">
+        <v>0.6961581072126426</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.4824131348688991</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.2713427190468156</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-0.008574392583400573</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.555440903755819</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.0326949765739812</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0.554633292955692</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.6234161493140992</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.5994681399374379</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>-0.4389189655883272</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1.082047445750512</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.064785437562568</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0.6467519762075268</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>-0.1776019725838051</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.262580322208242</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>-0.6217944364129872</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0.1897081843978529</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>-0.1244973286161158</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_selected.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP15"/>
+  <dimension ref="A1:AP10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -756,29 +756,29 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ChZKNjKb</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.453818357394956</v>
+        <v>1.607312488924654</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.8644088099435222</v>
+        <v>0.07008083987312229</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.2972647030472513</v>
+        <v>0.4943117908384131</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4167423534753607</v>
+        <v>0.942940809258732</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3678697099325769</v>
+        <v>-0.1423850690800846</v>
       </c>
       <c r="G3" t="n">
         <v>-0.2304341233182217</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2924698004996741</v>
+        <v>-0.8650948835832468</v>
       </c>
       <c r="I3" t="n">
         <v>-0.610951582512485</v>
@@ -787,83 +787,87 @@
         <v>-1.007897383813373</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02375662033231982</v>
+        <v>-0.4943945312401692</v>
       </c>
       <c r="L3" t="n">
-        <v>-2.009408789391938</v>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+        <v>-1.650379467449576</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.02256820770482074</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-0.005351037217539404</v>
+      </c>
       <c r="O3" t="n">
-        <v>2.261902640026929</v>
+        <v>0.881825974266928</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.616780043755007</v>
+        <v>-1.147562916718839</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.139175203184027</v>
+        <v>-1.266881434203879</v>
       </c>
       <c r="R3" t="n">
-        <v>-2.469696644960085</v>
+        <v>-0.2100276256746462</v>
       </c>
       <c r="S3" t="n">
-        <v>3.509462102463153</v>
+        <v>0.2079681458952584</v>
       </c>
       <c r="T3" t="n">
         <v>-0.9497785234691912</v>
       </c>
       <c r="U3" t="n">
-        <v>3.094443235804783</v>
+        <v>-0.03408967350775372</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.5912489864002151</v>
+        <v>0.1383714323901744</v>
       </c>
       <c r="W3" t="n">
-        <v>-2.327504892377828</v>
+        <v>-1.306985623297709</v>
       </c>
       <c r="X3" t="n">
-        <v>0.5906327669452608</v>
+        <v>-0.08157418558663432</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4351681203790291</v>
+        <v>-1.840347452012947</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.1453562585067054</v>
+        <v>-1.169190745063825</v>
       </c>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="n">
-        <v>-0.1808034209530883</v>
+        <v>1.468889717755221</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.1055750172136678</v>
+        <v>-0.9299825033721677</v>
       </c>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
-        <v>0.7706632951592588</v>
+        <v>-1.651969663118702</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.380493889641392</v>
+        <v>0.2756474688978721</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.8403976760258079</v>
+        <v>-1.925651549558445</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.2863938153517505</v>
+        <v>0.5435232727324034</v>
       </c>
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="n">
-        <v>0.9493481204015384</v>
+        <v>-2.376562156654253</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.01011206808736213</v>
+        <v>-0.8503773459906003</v>
       </c>
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="n">
-        <v>1.656116824825132</v>
+        <v>0.06551445298156297</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.01303597738284825</v>
+        <v>-0.6510974888260194</v>
       </c>
       <c r="AP3" t="n">
         <v>-0.1244973286161158</v>
@@ -872,23 +876,23 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>p6XSLUlB</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.545914836312775</v>
+        <v>1.453818357394956</v>
       </c>
       <c r="C4" t="n">
-        <v>1.62756358956753</v>
+        <v>-0.8644088099435222</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6559717790263305</v>
+        <v>-0.2972647030472513</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.758211263762574</v>
+        <v>1.282046480763571</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0135261133960064</v>
+        <v>-0.3975124585864154</v>
       </c>
       <c r="G4" t="n">
         <v>-0.2304341233182217</v>
@@ -897,16 +901,16 @@
         <v>0.2924698004996741</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6112110282974008</v>
+        <v>-0.610951582512485</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5806554141095995</v>
+        <v>-1.007897383813373</v>
       </c>
       <c r="K4" t="n">
         <v>0.02375662033231982</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.906828983122691</v>
+        <v>-2.009408789391938</v>
       </c>
       <c r="M4" t="n">
         <v>0.02256820770482074</v>
@@ -915,75 +919,75 @@
         <v>-0.005351037217539404</v>
       </c>
       <c r="O4" t="n">
-        <v>1.341851529520262</v>
+        <v>-0.0382251362397396</v>
       </c>
       <c r="P4" t="n">
-        <v>-4.820605734309258</v>
+        <v>-0.7802586349597975</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.139175203184027</v>
+        <v>1.740689362531003</v>
       </c>
       <c r="R4" t="n">
-        <v>-3.976142657817044</v>
+        <v>-0.7121762966269659</v>
       </c>
       <c r="S4" t="n">
-        <v>1.985695660970278</v>
+        <v>1.477773513805987</v>
       </c>
       <c r="T4" t="n">
-        <v>-2.908456167603774</v>
+        <v>0.5192297096317455</v>
       </c>
       <c r="U4" t="n">
-        <v>2.051598932700604</v>
+        <v>0.4873324780443357</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.050489823980994</v>
+        <v>0.1383714323901744</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2966875138281929</v>
+        <v>-0.8696202222633719</v>
       </c>
       <c r="X4" t="n">
-        <v>0.7124858346939471</v>
+        <v>0.5886176870311318</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.4952676384776727</v>
+        <v>0.4509543230111798</v>
       </c>
       <c r="Z4" t="n">
-        <v>-1.054440375697624</v>
+        <v>0.1534271875300206</v>
       </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="n">
-        <v>0.4442244939232457</v>
+        <v>-0.259424232716695</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.2685312646682247</v>
+        <v>0.1047453574452163</v>
       </c>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="n">
-        <v>-0.420517024063075</v>
+        <v>0.7452335961067275</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.2248327216689833</v>
+        <v>0.3545304185500082</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0.3174350824225947</v>
+        <v>0.8538889739670089</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.6972868244958977</v>
+        <v>0.2348161019936554</v>
       </c>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="n">
-        <v>-1.369526462055643</v>
+        <v>0.9935673575636876</v>
       </c>
       <c r="AK4" t="n">
-        <v>-1.227290207929787</v>
+        <v>-0.01011206808736213</v>
       </c>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="n">
-        <v>0.5864711174291231</v>
+        <v>1.677275602496138</v>
       </c>
       <c r="AO4" t="n">
-        <v>-1.038700048690099</v>
+        <v>-0.01303597738284825</v>
       </c>
       <c r="AP4" t="n">
         <v>-0.1244973286161158</v>
@@ -992,118 +996,114 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SU02594U</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1.453818357394956</v>
       </c>
       <c r="C5" t="n">
-        <v>0.07008083987312229</v>
+        <v>1.62756358956753</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4943117908384131</v>
+        <v>0.6559717790263305</v>
       </c>
       <c r="E5" t="n">
-        <v>0.942940809258732</v>
+        <v>-1.758211263762574</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3678697099325769</v>
+        <v>1.048209415282792</v>
       </c>
       <c r="G5" t="n">
         <v>-0.2304341233182217</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8650948835832468</v>
+        <v>0.2924698004996741</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.610951582512485</v>
+        <v>0.6112110282974008</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.007897383813373</v>
+        <v>0.5806554141095995</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.4943945312401692</v>
+        <v>0.02375662033231982</v>
       </c>
       <c r="L5" t="n">
         <v>-1.54779966118033</v>
       </c>
-      <c r="M5" t="n">
-        <v>0.02256820770482074</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-0.005351037217539404</v>
-      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>0.881825974266928</v>
+        <v>1.341851529520262</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.025128156132492</v>
+        <v>-3.718692889032133</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.387184266073274</v>
+        <v>1.981295026269794</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2921210452776735</v>
+        <v>-3.222919651388565</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8078761484333244</v>
+        <v>1.223812440223842</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9497785234691912</v>
+        <v>-1.929117345536482</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5555118250598432</v>
+        <v>0.4873324780443357</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.61271757270676</v>
+        <v>-2.926034326529461</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.4322548212290351</v>
+        <v>1.025629848885421</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.0704319790026163</v>
+        <v>0.6225184432335839</v>
       </c>
       <c r="Y5" t="n">
-        <v>-1.840282701808398</v>
+        <v>-0.4690637321975425</v>
       </c>
       <c r="Z5" t="n">
-        <v>-1.197996221644789</v>
+        <v>-1.030875036056839</v>
       </c>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
-        <v>1.453676153582566</v>
+        <v>0.4291055252396568</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.9476989159176191</v>
+        <v>-0.2540290058778424</v>
       </c>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
-        <v>-1.676547766347071</v>
+        <v>-0.4053034291357286</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.2247715715663637</v>
+        <v>-0.2284178378845431</v>
       </c>
       <c r="AG5" t="n">
-        <v>-1.925885461729405</v>
+        <v>-0.299253727316189</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.5441887615623552</v>
+        <v>0.7139002256896511</v>
       </c>
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="n">
-        <v>-2.409869620944682</v>
+        <v>-1.358211880677411</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.9437401546465152</v>
+        <v>-1.250768107765167</v>
       </c>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="n">
-        <v>0.05203568812216311</v>
+        <v>0.6276642410502303</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.695841027977622</v>
+        <v>-1.050616829359027</v>
       </c>
       <c r="AP5" t="n">
         <v>-0.1244973286161158</v>
@@ -1128,7 +1128,7 @@
         <v>0.03086348590088838</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7660297989844487</v>
+        <v>-1.843234332455623</v>
       </c>
       <c r="G6" t="n">
         <v>-0.2304341233182217</v>
@@ -1146,7 +1146,7 @@
         <v>1.060058923477298</v>
       </c>
       <c r="L6" t="n">
-        <v>0.9141156892815804</v>
+        <v>1.170565204954696</v>
       </c>
       <c r="M6" t="n">
         <v>0.02256820770482074</v>
@@ -1155,75 +1155,75 @@
         <v>-0.005351037217539404</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4982506914930734</v>
+        <v>-0.0382251362397396</v>
       </c>
       <c r="P6" t="n">
-        <v>1.056262773835412</v>
+        <v>-0.4129543532007556</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.05644971635946939</v>
+        <v>-0.6653672748569023</v>
       </c>
       <c r="R6" t="n">
-        <v>0.04104670980151362</v>
+        <v>-1.465399303055446</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.299954001269033</v>
+        <v>-0.04599292768688727</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5192297096317455</v>
+        <v>0.02956029859809994</v>
       </c>
       <c r="U6" t="n">
         <v>-0.03408967350775372</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.007552651367903501</v>
+        <v>-0.2994008188840592</v>
       </c>
       <c r="W6" t="n">
-        <v>1.754572183942649</v>
+        <v>0.8798413818739753</v>
       </c>
       <c r="X6" t="n">
-        <v>0.1485005269621932</v>
+        <v>0.08401796970997172</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.054047862282065</v>
+        <v>1.036799841041632</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.810206431619437</v>
+        <v>0.8024988135191197</v>
       </c>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="n">
-        <v>-1.125001227593124</v>
+        <v>-1.090603263315954</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.1144115718975815</v>
+        <v>0.1157187865721083</v>
       </c>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="n">
-        <v>-0.1013099134869722</v>
+        <v>-0.07423915638701858</v>
       </c>
       <c r="AF6" t="n">
-        <v>-1.353643956390671</v>
+        <v>-1.300809515842921</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.4921804241906396</v>
+        <v>0.4819922496332898</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.059277007033653</v>
+        <v>0.9551815831519862</v>
       </c>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="n">
-        <v>0.04927919429747567</v>
+        <v>0.04774306129413899</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.2174071509580034</v>
+        <v>-0.1983890118330842</v>
       </c>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="n">
-        <v>0.7476084298757015</v>
+        <v>0.6523849204866555</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.2773309485697404</v>
+        <v>0.2782631056353983</v>
       </c>
       <c r="AP6" t="n">
         <v>-0.1244973286161158</v>
@@ -1245,7 +1245,7 @@
         <v>0.1208214733008109</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1211494013254189</v>
+        <v>0.3582758583883194</v>
       </c>
       <c r="F7" t="n">
         <v>1.74272286449447</v>
@@ -1266,73 +1266,67 @@
         <v>-1.012545682812658</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4525065610699723</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.02256820770482074</v>
-      </c>
-      <c r="N7" t="n">
-        <v>-0.005351037217539404</v>
-      </c>
+        <v>-0.009102567141635841</v>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
-        <v>0.4218004190135942</v>
+        <v>0.881825974266928</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0767846891446337</v>
+        <v>1.056262773835412</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.3044587792487164</v>
+        <v>0.1767525482288647</v>
       </c>
       <c r="R7" t="n">
         <v>-0.9632506321031258</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.569759369179762</v>
+        <v>-1.06183722201547</v>
       </c>
       <c r="T7" t="n">
-        <v>-4.867133811738356</v>
+        <v>-4.37746440070471</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.076933976611933</v>
+        <v>-0.5555118250598432</v>
       </c>
       <c r="V7" t="n">
-        <v>0.576143683664408</v>
+        <v>2.181308605003265</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.5780432882404807</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0.8088096179422681</v>
-      </c>
+        <v>-0.1406778872061439</v>
+      </c>
+      <c r="X7" t="inlineStr"/>
       <c r="Y7" t="n">
-        <v>-0.3164962956384968</v>
+        <v>-0.3505535675951998</v>
       </c>
       <c r="Z7" t="n">
-        <v>-1.132864580927866</v>
+        <v>-1.146839287792183</v>
       </c>
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="n">
-        <v>-1.828999341403407</v>
+        <v>-1.820818462555847</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.6144068443147668</v>
+        <v>-0.6170772069349184</v>
       </c>
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="n">
-        <v>-1.197863195143588</v>
+        <v>-1.200382651744966</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.6402218220376218</v>
+        <v>-0.6076714330661251</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.08358788706605595</v>
+        <v>-0.1024827924313463</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0.9686285048337927</v>
+        <v>-1.013387040322689</v>
       </c>
       <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="n">
-        <v>-1.210344559973232</v>
+        <v>-1.220242332842101</v>
       </c>
       <c r="AK7" t="n">
         <v>-0.9050349641283204</v>
@@ -1340,10 +1334,10 @@
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="n">
-        <v>-0.07362496260912958</v>
+        <v>-0.1842697647343616</v>
       </c>
       <c r="AO7" t="n">
-        <v>-1.433992904345862</v>
+        <v>-1.427234765619839</v>
       </c>
       <c r="AP7" t="n">
         <v>-0.1244973286161158</v>
@@ -1368,7 +1362,7 @@
         <v>-1.430798891275143</v>
       </c>
       <c r="F8" t="n">
-        <v>0.05604734498039485</v>
+        <v>-0.3975124585864154</v>
       </c>
       <c r="G8" t="n">
         <v>-0.2304341233182217</v>
@@ -1386,7 +1380,7 @@
         <v>-0.4943945312401692</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.086190532968721</v>
+        <v>-0.6245814047571133</v>
       </c>
       <c r="M8" t="n">
         <v>0.02256820770482074</v>
@@ -1395,75 +1389,75 @@
         <v>-0.005351037217539404</v>
       </c>
       <c r="O8" t="n">
-        <v>0.881825974266928</v>
+        <v>1.341851529520262</v>
       </c>
       <c r="P8" t="n">
-        <v>0.199219449730981</v>
+        <v>-0.04565007144171361</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.101597858139189</v>
+        <v>1.740689362531003</v>
       </c>
       <c r="R8" t="n">
-        <v>1.045344051706153</v>
+        <v>0.04104670980151362</v>
       </c>
       <c r="S8" t="n">
         <v>1.985695660970278</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5192297096317455</v>
+        <v>-0.4601091124355456</v>
       </c>
       <c r="U8" t="n">
         <v>3.615865387356873</v>
       </c>
       <c r="V8" t="n">
-        <v>2.910929023793654</v>
+        <v>2.765004940035576</v>
       </c>
       <c r="W8" t="n">
-        <v>1.025629848885421</v>
+        <v>1.608783716931203</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.0733953318175113</v>
+        <v>-0.006927328179307571</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.563288629369048</v>
+        <v>0.562437956403455</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.2212491408708654</v>
+        <v>0.1973235321177838</v>
       </c>
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="n">
-        <v>-0.6064961694068275</v>
+        <v>-0.4951692391245345</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.06439279314363468</v>
+        <v>0.05712597864859388</v>
       </c>
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="n">
-        <v>0.04380006566068867</v>
+        <v>0.04425571206731857</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.5090379948501089</v>
+        <v>-0.523092339112188</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.5746474595745067</v>
+        <v>0.5390928095886501</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.2609536857990569</v>
+        <v>0.1883896428914851</v>
       </c>
       <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="n">
-        <v>0.1705134105305575</v>
+        <v>0.1297870036035469</v>
       </c>
       <c r="AK8" t="n">
-        <v>-0.0329160425745702</v>
+        <v>-0.1179862719051748</v>
       </c>
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="n">
-        <v>-0.4245683917791569</v>
+        <v>-0.362605716851976</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.4052410627586161</v>
+        <v>-0.3800728219858399</v>
       </c>
       <c r="AP8" t="n">
         <v>-0.1244973286161158</v>
@@ -1476,7 +1470,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.453818357394956</v>
+        <v>1.515216010006835</v>
       </c>
       <c r="C9" t="n">
         <v>-0.7973779067921173</v>
@@ -1485,10 +1479,10 @@
         <v>0.4497159320279531</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.793291160814799</v>
+        <v>-0.7642808472828727</v>
       </c>
       <c r="F9" t="n">
-        <v>1.260815573204735</v>
+        <v>0.4103909415169653</v>
       </c>
       <c r="G9" t="n">
         <v>-0.2304341233182217</v>
@@ -1506,78 +1500,82 @@
         <v>0.02375662033231982</v>
       </c>
       <c r="L9" t="n">
-        <v>1.273145011223942</v>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+        <v>0.1960570453968566</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.02256820770482074</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-0.005351037217539404</v>
+      </c>
       <c r="O9" t="n">
-        <v>-0.9582762467464072</v>
+        <v>-0.0382251362397396</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0767846891446337</v>
+        <v>-0.9026933955461448</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.507487097942669</v>
+        <v>0.1767525482288647</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5431953807538333</v>
+        <v>-0.4611019611508061</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5539150748511786</v>
+        <v>1.223812440223842</v>
       </c>
       <c r="T9" t="n">
-        <v>1.008899120665391</v>
+        <v>0.5192297096317455</v>
       </c>
       <c r="U9" t="n">
-        <v>4.137287538908963</v>
+        <v>2.051598932700604</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.174945321432527</v>
+        <v>-1.320869405190604</v>
       </c>
       <c r="W9" t="n">
-        <v>-1.452774090309154</v>
+        <v>-0.8696202222633719</v>
       </c>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="n">
-        <v>0.2408205750526639</v>
+        <v>0.2732195579771568</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.4506880041122437</v>
+        <v>0.4536894190375754</v>
       </c>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="n">
-        <v>0.5009364830102572</v>
+        <v>0.5621734708750332</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.3914120755139429</v>
+        <v>0.3864087541992942</v>
       </c>
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="n">
-        <v>1.1806110474798</v>
+        <v>1.166030362467549</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.2714151346006083</v>
+        <v>-0.2857228592167813</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.797643729222633</v>
+        <v>0.7582685137777698</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0.2647222525251339</v>
+        <v>-0.1963951328678784</v>
       </c>
       <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="n">
-        <v>0.41298296911706</v>
+        <v>0.4374114975749084</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.5223584479427571</v>
+        <v>0.513518203854226</v>
       </c>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" t="n">
-        <v>0.2535324109266778</v>
+        <v>0.1669908118441515</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.7163769264948451</v>
+        <v>0.7357191856072572</v>
       </c>
       <c r="AP9" t="n">
         <v>-0.1244973286161158</v>
@@ -1602,7 +1600,7 @@
         <v>0.03086348590088838</v>
       </c>
       <c r="F10" t="n">
-        <v>1.74272286449447</v>
+        <v>1.048209415282792</v>
       </c>
       <c r="G10" t="n">
         <v>-0.2304341233182217</v>
@@ -1620,7 +1618,7 @@
         <v>1.060058923477298</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.496509758045706</v>
+        <v>-1.599089564314953</v>
       </c>
       <c r="M10" t="n">
         <v>0.02256820770482074</v>
@@ -1629,691 +1627,77 @@
         <v>-0.005351037217539404</v>
       </c>
       <c r="O10" t="n">
-        <v>1.801877084773595</v>
+        <v>2.261902640026929</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.4129543532007556</v>
+        <v>-0.1680848320280609</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.703112017486166</v>
+        <v>1.981295026269794</v>
       </c>
       <c r="R10" t="n">
-        <v>-1.214324967579286</v>
+        <v>-1.465399303055446</v>
       </c>
       <c r="S10" t="n">
         <v>0.4619292194774042</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9497785234691912</v>
+        <v>-1.929117345536482</v>
       </c>
       <c r="U10" t="n">
         <v>1.530176781148515</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.050489823980994</v>
+        <v>-0.4453249026421371</v>
       </c>
       <c r="W10" t="n">
-        <v>-2.91065876042361</v>
+        <v>-2.764870293412165</v>
       </c>
       <c r="X10" t="n">
-        <v>0.9853365451258583</v>
+        <v>0.9113268085737301</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.4294611992885234</v>
+        <v>0.329002676074807</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.6579080416419949</v>
+        <v>0.6553549711847321</v>
       </c>
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="n">
-        <v>2.270430278186216</v>
+        <v>2.319898282445731</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.4837074859613015</v>
+        <v>0.4853856845719087</v>
       </c>
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="n">
-        <v>1.384914855395015</v>
+        <v>1.405258127314685</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.6177083277128748</v>
+        <v>0.7305928607226747</v>
       </c>
       <c r="AG10" t="n">
-        <v>-0.09860808063646979</v>
+        <v>-0.1193829467831751</v>
       </c>
       <c r="AH10" t="n">
-        <v>-1.064717962066928</v>
+        <v>-1.09231881844585</v>
       </c>
       <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="n">
-        <v>1.200902216879667</v>
+        <v>1.21446140569224</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.301339969429545</v>
+        <v>1.347719078297672</v>
       </c>
       <c r="AL10" t="inlineStr"/>
       <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="n">
-        <v>-0.4618772605239777</v>
+        <v>-0.5149818321399467</v>
       </c>
       <c r="AO10" t="n">
-        <v>1.949284112087189</v>
+        <v>1.990868674516283</v>
       </c>
       <c r="AP10" t="n">
-        <v>-0.1244973286161158</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>hhlQ5IbD</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1.607312488924654</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.1371117430245272</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1.65937860226168</v>
-      </c>
-      <c r="E11" t="n">
-        <v>-1.793291160814799</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.9489932082525525</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-0.2304341233182217</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-0.1705560731334942</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.6112110282974008</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1.374931813071086</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1.578210075049787</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2.093783461377912</v>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="n">
-        <v>-2.798378467759743</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.301132295008107</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>-3.432332407852994</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2.551790064563112</v>
-      </c>
-      <c r="S11" t="n">
-        <v>-0.5539150748511786</v>
-      </c>
-      <c r="T11" t="n">
-        <v>4.926254408934556</v>
-      </c>
-      <c r="U11" t="n">
-        <v>-1.076933976611933</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0.576143683664408</v>
-      </c>
-      <c r="W11" t="n">
-        <v>-0.8696202222633719</v>
-      </c>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="n">
-        <v>0.2947720475497861</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.113442820136443</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>-0.1098230912000561</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0.6334770859766959</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0.4204833743722263</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0.0326949765739812</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0.7266733148718427</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0.7847197535738653</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0.05945590303603123</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0.1007324869851525</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>-0.5173603621389383</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.649163918962556</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>0.6949905841921701</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>-0.1776019725838051</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0.002918637068733171</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>0.3593473223106401</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>1.02311486091306</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>-0.1244973286161158</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>xrJSdNFr</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1.453818357394956</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1.272694102295386</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.6559717790263305</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1.445752667007287</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.0135261133960064</v>
-      </c>
-      <c r="G12" t="n">
-        <v>-0.2304341233182217</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.2924698004996741</v>
-      </c>
-      <c r="I12" t="n">
-        <v>-0.9164922352149566</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.5806554141095995</v>
-      </c>
-      <c r="K12" t="n">
-        <v>-0.4943945312401692</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.9654055924162035</v>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="n">
-        <v>0.881825974266928</v>
-      </c>
-      <c r="P12" t="n">
-        <v>-2.616780043755007</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>-2.229304089159041</v>
-      </c>
-      <c r="R12" t="n">
-        <v>-1.967547974007765</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.477773513805987</v>
-      </c>
-      <c r="T12" t="n">
-        <v>-1.929117345536482</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.008754629596425</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.451688186212875</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2.337726051988432</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.300533567282685</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>-0.5958406208672474</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>-1.121422642825057</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>-0.02644307020855297</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>-1.139365606973121</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>-0.5482626187779959</v>
-      </c>
-      <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="n">
-        <v>-1.230931063036714</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>-0.01033444251915991</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>-0.2010529481030272</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0.3699741104019082</v>
-      </c>
-      <c r="AI12" t="inlineStr"/>
-      <c r="AJ12" t="n">
-        <v>-1.135048627375482</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>-0.6611693135725666</v>
-      </c>
-      <c r="AL12" t="inlineStr"/>
-      <c r="AM12" t="n">
-        <v>-0.370709828862477</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>0.724077854098284</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>-1.19642231886209</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>-0.1244973286161158</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>ObHze1pe</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1.453818357394956</v>
-      </c>
-      <c r="C13" t="n">
-        <v>1.753739407264292</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.2972647030472513</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.1211494013254189</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.3678697099325769</v>
-      </c>
-      <c r="G13" t="n">
-        <v>-0.2304341233182217</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.7554956741328426</v>
-      </c>
-      <c r="I13" t="n">
-        <v>-0.1526406034587778</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.5806554141095995</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.02375662033231982</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.1447671422622335</v>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="n">
-        <v>0.881825974266928</v>
-      </c>
-      <c r="P13" t="n">
-        <v>-2.371910522582313</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>-0.545064442987507</v>
-      </c>
-      <c r="R13" t="n">
-        <v>-2.469696644960085</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.4619292194774042</v>
-      </c>
-      <c r="T13" t="n">
-        <v>-1.929117345536482</v>
-      </c>
-      <c r="U13" t="n">
-        <v>-1.076933976611933</v>
-      </c>
-      <c r="V13" t="n">
-        <v>-0.8830971539163709</v>
-      </c>
-      <c r="W13" t="n">
-        <v>-2.035927958354937</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0.6824967042071594</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0.6370348766560953</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0.2360919147121103</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0.08187651063308733</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0.2201074839741273</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0.2547454426332818</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0.3934247694328797</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.135180420465523</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0.7333315263353567</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.017131316306373</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0.09126685725348596</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0.9487634617597244</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.388334177126735</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>0.5665473087149022</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>-0.6996963436424987</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>-0.328009432756053</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>0.5322256961077512</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>1.161481925346727</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>-0.1244973286161158</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>8nivFMyR</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1.607312488924654</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.4801522473875992</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.3084136677498663</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.4017885777432169</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.05604734498039485</v>
-      </c>
-      <c r="G14" t="n">
-        <v>-0.2304341233182217</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.7554956741328426</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1.069522007351108</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.5806554141095995</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.02375662033231982</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.1447671422622335</v>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="n">
-        <v>1.801877084773595</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0.5665237314900229</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.34220352187798</v>
-      </c>
-      <c r="R14" t="n">
-        <v>-0.4611019611508061</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.49361780813457</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.008899120665391</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.051598932700604</v>
-      </c>
-      <c r="V14" t="n">
-        <v>2.035384521245187</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0.8798413818739753</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0.4712689155610916</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0.3054089651391695</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0.7240761916315998</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0.7984235660288179</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0.1636546357862854</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0.5705879944289084</v>
-      </c>
-      <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="n">
-        <v>0.5530251291675776</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0.2132841158128733</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0.2309265194700102</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>-0.06053858941019961</v>
-      </c>
-      <c r="AI14" t="inlineStr"/>
-      <c r="AJ14" t="n">
-        <v>0.8440855908339702</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>0.9235160184717908</v>
-      </c>
-      <c r="AL14" t="inlineStr"/>
-      <c r="AM14" t="n">
-        <v>1.737622228892209</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>0.04976520099344014</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0.5019808013934147</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>-0.1244973286161158</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>OCd990al</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1.453818357394956</v>
-      </c>
-      <c r="C15" t="n">
-        <v>-0.5529122600046407</v>
-      </c>
-      <c r="D15" t="n">
-        <v>-0.8268405264214634</v>
-      </c>
-      <c r="E15" t="n">
-        <v>-1.489265386362184</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1.74272286449447</v>
-      </c>
-      <c r="G15" t="n">
-        <v>-0.2304341233182217</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.06095686368308995</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.0001297228924578849</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.5806554141095995</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.02375662033231982</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.5550863673392186</v>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="n">
-        <v>-2.798378467759743</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0.8113932526627176</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>-0.7856701067262976</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.04104670980151362</v>
-      </c>
-      <c r="S15" t="n">
-        <v>-1.06183722201547</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0.02956029859809994</v>
-      </c>
-      <c r="U15" t="n">
-        <v>-5.248311189028649</v>
-      </c>
-      <c r="V15" t="n">
-        <v>-0.007552651367903501</v>
-      </c>
-      <c r="W15" t="n">
-        <v>-0.5780432882404807</v>
-      </c>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="n">
-        <v>0.6961581072126426</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0.4824131348688991</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0.2713427190468156</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>-0.008574392583400573</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0.555440903755819</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0.0326949765739812</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0.554633292955692</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>0.6234161493140992</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0.5994681399374379</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>-0.4389189655883272</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1.082047445750512</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.064785437562568</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>0.6467519762075268</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>-0.1776019725838051</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.262580322208242</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>-0.6217944364129872</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0.1897081843978529</v>
-      </c>
-      <c r="AP15" t="n">
         <v>-0.1244973286161158</v>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_selected.xlsx
@@ -709,45 +709,45 @@
       </c>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="n">
-        <v>-1.426422580272545</v>
+        <v>-1.372788034944237</v>
       </c>
       <c r="Z2" t="n">
-        <v>-5.142309059685487</v>
+        <v>-5.073840896956605</v>
       </c>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="n">
-        <v>-0.02033440592676761</v>
+        <v>-0.008708946511814268</v>
       </c>
       <c r="AC2" t="n">
-        <v>-2.688821830586664</v>
+        <v>-2.695267463468531</v>
       </c>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="n">
-        <v>-1.28402057009189</v>
+        <v>-1.2931804030017</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.4437753571286891</v>
+        <v>0.414776638372091</v>
       </c>
       <c r="AG2" t="n">
-        <v>-1.007185220929726</v>
+        <v>-1.014696400641649</v>
       </c>
       <c r="AH2" t="n">
-        <v>-1.102517807333721</v>
+        <v>-1.087796342754121</v>
       </c>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="n">
-        <v>-1.572739107969445</v>
+        <v>-1.530165823895897</v>
       </c>
       <c r="AK2" t="n">
-        <v>-3.255834176743024</v>
+        <v>-3.2693028053144</v>
       </c>
       <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="n">
-        <v>-1.00635301316531</v>
+        <v>-1.049881494975946</v>
       </c>
       <c r="AO2" t="n">
-        <v>-2.082337273419576</v>
+        <v>-2.086357200765227</v>
       </c>
       <c r="AP2" t="n">
         <v>-0.1244973286161158</v>
@@ -756,29 +756,29 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SU02594U</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.607312488924654</v>
+        <v>1.453818357394956</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07008083987312229</v>
+        <v>-0.8644088099435222</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4943117908384131</v>
+        <v>-0.2972647030472513</v>
       </c>
       <c r="E3" t="n">
-        <v>0.942940809258732</v>
+        <v>1.282046480763571</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1423850690800846</v>
+        <v>-0.3975124585864154</v>
       </c>
       <c r="G3" t="n">
         <v>-0.2304341233182217</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.8650948835832468</v>
+        <v>0.2924698004996741</v>
       </c>
       <c r="I3" t="n">
         <v>-0.610951582512485</v>
@@ -787,10 +787,10 @@
         <v>-1.007897383813373</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.4943945312401692</v>
+        <v>0.02375662033231982</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.650379467449576</v>
+        <v>-2.009408789391938</v>
       </c>
       <c r="M3" t="n">
         <v>0.02256820770482074</v>
@@ -799,75 +799,75 @@
         <v>-0.005351037217539404</v>
       </c>
       <c r="O3" t="n">
-        <v>0.881825974266928</v>
+        <v>-0.0382251362397396</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.147562916718839</v>
+        <v>-0.7802586349597975</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.266881434203879</v>
+        <v>1.740689362531003</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.2100276256746462</v>
+        <v>-0.7121762966269659</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2079681458952584</v>
+        <v>1.477773513805987</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9497785234691912</v>
+        <v>0.5192297096317455</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.03408967350775372</v>
+        <v>0.4873324780443357</v>
       </c>
       <c r="V3" t="n">
         <v>0.1383714323901744</v>
       </c>
       <c r="W3" t="n">
-        <v>-1.306985623297709</v>
+        <v>-0.8696202222633719</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.08157418558663432</v>
+        <v>0.5886176870311318</v>
       </c>
       <c r="Y3" t="n">
-        <v>-1.840347452012947</v>
+        <v>0.4509543230111798</v>
       </c>
       <c r="Z3" t="n">
-        <v>-1.169190745063825</v>
+        <v>0.1534271875300206</v>
       </c>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="n">
-        <v>1.468889717755221</v>
+        <v>-0.259424232716695</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.9299825033721677</v>
+        <v>0.1047453574452163</v>
       </c>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
-        <v>-1.651969663118702</v>
+        <v>0.7452335961067275</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.2756474688978721</v>
+        <v>0.3545304185500082</v>
       </c>
       <c r="AG3" t="n">
-        <v>-1.925651549558445</v>
+        <v>0.8538889739670089</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.5435232727324034</v>
+        <v>0.2348161019936554</v>
       </c>
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="n">
-        <v>-2.376562156654253</v>
+        <v>0.9935673575636876</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.8503773459906003</v>
+        <v>-0.01011206808736213</v>
       </c>
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="n">
-        <v>0.06551445298156297</v>
+        <v>1.677275602496138</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.6510974888260194</v>
+        <v>-0.01303597738284825</v>
       </c>
       <c r="AP3" t="n">
         <v>-0.1244973286161158</v>
@@ -876,23 +876,23 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ChZKNjKb</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1.453818357394956</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.8644088099435222</v>
+        <v>1.62756358956753</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2972647030472513</v>
+        <v>0.6559717790263305</v>
       </c>
       <c r="E4" t="n">
-        <v>1.282046480763571</v>
+        <v>1.773165039494718</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3975124585864154</v>
+        <v>1.048209415282792</v>
       </c>
       <c r="G4" t="n">
         <v>-0.2304341233182217</v>
@@ -901,16 +901,16 @@
         <v>0.2924698004996741</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.610951582512485</v>
+        <v>0.6112110282974008</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.007897383813373</v>
+        <v>0.5806554141095995</v>
       </c>
       <c r="K4" t="n">
         <v>0.02375662033231982</v>
       </c>
       <c r="L4" t="n">
-        <v>-2.009408789391938</v>
+        <v>-1.291350145507214</v>
       </c>
       <c r="M4" t="n">
         <v>0.02256820770482074</v>
@@ -919,75 +919,75 @@
         <v>-0.005351037217539404</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0382251362397396</v>
+        <v>0.4218004190135942</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.7802586349597975</v>
+        <v>-2.49434528316866</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.740689362531003</v>
+        <v>1.379780866922818</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.7121762966269659</v>
+        <v>-2.469696644960085</v>
       </c>
       <c r="S4" t="n">
-        <v>1.477773513805987</v>
+        <v>2.239656734552424</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5192297096317455</v>
+        <v>-0.9497785234691912</v>
       </c>
       <c r="U4" t="n">
         <v>0.4873324780443357</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1383714323901744</v>
+        <v>-1.904565740222916</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.8696202222633719</v>
+        <v>0.5882644478510841</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5886176870311318</v>
+        <v>0.6225184432335839</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4509543230111798</v>
+        <v>-0.458033798287068</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.1534271875300206</v>
+        <v>-1.036639686597212</v>
       </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="n">
-        <v>-0.259424232716695</v>
+        <v>0.4291055252396568</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.1047453574452163</v>
+        <v>-0.2540290058778424</v>
       </c>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="n">
-        <v>0.7452335961067275</v>
+        <v>-0.4053034291357286</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.3545304185500082</v>
+        <v>-0.2725496267652841</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.8538889739670089</v>
+        <v>-0.299253727316189</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.2348161019936554</v>
+        <v>0.7313573301232845</v>
       </c>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="n">
-        <v>0.9935673575636876</v>
+        <v>-1.390495655743276</v>
       </c>
       <c r="AK4" t="n">
-        <v>-0.01011206808736213</v>
+        <v>-1.247546728384069</v>
       </c>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="n">
-        <v>1.677275602496138</v>
+        <v>0.6276642410502303</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.01303597738284825</v>
+        <v>-1.050616829359027</v>
       </c>
       <c r="AP4" t="n">
         <v>-0.1244973286161158</v>
@@ -996,114 +996,118 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>p6XSLUlB</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.453818357394956</v>
+        <v>1.607312488924654</v>
       </c>
       <c r="C5" t="n">
-        <v>1.62756358956753</v>
+        <v>0.07008083987312229</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6559717790263305</v>
+        <v>0.4943117908384131</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.758211263762574</v>
+        <v>0.942940809258732</v>
       </c>
       <c r="F5" t="n">
-        <v>1.048209415282792</v>
+        <v>-0.1423850690800846</v>
       </c>
       <c r="G5" t="n">
         <v>-0.2304341233182217</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2924698004996741</v>
+        <v>-0.8650948835832468</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6112110282974008</v>
+        <v>-0.610951582512485</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5806554141095995</v>
+        <v>-1.007897383813373</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02375662033231982</v>
+        <v>-0.4943945312401692</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.54779966118033</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+        <v>-1.650379467449576</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.02256820770482074</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-0.005351037217539404</v>
+      </c>
       <c r="O5" t="n">
-        <v>1.341851529520262</v>
+        <v>0.881825974266928</v>
       </c>
       <c r="P5" t="n">
-        <v>-3.718692889032133</v>
+        <v>-1.147562916718839</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.981295026269794</v>
+        <v>-1.266881434203879</v>
       </c>
       <c r="R5" t="n">
-        <v>-3.222919651388565</v>
+        <v>-0.2100276256746462</v>
       </c>
       <c r="S5" t="n">
-        <v>1.223812440223842</v>
+        <v>0.2079681458952584</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.929117345536482</v>
+        <v>-0.9497785234691912</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4873324780443357</v>
+        <v>-0.03408967350775372</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.926034326529461</v>
+        <v>0.1383714323901744</v>
       </c>
       <c r="W5" t="n">
-        <v>1.025629848885421</v>
+        <v>-1.306985623297709</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6225184432335839</v>
+        <v>-0.08157418558663432</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.4690637321975425</v>
+        <v>-1.836838436750097</v>
       </c>
       <c r="Z5" t="n">
-        <v>-1.030875036056839</v>
+        <v>-1.164696359696084</v>
       </c>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
-        <v>0.4291055252396568</v>
+        <v>1.41260213984713</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.2540290058778424</v>
+        <v>-0.9316181824906045</v>
       </c>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
-        <v>-0.4053034291357286</v>
+        <v>-1.689184035142783</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.2284178378845431</v>
+        <v>0.3173243744674072</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.299253727316189</v>
+        <v>-1.925587755330002</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.7139002256896511</v>
+        <v>0.600754863502299</v>
       </c>
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="n">
-        <v>-1.358211880677411</v>
+        <v>-2.326951094438668</v>
       </c>
       <c r="AK5" t="n">
-        <v>-1.250768107765167</v>
+        <v>-0.8503773459906003</v>
       </c>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="n">
-        <v>0.6276642410502303</v>
+        <v>0.03398711742274086</v>
       </c>
       <c r="AO5" t="n">
-        <v>-1.050616829359027</v>
+        <v>-0.6490001354282878</v>
       </c>
       <c r="AP5" t="n">
         <v>-0.1244973286161158</v>
@@ -1185,45 +1189,45 @@
         <v>0.08401796970997172</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.036799841041632</v>
+        <v>1.047412831781418</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.8024988135191197</v>
+        <v>0.8667963297777855</v>
       </c>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="n">
-        <v>-1.090603263315954</v>
+        <v>-1.133272473523469</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.1157187865721083</v>
+        <v>0.1060030370480539</v>
       </c>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="n">
-        <v>-0.07423915638701858</v>
+        <v>-0.08279518335600816</v>
       </c>
       <c r="AF6" t="n">
-        <v>-1.300809515842921</v>
+        <v>-1.240033150841297</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.4819922496332898</v>
+        <v>0.4822232739996728</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.9551815831519862</v>
+        <v>0.9894354745632675</v>
       </c>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="n">
-        <v>0.04774306129413899</v>
+        <v>0.09408822461075424</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.1983890118330842</v>
+        <v>-0.08053739876652269</v>
       </c>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="n">
-        <v>0.6523849204866555</v>
+        <v>0.6752503676713434</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.2782631056353983</v>
+        <v>0.2407178904908249</v>
       </c>
       <c r="AP6" t="n">
         <v>-0.1244973286161158</v>
@@ -1236,7 +1240,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.545914836312775</v>
+        <v>1.607312488924654</v>
       </c>
       <c r="C7" t="n">
         <v>-0.2847886473990212</v>
@@ -1248,7 +1252,7 @@
         <v>0.3582758583883194</v>
       </c>
       <c r="F7" t="n">
-        <v>1.74272286449447</v>
+        <v>-1.800713100871234</v>
       </c>
       <c r="G7" t="n">
         <v>-0.2304341233182217</v>
@@ -1266,43 +1270,47 @@
         <v>-1.012545682812658</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.009102567141635841</v>
-      </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+        <v>-0.8810309204302289</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.02256820770482074</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-0.005351037217539404</v>
+      </c>
       <c r="O7" t="n">
-        <v>0.881825974266928</v>
+        <v>0.4218004190135942</v>
       </c>
       <c r="P7" t="n">
-        <v>1.056262773835412</v>
+        <v>-0.04565007144171361</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1767525482288647</v>
+        <v>-0.4247616111181118</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.9632506321031258</v>
+        <v>-2.218622309483925</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.06183722201547</v>
+        <v>-0.5539150748511786</v>
       </c>
       <c r="T7" t="n">
-        <v>-4.37746440070471</v>
+        <v>-2.908456167603774</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5555118250598432</v>
+        <v>-1.076933976611933</v>
       </c>
       <c r="V7" t="n">
-        <v>2.181308605003265</v>
+        <v>1.889460437487109</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.1406778872061439</v>
+        <v>-0.5780432882404807</v>
       </c>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="n">
-        <v>-0.3505535675951998</v>
+        <v>-0.3563447903683006</v>
       </c>
       <c r="Z7" t="n">
-        <v>-1.146839287792183</v>
+        <v>-1.180565319670681</v>
       </c>
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="n">
@@ -1316,20 +1324,20 @@
         <v>-1.200382651744966</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.6076714330661251</v>
+        <v>-0.570187960543127</v>
       </c>
       <c r="AG7" t="n">
         <v>-0.1024827924313463</v>
       </c>
       <c r="AH7" t="n">
-        <v>-1.013387040322689</v>
+        <v>-0.8343431421008286</v>
       </c>
       <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="n">
-        <v>-1.220242332842101</v>
+        <v>-1.198298776812089</v>
       </c>
       <c r="AK7" t="n">
-        <v>-0.9050349641283204</v>
+        <v>-1.015373308339389</v>
       </c>
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr"/>
@@ -1537,34 +1545,34 @@
       </c>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="n">
-        <v>0.2732195579771568</v>
+        <v>0.2710439266338129</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.4536894190375754</v>
+        <v>0.4546275846319501</v>
       </c>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="n">
-        <v>0.5621734708750332</v>
+        <v>0.5487343876007319</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.3864087541992942</v>
+        <v>0.3870533810480162</v>
       </c>
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="n">
-        <v>1.166030362467549</v>
+        <v>1.167967468848685</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.2857228592167813</v>
+        <v>-0.2800560129197587</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.7582685137777698</v>
+        <v>0.7702830934679684</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0.1963951328678784</v>
+        <v>-0.1534659990911417</v>
       </c>
       <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="n">
-        <v>0.4374114975749084</v>
+        <v>0.4498953568048402</v>
       </c>
       <c r="AK9" t="n">
         <v>0.513518203854226</v>
@@ -1572,7 +1580,7 @@
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" t="n">
-        <v>0.1669908118441515</v>
+        <v>0.1632066666296132</v>
       </c>
       <c r="AO9" t="n">
         <v>0.7357191856072572</v>

--- a/data/france/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_selected.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP10"/>
+  <dimension ref="A1:AP9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.638011315230593</v>
+        <v>1.545914836312775</v>
       </c>
       <c r="C2" t="n">
         <v>1.434356868719363</v>
@@ -709,45 +709,55 @@
       </c>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="n">
-        <v>-1.372788034944237</v>
+        <v>-1.399094024127298</v>
       </c>
       <c r="Z2" t="n">
-        <v>-5.073840896956605</v>
-      </c>
-      <c r="AA2" t="inlineStr"/>
+        <v>-5.293553505847798</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-0.2840277779144467</v>
+      </c>
       <c r="AB2" t="n">
-        <v>-0.008708946511814268</v>
+        <v>-0.01173534201280535</v>
       </c>
       <c r="AC2" t="n">
-        <v>-2.695267463468531</v>
-      </c>
-      <c r="AD2" t="inlineStr"/>
+        <v>-2.532114324392467</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-1.698808029148732</v>
+      </c>
       <c r="AE2" t="n">
-        <v>-1.2931804030017</v>
+        <v>-1.227451494364216</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.414776638372091</v>
+        <v>0.4682714613933115</v>
       </c>
       <c r="AG2" t="n">
-        <v>-1.014696400641649</v>
+        <v>-0.9735447986206999</v>
       </c>
       <c r="AH2" t="n">
-        <v>-1.087796342754121</v>
-      </c>
-      <c r="AI2" t="inlineStr"/>
+        <v>-1.081313587984082</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.2823435418057868</v>
+      </c>
       <c r="AJ2" t="n">
-        <v>-1.530165823895897</v>
+        <v>-1.535397350856816</v>
       </c>
       <c r="AK2" t="n">
-        <v>-3.2693028053144</v>
-      </c>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
+        <v>-3.293828360886823</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>-1.541784038898458</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.235892574641727</v>
+      </c>
       <c r="AN2" t="n">
-        <v>-1.049881494975946</v>
+        <v>-1.048570076283611</v>
       </c>
       <c r="AO2" t="n">
-        <v>-2.086357200765227</v>
+        <v>-1.987294705461664</v>
       </c>
       <c r="AP2" t="n">
         <v>-0.1244973286161158</v>
@@ -756,23 +766,23 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ChZKNjKb</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1.453818357394956</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.8644088099435222</v>
+        <v>1.62756358956753</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.2972647030472513</v>
+        <v>0.6559717790263305</v>
       </c>
       <c r="E3" t="n">
-        <v>1.282046480763571</v>
+        <v>1.773165039494718</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3975124585864154</v>
+        <v>1.048209415282792</v>
       </c>
       <c r="G3" t="n">
         <v>-0.2304341233182217</v>
@@ -781,16 +791,16 @@
         <v>0.2924698004996741</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.610951582512485</v>
+        <v>0.6112110282974008</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.007897383813373</v>
+        <v>0.5806554141095995</v>
       </c>
       <c r="K3" t="n">
         <v>0.02375662033231982</v>
       </c>
       <c r="L3" t="n">
-        <v>-2.009408789391938</v>
+        <v>-1.291350145507214</v>
       </c>
       <c r="M3" t="n">
         <v>0.02256820770482074</v>
@@ -799,75 +809,85 @@
         <v>-0.005351037217539404</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0382251362397396</v>
+        <v>0.4218004190135942</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.7802586349597975</v>
+        <v>-2.49434528316866</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.740689362531003</v>
+        <v>1.379780866922818</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.7121762966269659</v>
+        <v>-2.469696644960085</v>
       </c>
       <c r="S3" t="n">
-        <v>1.477773513805987</v>
+        <v>2.239656734552424</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5192297096317455</v>
+        <v>-0.9497785234691912</v>
       </c>
       <c r="U3" t="n">
         <v>0.4873324780443357</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1383714323901744</v>
+        <v>-1.904565740222916</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.8696202222633719</v>
+        <v>0.5882644478510841</v>
       </c>
       <c r="X3" t="n">
-        <v>0.5886176870311318</v>
+        <v>0.6225184432335839</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4509543230111798</v>
+        <v>-0.4341805277586076</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.1534271875300206</v>
-      </c>
-      <c r="AA3" t="inlineStr"/>
+        <v>-1.049398464751491</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.1150051796877471</v>
+      </c>
       <c r="AB3" t="n">
-        <v>-0.259424232716695</v>
+        <v>0.4931144146384643</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.1047453574452163</v>
-      </c>
-      <c r="AD3" t="inlineStr"/>
+        <v>-0.2452175969035678</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.0326949765739812</v>
+      </c>
       <c r="AE3" t="n">
-        <v>0.7452335961067275</v>
+        <v>-0.4007433101516943</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.3545304185500082</v>
+        <v>-0.2935578111033451</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.8538889739670089</v>
+        <v>-0.3123799805057446</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.2348161019936554</v>
-      </c>
-      <c r="AI3" t="inlineStr"/>
+        <v>0.6469157742796354</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.2823435418057868</v>
+      </c>
       <c r="AJ3" t="n">
-        <v>0.9935673575636876</v>
+        <v>-1.390046220030712</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.01011206808736213</v>
-      </c>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
+        <v>-1.273987842816045</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>-1.52494228499334</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.0669692312283692</v>
+      </c>
       <c r="AN3" t="n">
-        <v>1.677275602496138</v>
+        <v>0.7354973632152686</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.01303597738284825</v>
+        <v>-1.052740664491578</v>
       </c>
       <c r="AP3" t="n">
         <v>-0.1244973286161158</v>
@@ -876,41 +896,41 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>p6XSLUlB</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1.453818357394956</v>
       </c>
       <c r="C4" t="n">
-        <v>1.62756358956753</v>
+        <v>0.07008083987312229</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6559717790263305</v>
+        <v>0.4943117908384131</v>
       </c>
       <c r="E4" t="n">
-        <v>1.773165039494718</v>
+        <v>0.942940809258732</v>
       </c>
       <c r="F4" t="n">
-        <v>1.048209415282792</v>
+        <v>-0.1423850690800846</v>
       </c>
       <c r="G4" t="n">
         <v>-0.2304341233182217</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2924698004996741</v>
+        <v>-0.8650948835832468</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6112110282974008</v>
+        <v>-0.610951582512485</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5806554141095995</v>
+        <v>-1.007897383813373</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02375662033231982</v>
+        <v>-0.4943945312401692</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.291350145507214</v>
+        <v>-1.650379467449576</v>
       </c>
       <c r="M4" t="n">
         <v>0.02256820770482074</v>
@@ -919,75 +939,85 @@
         <v>-0.005351037217539404</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4218004190135942</v>
+        <v>0.881825974266928</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.49434528316866</v>
+        <v>-1.147562916718839</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.379780866922818</v>
+        <v>-1.266881434203879</v>
       </c>
       <c r="R4" t="n">
-        <v>-2.469696644960085</v>
+        <v>-0.2100276256746462</v>
       </c>
       <c r="S4" t="n">
-        <v>2.239656734552424</v>
+        <v>0.2079681458952584</v>
       </c>
       <c r="T4" t="n">
         <v>-0.9497785234691912</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4873324780443357</v>
+        <v>-0.03408967350775372</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.904565740222916</v>
+        <v>0.1383714323901744</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5882644478510841</v>
+        <v>-1.306985623297709</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6225184432335839</v>
+        <v>-0.08157418558663432</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.458033798287068</v>
+        <v>-1.840958409636392</v>
       </c>
       <c r="Z4" t="n">
-        <v>-1.036639686597212</v>
-      </c>
-      <c r="AA4" t="inlineStr"/>
+        <v>-1.164984439692375</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-0.7303342295609303</v>
+      </c>
       <c r="AB4" t="n">
-        <v>0.4291055252396568</v>
+        <v>1.405893712877917</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.2540290058778424</v>
-      </c>
-      <c r="AD4" t="inlineStr"/>
+        <v>-0.945575638645077</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-1.049494402002715</v>
+      </c>
       <c r="AE4" t="n">
-        <v>-0.4053034291357286</v>
+        <v>-1.711081865390963</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.2725496267652841</v>
+        <v>0.3299045833586772</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0.299253727316189</v>
+        <v>-1.946036299559198</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.7313573301232845</v>
-      </c>
-      <c r="AI4" t="inlineStr"/>
+        <v>0.5918366623361107</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-0.6506443461297259</v>
+      </c>
       <c r="AJ4" t="n">
-        <v>-1.390495655743276</v>
+        <v>-2.330833581113332</v>
       </c>
       <c r="AK4" t="n">
-        <v>-1.247546728384069</v>
-      </c>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
+        <v>-0.8908749076054666</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>-0.5144370506861887</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>-0.8777770326262624</v>
+      </c>
       <c r="AN4" t="n">
-        <v>0.6276642410502303</v>
+        <v>-0.08829082783767538</v>
       </c>
       <c r="AO4" t="n">
-        <v>-1.050616829359027</v>
+        <v>-0.6523144716617398</v>
       </c>
       <c r="AP4" t="n">
         <v>-0.1244973286161158</v>
@@ -996,29 +1026,29 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SU02594U</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.607312488924654</v>
+        <v>1.638011315230593</v>
       </c>
       <c r="C5" t="n">
-        <v>0.07008083987312229</v>
+        <v>-0.8644088099435222</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4943117908384131</v>
+        <v>-0.2972647030472513</v>
       </c>
       <c r="E5" t="n">
-        <v>0.942940809258732</v>
+        <v>1.282046480763571</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1423850690800846</v>
+        <v>-0.3975124585864154</v>
       </c>
       <c r="G5" t="n">
         <v>-0.2304341233182217</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8650948835832468</v>
+        <v>0.2924698004996741</v>
       </c>
       <c r="I5" t="n">
         <v>-0.610951582512485</v>
@@ -1027,10 +1057,10 @@
         <v>-1.007897383813373</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.4943945312401692</v>
+        <v>0.02375662033231982</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.650379467449576</v>
+        <v>-2.009408789391938</v>
       </c>
       <c r="M5" t="n">
         <v>0.02256820770482074</v>
@@ -1039,75 +1069,85 @@
         <v>-0.005351037217539404</v>
       </c>
       <c r="O5" t="n">
-        <v>0.881825974266928</v>
+        <v>-0.0382251362397396</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.147562916718839</v>
+        <v>-0.7802586349597975</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.266881434203879</v>
+        <v>1.740689362531003</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.2100276256746462</v>
+        <v>-0.7121762966269659</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2079681458952584</v>
+        <v>1.477773513805987</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9497785234691912</v>
+        <v>0.5192297096317455</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.03408967350775372</v>
+        <v>0.4873324780443357</v>
       </c>
       <c r="V5" t="n">
         <v>0.1383714323901744</v>
       </c>
       <c r="W5" t="n">
-        <v>-1.306985623297709</v>
+        <v>-0.8696202222633719</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.08157418558663432</v>
+        <v>0.5886176870311318</v>
       </c>
       <c r="Y5" t="n">
-        <v>-1.836838436750097</v>
+        <v>0.4695450113860344</v>
       </c>
       <c r="Z5" t="n">
-        <v>-1.164696359696084</v>
-      </c>
-      <c r="AA5" t="inlineStr"/>
+        <v>0.1535983159035849</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-0.06887754517744298</v>
+      </c>
       <c r="AB5" t="n">
-        <v>1.41260213984713</v>
+        <v>-0.3285137334784797</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.9316181824906045</v>
-      </c>
-      <c r="AD5" t="inlineStr"/>
+        <v>0.1036351137941933</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.0326949765739812</v>
+      </c>
       <c r="AE5" t="n">
-        <v>-1.689184035142783</v>
+        <v>0.7196375982988346</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.3173243744674072</v>
+        <v>0.3201490351875603</v>
       </c>
       <c r="AG5" t="n">
-        <v>-1.925587755330002</v>
+        <v>0.8513135773372487</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.600754863502299</v>
-      </c>
-      <c r="AI5" t="inlineStr"/>
+        <v>0.2731134253825242</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-1.103809891698403</v>
+      </c>
       <c r="AJ5" t="n">
-        <v>-2.326951094438668</v>
+        <v>0.9437266991013616</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.8503773459906003</v>
-      </c>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
+        <v>-0.01011206808736213</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.068687816395015</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>-1.496932776169411</v>
+      </c>
       <c r="AN5" t="n">
-        <v>0.03398711742274086</v>
+        <v>1.710923861349014</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.6490001354282878</v>
+        <v>-0.01303597738284825</v>
       </c>
       <c r="AP5" t="n">
         <v>-0.1244973286161158</v>
@@ -1194,14 +1234,18 @@
       <c r="Z6" t="n">
         <v>0.8667963297777855</v>
       </c>
-      <c r="AA6" t="inlineStr"/>
+      <c r="AA6" t="n">
+        <v>-0.2646717016128478</v>
+      </c>
       <c r="AB6" t="n">
         <v>-1.133272473523469</v>
       </c>
       <c r="AC6" t="n">
         <v>0.1060030370480539</v>
       </c>
-      <c r="AD6" t="inlineStr"/>
+      <c r="AD6" t="n">
+        <v>0.0326949765739812</v>
+      </c>
       <c r="AE6" t="n">
         <v>-0.08279518335600816</v>
       </c>
@@ -1214,15 +1258,21 @@
       <c r="AH6" t="n">
         <v>0.9894354745632675</v>
       </c>
-      <c r="AI6" t="inlineStr"/>
+      <c r="AI6" t="n">
+        <v>-1.67248822339243</v>
+      </c>
       <c r="AJ6" t="n">
         <v>0.09408822461075424</v>
       </c>
       <c r="AK6" t="n">
         <v>-0.08053739876652269</v>
       </c>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr"/>
+      <c r="AL6" t="n">
+        <v>-0.5144370506861887</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-0.7603509433335963</v>
+      </c>
       <c r="AN6" t="n">
         <v>0.6752503676713434</v>
       </c>
@@ -1240,7 +1290,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.607312488924654</v>
+        <v>1.576613662618714</v>
       </c>
       <c r="C7" t="n">
         <v>-0.2847886473990212</v>
@@ -1307,45 +1357,49 @@
       </c>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="n">
-        <v>-0.3563447903683006</v>
+        <v>-0.3879483910798276</v>
       </c>
       <c r="Z7" t="n">
-        <v>-1.180565319670681</v>
-      </c>
-      <c r="AA7" t="inlineStr"/>
+        <v>-1.236683086932383</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.001846579770707041</v>
+      </c>
       <c r="AB7" t="n">
-        <v>-1.820818462555847</v>
+        <v>-1.844309537603664</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.6170772069349184</v>
+        <v>-0.609092664466501</v>
       </c>
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="n">
-        <v>-1.200382651744966</v>
+        <v>-1.200166953586087</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.570187960543127</v>
+        <v>-0.5557405180093393</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.1024827924313463</v>
+        <v>-0.09450430405688781</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0.8343431421008286</v>
+        <v>-0.7923435691342182</v>
       </c>
       <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="n">
-        <v>-1.198298776812089</v>
+        <v>-1.225137242640447</v>
       </c>
       <c r="AK7" t="n">
-        <v>-1.015373308339389</v>
+        <v>-1.074203754659676</v>
       </c>
       <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="inlineStr"/>
+      <c r="AM7" t="n">
+        <v>-0.349359630809265</v>
+      </c>
       <c r="AN7" t="n">
-        <v>-0.1842697647343616</v>
+        <v>-0.2622096842536142</v>
       </c>
       <c r="AO7" t="n">
-        <v>-1.427234765619839</v>
+        <v>-1.419076541777341</v>
       </c>
       <c r="AP7" t="n">
         <v>-0.1244973286161158</v>
@@ -1358,7 +1412,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.453818357394956</v>
+        <v>1.545914836312775</v>
       </c>
       <c r="C8" t="n">
         <v>-0.675145083398379</v>
@@ -1427,45 +1481,55 @@
         <v>-0.006927328179307571</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.562437956403455</v>
+        <v>0.5471481797587877</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.1973235321177838</v>
-      </c>
-      <c r="AA8" t="inlineStr"/>
+        <v>0.1964138807883207</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-0.08637246029619589</v>
+      </c>
       <c r="AB8" t="n">
-        <v>-0.4951692391245345</v>
+        <v>-0.5013407793077793</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.05712597864859388</v>
-      </c>
-      <c r="AD8" t="inlineStr"/>
+        <v>0.06087350781214443</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.114884355150677</v>
+      </c>
       <c r="AE8" t="n">
-        <v>0.04425571206731857</v>
+        <v>0.06414333758034731</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.523092339112188</v>
+        <v>-0.4568551887497855</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.5390928095886501</v>
+        <v>0.5399504875488308</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.1883896428914851</v>
-      </c>
-      <c r="AI8" t="inlineStr"/>
+        <v>0.2418001653428953</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1.215331429741299</v>
+      </c>
       <c r="AJ8" t="n">
-        <v>0.1297870036035469</v>
+        <v>0.1360214683981903</v>
       </c>
       <c r="AK8" t="n">
-        <v>-0.1179862719051748</v>
-      </c>
-      <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="inlineStr"/>
+        <v>-0.1299722945515987</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>3.106540038914435</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>-1.123304310238201</v>
+      </c>
       <c r="AN8" t="n">
-        <v>-0.362605716851976</v>
+        <v>-0.4005841190146444</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.3800728219858399</v>
+        <v>-0.3579340916764525</v>
       </c>
       <c r="AP8" t="n">
         <v>-0.1244973286161158</v>
@@ -1478,7 +1542,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.515216010006835</v>
+        <v>1.453818357394956</v>
       </c>
       <c r="C9" t="n">
         <v>-0.7973779067921173</v>
@@ -1545,167 +1609,51 @@
       </c>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="n">
-        <v>0.2710439266338129</v>
+        <v>0.2845269403257247</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.4546275846319501</v>
-      </c>
-      <c r="AA9" t="inlineStr"/>
+        <v>0.4707335492417696</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.1879626980553124</v>
+      </c>
       <c r="AB9" t="n">
-        <v>0.5487343876007319</v>
+        <v>0.5635652205992338</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.3870533810480162</v>
+        <v>0.390071973388228</v>
       </c>
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="n">
-        <v>1.167967468848685</v>
+        <v>1.167270597873834</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.2800560129197587</v>
+        <v>-0.2362179532228084</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.7702830934679684</v>
+        <v>0.7589773385382548</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0.1534659990911417</v>
+        <v>-0.1410642233341274</v>
       </c>
       <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="n">
-        <v>0.4498953568048402</v>
+        <v>0.5078101282614133</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.513518203854226</v>
+        <v>0.4894645164505488</v>
       </c>
       <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="inlineStr"/>
+      <c r="AM9" t="n">
+        <v>0.4832980932660035</v>
+      </c>
       <c r="AN9" t="n">
-        <v>0.1632066666296132</v>
+        <v>0.1300251190198585</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.7357191856072572</v>
+        <v>0.772306350434349</v>
       </c>
       <c r="AP9" t="n">
-        <v>-0.1244973286161158</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>vmgpBDzg</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1.453818357394956</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-1.408542023760809</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1.308186214129307</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.03086348590088838</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1.048209415282792</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-0.2304341233182217</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2.8391121054821</v>
-      </c>
-      <c r="I10" t="n">
-        <v>3.055536249917173</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1.374931813071086</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1.060058923477298</v>
-      </c>
-      <c r="L10" t="n">
-        <v>-1.599089564314953</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.02256820770482074</v>
-      </c>
-      <c r="N10" t="n">
-        <v>-0.005351037217539404</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2.261902640026929</v>
-      </c>
-      <c r="P10" t="n">
-        <v>-0.1680848320280609</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.981295026269794</v>
-      </c>
-      <c r="R10" t="n">
-        <v>-1.465399303055446</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.4619292194774042</v>
-      </c>
-      <c r="T10" t="n">
-        <v>-1.929117345536482</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.530176781148515</v>
-      </c>
-      <c r="V10" t="n">
-        <v>-0.4453249026421371</v>
-      </c>
-      <c r="W10" t="n">
-        <v>-2.764870293412165</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0.9113268085737301</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0.329002676074807</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0.6553549711847321</v>
-      </c>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="n">
-        <v>2.319898282445731</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0.4853856845719087</v>
-      </c>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="n">
-        <v>1.405258127314685</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0.7305928607226747</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>-0.1193829467831751</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>-1.09231881844585</v>
-      </c>
-      <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="n">
-        <v>1.21446140569224</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1.347719078297672</v>
-      </c>
-      <c r="AL10" t="inlineStr"/>
-      <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="n">
-        <v>-0.5149818321399467</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>1.990868674516283</v>
-      </c>
-      <c r="AP10" t="n">
         <v>-0.1244973286161158</v>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_selected.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP9"/>
+  <dimension ref="A1:AP6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -709,43 +709,43 @@
       </c>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="n">
-        <v>-1.399094024127298</v>
+        <v>-1.429331946165173</v>
       </c>
       <c r="Z2" t="n">
-        <v>-5.293553505847798</v>
+        <v>-5.469187832948998</v>
       </c>
       <c r="AA2" t="n">
         <v>-0.2840277779144467</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.01173534201280535</v>
+        <v>-0.03012295504493269</v>
       </c>
       <c r="AC2" t="n">
-        <v>-2.532114324392467</v>
+        <v>-2.136881539631822</v>
       </c>
       <c r="AD2" t="n">
         <v>-1.698808029148732</v>
       </c>
       <c r="AE2" t="n">
-        <v>-1.227451494364216</v>
+        <v>-1.082019563378821</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.4682714613933115</v>
+        <v>0.5838344778657885</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0.9735447986206999</v>
+        <v>-0.882127219213666</v>
       </c>
       <c r="AH2" t="n">
-        <v>-1.081313587984082</v>
+        <v>-1.041815359885711</v>
       </c>
       <c r="AI2" t="n">
         <v>0.2823435418057868</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-1.535397350856816</v>
+        <v>-1.466724768528253</v>
       </c>
       <c r="AK2" t="n">
-        <v>-3.293828360886823</v>
+        <v>-3.20431222173137</v>
       </c>
       <c r="AL2" t="n">
         <v>-1.541784038898458</v>
@@ -754,10 +754,10 @@
         <v>1.235892574641727</v>
       </c>
       <c r="AN2" t="n">
-        <v>-1.048570076283611</v>
+        <v>-1.103313400158459</v>
       </c>
       <c r="AO2" t="n">
-        <v>-1.987294705461664</v>
+        <v>-1.81151651593751</v>
       </c>
       <c r="AP2" t="n">
         <v>-0.1244973286161158</v>
@@ -766,41 +766,41 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>p6XSLUlB</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1.453818357394956</v>
       </c>
       <c r="C3" t="n">
-        <v>1.62756358956753</v>
+        <v>0.07008083987312229</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6559717790263305</v>
+        <v>0.4943117908384131</v>
       </c>
       <c r="E3" t="n">
-        <v>1.773165039494718</v>
+        <v>0.942940809258732</v>
       </c>
       <c r="F3" t="n">
-        <v>1.048209415282792</v>
+        <v>-0.1423850690800846</v>
       </c>
       <c r="G3" t="n">
         <v>-0.2304341233182217</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2924698004996741</v>
+        <v>-0.8650948835832468</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6112110282974008</v>
+        <v>-0.610951582512485</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5806554141095995</v>
+        <v>-1.007897383813373</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02375662033231982</v>
+        <v>-0.4943945312401692</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.291350145507214</v>
+        <v>-1.650379467449576</v>
       </c>
       <c r="M3" t="n">
         <v>0.02256820770482074</v>
@@ -809,85 +809,85 @@
         <v>-0.005351037217539404</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4218004190135942</v>
+        <v>0.881825974266928</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.49434528316866</v>
+        <v>-1.147562916718839</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.379780866922818</v>
+        <v>-1.266881434203879</v>
       </c>
       <c r="R3" t="n">
-        <v>-2.469696644960085</v>
+        <v>-0.2100276256746462</v>
       </c>
       <c r="S3" t="n">
-        <v>2.239656734552424</v>
+        <v>0.2079681458952584</v>
       </c>
       <c r="T3" t="n">
         <v>-0.9497785234691912</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4873324780443357</v>
+        <v>-0.03408967350775372</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.904565740222916</v>
+        <v>0.1383714323901744</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5882644478510841</v>
+        <v>-1.306985623297709</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6225184432335839</v>
+        <v>-0.08157418558663432</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.4341805277586076</v>
+        <v>-1.840958409636392</v>
       </c>
       <c r="Z3" t="n">
-        <v>-1.049398464751491</v>
+        <v>-1.164984439692375</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.1150051796877471</v>
+        <v>-0.7303342295609303</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.4931144146384643</v>
+        <v>1.405893712877917</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.2452175969035678</v>
+        <v>-0.945575638645077</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.0326949765739812</v>
+        <v>-1.049494402002715</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.4007433101516943</v>
+        <v>-1.711081865390963</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.2935578111033451</v>
+        <v>0.3299045833586772</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.3123799805057446</v>
+        <v>-1.946036299559198</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.6469157742796354</v>
+        <v>0.5918366623361107</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.2823435418057868</v>
+        <v>-0.6506443461297259</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-1.390046220030712</v>
+        <v>-2.330833581113332</v>
       </c>
       <c r="AK3" t="n">
-        <v>-1.273987842816045</v>
+        <v>-0.8908749076054666</v>
       </c>
       <c r="AL3" t="n">
-        <v>-1.52494228499334</v>
+        <v>-0.5144370506861887</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.0669692312283692</v>
+        <v>-0.8777770326262624</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.7354973632152686</v>
+        <v>-0.08829082783767538</v>
       </c>
       <c r="AO3" t="n">
-        <v>-1.052740664491578</v>
+        <v>-0.6523144716617398</v>
       </c>
       <c r="AP3" t="n">
         <v>-0.1244973286161158</v>
@@ -896,29 +896,29 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>SU02594U</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.453818357394956</v>
+        <v>1.638011315230593</v>
       </c>
       <c r="C4" t="n">
-        <v>0.07008083987312229</v>
+        <v>-0.8644088099435222</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4943117908384131</v>
+        <v>-0.2972647030472513</v>
       </c>
       <c r="E4" t="n">
-        <v>0.942940809258732</v>
+        <v>1.282046480763571</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1423850690800846</v>
+        <v>-0.3975124585864154</v>
       </c>
       <c r="G4" t="n">
         <v>-0.2304341233182217</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.8650948835832468</v>
+        <v>0.2924698004996741</v>
       </c>
       <c r="I4" t="n">
         <v>-0.610951582512485</v>
@@ -927,10 +927,10 @@
         <v>-1.007897383813373</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.4943945312401692</v>
+        <v>0.02375662033231982</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.650379467449576</v>
+        <v>-2.009408789391938</v>
       </c>
       <c r="M4" t="n">
         <v>0.02256820770482074</v>
@@ -939,85 +939,85 @@
         <v>-0.005351037217539404</v>
       </c>
       <c r="O4" t="n">
-        <v>0.881825974266928</v>
+        <v>-0.0382251362397396</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.147562916718839</v>
+        <v>-0.7802586349597975</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.266881434203879</v>
+        <v>1.740689362531003</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.2100276256746462</v>
+        <v>-0.7121762966269659</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2079681458952584</v>
+        <v>1.477773513805987</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9497785234691912</v>
+        <v>0.5192297096317455</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.03408967350775372</v>
+        <v>0.4873324780443357</v>
       </c>
       <c r="V4" t="n">
         <v>0.1383714323901744</v>
       </c>
       <c r="W4" t="n">
-        <v>-1.306985623297709</v>
+        <v>-0.8696202222633719</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.08157418558663432</v>
+        <v>0.5886176870311318</v>
       </c>
       <c r="Y4" t="n">
-        <v>-1.840958409636392</v>
+        <v>0.4695450113860344</v>
       </c>
       <c r="Z4" t="n">
-        <v>-1.164984439692375</v>
+        <v>0.1535983159035849</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.7303342295609303</v>
+        <v>-0.06887754517744298</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.405893712877917</v>
+        <v>-0.3285137334784797</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.945575638645077</v>
+        <v>0.1036351137941933</v>
       </c>
       <c r="AD4" t="n">
-        <v>-1.049494402002715</v>
+        <v>0.0326949765739812</v>
       </c>
       <c r="AE4" t="n">
-        <v>-1.711081865390963</v>
+        <v>0.7196375982988346</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.3299045833586772</v>
+        <v>0.3201490351875603</v>
       </c>
       <c r="AG4" t="n">
-        <v>-1.946036299559198</v>
+        <v>0.8513135773372487</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.5918366623361107</v>
+        <v>0.2731134253825242</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.6506443461297259</v>
+        <v>-1.103809891698403</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-2.330833581113332</v>
+        <v>0.9437266991013616</v>
       </c>
       <c r="AK4" t="n">
-        <v>-0.8908749076054666</v>
+        <v>-0.01011206808736213</v>
       </c>
       <c r="AL4" t="n">
-        <v>-0.5144370506861887</v>
+        <v>1.068687816395015</v>
       </c>
       <c r="AM4" t="n">
-        <v>-0.8777770326262624</v>
+        <v>-1.496932776169411</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0.08829082783767538</v>
+        <v>1.710923861349014</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.6523144716617398</v>
+        <v>-0.01303597738284825</v>
       </c>
       <c r="AP4" t="n">
         <v>-0.1244973286161158</v>
@@ -1026,23 +1026,23 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>ChZKNjKb</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.638011315230593</v>
+        <v>1.453818357394956</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.8644088099435222</v>
+        <v>1.62756358956753</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2972647030472513</v>
+        <v>0.6559717790263305</v>
       </c>
       <c r="E5" t="n">
-        <v>1.282046480763571</v>
+        <v>1.773165039494718</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3975124585864154</v>
+        <v>1.048209415282792</v>
       </c>
       <c r="G5" t="n">
         <v>-0.2304341233182217</v>
@@ -1051,16 +1051,16 @@
         <v>0.2924698004996741</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.610951582512485</v>
+        <v>0.6112110282974008</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.007897383813373</v>
+        <v>0.5806554141095995</v>
       </c>
       <c r="K5" t="n">
         <v>0.02375662033231982</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.009408789391938</v>
+        <v>-1.291350145507214</v>
       </c>
       <c r="M5" t="n">
         <v>0.02256820770482074</v>
@@ -1069,85 +1069,85 @@
         <v>-0.005351037217539404</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0382251362397396</v>
+        <v>0.4218004190135942</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.7802586349597975</v>
+        <v>-2.49434528316866</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.740689362531003</v>
+        <v>1.379780866922818</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.7121762966269659</v>
+        <v>-2.469696644960085</v>
       </c>
       <c r="S5" t="n">
-        <v>1.477773513805987</v>
+        <v>2.239656734552424</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5192297096317455</v>
+        <v>-0.9497785234691912</v>
       </c>
       <c r="U5" t="n">
         <v>0.4873324780443357</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1383714323901744</v>
+        <v>-1.904565740222916</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.8696202222633719</v>
+        <v>0.5882644478510841</v>
       </c>
       <c r="X5" t="n">
-        <v>0.5886176870311318</v>
+        <v>0.6225184432335839</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4695450113860344</v>
+        <v>-0.4315437945427379</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.1535983159035849</v>
+        <v>-1.06638827556814</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.06887754517744298</v>
+        <v>0.2117855611957419</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.3285137334784797</v>
+        <v>0.4896459133726851</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.1036351137941933</v>
+        <v>-0.2409865155898819</v>
       </c>
       <c r="AD5" t="n">
         <v>0.0326949765739812</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.7196375982988346</v>
+        <v>-0.3952822539545508</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.3201490351875603</v>
+        <v>-0.2954193968325032</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.8513135773372487</v>
+        <v>-0.3120875902920417</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.2731134253825242</v>
+        <v>0.6315294466824208</v>
       </c>
       <c r="AI5" t="n">
-        <v>-1.103809891698403</v>
+        <v>0.8154794777689368</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.9437266991013616</v>
+        <v>-1.393373458509122</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.01011206808736213</v>
+        <v>-1.314898540510184</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.068687816395015</v>
+        <v>-1.945986132621319</v>
       </c>
       <c r="AM5" t="n">
-        <v>-1.496932776169411</v>
+        <v>0.4779605437527005</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.710923861349014</v>
+        <v>0.7714737723620317</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.01303597738284825</v>
+        <v>-1.046914682831213</v>
       </c>
       <c r="AP5" t="n">
         <v>-0.1244973286161158</v>
@@ -1235,7 +1235,7 @@
         <v>0.8667963297777855</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.2646717016128478</v>
+        <v>-0.2200038332245425</v>
       </c>
       <c r="AB6" t="n">
         <v>-1.133272473523469</v>
@@ -1259,7 +1259,7 @@
         <v>0.9894354745632675</v>
       </c>
       <c r="AI6" t="n">
-        <v>-1.67248822339243</v>
+        <v>-2.20562415935558</v>
       </c>
       <c r="AJ6" t="n">
         <v>0.09408822461075424</v>
@@ -1268,10 +1268,10 @@
         <v>-0.08053739876652269</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.5144370506861887</v>
+        <v>-0.570576230369921</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0.7603509433335963</v>
+        <v>-0.7443382947936873</v>
       </c>
       <c r="AN6" t="n">
         <v>0.6752503676713434</v>
@@ -1280,380 +1280,6 @@
         <v>0.2407178904908249</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.1244973286161158</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>tYQyK8JN</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1.576613662618714</v>
-      </c>
-      <c r="C7" t="n">
-        <v>-0.2847886473990212</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.1208214733008109</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.3582758583883194</v>
-      </c>
-      <c r="F7" t="n">
-        <v>-1.800713100871234</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-0.2304341233182217</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-2.254172504482752</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-3.513587783185964</v>
-      </c>
-      <c r="J7" t="n">
-        <v>-1.007897383813373</v>
-      </c>
-      <c r="K7" t="n">
-        <v>-1.012545682812658</v>
-      </c>
-      <c r="L7" t="n">
-        <v>-0.8810309204302289</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.02256820770482074</v>
-      </c>
-      <c r="N7" t="n">
-        <v>-0.005351037217539404</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.4218004190135942</v>
-      </c>
-      <c r="P7" t="n">
-        <v>-0.04565007144171361</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>-0.4247616111181118</v>
-      </c>
-      <c r="R7" t="n">
-        <v>-2.218622309483925</v>
-      </c>
-      <c r="S7" t="n">
-        <v>-0.5539150748511786</v>
-      </c>
-      <c r="T7" t="n">
-        <v>-2.908456167603774</v>
-      </c>
-      <c r="U7" t="n">
-        <v>-1.076933976611933</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.889460437487109</v>
-      </c>
-      <c r="W7" t="n">
-        <v>-0.5780432882404807</v>
-      </c>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="n">
-        <v>-0.3879483910798276</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>-1.236683086932383</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0.001846579770707041</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>-1.844309537603664</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>-0.609092664466501</v>
-      </c>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="n">
-        <v>-1.200166953586087</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>-0.5557405180093393</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>-0.09450430405688781</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>-0.7923435691342182</v>
-      </c>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="n">
-        <v>-1.225137242640447</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>-1.074203754659676</v>
-      </c>
-      <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="n">
-        <v>-0.349359630809265</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>-0.2622096842536142</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>-1.419076541777341</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>-0.1244973286161158</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>6FCg7VZH</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1.545914836312775</v>
-      </c>
-      <c r="C8" t="n">
-        <v>-0.675145083398379</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1.77086824928783</v>
-      </c>
-      <c r="E8" t="n">
-        <v>-1.430798891275143</v>
-      </c>
-      <c r="F8" t="n">
-        <v>-0.3975124585864154</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-0.2304341233182217</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1.218521547766011</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-0.3054109298100136</v>
-      </c>
-      <c r="J8" t="n">
-        <v>-0.2136209848518865</v>
-      </c>
-      <c r="K8" t="n">
-        <v>-0.4943945312401692</v>
-      </c>
-      <c r="L8" t="n">
-        <v>-0.6245814047571133</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.02256820770482074</v>
-      </c>
-      <c r="N8" t="n">
-        <v>-0.005351037217539404</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.341851529520262</v>
-      </c>
-      <c r="P8" t="n">
-        <v>-0.04565007144171361</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.740689362531003</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.04104670980151362</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.985695660970278</v>
-      </c>
-      <c r="T8" t="n">
-        <v>-0.4601091124355456</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3.615865387356873</v>
-      </c>
-      <c r="V8" t="n">
-        <v>2.765004940035576</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.608783716931203</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-0.006927328179307571</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0.5471481797587877</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0.1964138807883207</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>-0.08637246029619589</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>-0.5013407793077793</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0.06087350781214443</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.114884355150677</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0.06414333758034731</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>-0.4568551887497855</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0.5399504875488308</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0.2418001653428953</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1.215331429741299</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0.1360214683981903</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>-0.1299722945515987</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>3.106540038914435</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>-1.123304310238201</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>-0.4005841190146444</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>-0.3579340916764525</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>-0.1244973286161158</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>bk9o9i55</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1.453818357394956</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-0.7973779067921173</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.4497159320279531</v>
-      </c>
-      <c r="E9" t="n">
-        <v>-0.7642808472828727</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.4103909415169653</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-0.2304341233182217</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-0.1705560731334942</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-0.3054109298100136</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.5806554141095995</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.02375662033231982</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.1960570453968566</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.02256820770482074</v>
-      </c>
-      <c r="N9" t="n">
-        <v>-0.005351037217539404</v>
-      </c>
-      <c r="O9" t="n">
-        <v>-0.0382251362397396</v>
-      </c>
-      <c r="P9" t="n">
-        <v>-0.9026933955461448</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.1767525482288647</v>
-      </c>
-      <c r="R9" t="n">
-        <v>-0.4611019611508061</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.223812440223842</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0.5192297096317455</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.051598932700604</v>
-      </c>
-      <c r="V9" t="n">
-        <v>-1.320869405190604</v>
-      </c>
-      <c r="W9" t="n">
-        <v>-0.8696202222633719</v>
-      </c>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="n">
-        <v>0.2845269403257247</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0.4707335492417696</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0.1879626980553124</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0.5635652205992338</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0.390071973388228</v>
-      </c>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="n">
-        <v>1.167270597873834</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>-0.2362179532228084</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0.7589773385382548</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>-0.1410642233341274</v>
-      </c>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="n">
-        <v>0.5078101282614133</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0.4894645164505488</v>
-      </c>
-      <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="n">
-        <v>0.4832980932660035</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>0.1300251190198585</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0.772306350434349</v>
-      </c>
-      <c r="AP9" t="n">
         <v>-0.1244973286161158</v>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_selected.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP6"/>
+  <dimension ref="A1:AP10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -638,41 +638,41 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>6ZfxDZ5t</t>
+          <t>Qw81zU34</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.545914836312775</v>
+        <v>1.453818357394956</v>
       </c>
       <c r="C2" t="n">
-        <v>1.434356868719363</v>
+        <v>-0.5529122600046407</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.8491384558266935</v>
+        <v>-1.350841867444368</v>
       </c>
       <c r="E2" t="n">
-        <v>0.942940809258732</v>
+        <v>-1.11507981780512</v>
       </c>
       <c r="F2" t="n">
-        <v>1.374205524096437</v>
+        <v>1.74272286449447</v>
       </c>
       <c r="G2" t="n">
         <v>-0.2304341233182217</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.1705560731334942</v>
+        <v>-0.6335819467666627</v>
       </c>
       <c r="I2" t="n">
-        <v>-3.208047130483493</v>
+        <v>-1.527573540619899</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.802173782774859</v>
+        <v>1.374931813071086</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.566999137530125</v>
+        <v>0.5419077719048088</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.3168419859493746</v>
+        <v>0.5550863673392186</v>
       </c>
       <c r="M2" t="n">
         <v>0.02256820770482074</v>
@@ -681,83 +681,75 @@
         <v>-0.005351037217539404</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0382251362397396</v>
+        <v>-1.571643653750852</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.2905195926144082</v>
+        <v>0.4032773840415596</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.545064442987507</v>
+        <v>-1.90849653750732</v>
       </c>
       <c r="R2" t="n">
-        <v>-1.716473638531606</v>
+        <v>0.7105782710712736</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8078761484333244</v>
+        <v>-1.908374133955956</v>
       </c>
       <c r="T2" t="n">
-        <v>-2.908456167603774</v>
+        <v>0.02956029859809994</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5555118250598432</v>
+        <v>-2.467393047417504</v>
       </c>
       <c r="V2" t="n">
-        <v>0.576143683664408</v>
+        <v>1.062557296191335</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.2864663542175895</v>
-      </c>
-      <c r="X2" t="inlineStr"/>
+        <v>0.2966875138281929</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.7157455227903363</v>
+      </c>
       <c r="Y2" t="n">
-        <v>-1.429331946165173</v>
+        <v>-0.4235204925070672</v>
       </c>
       <c r="Z2" t="n">
-        <v>-5.469187832948998</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-0.2840277779144467</v>
-      </c>
+        <v>0.07642777865211062</v>
+      </c>
+      <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="n">
-        <v>-0.03012295504493269</v>
+        <v>0.2740087910009387</v>
       </c>
       <c r="AC2" t="n">
-        <v>-2.136881539631822</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-1.698808029148732</v>
-      </c>
+        <v>0.1763245908221197</v>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="n">
-        <v>-1.082019563378821</v>
+        <v>0.01795329988835716</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.5838344778657885</v>
+        <v>0.1439399061231477</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0.882127219213666</v>
+        <v>-0.07376574173919211</v>
       </c>
       <c r="AH2" t="n">
-        <v>-1.041815359885711</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0.2823435418057868</v>
-      </c>
+        <v>-0.2282901445467781</v>
+      </c>
+      <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="n">
-        <v>-1.466724768528253</v>
+        <v>-0.09157475321293676</v>
       </c>
       <c r="AK2" t="n">
-        <v>-3.20431222173137</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>-1.541784038898458</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.235892574641727</v>
-      </c>
+        <v>-1.186841461124843</v>
+      </c>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="n">
-        <v>-1.103313400158459</v>
+        <v>-0.1928525664756904</v>
       </c>
       <c r="AO2" t="n">
-        <v>-1.81151651593751</v>
+        <v>-0.9195587237356364</v>
       </c>
       <c r="AP2" t="n">
         <v>-0.1244973286161158</v>
@@ -766,41 +758,41 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SU02594U</t>
+          <t>E3tkRPQj</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1.453818357394956</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07008083987312229</v>
+        <v>1.272694102295386</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4943117908384131</v>
+        <v>0.0595021674364284</v>
       </c>
       <c r="E3" t="n">
-        <v>0.942940809258732</v>
+        <v>0.03086348590088838</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1423850690800846</v>
+        <v>0.3678697099325769</v>
       </c>
       <c r="G3" t="n">
         <v>-0.2304341233182217</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.8650948835832468</v>
+        <v>-1.096607820399831</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.610951582512485</v>
+        <v>-0.1526406034587778</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.007897383813373</v>
+        <v>-0.2136209848518865</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.4943945312401692</v>
+        <v>1.060058923477298</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.650379467449576</v>
+        <v>1.341531548736774</v>
       </c>
       <c r="M3" t="n">
         <v>0.02256820770482074</v>
@@ -809,85 +801,75 @@
         <v>-0.005351037217539404</v>
       </c>
       <c r="O3" t="n">
-        <v>0.881825974266928</v>
+        <v>-1.571643653750852</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.147562916718839</v>
+        <v>0.9746396001111807</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.266881434203879</v>
+        <v>0.4975600998805856</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.2100276256746462</v>
+        <v>0.7105782710712731</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2079681458952584</v>
+        <v>0.4619292194774042</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9497785234691912</v>
+        <v>1.988237942732682</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.03408967350775372</v>
+        <v>-0.3817044412091469</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1383714323901744</v>
+        <v>-1.174945321432527</v>
       </c>
       <c r="W3" t="n">
-        <v>-1.306985623297709</v>
+        <v>1.26861062723783</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.08157418558663432</v>
+        <v>1.044104770366681</v>
       </c>
       <c r="Y3" t="n">
-        <v>-1.840958409636392</v>
+        <v>1.497338193147307</v>
       </c>
       <c r="Z3" t="n">
-        <v>-1.164984439692375</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>-0.7303342295609303</v>
-      </c>
+        <v>0.2980833363706666</v>
+      </c>
+      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="n">
-        <v>1.405893712877917</v>
+        <v>-1.95428399919316</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.945575638645077</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>-1.049494402002715</v>
-      </c>
+        <v>0.2272449176768788</v>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
-        <v>-1.711081865390963</v>
+        <v>0.7068727982306613</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.3299045833586772</v>
+        <v>-1.820027974886559</v>
       </c>
       <c r="AG3" t="n">
-        <v>-1.946036299559198</v>
+        <v>1.867965179637492</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.5918366623361107</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>-0.6506443461297259</v>
-      </c>
+        <v>-0.2469799645952813</v>
+      </c>
+      <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="n">
-        <v>-2.330833581113332</v>
+        <v>0.2556695735626068</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.8908749076054666</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>-0.5144370506861887</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>-0.8777770326262624</v>
-      </c>
+        <v>-0.06562057748046309</v>
+      </c>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="n">
-        <v>-0.08829082783767538</v>
+        <v>0.1492702003966213</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.6523144716617398</v>
+        <v>-0.1668418932164831</v>
       </c>
       <c r="AP3" t="n">
         <v>-0.1244973286161158</v>
@@ -896,20 +878,20 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ChZKNjKb</t>
+          <t>fJaIWo3T</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1.638011315230593</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.8644088099435222</v>
+        <v>-0.2847886473990212</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2972647030472513</v>
+        <v>-0.8881598322858459</v>
       </c>
       <c r="E4" t="n">
-        <v>1.282046480763571</v>
+        <v>-0.1211494013254189</v>
       </c>
       <c r="F4" t="n">
         <v>-0.3975124585864154</v>
@@ -921,16 +903,16 @@
         <v>0.2924698004996741</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.610951582512485</v>
+        <v>0.7639813546486365</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.007897383813373</v>
+        <v>-0.2136209848518865</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02375662033231982</v>
+        <v>-0.4943945312401692</v>
       </c>
       <c r="L4" t="n">
-        <v>-2.009408789391938</v>
+        <v>0.1789604110186492</v>
       </c>
       <c r="M4" t="n">
         <v>0.02256820770482074</v>
@@ -939,85 +921,73 @@
         <v>-0.005351037217539404</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0382251362397396</v>
+        <v>0.5751422707647056</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.7802586349597975</v>
+        <v>-1.22918609044307</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.740689362531003</v>
+        <v>-1.026275770465088</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.7121762966269659</v>
+        <v>-1.298016412738006</v>
       </c>
       <c r="S4" t="n">
-        <v>1.477773513805987</v>
+        <v>-1.231144604403567</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5192297096317455</v>
+        <v>-1.276224797491622</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4873324780443357</v>
+        <v>-0.3817044412091469</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1383714323901744</v>
+        <v>1.257122741202105</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.8696202222633719</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.5886176870311318</v>
-      </c>
+        <v>-0.0920817315356617</v>
+      </c>
+      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
-        <v>0.4695450113860344</v>
+        <v>0.5856620231757699</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.1535983159035849</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>-0.06887754517744298</v>
-      </c>
+        <v>0.145112826625887</v>
+      </c>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="n">
-        <v>-0.3285137334784797</v>
+        <v>-0.8177318832757947</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.1036351137941933</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0.0326949765739812</v>
-      </c>
+        <v>0.2044295559661921</v>
+      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="n">
-        <v>0.7196375982988346</v>
+        <v>0.3795221249164104</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.3201490351875603</v>
+        <v>0.08955871693930147</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.8513135773372487</v>
+        <v>0.7884171935903409</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.2731134253825242</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>-1.103809891698403</v>
-      </c>
+        <v>-0.6251373381982024</v>
+      </c>
+      <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="n">
-        <v>0.9437266991013616</v>
+        <v>0.5535664082192722</v>
       </c>
       <c r="AK4" t="n">
         <v>-0.01011206808736213</v>
       </c>
-      <c r="AL4" t="n">
-        <v>1.068687816395015</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>-1.496932776169411</v>
-      </c>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="n">
-        <v>1.710923861349014</v>
+        <v>-1.919059481753211</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.01303597738284825</v>
+        <v>0.2347624425713414</v>
       </c>
       <c r="AP4" t="n">
         <v>-0.1244973286161158</v>
@@ -1026,20 +996,20 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>p6XSLUlB</t>
+          <t>M51AY7YG</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1.453818357394956</v>
       </c>
       <c r="C5" t="n">
-        <v>1.62756358956753</v>
+        <v>1.753739407264292</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6559717790263305</v>
+        <v>1.65937860226168</v>
       </c>
       <c r="E5" t="n">
-        <v>1.773165039494718</v>
+        <v>1.445752667007287</v>
       </c>
       <c r="F5" t="n">
         <v>1.048209415282792</v>
@@ -1048,19 +1018,19 @@
         <v>-0.2304341233182217</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2924698004996741</v>
+        <v>-0.1705560731334942</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6112110282974008</v>
+        <v>-0.610951582512485</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5806554141095995</v>
+        <v>-1.007897383813373</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02375662033231982</v>
+        <v>-1.530696834385147</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.291350145507214</v>
+        <v>0.07638060474940293</v>
       </c>
       <c r="M5" t="n">
         <v>0.02256820770482074</v>
@@ -1069,86 +1039,62 @@
         <v>-0.005351037217539404</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4218004190135942</v>
+        <v>-0.9582762467464072</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.49434528316866</v>
+        <v>-0.004838484579597983</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.379780866922818</v>
+        <v>-1.82829464959439</v>
       </c>
       <c r="R5" t="n">
-        <v>-2.469696644960085</v>
+        <v>0.5431953807538331</v>
       </c>
       <c r="S5" t="n">
-        <v>2.239656734552424</v>
+        <v>-1.739066751567859</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9497785234691912</v>
+        <v>0.3560065726205305</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4873324780443357</v>
+        <v>-1.424548744313326</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.904565740222916</v>
+        <v>0.1870127936428668</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5882644478510841</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0.6225184432335839</v>
-      </c>
+        <v>-0.8696202222633719</v>
+      </c>
+      <c r="X5" t="inlineStr"/>
       <c r="Y5" t="n">
-        <v>-0.4315437945427379</v>
+        <v>-0.8664016107759375</v>
       </c>
       <c r="Z5" t="n">
-        <v>-1.06638827556814</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0.2117855611957419</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0.4896459133726851</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-0.2409865155898819</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0.0326949765739812</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-0.3952822539545508</v>
-      </c>
+        <v>-0.1004005495084013</v>
+      </c>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>-0.2954193968325032</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>-0.3120875902920417</v>
-      </c>
+        <v>1.255062619898986</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>0.6315294466824208</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0.8154794777689368</v>
-      </c>
+        <v>-0.2605315806867093</v>
+      </c>
+      <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="n">
-        <v>-1.393373458509122</v>
+        <v>0.7259773009248448</v>
       </c>
       <c r="AK5" t="n">
-        <v>-1.314898540510184</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>-1.945986132621319</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0.4779605437527005</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0.7714737723620317</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>-1.046914682831213</v>
-      </c>
+        <v>1.079533965041078</v>
+      </c>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="n">
         <v>-0.1244973286161158</v>
       </c>
@@ -1156,41 +1102,41 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>IgtCPCkn</t>
+          <t>hCffxjZi</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.453818357394956</v>
+        <v>1.545914836312775</v>
       </c>
       <c r="C6" t="n">
-        <v>-1.444028972488023</v>
+        <v>0.6299860309025043</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5871377853152412</v>
+        <v>-0.6930529499900836</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03086348590088838</v>
+        <v>-1.758211263762574</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.843234332455623</v>
+        <v>0.05604734498039485</v>
       </c>
       <c r="G6" t="n">
         <v>-0.2304341233182217</v>
       </c>
       <c r="H6" t="n">
-        <v>2.144573295032348</v>
+        <v>1.913060358215763</v>
       </c>
       <c r="I6" t="n">
-        <v>1.527832986404815</v>
+        <v>0.7639813546486365</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2136209848518865</v>
+        <v>2.169208212032572</v>
       </c>
       <c r="K6" t="n">
-        <v>1.060058923477298</v>
+        <v>1.578210075049787</v>
       </c>
       <c r="L6" t="n">
-        <v>1.170565204954696</v>
+        <v>-0.09458573903267389</v>
       </c>
       <c r="M6" t="n">
         <v>0.02256820770482074</v>
@@ -1199,87 +1145,543 @@
         <v>-0.005351037217539404</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0382251362397396</v>
+        <v>-0.3449088397419623</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4129543532007556</v>
+        <v>2.035740858526191</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.6653672748569023</v>
+        <v>-0.545064442987507</v>
       </c>
       <c r="R6" t="n">
-        <v>-1.465399303055446</v>
+        <v>0.8779611613887134</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.04599292768688727</v>
+        <v>-0.8925298396273726</v>
       </c>
       <c r="T6" t="n">
-        <v>0.02956029859809994</v>
+        <v>1.008899120665391</v>
       </c>
       <c r="U6" t="n">
+        <v>-1.772163512014719</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-0.2021180963786738</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-1.161197156286263</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.1635543592618822</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.3612613685938257</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.6992430290578941</v>
+      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="n">
+        <v>-0.3538696737662351</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.2664914295638132</v>
+      </c>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="n">
+        <v>0.3504299952772304</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-0.09629463180020989</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.4059383062699066</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.00267283341478842</v>
+      </c>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="n">
+        <v>0.6633550801432586</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.023810167311611</v>
+      </c>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="n">
+        <v>-0.09245558998622642</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.7524980127891074</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-0.1244973286161158</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>8MPiooIM</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.453818357394956</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.8170928783072364</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.8268405264214634</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.942940809258732</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.260815573204735</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.2304341233182217</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.218521547766011</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.597225270863465</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.169208212032572</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.614512378194765</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.751850773813759</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.02256820770482074</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-0.005351037217539404</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-1.878327357253075</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.056262773835412</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-1.106477658378018</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.049641393610792</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-1.231144604403567</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.641130490777543</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-1.772163512014719</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.6734264061697932</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.3938798251691568</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.5475456170166162</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.518375888201992</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>5.293618934568297</v>
+      </c>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="n">
+        <v>-2.517377239168495</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.639887152772503</v>
+      </c>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="n">
+        <v>1.950564132256606</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-0.3584473952752774</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.892890342058713</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.432511073035144</v>
+      </c>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="n">
+        <v>2.709825888810198</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>2.660555691820289</v>
+      </c>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="n">
+        <v>0.6714732301331527</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1.787774953835961</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>-0.1244973286161158</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>CGH7Enso</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.453818357394956</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.2808456530959973</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-1.384288761552213</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.4167423534753607</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-0.7660297989844487</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-0.2304341233182217</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.1705560731334942</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-0.610951582512485</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-1.007897383813373</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-1.012545682812658</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-1.017803995455891</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.02256820770482074</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-0.005351037217539404</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.495193381271373</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-0.5762007006492185</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.379780866922818</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.04104670980151362</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.139158749029793</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-0.2968859754243304</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.703984164999211</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.08973007113748141</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-0.8696202222633719</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.183184795812652</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-2.670110724817361</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-1.945507136606524</v>
+      </c>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="n">
+        <v>1.320340006177421</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-0.9106115742109112</v>
+      </c>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="n">
+        <v>-1.841564254749213</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.6840865762224947</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>-2.455684715206838</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-0.4051958684862741</v>
+      </c>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="n">
+        <v>-2.616718365609065</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>-1.366986742140946</v>
+      </c>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="n">
+        <v>-0.2987996226131886</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>-0.7051625986342055</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>-0.1244973286161158</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>0dMqm7mA</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.453818357394956</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.1371117430245272</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.4943117908384131</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0.1211494013254189</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.3678697099325769</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.2304341233182217</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.607599168665516</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.291684618160994</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-0.2136209848518865</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-0.4943945312401692</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.238951742467526</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.02256820770482074</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-0.005351037217539404</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-0.9582762467464072</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.2400310365930966</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-1.90849653750732</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.7105782710712731</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-1.400451986791664</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.335345394687822</v>
+      </c>
+      <c r="U9" t="n">
         <v>-0.03408967350775372</v>
       </c>
-      <c r="V6" t="n">
-        <v>-0.2994008188840592</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.8798413818739753</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0.08401796970997172</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.047412831781418</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0.8667963297777855</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>-0.2200038332245425</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>-1.133272473523469</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0.1060030370480539</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0.0326949765739812</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>-0.08279518335600816</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>-1.240033150841297</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0.4822232739996728</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0.9894354745632675</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>-2.20562415935558</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0.09408822461075424</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>-0.08053739876652269</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>-0.570576230369921</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>-0.7443382947936873</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>0.6752503676713434</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0.2407178904908249</v>
-      </c>
-      <c r="AP6" t="n">
+      <c r="V9" t="n">
+        <v>-0.7858144314109854</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-1.258389467627227</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-0.2884557234375155</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.269829558628543</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.212402944960209</v>
+      </c>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="n">
+        <v>0.5735343796188878</v>
+      </c>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="n">
+        <v>-0.6291113375103921</v>
+      </c>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="n">
+        <v>0.8076609319050403</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.812837842663346</v>
+      </c>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="n">
+        <v>-0.1244973286161158</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>vsYzkTIc</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.545914836312775</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.4525512872664325</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.469846202317225</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-1.793291160814799</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-1.418022016611738</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0.2304341233182217</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.06095686368308995</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-1.527573540619899</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="n">
+        <v>0.02375662033231982</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-1.188770339237968</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.02256820770482074</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0.005351037217539404</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.801877084773595</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-0.9026933955461448</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.021395970226259</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-1.130633522420566</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.477773513805987</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-1.602671071514052</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.356369397297818</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.7707091286751784</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0.5780432882404807</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.876122177132721</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-1.564420618455418</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-1.459938616419383</v>
+      </c>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="n">
+        <v>0.8230286867599538</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-0.7875738834909326</v>
+      </c>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="n">
+        <v>-1.359148621726705</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>-0.02732849721223683</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>-1.604439339723106</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.9742475485273814</v>
+      </c>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="n">
+        <v>-1.924042932498301</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>-1.808331456074549</v>
+      </c>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="n">
+        <v>0.2473876798878442</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>-0.2821963300917094</v>
+      </c>
+      <c r="AP10" t="n">
         <v>-0.1244973286161158</v>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_selected.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,687 +493,208 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>S66OuPup</t>
+          <t>Qw81zU34</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>-0.257225400694654</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.151305327682867</v>
+        <v>0.9347397838772308</v>
       </c>
       <c r="D2" t="n">
-        <v>2.972922736479445</v>
+        <v>-2.416772637565137</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5876933990425653</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-1.009133918893522</v>
-      </c>
+        <v>3.89635088523469</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>-2.753769071947779</v>
+        <v>-0.3743866171630088</v>
       </c>
       <c r="H2" t="n">
-        <v>1.008494031355277</v>
+        <v>0.102435482297003</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3538771266030103</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
+        <v>-1.049195051146014</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-0.1443748629859064</v>
+      </c>
       <c r="K2" t="n">
-        <v>0.0264694096101723</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
+        <v>-0.01160671425672479</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-1.344743261141947</v>
+      </c>
       <c r="M2" t="n">
-        <v>-0.08077595208253514</v>
+        <v>-0.03980950719195636</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>EsTauGo1</t>
+          <t>E3tkRPQj</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>-0.257225400694654</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.6339920439317994</v>
+        <v>0.4520530676282984</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.7018695640054968</v>
+        <v>1.013033509554143</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3513607214574137</v>
+        <v>1.060358754212869</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6671008707557337</v>
+        <v>-0.1710165240688941</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.3190521414703397</v>
+        <v>2.61367507024112</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3124293492667807</v>
+        <v>-2.0609241539353</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5098702963607098</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
+        <v>-0.05770755283280596</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-0.0109338651440155</v>
+      </c>
       <c r="K3" t="n">
-        <v>1.399912547000236</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
+        <v>0.1938408763014146</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.02698059614940806</v>
+      </c>
       <c r="M3" t="n">
-        <v>1.203990988281151</v>
+        <v>0.5213814306465047</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>nTCJapXF</t>
+          <t>fJaIWo3T</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>-0.257225400694654</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.6339920439317994</v>
+        <v>-2.685410587989762</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.3343903339570026</v>
+        <v>-1.681814177468148</v>
       </c>
       <c r="E4" t="n">
-        <v>1.533024109383172</v>
+        <v>-1.775633376808952</v>
       </c>
       <c r="F4" t="n">
         <v>1.505218265580361</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2896270911490199</v>
+        <v>-0.6510589956263541</v>
       </c>
       <c r="H4" t="n">
-        <v>2.29539156957873</v>
+        <v>-0.9531712717994073</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7377089654983506</v>
-      </c>
-      <c r="J4" t="inlineStr"/>
+        <v>-0.009255785218725512</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.05657158082305871</v>
+      </c>
       <c r="K4" t="n">
-        <v>-0.37338887801608</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
+        <v>0.4843240071655153</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.02698059614940806</v>
+      </c>
       <c r="M4" t="n">
-        <v>0.4658546228128857</v>
+        <v>0.2778038336163575</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6HPisxHl</t>
+          <t>M51AY7YG</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>-0.257225400694654</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.151305327682867</v>
+        <v>-1.478693797367431</v>
       </c>
       <c r="D5" t="n">
-        <v>1.380512739602637</v>
+        <v>-0.9468557173711597</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5876933990425653</v>
+        <v>1.060358754212869</v>
       </c>
       <c r="F5" t="n">
         <v>-0.1710165240688941</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8429718480757106</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.2955170915242485</v>
-      </c>
+        <v>0.1789581397636818</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>-0.967524078030543</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
+        <v>0.8974844372733546</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.0177167020396846</v>
+      </c>
       <c r="K5" t="n">
-        <v>-1.19425721688843</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="n">
-        <v>-1.217718190702497</v>
-      </c>
+        <v>0.4803130859736822</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.57567013906595</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>6V4QeyWs</t>
+          <t>hCffxjZi</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>-0.257225400694654</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.6339920439317994</v>
+        <v>3.348173365121892</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.559321100785317</v>
+        <v>-0.7018695640054968</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5939699888831931</v>
-      </c>
-      <c r="F6" t="n">
-        <v>-0.1710165240688941</v>
-      </c>
+        <v>2.005689464553476</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
         <v>1.838992410543753</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8502883705323349</v>
+        <v>-0.3866106374245671</v>
       </c>
       <c r="I6" t="n">
-        <v>1.175120756458801</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
+        <v>1.208824366984001</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-0.1569340157239667</v>
+      </c>
       <c r="K6" t="n">
-        <v>1.432884505822329</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
+        <v>0.537650462225398</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-0.5217089467671338</v>
+      </c>
       <c r="M6" t="n">
-        <v>1.044814139158103</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>v39B1623</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>-0.257225400694654</v>
-      </c>
-      <c r="C7" t="n">
-        <v>-1.961380513616363</v>
-      </c>
-      <c r="D7" t="n">
-        <v>3.095415813162277</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-2.484631409564407</v>
-      </c>
-      <c r="F7" t="n">
-        <v>-0.1710165240688941</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-3.030441450411124</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="n">
-        <v>-3.057294959766423</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="n">
-        <v>-2.182434848400367</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>noOg1c8K</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>-0.257225400694654</v>
-      </c>
-      <c r="C8" t="n">
-        <v>2.141456574499562</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2.237964276382457</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1.296691431798021</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1.505218265580361</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-0.2083831900850016</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-0.5021777319985441</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1.148681433158505</v>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="n">
-        <v>-0.1451779628984234</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="n">
-        <v>-0.1516034802969752</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>fiy8wfGD</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>-0.257225400694654</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-1.358022118305198</v>
-      </c>
-      <c r="D9" t="n">
-        <v>-0.8243626406883283</v>
-      </c>
-      <c r="E9" t="n">
-        <v>-0.8303026664683448</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-1.009133918893522</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-0.2637176657776706</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.762812045668051</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.02865492533715</v>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="n">
-        <v>1.459871707601368</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="n">
-        <v>1.309697578008861</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>0K4Ww3Ad</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>-0.257225400694654</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.3313813885660653</v>
-      </c>
-      <c r="D10" t="n">
-        <v>-0.08940418059133975</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.5876933990425653</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-1.84725131371815</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.8429718480757106</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-0.9006728050569671</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.3854404322435722</v>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="n">
-        <v>1.526610575655769</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="n">
-        <v>0.7934627890312492</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>Qw81zU34</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>-0.257225400694654</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.9347397838772308</v>
-      </c>
-      <c r="D11" t="n">
-        <v>-2.416772637565137</v>
-      </c>
-      <c r="E11" t="n">
-        <v>3.89635088523469</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="n">
-        <v>-0.3743866171630088</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.102435482297003</v>
-      </c>
-      <c r="I11" t="n">
-        <v>-1.049195051146014</v>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="n">
-        <v>-0.01160671425672479</v>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="n">
-        <v>-0.03980950719195636</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>fJaIWo3T</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>-0.257225400694654</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-2.685410587989762</v>
-      </c>
-      <c r="D12" t="n">
-        <v>-1.681814177468148</v>
-      </c>
-      <c r="E12" t="n">
-        <v>-1.775633376808952</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1.505218265580361</v>
-      </c>
-      <c r="G12" t="n">
-        <v>-0.6510589956263541</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-0.9531712717994073</v>
-      </c>
-      <c r="I12" t="n">
-        <v>-0.009255785218725512</v>
-      </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="n">
-        <v>0.4843240071655153</v>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="n">
-        <v>0.2778038336163575</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>E3tkRPQj</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>-0.257225400694654</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.4520530676282984</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1.013033509554143</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1.060358754212869</v>
-      </c>
-      <c r="F13" t="n">
-        <v>-0.1710165240688941</v>
-      </c>
-      <c r="G13" t="n">
-        <v>2.61367507024112</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-2.0609241539353</v>
-      </c>
-      <c r="I13" t="n">
-        <v>-0.05770755283280596</v>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="n">
-        <v>0.1938408763014146</v>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="n">
-        <v>0.5213814306465047</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>M51AY7YG</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>-0.257225400694654</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-1.478693797367431</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.9468557173711597</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1.060358754212869</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-0.1710165240688941</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.1789581397636818</v>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="n">
-        <v>0.8974844372733546</v>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="n">
-        <v>0.4803130859736822</v>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>hCffxjZi</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>-0.257225400694654</v>
-      </c>
-      <c r="C15" t="n">
-        <v>3.348173365121892</v>
-      </c>
-      <c r="D15" t="n">
-        <v>-0.7018695640054968</v>
-      </c>
-      <c r="E15" t="n">
-        <v>2.005689464553476</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="n">
-        <v>1.838992410543753</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-0.3866106374245671</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1.208824366984001</v>
-      </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="n">
-        <v>0.537650462225398</v>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="n">
         <v>0.3799731600302206</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>8MPiooIM</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>-0.257225400694654</v>
-      </c>
-      <c r="C16" t="n">
-        <v>2.141456574499562</v>
-      </c>
-      <c r="D16" t="n">
-        <v>-3.396717251027788</v>
-      </c>
-      <c r="E16" t="n">
-        <v>3.423685530064386</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-0.1710165240688941</v>
-      </c>
-      <c r="G16" t="n">
-        <v>2.170999264699768</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-2.194343076126391</v>
-      </c>
-      <c r="I16" t="n">
-        <v>2.391798476545713</v>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="n">
-        <v>2.434757208472348</v>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="n">
-        <v>1.881047865132432</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>CGH7Enso</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>-0.257225400694654</v>
-      </c>
-      <c r="C17" t="n">
-        <v>-0.2719770067451001</v>
-      </c>
-      <c r="D17" t="n">
-        <v>2.237964276382457</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1.060358754212869</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="n">
-        <v>-2.69843459625511</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1.017106755205637</v>
-      </c>
-      <c r="I17" t="n">
-        <v>-1.193632326896252</v>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="n">
-        <v>-2.256809245307932</v>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="n">
-        <v>-1.638981572800233</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>0dMqm7mA</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>-0.257225400694654</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.5727247466905315</v>
-      </c>
-      <c r="D18" t="n">
-        <v>-0.2118972572741712</v>
-      </c>
-      <c r="E18" t="n">
-        <v>1.769356786968324</v>
-      </c>
-      <c r="F18" t="n">
-        <v>-1.84725131371815</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1.506985556387739</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.1491007860680623</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.8521233668294613</v>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="n">
-        <v>0.03626183386615837</v>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="n">
-        <v>0.6778436358310174</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>vsYzkTIc</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>-0.257225400694654</v>
-      </c>
-      <c r="C19" t="n">
-        <v>-1.237350439242965</v>
-      </c>
-      <c r="D19" t="n">
-        <v>3.462895043210771</v>
-      </c>
-      <c r="E19" t="n">
-        <v>-0.8303026664683448</v>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="n">
-        <v>-1.702414033787066</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.3302420281391246</v>
-      </c>
-      <c r="I19" t="n">
-        <v>-2.047166495774601</v>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="n">
-        <v>-1.757182739750638</v>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="n">
-        <v>-1.287517444697798</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_selected.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,208 +493,695 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Qw81zU34</t>
+          <t>Ee8YgF0f</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>-0.257225400694654</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9347397838772308</v>
+        <v>-0.5133203648695663</v>
       </c>
       <c r="D2" t="n">
-        <v>-2.416772637565137</v>
+        <v>2.360457353065288</v>
       </c>
       <c r="E2" t="n">
-        <v>3.89635088523469</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+        <v>-0.1213046337128897</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-1.009133918893522</v>
+      </c>
       <c r="G2" t="n">
-        <v>-0.3743866171630088</v>
+        <v>-1.093734801167706</v>
       </c>
       <c r="H2" t="n">
-        <v>0.102435482297003</v>
+        <v>-1.790093137586132</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.049195051146014</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-0.1443748629859064</v>
-      </c>
+        <v>-1.12231855098952</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>-0.01160671425672479</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-1.344743261141947</v>
-      </c>
+        <v>-1.299994787942761</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>-0.03980950719195636</v>
+        <v>-1.619670582964764</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>E3tkRPQj</t>
+          <t>zZA5hNtm</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>-0.257225400694654</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4520530676282984</v>
+        <v>1.055411462939464</v>
       </c>
       <c r="D3" t="n">
-        <v>1.013033509554143</v>
+        <v>-1.191841870736823</v>
       </c>
       <c r="E3" t="n">
-        <v>1.060358754212869</v>
+        <v>1.533024109383172</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1710165240688941</v>
+        <v>-1.009133918893522</v>
       </c>
       <c r="G3" t="n">
-        <v>2.61367507024112</v>
+        <v>-0.7617279470116921</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.0609241539353</v>
+        <v>-0.4946024498846983</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.05770755283280596</v>
-      </c>
-      <c r="J3" t="n">
-        <v>-0.0109338651440155</v>
-      </c>
+        <v>0.745784260100698</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>0.1938408763014146</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.02698059614940806</v>
-      </c>
+        <v>1.112241962217474</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>0.5213814306465047</v>
+        <v>0.498245260715833</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>fJaIWo3T</t>
+          <t>p4Um50Qh</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>-0.257225400694654</v>
       </c>
       <c r="C4" t="n">
-        <v>-2.685410587989762</v>
+        <v>-1.116678760180732</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.681814177468148</v>
+        <v>-0.7018695640054968</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.775633376808952</v>
+        <v>0.3513607214574137</v>
       </c>
       <c r="F4" t="n">
-        <v>1.505218265580361</v>
+        <v>0.6671008707557337</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.6510589956263541</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-0.9531712717994073</v>
-      </c>
+        <v>0.2342926154563509</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>-0.009255785218725512</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.05657158082305871</v>
-      </c>
+        <v>-0.005150278299046318</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>0.4843240071655153</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.02698059614940806</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.2778038336163575</v>
-      </c>
+        <v>-0.863133109136752</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>M51AY7YG</t>
+          <t>bDeVnJAO</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>-0.257225400694654</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.478693797367431</v>
+        <v>-1.398246011325942</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.9468557173711597</v>
+        <v>-1.763476228590036</v>
       </c>
       <c r="E5" t="n">
-        <v>1.060358754212869</v>
+        <v>0.1938056030673125</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1710165240688941</v>
+        <v>-1.009133918893522</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1789581397636818</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
+        <v>-0.8539520731661409</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-1.619326312880281</v>
+      </c>
       <c r="I5" t="n">
-        <v>0.8974844372733546</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.0177167020396846</v>
-      </c>
+        <v>-1.606175951065896</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>0.4803130859736822</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.57567013906595</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
+        <v>-0.8381676772391242</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>-0.976700996478008</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hCffxjZi</t>
+          <t>lxyu7Met</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>-0.257225400694654</v>
       </c>
       <c r="C6" t="n">
-        <v>3.348173365121892</v>
+        <v>0.5727247466905315</v>
       </c>
       <c r="D6" t="n">
+        <v>-1.069348794053991</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.115028043872262</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.6671008707557337</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.170999264699768</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-1.154474117429278</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.2716491055914796</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>0.8082981698934543</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>0.4941732948080309</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>xb7MlutC</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>-0.257225400694654</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-1.84070883455413</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.747991969651131</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.3576373112980414</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-1.84725131371815</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-3.971127537186497</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.002606183122328376</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-1.901077075241237</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="n">
+        <v>-1.418403662073745</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>-1.072484739991007</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>v3PZcqJP</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>-0.257225400694654</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.8542919978357418</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.5385454617617218</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.060358754212869</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-1.009133918893522</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.2342926154563509</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.223577235145729</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-0.025570468495716</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="n">
+        <v>0.09877294081349124</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>0.5160138392225894</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>zBdshgV6</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>-0.257225400694654</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.538098179188396</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.5793764873226654</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.769356786968324</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.6671008707557337</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.503006118855782</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.8208485144620038</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.326176416070593</v>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="n">
+        <v>1.3688863792729</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>1.546653089067743</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>MRfkjXaJ</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-0.257225400694654</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.8140681048149977</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-2.049293407516643</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.5876933990425653</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.505218265580361</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0.04237976300699443</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-1.261467636897662</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-0.7346558287590801</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="n">
+        <v>-1.074872954879243</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>-1.368010750572166</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>S66OuPup</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>-0.257225400694654</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.151305327682867</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.972922736479445</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.5876933990425653</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-1.009133918893522</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-2.753769071947779</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.02227438951586</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.4746016148576501</v>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="n">
+        <v>0.1049297301005506</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="n">
+        <v>-0.08077595208253861</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>6HPisxHl</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>-0.257225400694654</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.151305327682867</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.380512739602637</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.5876933990425653</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.1710165240688941</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.8429718480757106</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.2091941092967357</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-0.6852054451681059</v>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="n">
+        <v>-1.245158764853928</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="n">
+        <v>-1.166078259417232</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>EsTauGo1</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>-0.257225400694654</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.6339920439317994</v>
+      </c>
+      <c r="D13" t="n">
         <v>-0.7018695640054968</v>
       </c>
-      <c r="E6" t="n">
-        <v>2.005689464553476</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="n">
-        <v>1.838992410543753</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-0.3866106374245671</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1.208824366984001</v>
-      </c>
-      <c r="J6" t="n">
-        <v>-0.1569340157239667</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.537650462225398</v>
-      </c>
-      <c r="L6" t="n">
-        <v>-0.5217089467671338</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.3799731600302206</v>
+      <c r="E13" t="n">
+        <v>0.3513607214574137</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.6671008707557337</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.3190521414703397</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.2371463130656443</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.7434770330714561</v>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="n">
+        <v>1.396582461383537</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="n">
+        <v>1.098119874678379</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>nTCJapXF</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>-0.257225400694654</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.6339920439317994</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.3343903339570026</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.533024109383172</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.505218265580361</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.2896270911490199</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.2277425386086</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.7161442583216291</v>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="n">
+        <v>-0.2223710370052542</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="n">
+        <v>0.4740910993082091</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>6V4QeyWs</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>-0.257225400694654</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.4520530676282984</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-1.191841870736823</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0.1213046337128897</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.1710165240688941</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.617654507773077</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.7382446629880589</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.024381923881661</v>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="n">
+        <v>1.400960907286967</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="n">
+        <v>1.090716300300563</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>v39B1623</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>-0.257225400694654</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-1.961380513616363</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3.095415813162277</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-2.484631409564407</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-0.1710165240688941</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-3.030441450411124</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="n">
+        <v>-2.840367551787905</v>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="n">
+        <v>-1.960727825039801</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>noOg1c8K</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>-0.257225400694654</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.8140681048149977</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.747991969651131</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.8240260766277171</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.505218265580361</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.04237976300699443</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.4940739418302463</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.0504541059882</v>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="n">
+        <v>-0.2183013570485611</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="n">
+        <v>-0.1486420505458514</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>fiy8wfGD</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>-0.257225400694654</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-1.358022118305198</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.8243626406883283</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.8303026664683448</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-1.009133918893522</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.2637176657776706</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.020802273731223</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.882565504803785</v>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="n">
+        <v>1.518883820044313</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="n">
+        <v>1.295301738940885</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>0K4Ww3Ad</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>-0.257225400694654</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.3313813885660653</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.08940418059133975</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.5876933990425653</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-1.84725131371815</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.8429718480757106</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-1.020996472121029</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.5180134505815642</v>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="n">
+        <v>1.387490998380562</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="n">
+        <v>0.8053085080357546</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_selected.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,695 +493,337 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Ee8YgF0f</t>
+          <t>S66OuPup</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>-0.257225400694654</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.5133203648695663</v>
+        <v>-0.151305327682867</v>
       </c>
       <c r="D2" t="n">
-        <v>2.360457353065288</v>
+        <v>2.972922736479445</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1213046337128897</v>
+        <v>0.5876933990425653</v>
       </c>
       <c r="F2" t="n">
         <v>-1.009133918893522</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.093734801167706</v>
+        <v>-2.753769071947779</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.790093137586132</v>
+        <v>1.02227438951586</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.12231855098952</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
+        <v>0.4746016148576501</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-0.1380952866168762</v>
+      </c>
       <c r="K2" t="n">
-        <v>-1.299994787942761</v>
+        <v>0.1049297301005506</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>-1.619670582964764</v>
+        <v>-0.08077595208253861</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>zZA5hNtm</t>
+          <t>EsTauGo1</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>-0.257225400694654</v>
       </c>
       <c r="C3" t="n">
-        <v>1.055411462939464</v>
+        <v>-0.6339920439317994</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.191841870736823</v>
+        <v>-0.7018695640054968</v>
       </c>
       <c r="E3" t="n">
-        <v>1.533024109383172</v>
+        <v>0.3513607214574137</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.009133918893522</v>
+        <v>0.6671008707557337</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.7617279470116921</v>
+        <v>-0.3190521414703397</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4946024498846983</v>
+        <v>0.2371463130656443</v>
       </c>
       <c r="I3" t="n">
-        <v>0.745784260100698</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
+        <v>0.7434770330714561</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.256733077585895</v>
+      </c>
       <c r="K3" t="n">
-        <v>1.112241962217474</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
+        <v>1.396582461383537</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.57567013906595</v>
+      </c>
       <c r="M3" t="n">
-        <v>0.498245260715833</v>
+        <v>1.098119874678379</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>p4Um50Qh</t>
+          <t>6HPisxHl</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>-0.257225400694654</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.116678760180732</v>
+        <v>-0.151305327682867</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.7018695640054968</v>
+        <v>1.380512739602637</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3513607214574137</v>
+        <v>0.5876933990425653</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6671008707557337</v>
+        <v>-0.1710165240688941</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2342926154563509</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
+        <v>0.8429718480757106</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.2091941092967374</v>
+      </c>
       <c r="I4" t="n">
-        <v>-0.005150278299046318</v>
-      </c>
-      <c r="J4" t="inlineStr"/>
+        <v>-0.6852054451681052</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-0.1616436980007393</v>
+      </c>
       <c r="K4" t="n">
-        <v>-0.863133109136752</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+        <v>-1.245158764853928</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-0.8875019753781621</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-1.166078259417232</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bDeVnJAO</t>
+          <t>nTCJapXF</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>-0.257225400694654</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.398246011325942</v>
+        <v>-0.6339920439317994</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.763476228590036</v>
+        <v>-0.3343903339570026</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1938056030673125</v>
+        <v>1.533024109383172</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.009133918893522</v>
+        <v>1.505218265580361</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.8539520731661409</v>
+        <v>0.2896270911490199</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.619326312880281</v>
+        <v>2.2277425386086</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.606175951065896</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
+        <v>0.7161442583216291</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.3878192342893996</v>
+      </c>
       <c r="K5" t="n">
-        <v>-0.8381676772391242</v>
+        <v>-0.2223710370052542</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>-0.976700996478008</v>
+        <v>0.4740910993082091</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>lxyu7Met</t>
+          <t>6V4QeyWs</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>-0.257225400694654</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5727247466905315</v>
+        <v>0.4520530676282984</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.069348794053991</v>
+        <v>-1.191841870736823</v>
       </c>
       <c r="E6" t="n">
-        <v>0.115028043872262</v>
+        <v>-0.1213046337128897</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6671008707557337</v>
+        <v>-0.1710165240688941</v>
       </c>
       <c r="G6" t="n">
-        <v>2.170999264699768</v>
+        <v>1.617654507773077</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.154474117429278</v>
+        <v>-0.7382446629880589</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2716491055914796</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
+        <v>1.024381923881661</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.1586146968197988</v>
+      </c>
       <c r="K6" t="n">
-        <v>0.8082981698934543</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
+        <v>1.400960907286967</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.02698059614940806</v>
+      </c>
       <c r="M6" t="n">
-        <v>0.4941732948080309</v>
+        <v>1.090716300300563</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>xb7MlutC</t>
+          <t>v39B1623</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>-0.257225400694654</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.84070883455413</v>
+        <v>-1.961380513616363</v>
       </c>
       <c r="D7" t="n">
-        <v>1.747991969651131</v>
+        <v>3.095415813162277</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3576373112980414</v>
+        <v>-2.484631409564407</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.84725131371815</v>
+        <v>-0.1710165240688941</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.971127537186497</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.002606183122328376</v>
-      </c>
+        <v>-3.030441450411124</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>-1.901077075241237</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
+        <v>-2.840367551787905</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-3.529066525893162</v>
+      </c>
       <c r="K7" t="n">
-        <v>-1.418403662073745</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="n">
-        <v>-1.072484739991007</v>
-      </c>
+        <v>-1.960727825039801</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-2.716467118433302</v>
+      </c>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>v3PZcqJP</t>
+          <t>noOg1c8K</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>-0.257225400694654</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8542919978357418</v>
+        <v>0.8140681048149977</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5385454617617218</v>
+        <v>1.747991969651131</v>
       </c>
       <c r="E8" t="n">
-        <v>1.060358754212869</v>
+        <v>0.8240260766277171</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.009133918893522</v>
+        <v>1.505218265580361</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2342926154563509</v>
+        <v>-0.04237976300699443</v>
       </c>
       <c r="H8" t="n">
-        <v>1.223577235145729</v>
+        <v>-0.4940739418302463</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.025570468495716</v>
-      </c>
-      <c r="J8" t="inlineStr"/>
+        <v>1.0504541059882</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.03145327534693807</v>
+      </c>
       <c r="K8" t="n">
-        <v>0.09877294081349124</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
+        <v>-0.2183013570485611</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.02698059614940806</v>
+      </c>
       <c r="M8" t="n">
-        <v>0.5160138392225894</v>
+        <v>-0.1486420505458514</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>zBdshgV6</t>
+          <t>fiy8wfGD</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>-0.257225400694654</v>
       </c>
       <c r="C9" t="n">
-        <v>1.538098179188396</v>
+        <v>-1.358022118305198</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5793764873226654</v>
+        <v>-0.8243626406883283</v>
       </c>
       <c r="E9" t="n">
-        <v>1.769356786968324</v>
+        <v>-0.8303026664683448</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6671008707557337</v>
+        <v>-1.009133918893522</v>
       </c>
       <c r="G9" t="n">
-        <v>2.503006118855782</v>
+        <v>-0.2637176657776706</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8208485144620038</v>
+        <v>2.020802273731223</v>
       </c>
       <c r="I9" t="n">
-        <v>1.326176416070593</v>
-      </c>
-      <c r="J9" t="inlineStr"/>
+        <v>1.882565504803785</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.3265933646913556</v>
+      </c>
       <c r="K9" t="n">
-        <v>1.3688863792729</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
+        <v>1.518883820044313</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.055773489117924</v>
+      </c>
       <c r="M9" t="n">
-        <v>1.546653089067743</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>MRfkjXaJ</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>-0.257225400694654</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.8140681048149977</v>
-      </c>
-      <c r="D10" t="n">
-        <v>-2.049293407516643</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.5876933990425653</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1.505218265580361</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-0.04237976300699443</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-1.261467636897662</v>
-      </c>
-      <c r="I10" t="n">
-        <v>-0.7346558287590801</v>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="n">
-        <v>-1.074872954879243</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="n">
-        <v>-1.368010750572166</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>S66OuPup</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>-0.257225400694654</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-0.151305327682867</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2.972922736479445</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.5876933990425653</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-1.009133918893522</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-2.753769071947779</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1.02227438951586</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.4746016148576501</v>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="n">
-        <v>0.1049297301005506</v>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="n">
-        <v>-0.08077595208253861</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>6HPisxHl</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>-0.257225400694654</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-0.151305327682867</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1.380512739602637</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.5876933990425653</v>
-      </c>
-      <c r="F12" t="n">
-        <v>-0.1710165240688941</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.8429718480757106</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.2091941092967357</v>
-      </c>
-      <c r="I12" t="n">
-        <v>-0.6852054451681059</v>
-      </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="n">
-        <v>-1.245158764853928</v>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="n">
-        <v>-1.166078259417232</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>EsTauGo1</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>-0.257225400694654</v>
-      </c>
-      <c r="C13" t="n">
-        <v>-0.6339920439317994</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.7018695640054968</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.3513607214574137</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.6671008707557337</v>
-      </c>
-      <c r="G13" t="n">
-        <v>-0.3190521414703397</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.2371463130656443</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.7434770330714561</v>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="n">
-        <v>1.396582461383537</v>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="n">
-        <v>1.098119874678379</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>nTCJapXF</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>-0.257225400694654</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-0.6339920439317994</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.3343903339570026</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1.533024109383172</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1.505218265580361</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.2896270911490199</v>
-      </c>
-      <c r="H14" t="n">
-        <v>2.2277425386086</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.7161442583216291</v>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="n">
-        <v>-0.2223710370052542</v>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="n">
-        <v>0.4740910993082091</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>6V4QeyWs</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>-0.257225400694654</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.4520530676282984</v>
-      </c>
-      <c r="D15" t="n">
-        <v>-1.191841870736823</v>
-      </c>
-      <c r="E15" t="n">
-        <v>-0.1213046337128897</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-0.1710165240688941</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1.617654507773077</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-0.7382446629880589</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1.024381923881661</v>
-      </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="n">
-        <v>1.400960907286967</v>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="n">
-        <v>1.090716300300563</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>v39B1623</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>-0.257225400694654</v>
-      </c>
-      <c r="C16" t="n">
-        <v>-1.961380513616363</v>
-      </c>
-      <c r="D16" t="n">
-        <v>3.095415813162277</v>
-      </c>
-      <c r="E16" t="n">
-        <v>-2.484631409564407</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-0.1710165240688941</v>
-      </c>
-      <c r="G16" t="n">
-        <v>-3.030441450411124</v>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="n">
-        <v>-2.840367551787905</v>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="n">
-        <v>-1.960727825039801</v>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>noOg1c8K</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>-0.257225400694654</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.8140681048149977</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1.747991969651131</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.8240260766277171</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1.505218265580361</v>
-      </c>
-      <c r="G17" t="n">
-        <v>-0.04237976300699443</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-0.4940739418302463</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1.0504541059882</v>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="n">
-        <v>-0.2183013570485611</v>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="n">
-        <v>-0.1486420505458514</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>fiy8wfGD</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>-0.257225400694654</v>
-      </c>
-      <c r="C18" t="n">
-        <v>-1.358022118305198</v>
-      </c>
-      <c r="D18" t="n">
-        <v>-0.8243626406883283</v>
-      </c>
-      <c r="E18" t="n">
-        <v>-0.8303026664683448</v>
-      </c>
-      <c r="F18" t="n">
-        <v>-1.009133918893522</v>
-      </c>
-      <c r="G18" t="n">
-        <v>-0.2637176657776706</v>
-      </c>
-      <c r="H18" t="n">
-        <v>2.020802273731223</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1.882565504803785</v>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="n">
-        <v>1.518883820044313</v>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="n">
         <v>1.295301738940885</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>0K4Ww3Ad</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>-0.257225400694654</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.3313813885660653</v>
-      </c>
-      <c r="D19" t="n">
-        <v>-0.08940418059133975</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.5876933990425653</v>
-      </c>
-      <c r="F19" t="n">
-        <v>-1.84725131371815</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.8429718480757106</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-1.020996472121029</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.5180134505815642</v>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="n">
-        <v>1.387490998380562</v>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="n">
-        <v>0.8053085080357546</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_selected.xlsx
@@ -425,66 +425,176 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:AI19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>id_team_away</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>id_competition</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>is_cup</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
+          <t>dif_mean_last_60_matches_expected_points_against</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
+          <t>dif_mean_last_60_matches_shots_on_goal</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_ball_possession</t>
+          <t>dif_mean_last_360_matches_shots_on_goal</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_60_matches_goal_attempts</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_goals</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_goals_against</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_points</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_points</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_goal_ratio</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_PPS</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_PPS_against</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_attacks</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_dangerous_attacks</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_dangerous_attacks_against</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_dangerous_attacks_against</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_dead_balls</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_ball_possession</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_ball_possession</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_yellow_cards</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_yellow_cards_against</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_defensive_actions_against</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_defensive_actions</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_defensive_actions_against</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_PPDA_against</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_PPDA</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_clean_sheet_against</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_clean_sheet</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_clean_sheet_against</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_age_player_start</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_start</t>
         </is>
@@ -493,208 +603,1949 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Qw81zU34</t>
+          <t>OUcd1IPH</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.257225400694654</v>
+        <v>-0.8518674200847456</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9347397838772308</v>
+        <v>-1.001692214537703</v>
       </c>
       <c r="D2" t="n">
-        <v>-2.416772637565137</v>
+        <v>-0.2402860741301242</v>
       </c>
       <c r="E2" t="n">
-        <v>3.89635088523469</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+        <v>0.6762457101420526</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.356693817118157</v>
+      </c>
       <c r="G2" t="n">
-        <v>-0.3743866171630088</v>
+        <v>-1.972162992361301</v>
       </c>
       <c r="H2" t="n">
-        <v>0.102435482297003</v>
+        <v>0.01191544005936178</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.049195051146014</v>
+        <v>-0.5621705644581586</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.1443748629859064</v>
+        <v>1.56071207237734</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.01160671425672479</v>
+        <v>-0.2872971140384382</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.344743261141947</v>
+        <v>-0.5392951265128135</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.03980950719195636</v>
+        <v>-1.592228169756162</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.433099419739398</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3.831656834422551</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-0.691024329349012</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-1.284769886701745</v>
+      </c>
+      <c r="R2" t="n">
+        <v>-0.2580591418560369</v>
+      </c>
+      <c r="S2" t="n">
+        <v>-0.4885395400158573</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.09305464052029536</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.6631720563583019</v>
+      </c>
+      <c r="V2" t="n">
+        <v>-1.403907677987274</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-1.996549091297335</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.143277705319474</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>-1.295511775404403</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.1859203427764414</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.2994257144874211</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-0.4703257818768421</v>
+      </c>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="n">
+        <v>1.028441902399717</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.1311478087006882</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.815980463026227</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.3711243380653336</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.2448153585984961</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-1.971958419153034</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>E3tkRPQj</t>
+          <t>rZUMHwAb</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.257225400694654</v>
+        <v>-0.8908562920247587</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4520530676282984</v>
+        <v>-1.001692214537703</v>
       </c>
       <c r="D3" t="n">
-        <v>1.013033509554143</v>
+        <v>-0.2402860741301242</v>
       </c>
       <c r="E3" t="n">
-        <v>1.060358754212869</v>
+        <v>-0.8705842260736799</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1710165240688941</v>
+        <v>1.152899534692019</v>
       </c>
       <c r="G3" t="n">
-        <v>2.61367507024112</v>
+        <v>1.617432285649069</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.0609241539353</v>
+        <v>0.3166632873596557</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.05770755283280596</v>
+        <v>-1.321376443564397</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.0109338651440155</v>
+        <v>1.087574072389573</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1938408763014146</v>
+        <v>0.2149145044820129</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02698059614940806</v>
+        <v>0.646014063229936</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5213814306465047</v>
+        <v>1.288590201312166</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-0.3845979233312813</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-0.2540905829327433</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.6232460630505057</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.697870904707625</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-0.07980312381646659</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-0.6100163814141872</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-1.30076297653173</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.8113675586359415</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.2842740016697285</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.138049282814796</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-0.4223094128834158</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.4031974785743386</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.446443355279844</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-0.2227370452659255</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-0.5450518595105116</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-3.270993666513398</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>-1.540836175459835</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>-0.7593240244164153</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.694201561436236</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-0.9317791141614961</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.086142135171787</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.6651590972344187</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>fJaIWo3T</t>
+          <t>4nvCemgd</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.257225400694654</v>
+        <v>-0.590084994201801</v>
       </c>
       <c r="C4" t="n">
-        <v>-2.685410587989762</v>
+        <v>-1.001692214537703</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.681814177468148</v>
+        <v>-0.2402860741301242</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.775633376808952</v>
+        <v>1.19185568888063</v>
       </c>
       <c r="F4" t="n">
-        <v>1.505218265580361</v>
+        <v>0.3566938171181572</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.6510589956263541</v>
+        <v>-0.5312359301198052</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.9531712717994073</v>
+        <v>-0.7118606972788367</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.009255785218725512</v>
+        <v>0.5713815506114733</v>
       </c>
       <c r="J4" t="n">
-        <v>0.05657158082305871</v>
+        <v>0.7721487390643957</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4843240071655153</v>
+        <v>0.5497222501623138</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02698059614940806</v>
+        <v>-0.2429678290771261</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2778038336163575</v>
+        <v>-0.1433497727262255</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.298189553417581</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.146527147642252</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-1.188683260156787</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-1.123807349839949</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-1.357304586433387</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.2099522980245397</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.8120722802133403</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-1.475077333647645</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.1187659938602187</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-1.396405102518758</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.5170428580383184</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.866481820568541</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-1.326707272227642</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-0.1195510831433454</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-0.4337180732018334</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.627674619468722</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.092964157663152</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.1311478087006882</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>-2.321289069739059</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>-0.0530533406459063</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-2.755935611599157</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-1.534277215152686</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>M51AY7YG</t>
+          <t>WhWcJjo3</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.257225400694654</v>
+        <v>-0.6959119323246935</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.478693797367431</v>
+        <v>-1.001692214537703</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.9468557173711597</v>
+        <v>-0.2402860741301242</v>
       </c>
       <c r="E5" t="n">
-        <v>1.060358754212869</v>
+        <v>-1.901804183550834</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1710165240688941</v>
+        <v>-0.6783736157278639</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1789581397636818</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
+        <v>-0.9430640048088399</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.9023281018415207</v>
+      </c>
       <c r="I5" t="n">
-        <v>0.8974844372733546</v>
+        <v>-1.4114298083392</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0177167020396846</v>
+        <v>0.7721487390643957</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4803130859736822</v>
+        <v>-2.965759079480844</v>
       </c>
       <c r="L5" t="n">
-        <v>0.57567013906595</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
+        <v>0.646014063229936</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-0.07409520783674416</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-0.07329787502410794</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-0.7821962203709022</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0.3314577274455188</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.5450141096370621</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-0.347187150875822</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.7262288739674418</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-1.11538523346381</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.192441707349873</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-0.6425708420635278</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.5021267392733906</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-1.205102971984861</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.09434125057820358</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.362408487779617</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.1692337120727199</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.3648723123381568</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-6.605218288253476</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-0.9112325911467608</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-0.7593240244164153</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.5010651500781964</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.1911701713393531</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-0.5091014671758978</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.230609459064999</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hCffxjZi</t>
+          <t>IHSe3ve5</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.257225400694654</v>
+        <v>1.7659568387447</v>
       </c>
       <c r="C6" t="n">
-        <v>3.348173365121892</v>
+        <v>-1.001692214537703</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7018695640054968</v>
+        <v>-0.2402860741301242</v>
       </c>
       <c r="E6" t="n">
-        <v>2.005689464553476</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
+        <v>1.19185568888063</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.789864108751109</v>
+      </c>
       <c r="G6" t="n">
-        <v>1.838992410543753</v>
+        <v>1.313037621748478</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3866106374245671</v>
+        <v>0.7737850583100973</v>
       </c>
       <c r="I6" t="n">
-        <v>1.208824366984001</v>
+        <v>2.130123428168072</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1569340157239667</v>
+        <v>0.4567234057392182</v>
       </c>
       <c r="K6" t="n">
-        <v>0.537650462225398</v>
+        <v>2.223760978563817</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5217089467671338</v>
+        <v>-0.8356224239485008</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3799731600302206</v>
+        <v>0.2049599506885182</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.4987041275402215</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-0.2059229713391029</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-0.4489505106640896</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.364449590706604</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-0.3768964872157504</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-0.8833392745604295</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-0.07930317645875429</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-0.9246368966164119</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.3504772047935329</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.7168588296189904</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.2039254343977402</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.020909934566608</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-1.158637537227188</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-0.5170548600878112</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.050513971754993</v>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="n">
+        <v>-0.4025191769831039</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.1311478087006882</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-0.2573180308703462</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-1.221016371493058</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.9274505935237081</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.9573853847098939</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>8Kp3c9Oq</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>-1.386571949547781</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-1.001692214537703</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.2402860741301242</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2.223075646357785</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.277073245360771</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.5789841126924474</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.4071128499785428</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-0.06608711640046895</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-0.331839927573726</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.5497222501623137</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-0.8356224239485006</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-1.159083391105284</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.7442528852080399</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.9195007891130955</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-0.4975356148496412</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-1.723604592461801</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.06874355788317532</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.05810624627662733</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.2150697551348729</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-1.009320040775063</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-1.966634904539607</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-1.118946613022023</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.3604841462180293</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>-0.06008686341986395</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.278373620279391</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-1.428158755179571</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-0.003358169039865349</v>
+      </c>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="n">
+        <v>1.742740989685028</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.1311478087006882</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-0.7407707066413958</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.0283544966825135</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.8530729335770342</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-0.09407607339262139</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Wf14adfU</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>-0.3115930517731366</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-1.001692214537703</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.2402860741301242</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3.769905582573517</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.471381821721564</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.205604210960035</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.7118606972788367</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-1.620912234419625</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.245286739052162</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.7171261230024641</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.4978504145120923</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.5118527284340628</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.9799719566625945</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-0.02780231112073705</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.08902051670454053</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.4770286170941191</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.970141083638592</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-1.095923747007507</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-0.6365848506682146</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-0.5647335339421433</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.4994344118220913</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.681409698954727</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.6736015698586073</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-0.6777993194121337</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-0.2762714284748063</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-2.082608196976785</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-0.4509217727675463</v>
+      </c>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="n">
+        <v>0.1100510852306646</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>-1.204559940974967</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.463986001545259</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>-1.755434880072567</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.9946520933141818</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.8255005867857137</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>z9REJaun</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>-0.30045337407599</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-1.001692214537703</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.2402860741301242</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-1.901804183550834</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1974526736033846</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.2983887420798428</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.5452241728348766</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.6161353440147097</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-0.6472652608989038</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-1.459124223919491</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.090505009383467</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.446043024254254</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.416224330486097</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.303069178769795</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.4926074071435345</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-2.43298592751681</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-1.030501886694175</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.546197553406169</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-0.005185470143647227</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-0.2260009573075373</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-1.155645666273009</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-0.8033904945930056</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-1.048544260164572</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-0.2145149774179313</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-0.4233324466002034</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.642496486295597</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>-0.2768073846458196</v>
+      </c>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="n">
+        <v>-0.1336230117781942</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.5763837252592399</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.6377265123009265</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.09733692726080598</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.4528880023247537</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.4978497074903121</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>xYNVFHvB</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.05601631223270043</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-1.001692214537703</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.2402860741301242</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-1.386194204812257</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.347208111052812</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.069521890628006</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.5833176537474132</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.2160800932272492</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.245286739052162</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-0.2872971140384382</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.090505009383467</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.8571964410718059</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0.0472360572020273</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.6515010410148571</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.04855662064008903</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-0.1148263950904748</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-0.4066058235556788</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-0.09373980547128506</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.02646380229872424</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-1.030490826814725</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.773846071955319</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.06631295376014246</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.612953840780341</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-1.141083661406336</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-0.2552627115997496</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.971841431696896</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8806661544797951</v>
+      </c>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="n">
+        <v>-0.747602641507959</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>-1.204559940974967</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.6614937057309666</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>-1.68163854951603</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>-0.5733509010827195</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>2.155013176627965</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Ee8YgF0f</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.1172845395670066</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-1.001692214537703</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.2402860741301242</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-0.8705842260736792</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-0.1210296134261604</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0712337852820555</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.1785519645033222</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.9102133551866168</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-1.751253927537026</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-0.1198932411982877</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-1.131949721384188</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-0.177977055170966</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.9449502464854882</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.332362533017534</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-1.214487054256616</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-1.504399032393433</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-1.060211223034103</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.029920977463267</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.055557799109394</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.9807338469532445</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-0.04674201394929177</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-1.602410730622293</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.143277705319474</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-1.604368003400539</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-0.02416682597412594</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.7616550919731053</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.1360541942802097</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.195223077171645</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.23517990884066</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.1311478087006882</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.08711986450499899</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>-0.5415003646164247</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>-1.874635942918353</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-1.696347382232734</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>zZA5hNtm</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.4459050316328306</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-1.001692214537703</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.2402860741301242</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-5.511074034720877</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.630622965236337</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0.4954247931903245</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.9261589819602442</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.5533708776565129</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.245286739052162</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-3.133162952320995</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.090505009383467</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-1.603163101054501</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.601803537893939</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.7096539059968232</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-1.55292969019902</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-0.5446038435518831</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.524501038539666</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.5136444015203645</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-0.4180438608497472</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-0.3530256735455143</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-0.4605120334730666</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-1.058336748811571</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.3604841462180291</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.4031974785743386</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-1.389733422852812</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-1.181844866688515</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-2.088242945670333</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>10.91267204907505</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.604152667793382</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-2.540267690650622</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-1.501320896402677</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.7760212131987899</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>-0.4829888844001676</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.5433272240158951</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>p4Um50Qh</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.654560061773234</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-1.001692214537703</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.2402860741301242</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-3.964244098505143</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0.2006501851835466</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.6586814468394298</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-1.397543353704499</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-0.189208205138926</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-1.435828594211848</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.7171261230024641</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-1.724604316255563</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.8160296408898232</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.262616376044065</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.2697298640305479</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0.3989584275876021</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.7067179213396702</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.4252555939623159</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-0.3974319089671098</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.8655900704404932</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.573515856063804</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.2677232008887777</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-0.1936133826717944</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.76951255260063</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.4031974785743385</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.6691208309027457</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-0.1116883710719168</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8683256550694738</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-3.699864475570126</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-0.790421709329586</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.021619641817792</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.985845992540925</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.6580680618994077</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0.452311989469409</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>-1.605804572284586</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>bDeVnJAO</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>-1.353152916456342</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-1.001692214537703</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.2402860741301242</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0.8705842260736796</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.2770732453607708</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0.8482698188190364</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-1.283262910966888</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-0.36979650348412</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.7721487390643957</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-0.2872971140384382</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.4978504145120923</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-2.312647172940858</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.7007893161896722</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.089995082510123</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-0.4321220725543767</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-0.3315651918230352</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-1.48604504390641</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-0.5492779607150222</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-0.4627421499483119</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-0.8822953245370859</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-0.7418756467492338</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-0.6499700073151947</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.143277705319474</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-0.2145149774179313</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-1.389733422852812</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.006564012420209</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-0.2227276230876286</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.605836094432029</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-0.4384976844735621</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>-1.649795857533519</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-0.9267140434764152</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.002854196466832</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>-1.884644166280006</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>-1.085299768377932</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>lxyu7Met</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>-0.6959119323246935</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-1.001692214537703</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.2402860741301242</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-4.995464055982299</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.1178321018459983</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.151887505565813</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.6214111346599499</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-2.221910091312432</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.402999405714751</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-3.635374570841446</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.831323252972685</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.5166054926911837</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-0.09496176142367974</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-0.7820925010937312</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.8176719311830625</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.3749040023817</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.9303143117410985</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-1.946261636795816</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-1.886695065134531</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.568542799927958</v>
+      </c>
+      <c r="V15" t="n">
+        <v>2.005557282888633</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.688348367392231</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-2.144455242906595</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.329766162562743</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.181748445906829</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.259918068055142</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-0.400826025845627</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>-6.229457872509628</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>-1.929973131489592</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>-2.540267690650622</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.125303495167189</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>-1.022764344116789</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>-0.9225346941011557</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0.67425460053953</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>xb7MlutC</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.465185540921742</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-1.001692214537703</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.2402860741301242</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3.254295603834939</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-0.2802707569409327</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.4405098031490003</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-1.702291201004793</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.7638164413281132</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.7721487390643957</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.223760978563817</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-0.2429678290771261</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-0.6260948279852565</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.071832183945455</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.876302688978599</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-1.932233286102706</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-1.467061205537799</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-4.149982202386655</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.576566763755751</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.8432168945529859</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-0.3318548875058518</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-3.538960978729953</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-2.281750536369355</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.6736015698586073</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.7120537065704735</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-0.44434116347526</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-0.4585213368893963</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>-2.181007808368134</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-1.528824231867586</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.575973441018954</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>-1.204559940974967</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-1.504466554356653</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.153698130340081</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>-0.04236305059540656</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>-1.171068768842837</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>v3PZcqJP</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.4904637424214169</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-1.001692214537703</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.2402860741301242</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-2.417414162289411</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.152899534692019</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.806204707322997</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.8499720201351705</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-0.2409286937849893</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-0.8049779275614928</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-1.459124223919491</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.646014063229936</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.4151679241177671</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.8508252241275815</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.245710369190828</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-0.7639059865011216</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.8763639634795372</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.9600236480810269</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.6857365935013321</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.3147197043080179</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.3244394797236959</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.2346215993268755</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-0.4371733580116094</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-0.7354268365239938</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-2.530936687388943</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-1.326707272227642</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.1007795817915878</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>-0.5153866200521225</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.899616609252132</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.6419843592597004</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0.5763837252592399</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.9061559910402023</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>-1.048623304209346</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.145759465700195</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0.4952167986388298</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>zBdshgV6</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.6519890690300423</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-1.001692214537703</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.2402860741301242</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-2.933024141027988</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.869484680508495</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.7532530076402719</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.497561195648296</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.08414545067201036</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.137838739003228</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-1.793931969599792</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2.42397784784406</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.150252599867295</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.528726351167135</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.7229565613108206</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.740061121441252</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.735529371454596</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.375954356840024</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.08847545662620981</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-0.1377878648548395</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.8113675586359415</v>
+      </c>
+      <c r="V18" t="n">
+        <v>2.270370095383849</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.731185414277812</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-0.7354268365239938</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.175338048564676</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.6271033971526324</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-1.222179200191776</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8567395475026666</v>
+      </c>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="n">
+        <v>0.1801828600605763</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0.1311478087006882</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0.05305355392194144</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>-1.445127358961884</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>-1.107830829505572</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1.473601738593307</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>MRfkjXaJ</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>-0.8295880646904524</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-1.001692214537703</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.2402860741301242</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-4.479854077243721</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.675176104147702</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-0.2542262532829356</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.8118785392226339</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-0.8104319514463937</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.2990107390766292</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-0.2872971140384382</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.090505009383467</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.7427012780656669</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.3992676494253197</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.2821558448907806</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.1796967345036009</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.8311773441917866</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.494791702199738</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-0.6403855917637696</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.3050591063415536</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.31946642358785</v>
+      </c>
+      <c r="V19" t="n">
+        <v>-0.01364041238738953</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.4476287941429848</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.2039254343977402</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>-2.067652345394741</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.446443355279844</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-1.061329262365618</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.1302602021984927</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>-2.760497454554507</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>-0.1355240097293489</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0.1311478087006882</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0.1491009767833386</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0.03314319299594994</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>-1.202644945549239</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>-1.395690467424738</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_selected.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI10"/>
+  <dimension ref="A1:AI5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1034,549 +1034,6 @@
       </c>
       <c r="AI5" t="n">
         <v>-1.085299768377932</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>lxyu7Met</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>-0.6959119323246935</v>
-      </c>
-      <c r="C6" t="n">
-        <v>-1.001692214537703</v>
-      </c>
-      <c r="D6" t="n">
-        <v>-0.2402860741301242</v>
-      </c>
-      <c r="E6" t="n">
-        <v>-4.995464055982299</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.1178321018459983</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1.151887505565813</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.6214111346599499</v>
-      </c>
-      <c r="I6" t="n">
-        <v>-2.221910091312432</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1.402999405714751</v>
-      </c>
-      <c r="K6" t="n">
-        <v>-3.635374570841446</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.831323252972685</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.5166054926911837</v>
-      </c>
-      <c r="N6" t="n">
-        <v>-0.09496176142367974</v>
-      </c>
-      <c r="O6" t="n">
-        <v>-0.7820925010937312</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.8176719311830625</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.3749040023817</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.9303143117410985</v>
-      </c>
-      <c r="S6" t="n">
-        <v>-1.946261636795816</v>
-      </c>
-      <c r="T6" t="n">
-        <v>-1.886695065134531</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.568542799927958</v>
-      </c>
-      <c r="V6" t="n">
-        <v>2.005557282888633</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.688348367392231</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-2.144455242906595</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.329766162562743</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.181748445906829</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.259918068055142</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>-0.400826025845627</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>-6.229457872509628</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>-1.929973131489592</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>-2.540267690650622</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.125303495167189</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>-1.022764344116789</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>-0.9225346941011557</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0.67425460053953</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>xb7MlutC</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1.465185540921742</v>
-      </c>
-      <c r="C7" t="n">
-        <v>-1.001692214537703</v>
-      </c>
-      <c r="D7" t="n">
-        <v>-0.2402860741301242</v>
-      </c>
-      <c r="E7" t="n">
-        <v>3.254295603834939</v>
-      </c>
-      <c r="F7" t="n">
-        <v>-0.2802707569409327</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.4405098031490003</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-1.702291201004793</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.7638164413281132</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.7721487390643957</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2.223760978563817</v>
-      </c>
-      <c r="L7" t="n">
-        <v>-0.2429678290771261</v>
-      </c>
-      <c r="M7" t="n">
-        <v>-0.6260948279852565</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1.071832183945455</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.876302688978599</v>
-      </c>
-      <c r="P7" t="n">
-        <v>-1.932233286102706</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>-1.467061205537799</v>
-      </c>
-      <c r="R7" t="n">
-        <v>-4.149982202386655</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.576566763755751</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.8432168945529859</v>
-      </c>
-      <c r="U7" t="n">
-        <v>-0.3318548875058518</v>
-      </c>
-      <c r="V7" t="n">
-        <v>-3.538960978729953</v>
-      </c>
-      <c r="W7" t="n">
-        <v>-2.281750536369355</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0.6736015698586073</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.7120537065704735</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>-0.44434116347526</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>-0.4585213368893963</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>-2.181007808368134</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>-1.528824231867586</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.575973441018954</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>-1.204559940974967</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>-1.504466554356653</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.153698130340081</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>-0.04236305059540656</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>-1.171068768842837</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>v3PZcqJP</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.4904637424214169</v>
-      </c>
-      <c r="C8" t="n">
-        <v>-1.001692214537703</v>
-      </c>
-      <c r="D8" t="n">
-        <v>-0.2402860741301242</v>
-      </c>
-      <c r="E8" t="n">
-        <v>-2.417414162289411</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1.152899534692019</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.806204707322997</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.8499720201351705</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-0.2409286937849893</v>
-      </c>
-      <c r="J8" t="n">
-        <v>-0.8049779275614928</v>
-      </c>
-      <c r="K8" t="n">
-        <v>-1.459124223919491</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.646014063229936</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.4151679241177671</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.8508252241275815</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.245710369190828</v>
-      </c>
-      <c r="P8" t="n">
-        <v>-0.7639059865011216</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.8763639634795372</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.9600236480810269</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.6857365935013321</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.3147197043080179</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0.3244394797236959</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0.2346215993268755</v>
-      </c>
-      <c r="W8" t="n">
-        <v>-0.4371733580116094</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-0.7354268365239938</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>-2.530936687388943</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>-1.326707272227642</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0.1007795817915878</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>-0.5153866200521225</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.899616609252132</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0.6419843592597004</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0.5763837252592399</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0.9061559910402023</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>-1.048623304209346</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.145759465700195</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0.4952167986388298</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>zBdshgV6</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.6519890690300423</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-1.001692214537703</v>
-      </c>
-      <c r="D9" t="n">
-        <v>-0.2402860741301242</v>
-      </c>
-      <c r="E9" t="n">
-        <v>-2.933024141027988</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.869484680508495</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.7532530076402719</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.497561195648296</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.08414545067201036</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.137838739003228</v>
-      </c>
-      <c r="K9" t="n">
-        <v>-1.793931969599792</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2.42397784784406</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.150252599867295</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1.528726351167135</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.7229565613108206</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.740061121441252</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.735529371454596</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.375954356840024</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.08847545662620981</v>
-      </c>
-      <c r="T9" t="n">
-        <v>-0.1377878648548395</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0.8113675586359415</v>
-      </c>
-      <c r="V9" t="n">
-        <v>2.270370095383849</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.731185414277812</v>
-      </c>
-      <c r="X9" t="n">
-        <v>-0.7354268365239938</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.175338048564676</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0.6271033971526324</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>-1.222179200191776</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0.8567395475026666</v>
-      </c>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="n">
-        <v>0.1801828600605763</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0.1311478087006882</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0.05305355392194144</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>-1.445127358961884</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>-1.107830829505572</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1.473601738593307</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>MRfkjXaJ</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>-0.8295880646904524</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-1.001692214537703</v>
-      </c>
-      <c r="D10" t="n">
-        <v>-0.2402860741301242</v>
-      </c>
-      <c r="E10" t="n">
-        <v>-4.479854077243721</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.675176104147702</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-0.2542262532829356</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.8118785392226339</v>
-      </c>
-      <c r="I10" t="n">
-        <v>-0.8104319514463937</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.2990107390766292</v>
-      </c>
-      <c r="K10" t="n">
-        <v>-0.2872971140384382</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.090505009383467</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.7427012780656669</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.3992676494253197</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.2821558448907806</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.1796967345036009</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.8311773441917866</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.494791702199738</v>
-      </c>
-      <c r="S10" t="n">
-        <v>-0.6403855917637696</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0.3050591063415536</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.31946642358785</v>
-      </c>
-      <c r="V10" t="n">
-        <v>-0.01364041238738953</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0.4476287941429848</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0.2039254343977402</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>-2.067652345394741</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.446443355279844</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>-1.061329262365618</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0.1302602021984927</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>-2.760497454554507</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>-0.1355240097293489</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0.1311478087006882</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0.1491009767833386</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0.03314319299594994</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>-1.202644945549239</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>-1.395690467424738</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_selected.xlsx
@@ -425,176 +425,121 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI5"/>
+  <dimension ref="A1:X11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>id_team_away</t>
+          <t>is_cup</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>id_competition</t>
+          <t>dif_mean_last_120_matches_shots_on_goal</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>is_cup</t>
+          <t>dif_mean_last_480_matches_shots_on_goal</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_expected_points_against</t>
+          <t>dif_mean_last_120_matches_goal_attempts</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_shots_on_goal</t>
+          <t>dif_mean_last_120_matches_goals</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_shots_on_goal</t>
+          <t>dif_mean_last_480_matches_goals</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_goal_attempts</t>
+          <t>dif_mean_last_480_matches_PPS</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_goal_attempts_against</t>
+          <t>dif_mean_last_480_matches_attacks</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_goals</t>
+          <t>dif_mean_last_480_matches_dangerous_attacks</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_goals_against</t>
+          <t>dif_mean_last_120_matches_dead_balls</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_points</t>
+          <t>dif_mean_last_480_matches_dead_balls</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_points</t>
+          <t>dif_mean_last_120_matches_ball_possession</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_goal_ratio</t>
+          <t>dif_mean_last_480_matches_ball_possession</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_PPS</t>
+          <t>dif_mean_last_120_matches_yellow_cards</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_PPS_against</t>
+          <t>dif_mean_last_120_matches_red_cards</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_attacks</t>
+          <t>dif_mean_last_120_matches_KGP</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_dangerous_attacks</t>
+          <t>dif_mean_last_120_matches_clean_sheet</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_dangerous_attacks_against</t>
+          <t>dif_mean_last_480_matches_clean_sheet</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_dangerous_attacks_against</t>
+          <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_dead_balls</t>
+          <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_ball_possession</t>
+          <t>dif_sum_wage_player_miss</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_ball_possession</t>
+          <t>dif_mean_value_player_sub</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_60_matches_yellow_cards</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_60_matches_yellow_cards_against</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_60_matches_defensive_actions_against</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_360_matches_defensive_actions</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_360_matches_defensive_actions_against</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_60_matches_PPDA_against</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_360_matches_PPDA</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_60_matches_clean_sheet_against</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_360_matches_clean_sheet</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_360_matches_clean_sheet_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_start</t>
         </is>
@@ -603,438 +548,660 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Ee8YgF0f</t>
+          <t>vwbmU7aL</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1172845395670066</v>
+        <v>-0.3599058830750308</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.001692214537703</v>
+        <v>-1.399205046743698</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.2402860741301242</v>
+        <v>0.1887921818847436</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.8705842260736792</v>
+        <v>-1.917294799224426</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1210296134261604</v>
+        <v>-0.7042458911759584</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0712337852820555</v>
+        <v>0.3233207387646438</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.1785519645033222</v>
+        <v>1.091247495617678</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9102133551866168</v>
+        <v>-0.1426783364988524</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.751253927537026</v>
+        <v>-0.5436480103036795</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.1198932411982877</v>
+        <v>1.298114160223867</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.131949721384188</v>
+        <v>-1.284601609526849</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.177977055170966</v>
+        <v>-0.905431810179587</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9449502464854882</v>
+        <v>-0.7767663967583719</v>
       </c>
       <c r="O2" t="n">
-        <v>1.332362533017534</v>
+        <v>-0.06678435085728443</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.214487054256616</v>
+        <v>0.1858363880754785</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.504399032393433</v>
+        <v>-0.5527502127431062</v>
       </c>
       <c r="R2" t="n">
-        <v>-1.060211223034103</v>
+        <v>-0.5455879371555369</v>
       </c>
       <c r="S2" t="n">
-        <v>1.029920977463267</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.055557799109394</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.9807338469532445</v>
-      </c>
-      <c r="V2" t="n">
-        <v>-0.04674201394929177</v>
-      </c>
-      <c r="W2" t="n">
-        <v>-1.602410730622293</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.143277705319474</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-1.604368003400539</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-0.02416682597412594</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0.7616550919731053</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0.1360541942802097</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.195223077171645</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.23517990884066</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0.1311478087006882</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0.08711986450499899</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-0.5415003646164247</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-1.874635942918353</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-1.696347382232734</v>
-      </c>
+        <v>-0.2106437397217683</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>p4Um50Qh</t>
+          <t>OUcd1IPH</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.654560061773234</v>
+        <v>-0.3599058830750308</v>
       </c>
       <c r="C3" t="n">
-        <v>-1.001692214537703</v>
+        <v>-0.160181668940519</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.2402860741301242</v>
+        <v>-0.8500966196195393</v>
       </c>
       <c r="E3" t="n">
-        <v>-3.964244098505143</v>
+        <v>-1.238626179273569</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2006501851835466</v>
+        <v>1.329099863617686</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.6586814468394298</v>
+        <v>-1.820608763272128</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.397543353704499</v>
+        <v>2.787288969631226</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.189208205138926</v>
+        <v>-1.46315648929382</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.435828594211848</v>
+        <v>-0.7323622745531668</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7171261230024641</v>
+        <v>-0.4379887815483052</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.724604316255563</v>
+        <v>-0.02653482393053162</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8160296408898232</v>
+        <v>-1.664847419785666</v>
       </c>
       <c r="N3" t="n">
-        <v>1.262616376044065</v>
+        <v>-2.005490241475471</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2697298640305479</v>
-      </c>
-      <c r="P3" t="n">
-        <v>-0.3989584275876021</v>
-      </c>
+        <v>2.454297851647062</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>0.7067179213396702</v>
+        <v>1.515489343415745</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4252555939623159</v>
+        <v>0.7998718564426567</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3974319089671098</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.8655900704404932</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.573515856063804</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0.2677232008887777</v>
-      </c>
-      <c r="W3" t="n">
-        <v>-0.1936133826717944</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.76951255260063</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.4031974785743385</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0.6691208309027457</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>-0.1116883710719168</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0.8683256550694738</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>-3.699864475570126</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>-0.790421709329586</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.021619641817792</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0.985845992540925</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0.6580680618994077</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0.452311989469409</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>-1.605804572284586</v>
-      </c>
+        <v>0.1414003832965</v>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>zZA5hNtm</t>
+          <t>rZUMHwAb</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4459050316328306</v>
+        <v>-0.3599058830750308</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.001692214537703</v>
+        <v>1.760304566654408</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2402860741301242</v>
+        <v>1.73930903955879</v>
       </c>
       <c r="E4" t="n">
-        <v>-5.511074034720877</v>
+        <v>1.03343833099669</v>
       </c>
       <c r="F4" t="n">
-        <v>1.630622965236337</v>
+        <v>0.5665952055700695</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.4954247931903245</v>
+        <v>0.7675955648010263</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9261589819602442</v>
+        <v>-0.6562832105058478</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5533708776565129</v>
+        <v>1.266475098573683</v>
       </c>
       <c r="J4" t="n">
-        <v>1.245286739052162</v>
+        <v>1.299304857050933</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.133162952320995</v>
+        <v>1.817677814330868</v>
       </c>
       <c r="L4" t="n">
-        <v>1.090505009383467</v>
+        <v>1.61976340013395</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.603163101054501</v>
+        <v>0.3040078643782428</v>
       </c>
       <c r="N4" t="n">
-        <v>1.601803537893939</v>
+        <v>1.120279008242407</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7096539059968232</v>
-      </c>
-      <c r="P4" t="n">
-        <v>-1.55292969019902</v>
-      </c>
+        <v>-0.6599801632112485</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>-0.5446038435518831</v>
+        <v>3.660206965711283</v>
       </c>
       <c r="R4" t="n">
-        <v>1.524501038539666</v>
+        <v>1.184288940327855</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5136444015203645</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-0.4180438608497472</v>
-      </c>
-      <c r="U4" t="n">
-        <v>-0.3530256735455143</v>
-      </c>
-      <c r="V4" t="n">
-        <v>-0.4605120334730666</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-1.058336748811571</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.3604841462180291</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.4031974785743386</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>-1.389733422852812</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>-1.181844866688515</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>-2.088242945670333</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>10.91267204907505</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.604152667793382</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>-2.540267690650622</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>-1.501320896402677</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0.7760212131987899</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>-0.4829888844001676</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0.5433272240158951</v>
-      </c>
+        <v>1.549937946264976</v>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bDeVnJAO</t>
+          <t>WhWcJjo3</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-1.353152916456342</v>
+        <v>-0.3599058830750308</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.001692214537703</v>
+        <v>0.02567183772995798</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2402860741301242</v>
+        <v>-0.2291652022913685</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8705842260736796</v>
+        <v>-0.677986884531557</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2770732453607708</v>
+        <v>1.837436302316097</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.8482698188190364</v>
+        <v>-0.2860398149792465</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.283262910966888</v>
+        <v>-0.4845792680536274</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.36979650348412</v>
+        <v>0.9219601602939977</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7721487390643957</v>
+        <v>1.054674343095693</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.2872971140384382</v>
+        <v>0.9559624855680369</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4978504145120923</v>
+        <v>-0.3014996428756983</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.312647172940858</v>
+        <v>-0.596040265525258</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7007893161896722</v>
+        <v>0.5025051360021022</v>
       </c>
       <c r="O5" t="n">
-        <v>1.089995082510123</v>
+        <v>-0.3633822570342667</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.4321220725543767</v>
+        <v>0.1858363880754785</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.3315651918230352</v>
+        <v>-1.870614536684635</v>
       </c>
       <c r="R5" t="n">
-        <v>-1.48604504390641</v>
+        <v>0.4154547725574584</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5492779607150222</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-0.4627421499483119</v>
-      </c>
-      <c r="U5" t="n">
-        <v>-0.8822953245370859</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-0.7418756467492338</v>
-      </c>
-      <c r="W5" t="n">
-        <v>-0.6499700073151947</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.143277705319474</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>-0.2145149774179313</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>-1.389733422852812</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.006564012420209</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>-0.2227276230876286</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>3.605836094432029</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-0.4384976844735621</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-1.649795857533519</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>-0.9267140434764152</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.002854196466832</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-1.884644166280006</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>-1.085299768377932</v>
-      </c>
+        <v>0.29759965264799</v>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>4nvCemgd</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>-0.3599058830750308</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.2734765132905936</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.2710648240687585</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-1.091089522762513</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.05825876687165833</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0.4292759610784082</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.221272465272898</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-0.9925946061301452</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-0.9860805424245932</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.614921266386672</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-0.8243173310134241</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-0.4085302384620284</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-1.349325897027453</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-0.06678435085728462</v>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="n">
+        <v>-2.321363737948043</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-0.3533793952129379</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-1.376613875158272</v>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>-0.007024646658704578</v>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>IHSe3ve5</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>-0.3599058830750308</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.09823050005036012</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.5307155105377356</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.6779868845315573</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-1.466750549223575</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.3625133506084603</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.06830926963173221</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.4956058800225147</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.728841904964643</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-0.4633333500413299</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.3533433535888</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.3040078643782428</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.6164763341286602</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-0.6599801632112483</v>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="n">
+        <v>1.88189734336607</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-1.122213562983334</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.2357301547206259</v>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>8Kp3c9Oq</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>-0.3599058830750308</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.7796933578421082</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.3363959147740002</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-2.123846118339904</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-0.8313300008505611</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-0.7084650594072828</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.8655957563581713</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-0.7256266712916576</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-0.3450909662028847</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-2.820378219892601</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.7513326731263426</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-2.189875495562708</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-0.858894635439133</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.5264114614966795</v>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="n">
+        <v>-0.002752470003933403</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-1.122213562983334</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-0.7587493589440563</v>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Wf14adfU</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>-0.3599058830750308</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.2115253444004349</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.9491029495091716</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-1.150104185366936</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.3124269862208639</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.168171227620716</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.350608844755859</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.111689908921399</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.9087087606825341</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.108029896526183</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.77329811430104</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.5477708995604407</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.8233605823499309</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.416205180027625</v>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="n">
+        <v>2.022066398036103</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.568706024213053</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.098043565487264</v>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>0.08266840437260832</v>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>z9REJaun</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-0.3599058830750308</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.4593300199610705</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.2113344014559312</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0.1763622523939675</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.4395110958954666</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0.532624482085888</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.5264460919323584</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-1.0178523543782</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-0.7804640869041674</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.5504493896796476</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.8592091610211889</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-1.327329371071853</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0.6017721255417903</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-0.6599801632112485</v>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="n">
+        <v>-1.216976055330588</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.4154547725574584</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-0.1296735914275664</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.4770873468466314</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.4219816391860958</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.1544228451976586</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.05634448291646473</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.2929448414309503</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>xYNVFHvB</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>-0.3599058830750308</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.193962748885521</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.9816469938562035</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-0.264884246300601</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.07493164426848</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.6311953989126634</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.2973406971206419</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-0.1221339553677344</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-0.378471134245941</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.133374465019209</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.6484851777353595</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.991598107947308</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-0.1479369775729723</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.750895757824043</v>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="n">
+        <v>-1.730776038338988</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.953123108098251</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.199722932387896</v>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_selected.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X11"/>
+  <dimension ref="A1:X15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,62 +548,60 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>vwbmU7aL</t>
+          <t>nVutWTU8</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>-0.3599058830750308</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.399205046743698</v>
+        <v>-0.2221328378306777</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1887921818847436</v>
+        <v>-0.126320676110503</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.917294799224426</v>
+        <v>-0.4419282341138679</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7042458911759584</v>
+        <v>-1.848002878247383</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3233207387646438</v>
+        <v>-0.9680212003489463</v>
       </c>
       <c r="H2" t="n">
-        <v>1.091247495617678</v>
+        <v>1.080129883034703</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1426783364988524</v>
+        <v>-1.20931393824817</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.5436480103036795</v>
+        <v>-1.000384519320315</v>
       </c>
       <c r="K2" t="n">
-        <v>1.298114160223867</v>
+        <v>0.5124325369401099</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.284601609526849</v>
+        <v>-0.3134203710604988</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.905431810179587</v>
+        <v>-0.2491467154582837</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.7767663967583719</v>
+        <v>-1.32389829288074</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.06678435085728443</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.1858363880754785</v>
-      </c>
+        <v>2.083550468925834</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>-0.5527502127431062</v>
+        <v>6.238196663178355</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.5455879371555369</v>
+        <v>0.2232462306148594</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2106437397217683</v>
+        <v>0.9238410136355638</v>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
@@ -614,60 +612,62 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>OUcd1IPH</t>
+          <t>vPIEF8pS</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>-0.3599058830750308</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.160181668940519</v>
+        <v>0.8620126177471037</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.8500966196195393</v>
+        <v>0.1507016166325716</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.238626179273569</v>
+        <v>0.1482183919303554</v>
       </c>
       <c r="F3" t="n">
-        <v>1.329099863617686</v>
+        <v>-0.1323673976402458</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.820608763272128</v>
+        <v>-0.8202378079904248</v>
       </c>
       <c r="H3" t="n">
-        <v>2.787288969631226</v>
+        <v>0.7388231898168749</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.46315648929382</v>
+        <v>-0.5799535444670618</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.7323622745531668</v>
+        <v>-0.4693338965721729</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.4379887815483052</v>
+        <v>2.083795783507624</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.02653482393053162</v>
+        <v>-0.3446279705705497</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.664847419785666</v>
+        <v>0.7165299239173476</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.005490241475471</v>
+        <v>-0.6104640202126301</v>
       </c>
       <c r="O3" t="n">
-        <v>2.454297851647062</v>
-      </c>
-      <c r="P3" t="inlineStr"/>
+        <v>2.305998898558571</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.012971111189509</v>
+      </c>
       <c r="Q3" t="n">
-        <v>1.515489343415745</v>
+        <v>-0.624250181427516</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7998718564426567</v>
+        <v>0.9920803983852555</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1414003832965</v>
+        <v>0.158081858664135</v>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
@@ -678,126 +678,132 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>rZUMHwAb</t>
+          <t>h8K6HUFF</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>-0.3599058830750308</v>
       </c>
       <c r="C4" t="n">
-        <v>1.760304566654408</v>
+        <v>-0.4699375133913136</v>
       </c>
       <c r="D4" t="n">
-        <v>1.73930903955879</v>
+        <v>0.2649733123890893</v>
       </c>
       <c r="E4" t="n">
-        <v>1.03343833099669</v>
+        <v>-0.087840258487334</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5665952055700695</v>
+        <v>-0.9584141105251638</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7675955648010263</v>
+        <v>0.7336073267435984</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6562832105058478</v>
+        <v>-0.2622816639326918</v>
       </c>
       <c r="I4" t="n">
-        <v>1.266475098573683</v>
+        <v>0.8219233574746149</v>
       </c>
       <c r="J4" t="n">
-        <v>1.299304857050933</v>
+        <v>0.8874850027560899</v>
       </c>
       <c r="K4" t="n">
-        <v>1.817677814330868</v>
+        <v>0.7025168006377931</v>
       </c>
       <c r="L4" t="n">
-        <v>1.61976340013395</v>
+        <v>1.074395300852931</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3040078643782428</v>
+        <v>-0.6710442763505508</v>
       </c>
       <c r="N4" t="n">
-        <v>1.120279008242407</v>
+        <v>0.6766988379726848</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6599801632112485</v>
+        <v>2.454297851647062</v>
       </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>3.660206965711283</v>
+        <v>0.8835593256553909</v>
       </c>
       <c r="R4" t="n">
-        <v>1.184288940327855</v>
+        <v>-0.3533793952129379</v>
       </c>
       <c r="S4" t="n">
-        <v>1.549937946264976</v>
-      </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
+        <v>0.08832296167220748</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-0.07007846772542183</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-1.216149413127242</v>
+      </c>
       <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>-0.1261814546045382</v>
+      </c>
       <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>WhWcJjo3</t>
+          <t>WMcg8Qx2</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>-0.3599058830750308</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02567183772995798</v>
+        <v>0.6761591110766267</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2291652022913685</v>
+        <v>-1.54202001798292</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.677986884531557</v>
+        <v>0.6793503553701563</v>
       </c>
       <c r="F5" t="n">
-        <v>1.837436302316097</v>
+        <v>-0.1959094524775471</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2860398149792465</v>
+        <v>-1.477448945456595</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4845792680536274</v>
+        <v>1.60576544886126</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9219601602939977</v>
+        <v>-0.7928228304790794</v>
       </c>
       <c r="J5" t="n">
-        <v>1.054674343095693</v>
+        <v>-0.6578452623248934</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9559624855680369</v>
+        <v>0.2589868520098661</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.3014996428756983</v>
+        <v>-0.1830700013749361</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.596040265525258</v>
+        <v>-0.1741427046329922</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5025051360021022</v>
+        <v>-0.9233404597420081</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3633822570342667</v>
+        <v>3.195792617089517</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1858363880754785</v>
+        <v>0.4615479624468221</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.870614536684635</v>
+        <v>-0.5551727921868214</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4154547725574584</v>
+        <v>0.9920803983852555</v>
       </c>
       <c r="S5" t="n">
-        <v>0.29759965264799</v>
+        <v>-1.180209361603619</v>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
@@ -808,126 +814,124 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>4nvCemgd</t>
+          <t>b9aoAn8k</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>-0.3599058830750308</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2734765132905936</v>
+        <v>-0.2221328378306774</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2710648240687585</v>
+        <v>-0.4526298517707815</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.091089522762513</v>
+        <v>-0.2058695836961789</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05825876687165833</v>
+        <v>-0.9584141105251638</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4292759610784082</v>
+        <v>-0.8565566680860766</v>
       </c>
       <c r="H6" t="n">
-        <v>1.221272465272898</v>
+        <v>1.533765638622004</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9925946061301452</v>
+        <v>-1.06944970261274</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.9860805424245932</v>
+        <v>-0.7520154659491481</v>
       </c>
       <c r="K6" t="n">
-        <v>1.614921266386672</v>
+        <v>-1.071602993873916</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.8243173310134241</v>
+        <v>-0.8815729848382364</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4085302384620284</v>
+        <v>-1.758602433317281</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.349325897027453</v>
+        <v>-1.352219383016562</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.06678435085728462</v>
+        <v>0.9713083207621521</v>
       </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>-2.321363737948043</v>
+        <v>-1.155109895349921</v>
       </c>
       <c r="R6" t="n">
         <v>-0.3533793952129379</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.376613875158272</v>
+        <v>-1.697172616097368</v>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="n">
-        <v>-0.007024646658704578</v>
-      </c>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>IHSe3ve5</t>
+          <t>S2WzL3M7</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>-0.3599058830750308</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.09823050005036012</v>
+        <v>1.760304566654408</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5307155105377356</v>
+        <v>0.8998160665919666</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6779868845315573</v>
+        <v>2.036687595271869</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.466750549223575</v>
+        <v>2.345772741014508</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3625133506084603</v>
+        <v>1.427595426644455</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.06830926963173221</v>
+        <v>-1.266248472944998</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4956058800225147</v>
+        <v>2.835534031190325</v>
       </c>
       <c r="J7" t="n">
-        <v>0.728841904964643</v>
+        <v>2.378369359167905</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.4633333500413299</v>
+        <v>1.006651622554088</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3533433535888</v>
+        <v>1.281953420069079</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3040078643782428</v>
+        <v>1.804088080884078</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6164763341286602</v>
+        <v>2.647338159342913</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6599801632112483</v>
+        <v>-0.6599801632112485</v>
       </c>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="n">
-        <v>1.88189734336607</v>
+        <v>0.9960030147557528</v>
       </c>
       <c r="R7" t="n">
-        <v>-1.122213562983334</v>
+        <v>0.4154547725574584</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2357301547206259</v>
+        <v>0.8503630864209818</v>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
@@ -938,60 +942,60 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>8Kp3c9Oq</t>
+          <t>OAZJOoNr</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>-0.3599058830750308</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.7796933578421082</v>
+        <v>-0.09823050005035978</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3363959147740002</v>
+        <v>-0.03299879124267988</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.123846118339904</v>
+        <v>-1.032074860158091</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8313300008505611</v>
+        <v>-0.4500776718267528</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.7084650594072828</v>
+        <v>-0.05967814951677503</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8655957563581713</v>
+        <v>0.433109739544968</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7256266712916576</v>
+        <v>-0.5723737272467045</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3450909662028847</v>
+        <v>-0.4999997465314437</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.820378219892601</v>
+        <v>0.4617433999540618</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7513326731263426</v>
+        <v>-0.1860607296613133</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.189875495562708</v>
+        <v>-1.271076362952884</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.858894635439133</v>
+        <v>-0.4997662607808213</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5264114614966795</v>
+        <v>-0.06678435085728443</v>
       </c>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="n">
-        <v>-0.002752470003933403</v>
+        <v>-0.08056346083691591</v>
       </c>
       <c r="R8" t="n">
-        <v>-1.122213562983334</v>
+        <v>-0.9300050210407351</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7587493589440563</v>
+        <v>-0.8796647803967308</v>
       </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
@@ -1002,200 +1006,190 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Wf14adfU</t>
+          <t>WzwSMPie</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>-0.3599058830750308</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2115253444004349</v>
+        <v>1.63640222887409</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9491029495091716</v>
+        <v>0.1932536459834503</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.150104185366936</v>
+        <v>0.3252623797436224</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3124269862208639</v>
+        <v>1.329099863617686</v>
       </c>
       <c r="G9" t="n">
-        <v>1.168171227620716</v>
+        <v>0.01135726802324986</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.350608844755859</v>
+        <v>0.08706755688098843</v>
       </c>
       <c r="I9" t="n">
-        <v>1.111689908921399</v>
+        <v>0.09866384902980778</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9087087606825341</v>
+        <v>-0.003420972625533916</v>
       </c>
       <c r="K9" t="n">
-        <v>1.108029896526183</v>
+        <v>0.841911927349427</v>
       </c>
       <c r="L9" t="n">
-        <v>1.77329811430104</v>
+        <v>1.157426661031835</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5477708995604407</v>
+        <v>0.3040078643782428</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8233605823499309</v>
+        <v>0.1998912317595236</v>
       </c>
       <c r="O9" t="n">
-        <v>1.416205180027625</v>
+        <v>-1.253175975565212</v>
       </c>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="n">
-        <v>2.022066398036103</v>
+        <v>1.021914134727448</v>
       </c>
       <c r="R9" t="n">
-        <v>1.568706024213053</v>
+        <v>0.7998718564426567</v>
       </c>
       <c r="S9" t="n">
-        <v>2.098043565487264</v>
+        <v>1.105640209471151</v>
       </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
-      <c r="V9" t="n">
-        <v>0.08266840437260832</v>
-      </c>
+      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>z9REJaun</t>
+          <t>vwbmU7aL</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>-0.3599058830750308</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4593300199610705</v>
+        <v>-1.399205046743698</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2113344014559312</v>
+        <v>0.1887921818847436</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1763622523939675</v>
+        <v>-1.917294799224426</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4395110958954666</v>
+        <v>-0.7042458911759584</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.532624482085888</v>
+        <v>0.3233207387646438</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5264460919323584</v>
+        <v>1.091247495617678</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.0178523543782</v>
+        <v>-0.1426783364988524</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7804640869041674</v>
+        <v>-0.5436480103036795</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5504493896796476</v>
+        <v>1.298114160223867</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.8592091610211889</v>
+        <v>-1.284601609526849</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.327329371071853</v>
+        <v>-0.905431810179587</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6017721255417903</v>
+        <v>-0.7767663967583719</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6599801632112485</v>
-      </c>
-      <c r="P10" t="inlineStr"/>
+        <v>-0.06678435085728443</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.1858363880754785</v>
+      </c>
       <c r="Q10" t="n">
-        <v>-1.216976055330588</v>
+        <v>-0.5527502127431062</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4154547725574584</v>
+        <v>-0.5455879371555369</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1296735914275664</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0.4770873468466314</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0.4219816391860958</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0.1544228451976586</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0.05634448291646473</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0.2929448414309503</v>
-      </c>
+        <v>-0.2106437397217683</v>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>xYNVFHvB</t>
+          <t>OUcd1IPH</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>-0.3599058830750308</v>
       </c>
       <c r="C11" t="n">
-        <v>2.193962748885521</v>
+        <v>-0.160181668940519</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9816469938562035</v>
+        <v>-0.8500966196195393</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.264884246300601</v>
+        <v>-1.238626179273569</v>
       </c>
       <c r="F11" t="n">
-        <v>1.07493164426848</v>
+        <v>1.329099863617686</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6311953989126634</v>
+        <v>-1.820608763272128</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2973406971206419</v>
+        <v>2.787288969631226</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1221339553677344</v>
+        <v>-1.46315648929382</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.378471134245941</v>
+        <v>-0.7323622745531668</v>
       </c>
       <c r="K11" t="n">
-        <v>1.133374465019209</v>
+        <v>-0.4379887815483052</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6484851777353595</v>
+        <v>-0.02653482393053162</v>
       </c>
       <c r="M11" t="n">
-        <v>1.991598107947308</v>
+        <v>-1.664847419785666</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1479369775729723</v>
+        <v>-2.005490241475471</v>
       </c>
       <c r="O11" t="n">
-        <v>2.750895757824043</v>
+        <v>2.454297851647062</v>
       </c>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="n">
-        <v>-1.730776038338988</v>
+        <v>1.515489343415745</v>
       </c>
       <c r="R11" t="n">
-        <v>1.953123108098251</v>
+        <v>0.7998718564426567</v>
       </c>
       <c r="S11" t="n">
-        <v>1.199722932387896</v>
+        <v>0.1414003832965</v>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
@@ -1203,6 +1197,266 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>rZUMHwAb</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>-0.3599058830750308</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.760304566654408</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.73930903955879</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.03343833099669</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.5665952055700695</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.7675955648010263</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.6562832105058478</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.266475098573683</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.299304857050933</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.817677814330868</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.61976340013395</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.3040078643782428</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.120279008242407</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-0.6599801632112485</v>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="n">
+        <v>3.660206965711283</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.184288940327855</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.549937946264976</v>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>WhWcJjo3</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>-0.3599058830750308</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.02567183772995798</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.2291652022913685</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.677986884531557</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.837436302316097</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.2860398149792465</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.4845792680536274</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.9219601602939977</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.054674343095693</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.9559624855680369</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-0.3014996428756983</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-0.596040265525258</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.5025051360021022</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-0.3633822570342667</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.1858363880754785</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-1.870614536684635</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.4154547725574584</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.29759965264799</v>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>4nvCemgd</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>-0.3599058830750308</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.2734765132905936</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.2710648240687585</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-1.091089522762513</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.05825876687165833</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0.4292759610784082</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.221272465272898</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-0.9925946061301452</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-0.9860805424245932</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.614921266386672</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-0.8243173310134241</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-0.4085302384620284</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-1.349325897027453</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-0.06678435085728462</v>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="n">
+        <v>-2.321363737948043</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-0.3533793952129379</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-1.376613875158272</v>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>-0.007024646658704578</v>
+      </c>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>IHSe3ve5</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>-0.3599058830750308</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.09823050005036012</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.5307155105377356</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0.6779868845315573</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-1.466750549223575</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0.3625133506084603</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.06830926963173221</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.4956058800225147</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.728841904964643</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-0.4633333500413299</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.3533433535888</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.3040078643782428</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.6164763341286602</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-0.6599801632112483</v>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="n">
+        <v>1.88189734336607</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-1.122213562983334</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.2357301547206259</v>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_selected.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X15"/>
+  <dimension ref="A1:Z19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,92 +436,92 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_shots_on_goal</t>
+          <t>dif_mean_last_360_matches_shots_on_goal</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_shots_on_goal</t>
+          <t>dif_mean_last_60_matches_goals</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_goal_attempts</t>
+          <t>dif_mean_last_360_matches_goals</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_goals</t>
+          <t>dif_mean_last_360_matches_PPS</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_goals</t>
+          <t>dif_mean_last_360_matches_attacks</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_PPS</t>
+          <t>dif_mean_last_360_matches_attacks_against</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_attacks</t>
+          <t>dif_mean_last_60_matches_dangerous_attacks</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_dangerous_attacks</t>
+          <t>dif_mean_last_360_matches_dangerous_attacks_against</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_dead_balls</t>
+          <t>dif_mean_last_360_matches_ball_possession</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_dead_balls</t>
+          <t>dif_mean_last_360_matches_ball_possession_against</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_ball_possession</t>
+          <t>dif_mean_last_360_matches_total_passes_against</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_ball_possession</t>
+          <t>dif_mean_last_60_matches_PPDA</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_yellow_cards</t>
+          <t>dif_mean_last_360_matches_PPDA_against</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_red_cards</t>
+          <t>dif_mean_last_360_matches_clean_sheet_against</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_KGP</t>
+          <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_clean_sheet</t>
+          <t>dif_mean_value_player_start</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_clean_sheet</t>
+          <t>dif_mean_wage_player_start</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_rat_player_sub</t>
+          <t>dif_mean_wage_player_sub</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>dif_sum_wage_player_miss</t>
+          <t>dif_sum_value_player_miss</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
@@ -540,6 +540,16 @@
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_start</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_start</t>
         </is>
@@ -548,914 +558,1108 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>nVutWTU8</t>
+          <t>AsQgyP6l</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.3599058830750308</v>
+        <v>-0.3397821287880394</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.2221328378306777</v>
+        <v>-1.679970890664118</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.126320676110503</v>
+        <v>-0.344582351993931</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.4419282341138679</v>
+        <v>-1.839640803605941</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.848002878247383</v>
+        <v>3.365305027325702</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.9680212003489463</v>
+        <v>-1.776687036581007</v>
       </c>
       <c r="H2" t="n">
-        <v>1.080129883034703</v>
+        <v>0.9903873516197658</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.20931393824817</v>
+        <v>-1.271453986565998</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.000384519320315</v>
+        <v>-0.04747374755303913</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5124325369401099</v>
+        <v>-1.629329114263644</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.3134203710604988</v>
+        <v>1.629329114263645</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.2491467154582837</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-1.32389829288074</v>
-      </c>
+        <v>1.349029710093369</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>2.083550468925834</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="n">
-        <v>6.238196663178355</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.2232462306148594</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.9238410136355638</v>
-      </c>
+        <v>-0.6526279469080508</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.6999283455829624</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>vPIEF8pS</t>
+          <t>KdJMr7EE</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.3599058830750308</v>
+        <v>-0.3397821287880394</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8620126177471037</v>
+        <v>-0.4950351505528262</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1507016166325716</v>
+        <v>1.602828576417274</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1482183919303554</v>
+        <v>-1.123982255905785</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1323673976402458</v>
+        <v>0.6660251849161902</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.8202378079904248</v>
+        <v>-1.009942682621856</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7388231898168749</v>
-      </c>
-      <c r="I3" t="n">
-        <v>-0.5799535444670618</v>
-      </c>
+        <v>-0.1341770386408202</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>-0.4693338965721729</v>
+        <v>-0.7487417065549438</v>
       </c>
       <c r="K3" t="n">
-        <v>2.083795783507624</v>
+        <v>-0.4333981120203173</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.3446279705705497</v>
+        <v>0.4333981120203173</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7165299239173476</v>
-      </c>
-      <c r="N3" t="n">
-        <v>-0.6104640202126301</v>
-      </c>
+        <v>0.6415402047801676</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>2.305998898558571</v>
+        <v>-0.5454532438658489</v>
       </c>
       <c r="P3" t="n">
-        <v>1.012971111189509</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>-0.624250181427516</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.9920803983852555</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.158081858664135</v>
-      </c>
+        <v>0.319795498060463</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>h8K6HUFF</t>
+          <t>vNHAXt6D</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.3599058830750308</v>
+        <v>-0.3397821287880394</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.4699375133913136</v>
+        <v>0.6975869958614518</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2649733123890893</v>
+        <v>1.153426054476227</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.087840258487334</v>
+        <v>-0.8420613177181349</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9584141105251638</v>
+        <v>-0.4520678841537329</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7336073267435984</v>
+        <v>-0.5454176586759988</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2622816639326918</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.8219233574746149</v>
-      </c>
+        <v>-0.07920375845903926</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>0.8874850027560899</v>
+        <v>0.003859678434304597</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7025168006377931</v>
+        <v>-0.03633822128081728</v>
       </c>
       <c r="L4" t="n">
-        <v>1.074395300852931</v>
+        <v>0.03633822128081728</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6710442763505508</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.6766988379726848</v>
-      </c>
+        <v>-0.0615757506443089</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>2.454297851647062</v>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="n">
-        <v>0.8835593256553909</v>
-      </c>
-      <c r="R4" t="n">
-        <v>-0.3533793952129379</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.08832296167220748</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-0.07007846772542183</v>
-      </c>
-      <c r="U4" t="n">
-        <v>-1.216149413127242</v>
-      </c>
+        <v>-0.2741189532455608</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-0.1382876934824242</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
-      <c r="W4" t="n">
-        <v>-0.1261814546045382</v>
-      </c>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>WMcg8Qx2</t>
+          <t>h2acepbK</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.3599058830750308</v>
+        <v>-0.3397821287880394</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6761591110766267</v>
+        <v>0.4902015260150001</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.54202001798292</v>
+        <v>-0.1947815113469151</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6793503553701563</v>
+        <v>0.3683882150508578</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1959094524775471</v>
+        <v>-0.5150468519976255</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.477448945456595</v>
+        <v>-0.1838592587664912</v>
       </c>
       <c r="H5" t="n">
-        <v>1.60576544886126</v>
+        <v>-0.5071818425664477</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7928228304790794</v>
+        <v>-0.7983458157174819</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.6578452623248934</v>
+        <v>-0.1556403657573964</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2589868520098661</v>
+        <v>0.01722174365825877</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.1830700013749361</v>
+        <v>-0.01722174365825877</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1741427046329922</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-0.9233404597420081</v>
-      </c>
+        <v>-0.3168691036781308</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>3.195792617089517</v>
+        <v>-0.6310359170892307</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4615479624468221</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-0.5551727921868214</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.9920803983852555</v>
-      </c>
-      <c r="S5" t="n">
-        <v>-1.180209361603619</v>
-      </c>
+        <v>-1.08768290911535</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>b9aoAn8k</t>
+          <t>WdE2Z2y1</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.3599058830750308</v>
+        <v>-0.3397821287880394</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.2221328378306774</v>
+        <v>0.2238388669959994</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4526298517707815</v>
+        <v>1.003625213829211</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2058695836961789</v>
+        <v>0.1775096348834394</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9584141105251638</v>
+        <v>0.8753220385774039</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.8565566680860766</v>
+        <v>-1.230070236657623</v>
       </c>
       <c r="H6" t="n">
-        <v>1.533765638622004</v>
+        <v>1.073256431392507</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.06944970261274</v>
+        <v>1.508056517169033</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.7520154659491481</v>
+        <v>-0.240610389299521</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.071602993873916</v>
+        <v>-0.7046677348209819</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.8815729848382364</v>
+        <v>0.7046677348209819</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.758602433317281</v>
-      </c>
-      <c r="N6" t="n">
-        <v>-1.352219383016562</v>
-      </c>
+        <v>0.9188121804100636</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>0.9713083207621521</v>
-      </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="n">
-        <v>-1.155109895349921</v>
-      </c>
-      <c r="R6" t="n">
-        <v>-0.3533793952129379</v>
-      </c>
-      <c r="S6" t="n">
-        <v>-1.697172616097368</v>
-      </c>
+        <v>-0.5158164219096564</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-0.5920986065549629</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>S2WzL3M7</t>
+          <t>vaZNtoqR</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.3599058830750308</v>
+        <v>-0.3397821287880394</v>
       </c>
       <c r="C7" t="n">
-        <v>1.760304566654408</v>
+        <v>1.06191282126738</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8998160665919666</v>
+        <v>-1.542989077170057</v>
       </c>
       <c r="E7" t="n">
-        <v>2.036687595271869</v>
+        <v>0.2229014923622768</v>
       </c>
       <c r="F7" t="n">
-        <v>2.345772741014508</v>
+        <v>1.590641838765807</v>
       </c>
       <c r="G7" t="n">
-        <v>1.427595426644455</v>
+        <v>0.06845070893705255</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.266248472944998</v>
+        <v>1.177843656134467</v>
       </c>
       <c r="I7" t="n">
-        <v>2.835534031190325</v>
+        <v>-0.7392072943614173</v>
       </c>
       <c r="J7" t="n">
-        <v>2.378369359167905</v>
+        <v>1.029357962562839</v>
       </c>
       <c r="K7" t="n">
-        <v>1.006651622554088</v>
+        <v>-1.340387198144943</v>
       </c>
       <c r="L7" t="n">
-        <v>1.281953420069079</v>
+        <v>1.340387198144943</v>
       </c>
       <c r="M7" t="n">
-        <v>1.804088080884078</v>
+        <v>1.591614228027269</v>
       </c>
       <c r="N7" t="n">
-        <v>2.647338159342913</v>
+        <v>1.433864764832862</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6599801632112485</v>
-      </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="n">
-        <v>0.9960030147557528</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.4154547725574584</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.8503630864209818</v>
-      </c>
+        <v>-0.9865438956689684</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-0.2450946552411284</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>OAZJOoNr</t>
+          <t>hQspntL6</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.3599058830750308</v>
+        <v>-0.3397821287880394</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.09823050005035978</v>
+        <v>-1.426712816890038</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.03299879124267988</v>
+        <v>1.453027735770259</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.032074860158091</v>
+        <v>-1.10393741855758</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4500776718267528</v>
+        <v>-0.06899406340457112</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.05967814951677503</v>
+        <v>-1.116236752930676</v>
       </c>
       <c r="H8" t="n">
-        <v>0.433109739544968</v>
+        <v>-0.2655864064218329</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5723737272467045</v>
+        <v>0.3844246114038081</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.4999997465314437</v>
+        <v>0.440599799439218</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4617433999540618</v>
+        <v>-0.6164198754514939</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1860607296613133</v>
+        <v>0.6164198754514939</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.271076362952884</v>
-      </c>
-      <c r="N8" t="n">
-        <v>-0.4997662607808213</v>
-      </c>
+        <v>0.3339457418728692</v>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
-        <v>-0.06678435085728443</v>
-      </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="n">
-        <v>-0.08056346083691591</v>
-      </c>
-      <c r="R8" t="n">
-        <v>-0.9300050210407351</v>
-      </c>
-      <c r="S8" t="n">
-        <v>-0.8796647803967308</v>
-      </c>
+        <v>-0.6734899235469289</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.7280354407826214</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>WzwSMPie</t>
+          <t>p0vxl2jf</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.3599058830750308</v>
+        <v>-0.3397821287880394</v>
       </c>
       <c r="C9" t="n">
-        <v>1.63640222887409</v>
+        <v>-1.341080678439926</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1932536459834503</v>
+        <v>0.1048201699471165</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3252623797436224</v>
+        <v>-0.1412747461150337</v>
       </c>
       <c r="F9" t="n">
-        <v>1.329099863617686</v>
+        <v>0.3078105789086623</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01135726802324986</v>
+        <v>0.1189523426926395</v>
       </c>
       <c r="H9" t="n">
-        <v>0.08706755688098843</v>
+        <v>0.03950549114739484</v>
       </c>
       <c r="I9" t="n">
-        <v>0.09866384902980778</v>
+        <v>0.857532782252324</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.003420972625533916</v>
+        <v>-0.0700903420545749</v>
       </c>
       <c r="K9" t="n">
-        <v>0.841911927349427</v>
+        <v>-0.3199236100307482</v>
       </c>
       <c r="L9" t="n">
-        <v>1.157426661031835</v>
+        <v>0.3199236100307482</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3040078643782428</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.1998912317595236</v>
-      </c>
+        <v>0.5612198653796493</v>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="n">
-        <v>-1.253175975565212</v>
-      </c>
-      <c r="P9" t="inlineStr"/>
+        <v>-0.08309463239486137</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-1.141648531898696</v>
+      </c>
       <c r="Q9" t="n">
-        <v>1.021914134727448</v>
+        <v>-0.4900257690315215</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7998718564426567</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.105640209471151</v>
-      </c>
+        <v>-0.05056661293584868</v>
+      </c>
+      <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
+      <c r="U9" t="n">
+        <v>-0.3655774974067835</v>
+      </c>
       <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
+      <c r="W9" t="n">
+        <v>-0.07602266345567892</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-0.3054759171730904</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-0.01132326390554637</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-0.5162609149027396</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>vwbmU7aL</t>
+          <t>lYpTkOLs</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.3599058830750308</v>
+        <v>-0.3397821287880394</v>
       </c>
       <c r="C10" t="n">
-        <v>-1.399205046743698</v>
+        <v>1.410669166955106</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1887921818847436</v>
+        <v>1.003625213829211</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.917294799224426</v>
+        <v>1.096468436150156</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7042458911759584</v>
+        <v>-0.586426994581646</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3233207387646438</v>
+        <v>-0.08876238327225723</v>
       </c>
       <c r="H10" t="n">
-        <v>1.091247495617678</v>
+        <v>-0.6330866557947976</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1426783364988524</v>
+        <v>1.153225389032646</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5436480103036795</v>
+        <v>-0.1953703767651475</v>
       </c>
       <c r="K10" t="n">
-        <v>1.298114160223867</v>
+        <v>0.2173403320558631</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.284601609526849</v>
+        <v>-0.2173403320558631</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.905431810179587</v>
+        <v>-0.3558225379066019</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7767663967583719</v>
+        <v>-1.32504284681168</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.06678435085728443</v>
+        <v>0.2131569611870179</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1858363880754785</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>-0.5527502127431062</v>
-      </c>
-      <c r="R10" t="n">
-        <v>-0.5455879371555369</v>
-      </c>
-      <c r="S10" t="n">
-        <v>-0.2106437397217683</v>
-      </c>
+        <v>-1.616970741830707</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>OUcd1IPH</t>
+          <t>nVutWTU8</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.3599058830750308</v>
+        <v>-0.3397821287880394</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.160181668940519</v>
+        <v>0.5795703395974802</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.8500966196195393</v>
+        <v>-0.1947815113469151</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.238626179273569</v>
+        <v>-0.9041356527319294</v>
       </c>
       <c r="F11" t="n">
-        <v>1.329099863617686</v>
+        <v>0.9554412675462656</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.820608763272128</v>
+        <v>-1.327754607746592</v>
       </c>
       <c r="H11" t="n">
-        <v>2.787288969631226</v>
+        <v>1.102080668604316</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.46315648929382</v>
+        <v>0.6209786968280659</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.7323622745531668</v>
+        <v>1.154286585411342</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4379887815483052</v>
+        <v>-1.395964487563834</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.02653482393053162</v>
+        <v>1.395964487563834</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.664847419785666</v>
-      </c>
-      <c r="N11" t="n">
-        <v>-2.005490241475471</v>
-      </c>
+        <v>1.505133169113963</v>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="n">
-        <v>2.454297851647062</v>
-      </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="n">
-        <v>1.515489343415745</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.7998718564426567</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.1414003832965</v>
-      </c>
+        <v>-1.129228172736146</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-0.3661425452343264</v>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>rZUMHwAb</t>
+          <t>h8K6HUFF</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.3599058830750308</v>
+        <v>-0.3397821287880394</v>
       </c>
       <c r="C12" t="n">
-        <v>1.760304566654408</v>
+        <v>0.1398882323554535</v>
       </c>
       <c r="D12" t="n">
-        <v>1.73930903955879</v>
+        <v>-0.943785714581994</v>
       </c>
       <c r="E12" t="n">
-        <v>1.03343833099669</v>
+        <v>0.4614997175715492</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5665952055700695</v>
+        <v>-0.02862546144870969</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7675955648010263</v>
+        <v>1.445591414041341</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6562832105058478</v>
+        <v>0.09847401253675316</v>
       </c>
       <c r="I12" t="n">
-        <v>1.266475098573683</v>
+        <v>1.034948346320517</v>
       </c>
       <c r="J12" t="n">
-        <v>1.299304857050933</v>
+        <v>0.2137037365745141</v>
       </c>
       <c r="K12" t="n">
-        <v>1.817677814330868</v>
+        <v>0.4702119556006181</v>
       </c>
       <c r="L12" t="n">
-        <v>1.61976340013395</v>
+        <v>-0.4702119556006181</v>
       </c>
       <c r="M12" t="n">
-        <v>0.3040078643782428</v>
+        <v>0.1712400506073971</v>
       </c>
       <c r="N12" t="n">
-        <v>1.120279008242407</v>
+        <v>-6.568945973140764</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.6599801632112485</v>
-      </c>
-      <c r="P12" t="inlineStr"/>
+        <v>0.2174675785527269</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.6212284790239172</v>
+      </c>
       <c r="Q12" t="n">
-        <v>3.660206965711283</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.184288940327855</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.549937946264976</v>
-      </c>
+        <v>-0.06867142387323254</v>
+      </c>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
+      <c r="U12" t="n">
+        <v>-1.288539626946734</v>
+      </c>
       <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
+      <c r="W12" t="n">
+        <v>-0.1013002184621252</v>
+      </c>
       <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>WhWcJjo3</t>
+          <t>WMcg8Qx2</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.3599058830750308</v>
+        <v>-0.3397821287880394</v>
       </c>
       <c r="C13" t="n">
-        <v>0.02567183772995798</v>
+        <v>-0.6263170035367062</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.2291652022913685</v>
+        <v>0.1048201699471166</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.677986884531557</v>
+        <v>-1.444958296539614</v>
       </c>
       <c r="F13" t="n">
-        <v>1.837436302316097</v>
+        <v>0.519976188739432</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.2860398149792465</v>
+        <v>-0.1363744539958892</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4845792680536274</v>
+        <v>0.6390834504056404</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9219601602939977</v>
+        <v>0.8279635215742916</v>
       </c>
       <c r="J13" t="n">
-        <v>1.054674343095693</v>
+        <v>0.6624407030085832</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9559624855680369</v>
+        <v>-0.6801471557688357</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.3014996428756983</v>
+        <v>0.6801471557688357</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.596040265525258</v>
+        <v>0.7511121375966963</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5025051360021022</v>
+        <v>-8.828314703914325</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.3633822570342667</v>
+        <v>0.7673220186089241</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1858363880754785</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>-1.870614536684635</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.4154547725574584</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.29759965264799</v>
-      </c>
+        <v>0.8604760733634145</v>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>4nvCemgd</t>
+          <t>vPIEF8pS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.3599058830750308</v>
+        <v>-0.3397821287880394</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2734765132905936</v>
+        <v>-0.07310225018955029</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.2710648240687585</v>
+        <v>0.4044218512411479</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.091089522762513</v>
+        <v>-0.5999714111643362</v>
       </c>
       <c r="F14" t="n">
-        <v>0.05825876687165833</v>
+        <v>0.3088468416833905</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.4292759610784082</v>
+        <v>0.2549182797269138</v>
       </c>
       <c r="H14" t="n">
-        <v>1.221272465272898</v>
+        <v>0.7395109804735696</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.9925946061301452</v>
+        <v>-0.4139454269030626</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.9860805424245932</v>
+        <v>0.2404997439987198</v>
       </c>
       <c r="K14" t="n">
-        <v>1.614921266386672</v>
+        <v>-0.1956564220741727</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.8243173310134241</v>
+        <v>0.1956564220741727</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.4085302384620284</v>
+        <v>0.4658847932918856</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.349325897027453</v>
+        <v>1.440019918210428</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.06678435085728462</v>
-      </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="n">
-        <v>-2.321363737948043</v>
-      </c>
-      <c r="R14" t="n">
-        <v>-0.3533793952129379</v>
-      </c>
-      <c r="S14" t="n">
-        <v>-1.376613875158272</v>
-      </c>
+        <v>0.3110623915284815</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-0.6262768343177483</v>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
-      <c r="V14" t="n">
-        <v>-0.007024646658704578</v>
-      </c>
+      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>IHSe3ve5</t>
+          <t>b9aoAn8k</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.3599058830750308</v>
+        <v>-0.3397821287880394</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.09823050005036012</v>
+        <v>-0.174739813789974</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.5307155105377356</v>
+        <v>0.2546210105941322</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.6779868845315573</v>
+        <v>-1.233905557492712</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.466750549223575</v>
+        <v>0.7099805576583906</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.3625133506084603</v>
+        <v>-1.182237710703874</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.06830926963173221</v>
+        <v>0.3309433679901582</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4956058800225147</v>
+        <v>-0.8574843370735463</v>
       </c>
       <c r="J15" t="n">
-        <v>0.728841904964643</v>
+        <v>-0.2484403914689321</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.4633333500413299</v>
+        <v>-1.132017752624897</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3533433535888</v>
+        <v>1.132017752624897</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3040078643782428</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.6164763341286602</v>
-      </c>
+        <v>1.019548358924464</v>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="n">
-        <v>-0.6599801632112483</v>
-      </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="n">
-        <v>1.88189734336607</v>
-      </c>
-      <c r="R15" t="n">
-        <v>-1.122213562983334</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.2357301547206259</v>
-      </c>
+        <v>-0.793329951481209</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.853068771307639</v>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>S2WzL3M7</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>-0.3397821287880394</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1.063240324274931</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.7040235325351795</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.456322612924203</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-0.4030326462002789</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.678773626629031</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-1.199657282960304</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.217718773441807</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-1.03505708000024</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.058098486774651</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-2.058098486774651</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-1.420688202188292</v>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="n">
+        <v>1.449538456104879</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-0.6379693859208064</v>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>OAZJOoNr</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>-0.3397821287880394</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.05271553485954149</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.1947815113469151</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-0.04013850225867744</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.6780734513560417</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-1.658580959497418</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.1956782883064726</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-0.7687765550394495</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.181453338036308</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-0.6964731504340289</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.6964731504340289</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.5373479750062705</v>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="n">
+        <v>-0.3245693333740461</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.642589871375658</v>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>WzwSMPie</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>-0.3397821287880394</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.2666226886237922</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.303226895123243</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.1918326584486375</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.2229995147537821</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.7957297313183426</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.2214069994887351</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-0.3252376448689658</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-0.2843230680773923</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.4938863201209681</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-0.4938863201209681</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-0.6203447609636492</v>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="n">
+        <v>0.2311656651236529</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-0.4952602945604044</v>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>vwbmU7aL</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>-0.3397821287880394</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7284145657034916</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.2546210105941322</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.5196944066469817</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.590677811224187</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.4166503564324059</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.5204850438845247</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-2.572501456399416</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.559789832462471</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-0.7076533750511067</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.7076533750511067</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.7975248711374195</v>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="n">
+        <v>-1.029189457934945</v>
+      </c>
+      <c r="P19" t="n">
+        <v>-0.7031778467840154</v>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_selected.xlsx
@@ -425,13 +425,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z19"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>is_cup</t>
+          <t>dif_mean_last_60_matches_shots_on_goal</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_goals</t>
+          <t>dif_mean_last_360_matches_goal_attempts</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -451,105 +451,60 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_PPS</t>
+          <t>dif_mean_last_360_matches_attacks</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_attacks</t>
+          <t>dif_mean_last_360_matches_ball_possession</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_attacks_against</t>
+          <t>dif_mean_last_360_matches_PPDA</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_dangerous_attacks</t>
+          <t>dif_mean_last_360_matches_clean_sheet</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_dangerous_attacks_against</t>
+          <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_ball_possession</t>
+          <t>dif_mean_value_player_start</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_ball_possession_against</t>
+          <t>dif_mean_wage_player_start</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_total_passes_against</t>
+          <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_PPDA</t>
+          <t>dif_mean_value_player_sub</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_PPDA_against</t>
+          <t>dif_mean_pot_player_start</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_clean_sheet_against</t>
+          <t>dif_mean_rep_player_start</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_start</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_sub</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_value_player_miss</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_sub</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_start</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_start</t>
         </is>
@@ -562,234 +517,216 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.3397821287880394</v>
+        <v>-1.29388645931665</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.679970890664118</v>
+        <v>-0.5642487880166785</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.344582351993931</v>
+        <v>-0.6144918953130225</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.839640803605941</v>
+        <v>-1.762725585504064</v>
       </c>
       <c r="F2" t="n">
-        <v>3.365305027325702</v>
+        <v>-1.498259591293429</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.776687036581007</v>
+        <v>-1.629559952498982</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9903873516197658</v>
+        <v>0.8342632496875461</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.271453986565998</v>
+        <v>-0.9588037966301947</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.04747374755303913</v>
+        <v>-1.161565284724227</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.629329114263644</v>
+        <v>-2.721382394656369</v>
       </c>
       <c r="L2" t="n">
-        <v>1.629329114263645</v>
+        <v>-1.50977081370936</v>
       </c>
       <c r="M2" t="n">
-        <v>1.349029710093369</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
+        <v>-1.142204249223775</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-5.08346743885591</v>
+      </c>
       <c r="O2" t="n">
-        <v>-0.6526279469080508</v>
+        <v>-1.252862560901653</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6999283455829624</v>
-      </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
+        <v>-1.579606915829348</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-0.8907303207558797</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>KdJMr7EE</t>
+          <t>vNHAXt6D</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.3397821287880394</v>
+        <v>0.3413235297949994</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.4950351505528262</v>
+        <v>0.06264463631029198</v>
       </c>
       <c r="D3" t="n">
-        <v>1.602828576417274</v>
+        <v>-0.1417219004067966</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.123982255905785</v>
+        <v>-1.087099914409313</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6660251849161902</v>
+        <v>-0.2358709668662519</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.009942682621856</v>
+        <v>-0.03604886768539108</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1341770386408202</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
+        <v>0.4605332218440122</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.2742522659632866</v>
+      </c>
       <c r="J3" t="n">
-        <v>-0.7487417065549438</v>
+        <v>0.2428082600555154</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.4333981120203173</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.4333981120203173</v>
-      </c>
+        <v>0.1955672788401513</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>0.6415402047801676</v>
-      </c>
-      <c r="N3" t="inlineStr"/>
+        <v>-0.1657059810377514</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.03944784539482284</v>
+      </c>
       <c r="O3" t="n">
-        <v>-0.5454532438658489</v>
+        <v>-0.1584798086754204</v>
       </c>
       <c r="P3" t="n">
-        <v>0.319795498060463</v>
-      </c>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
+        <v>0.6809967731095202</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.8621642162995944</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>vNHAXt6D</t>
+          <t>h2acepbK</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.3397821287880394</v>
+        <v>-0.005539195168077832</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6975869958614518</v>
+        <v>-0.153637660539221</v>
       </c>
       <c r="D4" t="n">
-        <v>1.153426054476227</v>
+        <v>-0.479805828437595</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.8420613177181349</v>
+        <v>-0.09667096196661726</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4520678841537329</v>
+        <v>0.2013955347996922</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.5454176586759988</v>
+        <v>0.01752858728224696</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.07920375845903926</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+        <v>0.4379886361499306</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.08080822093010347</v>
+      </c>
       <c r="J4" t="n">
-        <v>0.003859678434304597</v>
+        <v>0.1778927589913883</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.03633822128081728</v>
+        <v>-0.1350962262436831</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03633822128081728</v>
+        <v>-0.2732269658060174</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0615757506443089</v>
-      </c>
-      <c r="N4" t="inlineStr"/>
+        <v>0.2873831961060264</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-0.1243010427541572</v>
+      </c>
       <c r="O4" t="n">
-        <v>-0.2741189532455608</v>
+        <v>0.1611831477901674</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.1382876934824242</v>
-      </c>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
+        <v>-0.3562596292131639</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-0.5439380591233129</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>h2acepbK</t>
+          <t>KdJMr7EE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.3397821287880394</v>
+        <v>-0.5506091915386274</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4902015260150001</v>
+        <v>0.2205650435337455</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1947815113469151</v>
+        <v>0.3628033460391649</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3683882150508578</v>
+        <v>-0.3511561789136991</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5150468519976255</v>
+        <v>-0.4441511514522613</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1838592587664912</v>
+        <v>-0.4332384184953889</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5071818425664477</v>
+        <v>0.7823408518472393</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7983458157174819</v>
+        <v>0.444938188051389</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1556403657573964</v>
+        <v>0.3267903673849529</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01722174365825877</v>
+        <v>-0.243563009104989</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.01722174365825877</v>
+        <v>-0.2739814511684221</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3168691036781308</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
+        <v>-0.556582014570988</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-0.1542350876269445</v>
+      </c>
       <c r="O5" t="n">
-        <v>-0.6310359170892307</v>
+        <v>-0.1973091793296432</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.08768290911535</v>
-      </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
+        <v>-0.01313310608511</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.1206803240790475</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -798,58 +735,51 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.3397821287880394</v>
+        <v>0.9854971618692854</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2238388669959994</v>
+        <v>-0.3966119392618281</v>
       </c>
       <c r="D6" t="n">
-        <v>1.003625213829211</v>
+        <v>-1.002169577297034</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1775096348834394</v>
+        <v>-0.04714951434448288</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8753220385774039</v>
+        <v>-1.263798060136973</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.230070236657623</v>
+        <v>-0.7045966245028606</v>
       </c>
       <c r="H6" t="n">
-        <v>1.073256431392507</v>
+        <v>0.7132066496642033</v>
       </c>
       <c r="I6" t="n">
-        <v>1.508056517169033</v>
+        <v>0.5416602105679804</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.240610389299521</v>
+        <v>2.949957321849873</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.7046677348209819</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.7046677348209819</v>
-      </c>
+        <v>0.7300047876712112</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>0.9188121804100636</v>
-      </c>
-      <c r="N6" t="inlineStr"/>
+        <v>1.641796135500174</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.86496510987348</v>
+      </c>
       <c r="O6" t="n">
-        <v>-0.5158164219096564</v>
+        <v>1.648947941477622</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.5920986065549629</v>
-      </c>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
+        <v>1.305059905066764</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.297897106497265</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -858,60 +788,53 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.3397821287880394</v>
+        <v>-0.401953737983023</v>
       </c>
       <c r="C7" t="n">
-        <v>1.06191282126738</v>
+        <v>0.5415554364770694</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.542989077170057</v>
+        <v>-0.1538582465412354</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2229014923622768</v>
+        <v>-0.2591632119767472</v>
       </c>
       <c r="F7" t="n">
-        <v>1.590641838765807</v>
+        <v>-0.652888710103732</v>
       </c>
       <c r="G7" t="n">
-        <v>0.06845070893705255</v>
+        <v>-1.340523682278827</v>
       </c>
       <c r="H7" t="n">
-        <v>1.177843656134467</v>
+        <v>1.050870395637057</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7392072943614173</v>
+        <v>0.1789526261307627</v>
       </c>
       <c r="J7" t="n">
-        <v>1.029357962562839</v>
+        <v>-0.0007196668096494676</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.340387198144943</v>
+        <v>0.003342471815688512</v>
       </c>
       <c r="L7" t="n">
-        <v>1.340387198144943</v>
+        <v>0.1024035449275556</v>
       </c>
       <c r="M7" t="n">
-        <v>1.591614228027269</v>
+        <v>-0.4023160830269383</v>
       </c>
       <c r="N7" t="n">
-        <v>1.433864764832862</v>
+        <v>-0.158391088537266</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9865438956689684</v>
+        <v>-0.2508507112348468</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.2450946552411284</v>
-      </c>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
+        <v>-0.4389103509700009</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.2506852288648377</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -920,58 +843,53 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.3397821287880394</v>
+        <v>0.58908261905434</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.426712816890038</v>
+        <v>-0.7059299542799403</v>
       </c>
       <c r="D8" t="n">
-        <v>1.453027735770259</v>
+        <v>-0.4962765839057622</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.10393741855758</v>
+        <v>-0.5299836286602968</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.06899406340457112</v>
+        <v>-0.4223564928183691</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.116236752930676</v>
+        <v>-0.616319947758629</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2655864064218329</v>
+        <v>0.3992382057445497</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3844246114038081</v>
+        <v>-0.7512856492493964</v>
       </c>
       <c r="J8" t="n">
-        <v>0.440599799439218</v>
+        <v>-0.1844306140309046</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6164198754514939</v>
+        <v>0.1948856446637084</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6164198754514939</v>
+        <v>0.03901767368683578</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3339457418728692</v>
-      </c>
-      <c r="N8" t="inlineStr"/>
+        <v>0.307366583917479</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.03148002362732954</v>
+      </c>
       <c r="O8" t="n">
-        <v>-0.6734899235469289</v>
+        <v>0.571731732381017</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7280354407826214</v>
-      </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
+        <v>-0.1028812274617733</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.1644893273175902</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -980,71 +898,52 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.3397821287880394</v>
+        <v>0.3908753476468674</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.341080678439926</v>
+        <v>-1.438886626936622</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1048201699471165</v>
+        <v>-1.447245991725727</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1412747461150337</v>
+        <v>-0.0119632226129656</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3078105789086623</v>
+        <v>0.0385848489959514</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1189523426926395</v>
+        <v>-0.3197268613605612</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03950549114739484</v>
+        <v>0.499057881539711</v>
       </c>
       <c r="I9" t="n">
-        <v>0.857532782252324</v>
+        <v>0.08080822093010356</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0700903420545749</v>
+        <v>-0.6953610013234306</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3199236100307482</v>
+        <v>-0.04321888017593566</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3199236100307482</v>
+        <v>-0.03972918768373378</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5612198653796493</v>
-      </c>
-      <c r="N9" t="inlineStr"/>
+        <v>-0.4451445168848887</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-0.08015243817818496</v>
+      </c>
       <c r="O9" t="n">
-        <v>-0.08309463239486137</v>
+        <v>-0.3480055429069284</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.141648531898696</v>
+        <v>-0.01132326390554637</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.4900257690315215</v>
-      </c>
-      <c r="R9" t="n">
-        <v>-0.05056661293584868</v>
-      </c>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="n">
-        <v>-0.3655774974067835</v>
-      </c>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="n">
-        <v>-0.07602266345567892</v>
-      </c>
-      <c r="X9" t="n">
-        <v>-0.3054759171730904</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>-0.01132326390554637</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>-0.5162609149027396</v>
+        <v>-0.253278721829869</v>
       </c>
     </row>
     <row r="10">
@@ -1054,60 +953,53 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.3397821287880394</v>
+        <v>1.183704433276758</v>
       </c>
       <c r="C10" t="n">
-        <v>1.410669166955106</v>
+        <v>1.274726674904435</v>
       </c>
       <c r="D10" t="n">
-        <v>1.003625213829211</v>
+        <v>0.8982473790657204</v>
       </c>
       <c r="E10" t="n">
-        <v>1.096468436150156</v>
+        <v>0.8911787484124257</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.586426994581646</v>
+        <v>0.3242010747721205</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.08876238327225723</v>
+        <v>0.2177125244871337</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6330866557947976</v>
+        <v>-0.279714212787334</v>
       </c>
       <c r="I10" t="n">
-        <v>1.153225389032646</v>
+        <v>1.097811840038381</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1953703767651475</v>
+        <v>1.537820882298196</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2173403320558631</v>
+        <v>0.7734078608747672</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.2173403320558631</v>
+        <v>0.7854361721947138</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3558225379066019</v>
+        <v>1.664138014248427</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.32504284681168</v>
+        <v>1.185666518488888</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2131569611870179</v>
+        <v>1.619312301678528</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.616970741830707</v>
-      </c>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
+        <v>0.8141420606378983</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.897414924050818</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1116,126 +1008,106 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.3397821287880394</v>
+        <v>-0.1541946487236823</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5795703395974802</v>
+        <v>0.23300985823342</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1947815113469151</v>
+        <v>-0.8408139658334453</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9041356527319294</v>
+        <v>-1.052710020227275</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9554412675462656</v>
+        <v>-1.331200998602019</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.327754607746592</v>
+        <v>-1.396119120484418</v>
       </c>
       <c r="H11" t="n">
-        <v>1.102080668604316</v>
+        <v>1.461503740713551</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6209786968280659</v>
+        <v>1.025270323150938</v>
       </c>
       <c r="J11" t="n">
-        <v>1.154286585411342</v>
+        <v>-1.461922099706225</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.395964487563834</v>
+        <v>-0.6088061889017686</v>
       </c>
       <c r="L11" t="n">
-        <v>1.395964487563834</v>
+        <v>-0.6613374210715158</v>
       </c>
       <c r="M11" t="n">
-        <v>1.505133169113963</v>
-      </c>
-      <c r="N11" t="inlineStr"/>
+        <v>-0.7903340793757727</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-1.010196798540621</v>
+      </c>
       <c r="O11" t="n">
-        <v>-1.129228172736146</v>
+        <v>-0.8321825767609083</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.3661425452343264</v>
-      </c>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
+        <v>0.3640897139124826</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-0.8579315495822822</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>h8K6HUFF</t>
+          <t>vPIEF8pS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.3397821287880394</v>
+        <v>0.7872898904618126</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1398882323554535</v>
+        <v>-0.0570830637314025</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.943785714581994</v>
+        <v>0.009115544406944625</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4614997175715492</v>
+        <v>-0.8054466810584212</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.02862546144870969</v>
+        <v>-0.3001869320873618</v>
       </c>
       <c r="G12" t="n">
-        <v>1.445591414041341</v>
+        <v>-0.1954190939026894</v>
       </c>
       <c r="H12" t="n">
-        <v>0.09847401253675316</v>
+        <v>-0.4066333216328177</v>
       </c>
       <c r="I12" t="n">
-        <v>1.034948346320517</v>
+        <v>0.5109367445921221</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2137037365745141</v>
+        <v>0.5298015725496977</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4702119556006181</v>
-      </c>
-      <c r="L12" t="n">
-        <v>-0.4702119556006181</v>
-      </c>
+        <v>0.153040452171914</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
-        <v>0.1712400506073971</v>
+        <v>1.378182504478566</v>
       </c>
       <c r="N12" t="n">
-        <v>-6.568945973140764</v>
+        <v>0.2464788874205426</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2174675785527269</v>
+        <v>1.276021276821361</v>
       </c>
       <c r="P12" t="n">
-        <v>0.6212284790239172</v>
+        <v>-0.01132326390554637</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.06867142387323254</v>
-      </c>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="n">
-        <v>-1.288539626946734</v>
-      </c>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="n">
-        <v>-0.1013002184621252</v>
-      </c>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
+        <v>-0.02938512764328166</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1244,122 +1116,108 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.3397821287880394</v>
+        <v>0.291771711943131</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.6263170035367062</v>
+        <v>-0.6927985291140774</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1048201699471166</v>
+        <v>-0.1441491696336843</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.444958296539614</v>
+        <v>-1.520412581102992</v>
       </c>
       <c r="F13" t="n">
-        <v>0.519976188739432</v>
+        <v>-0.443999222725058</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1363744539958892</v>
+        <v>-0.680068038245548</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6390834504056404</v>
+        <v>-0.6790439318505634</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8279635215742916</v>
+        <v>-0.8946618238034024</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6624407030085832</v>
+        <v>-0.4504465177147476</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.6801471557688357</v>
+        <v>-0.3253463768016766</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6801471557688357</v>
+        <v>-0.2873148493770893</v>
       </c>
       <c r="M13" t="n">
-        <v>0.7511121375966963</v>
+        <v>-0.7841097120272776</v>
       </c>
       <c r="N13" t="n">
-        <v>-8.828314703914325</v>
+        <v>-0.4990580440502889</v>
       </c>
       <c r="O13" t="n">
-        <v>0.7673220186089241</v>
+        <v>-0.620757501065707</v>
       </c>
       <c r="P13" t="n">
-        <v>0.8604760733634145</v>
-      </c>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
+        <v>0.06459407519394018</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-0.4663596660075135</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>vPIEF8pS</t>
+          <t>h8K6HUFF</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.3397821287880394</v>
+        <v>-1.095679187909177</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.07310225018955029</v>
+        <v>0.551210896157851</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4044218512411479</v>
+        <v>0.697419746602981</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.5999714111643362</v>
+        <v>1.017561609531415</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3088468416833905</v>
+        <v>0.690709756965144</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2549182797269138</v>
+        <v>0.470666723364478</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7395109804735696</v>
+        <v>-0.5601901513631182</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4139454269030626</v>
+        <v>0.4904544339415496</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2404997439987198</v>
+        <v>-0.9393888284555797</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.1956564220741727</v>
+        <v>-0.3362033468987518</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1956564220741727</v>
+        <v>-0.3800979512604522</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4658847932918856</v>
+        <v>-0.8404856160878525</v>
       </c>
       <c r="N14" t="n">
-        <v>1.440019918210428</v>
+        <v>-0.2141951866834052</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3110623915284815</v>
+        <v>-1.521542908594495</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.6262768343177483</v>
-      </c>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
+        <v>-0.2307204587342647</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-1.064245515383397</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1368,58 +1226,51 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.3397821287880394</v>
+        <v>0.1926680762393949</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.174739813789974</v>
+        <v>-0.2177499128196124</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2546210105941322</v>
+        <v>-0.2257516493566736</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.233905557492712</v>
+        <v>-1.030786462686226</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7099805576583906</v>
+        <v>-0.8051749652349274</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.182237710703874</v>
+        <v>-1.132086193630715</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3309433679901582</v>
+        <v>0.6217988839475922</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.8574843370735463</v>
+        <v>-1.997292880492545</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.2484403914689321</v>
+        <v>-2.838549257181801</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.132017752624897</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.132017752624897</v>
-      </c>
+        <v>-0.734908896537856</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
-        <v>1.019548358924464</v>
-      </c>
-      <c r="N15" t="inlineStr"/>
+        <v>-1.497835890333133</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-1.841465495959452</v>
+      </c>
       <c r="O15" t="n">
-        <v>-0.793329951481209</v>
+        <v>-1.093026339807063</v>
       </c>
       <c r="P15" t="n">
-        <v>1.853068771307639</v>
-      </c>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
+        <v>-1.327706432877856</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-1.776669398434817</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -1428,58 +1279,53 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.3397821287880394</v>
+        <v>1.481015340387967</v>
       </c>
       <c r="C16" t="n">
-        <v>1.063240324274931</v>
+        <v>0.8160866935996489</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7040235325351795</v>
+        <v>1.259777673375459</v>
       </c>
       <c r="E16" t="n">
-        <v>1.456322612924203</v>
+        <v>1.138107238611612</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4030326462002789</v>
+        <v>2.087665715823892</v>
       </c>
       <c r="G16" t="n">
-        <v>2.678773626629031</v>
+        <v>2.059071779537828</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.199657282960304</v>
+        <v>-1.053978280385811</v>
       </c>
       <c r="I16" t="n">
-        <v>2.217718773441807</v>
+        <v>0.5874759054442605</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.03505708000024</v>
+        <v>2.02004483084901</v>
       </c>
       <c r="K16" t="n">
-        <v>2.058098486774651</v>
+        <v>3.472160808530099</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.058098486774651</v>
+        <v>2.276208037851773</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.420688202188292</v>
-      </c>
-      <c r="N16" t="inlineStr"/>
+        <v>1.891564988082768</v>
+      </c>
+      <c r="N16" t="n">
+        <v>6.029902751881044</v>
+      </c>
       <c r="O16" t="n">
-        <v>1.449538456104879</v>
+        <v>1.868352536910963</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.6379693859208064</v>
-      </c>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
+        <v>1.449125949775643</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.172261815153196</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1488,58 +1334,53 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.3397821287880394</v>
+        <v>0.192668076239395</v>
       </c>
       <c r="C17" t="n">
-        <v>0.05271553485954149</v>
+        <v>-0.01825795217289069</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1947815113469151</v>
+        <v>-0.4678976091101948</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.04013850225867744</v>
+        <v>-0.2181532631646668</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6780734513560417</v>
+        <v>-0.7439021264915837</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.658580959497418</v>
+        <v>-0.6963993641710085</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1956782883064726</v>
+        <v>0.68723764207664</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7687765550394495</v>
+        <v>-0.6770372731410716</v>
       </c>
       <c r="J17" t="n">
-        <v>1.181453338036308</v>
+        <v>-1.409271207055457</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6964731504340289</v>
+        <v>-0.7195406258586522</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6964731504340289</v>
+        <v>-0.7127616590286271</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5373479750062705</v>
-      </c>
-      <c r="N17" t="inlineStr"/>
+        <v>-0.6569576872598066</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-0.6964124518891784</v>
+      </c>
       <c r="O17" t="n">
-        <v>-0.3245693333740461</v>
+        <v>-1.372769756210096</v>
       </c>
       <c r="P17" t="n">
-        <v>0.642589871375658</v>
-      </c>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
+        <v>-0.2745998977000082</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-1.418653192577649</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1548,58 +1389,53 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.3397821287880394</v>
+        <v>1.67922261179544</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.2666226886237922</v>
+        <v>0.3722291646014643</v>
       </c>
       <c r="D18" t="n">
-        <v>1.303226895123243</v>
+        <v>-0.09892531140640647</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1918326584486375</v>
+        <v>0.1925480481043226</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2229995147537821</v>
+        <v>0.2825273382428873</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7957297313183426</v>
+        <v>0.4943488187582914</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2214069994887351</v>
+        <v>-0.1248321898425265</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3252376448689658</v>
+        <v>1.56691364924385</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2843230680773923</v>
+        <v>-0.6137630463638948</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4938863201209681</v>
+        <v>-0.6629900607018153</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.4938863201209681</v>
+        <v>-0.4550668360480079</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6203447609636492</v>
-      </c>
-      <c r="N18" t="inlineStr"/>
+        <v>-1.241657716169852</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-1.00640228807163</v>
+      </c>
       <c r="O18" t="n">
-        <v>0.2311656651236529</v>
+        <v>-1.275881124393324</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.4952602945604044</v>
-      </c>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
+        <v>-0.5258334300640459</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-0.6084222998805342</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -1608,58 +1444,53 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.3397821287880394</v>
+        <v>-0.7488164629460999</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7284145657034916</v>
+        <v>0.3774126219037787</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2546210105941322</v>
+        <v>0.2587775220296883</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5196944066469817</v>
+        <v>0.2012314963852872</v>
       </c>
       <c r="F19" t="n">
-        <v>1.590677811224187</v>
+        <v>-0.08846739107241658</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4166503564324059</v>
+        <v>-0.7075832396950297</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5204850438845247</v>
+        <v>0.3404585756684158</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.572501456399416</v>
+        <v>0.1448154417131421</v>
       </c>
       <c r="J19" t="n">
-        <v>0.559789832462471</v>
+        <v>-0.8129872782915116</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.7076533750511067</v>
+        <v>0.1392894136619745</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7076533750511067</v>
+        <v>0.4472052060124193</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7975248711374195</v>
-      </c>
-      <c r="N19" t="inlineStr"/>
+        <v>0.8134472776366138</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.1990093079160155</v>
+      </c>
       <c r="O19" t="n">
-        <v>-1.029189457934945</v>
+        <v>0.00267212539827886</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.7031778467840154</v>
-      </c>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
+        <v>-0.006616618937118948</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-0.1522954259273151</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_selected.xlsx
@@ -425,48 +425,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_shots_on_goal</t>
+          <t>dif_mean_last_360_matches_goal_attempts</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_shots_on_goal</t>
+          <t>dif_mean_last_360_matches_goals</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_goal_attempts</t>
+          <t>dif_mean_last_360_matches_points</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_goals</t>
+          <t>dif_mean_last_360_matches_goal_ratio</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_attacks</t>
+          <t>dif_mean_last_360_matches_dangerous_attacks</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_60_matches_ball_possession</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_360_matches_ball_possession</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_360_matches_PPDA</t>
-        </is>
-      </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_clean_sheet</t>
+          <t>dif_mean_last_360_matches_total_passes</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -486,12 +486,12 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_sub</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
@@ -513,272 +513,975 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>nVutWTU8</t>
+          <t>UTsToXQN</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.1541946487236823</v>
+        <v>-1.089104005994074</v>
       </c>
       <c r="C2" t="n">
-        <v>0.23300985823342</v>
+        <v>-2.119044338745529</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.8408139658334453</v>
+        <v>-1.979962415025062</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.052710020227275</v>
+        <v>1.054080412946867</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.331200998602019</v>
+        <v>-1.183285528860827</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.396119120484418</v>
+        <v>-0.6564714590565774</v>
       </c>
       <c r="H2" t="n">
-        <v>1.461503740713551</v>
+        <v>-1.657317338973111</v>
       </c>
       <c r="I2" t="n">
-        <v>1.025270323150938</v>
+        <v>-1.541940539902537</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.461922099706225</v>
+        <v>-1.068585671627444</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.6088061889017686</v>
+        <v>-0.8001539872911598</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.6613374210715158</v>
+        <v>-0.4572391945066741</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.7903340793757727</v>
+        <v>-0.5094268879828273</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.010196798540621</v>
+        <v>-0.9567348314201104</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.8321825767609083</v>
+        <v>-0.7677086706682111</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3640897139124826</v>
+        <v>0.4097641509537051</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.8579315495822822</v>
+        <v>-0.7892909646907847</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>vPIEF8pS</t>
+          <t>Y1lKmgdB</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7872898904618126</v>
+        <v>0.8749413522637783</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.0570830637314025</v>
+        <v>-0.5883840703364156</v>
       </c>
       <c r="D3" t="n">
-        <v>0.009115544406944625</v>
+        <v>-1.047888760187941</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.8054466810584212</v>
+        <v>0.2041862634844467</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3001869320873618</v>
+        <v>1.033202657524469</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.1954190939026894</v>
+        <v>-0.9528050171482207</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4066333216328177</v>
+        <v>-0.1243384133909171</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5109367445921221</v>
+        <v>-0.3717225996320591</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5298015725496977</v>
+        <v>-0.6702640728706372</v>
       </c>
       <c r="K3" t="n">
-        <v>0.153040452171914</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
+        <v>-0.4488601885245642</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.3345956744599414</v>
+      </c>
       <c r="M3" t="n">
-        <v>1.378182504478566</v>
+        <v>-0.2958967051057916</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2464788874205426</v>
+        <v>-0.8805604131422201</v>
       </c>
       <c r="O3" t="n">
-        <v>1.276021276821361</v>
+        <v>-0.7231280416971764</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.01132326390554637</v>
+        <v>-0.6657896516321498</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.02938512764328166</v>
+        <v>-1.472103788600626</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>h8K6HUFF</t>
+          <t>EuWhpKkJ</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-1.095679187909177</v>
+        <v>-0.08929178515082328</v>
       </c>
       <c r="C4" t="n">
-        <v>0.551210896157851</v>
+        <v>0.5649224108178401</v>
       </c>
       <c r="D4" t="n">
-        <v>0.697419746602981</v>
+        <v>1.082565308011193</v>
       </c>
       <c r="E4" t="n">
-        <v>1.017561609531415</v>
+        <v>0.2637945906450659</v>
       </c>
       <c r="F4" t="n">
-        <v>0.690709756965144</v>
+        <v>0.1406205722589951</v>
       </c>
       <c r="G4" t="n">
-        <v>0.470666723364478</v>
+        <v>-0.4918417045612208</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5601901513631182</v>
+        <v>0.304762841104986</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4904544339415496</v>
+        <v>0.2889037020777884</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.9393888284555797</v>
+        <v>-1.661003630797847</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.3362033468987518</v>
+        <v>-0.9911791101728817</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.3800979512604522</v>
-      </c>
-      <c r="M4" t="n">
-        <v>-0.8404856160878525</v>
-      </c>
+        <v>-0.7547387141448741</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>-0.2141951866834052</v>
+        <v>-1.692819827955905</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.521542908594495</v>
+        <v>-2.081418477291888</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2307204587342647</v>
+        <v>-0.7908495291758721</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.064245515383397</v>
+        <v>-1.455733035542072</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>WMcg8Qx2</t>
+          <t>4Md3iycn</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.291771711943131</v>
+        <v>-0.3816199284901388</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.6927985291140774</v>
+        <v>-0.7114034283262028</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1441491696336843</v>
+        <v>-0.9058584889746654</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.520412581102992</v>
+        <v>0.5607658645393837</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.443999222725058</v>
+        <v>0.2639275152827336</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.680068038245548</v>
+        <v>-0.2613600482677215</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6790439318505634</v>
+        <v>-0.236280079356351</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8946618238034024</v>
+        <v>-0.1595426378963365</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.4504465177147476</v>
+        <v>-0.3780587537936612</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.3253463768016766</v>
-      </c>
-      <c r="L5" t="n">
-        <v>-0.2873148493770893</v>
-      </c>
+        <v>-0.223421286671909</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>-0.7841097120272776</v>
+        <v>-0.1417370357195767</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4990580440502889</v>
+        <v>0.3814590297612275</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.620757501065707</v>
+        <v>-0.04816084630145995</v>
       </c>
       <c r="P5" t="n">
-        <v>0.06459407519394018</v>
+        <v>-0.2215856258693287</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.4663596660075135</v>
+        <v>-0.8997061238694745</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>b9aoAn8k</t>
+          <t>vuBo4Eth</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1926680762393949</v>
+        <v>-0.02213126811697107</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.2177499128196124</v>
+        <v>-0.03803431090841986</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2257516493566736</v>
+        <v>0.5219195005903686</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.030786462686226</v>
+        <v>0.8727478669138413</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8051749652349274</v>
+        <v>0.3779572376946718</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.132086193630715</v>
+        <v>-0.6893974099556495</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6217988839475922</v>
+        <v>0.2137918965918375</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.997292880492545</v>
+        <v>0.1655782564498114</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.838549257181801</v>
+        <v>-0.6492546164461913</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.734908896537856</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
+        <v>-0.2116020972123646</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-0.2081936083390243</v>
+      </c>
       <c r="M6" t="n">
-        <v>-1.497835890333133</v>
+        <v>-0.301106616747537</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.841465495959452</v>
+        <v>-0.7489636071862401</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.093026339807063</v>
+        <v>-0.9331287283426219</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.327706432877856</v>
+        <v>-0.4144601452423908</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.776669398434817</v>
+        <v>-0.1769060157715691</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>n5Eg2hB4</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.4381581325543281</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.3352862759035707</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.813496849768266</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.357578704672834</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.8091143970631965</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.06380434287329315</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.4024629266998628</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.4734535241602817</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-0.5180763954717099</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-0.659927723724715</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-0.4660113210531162</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-0.5536849897265729</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-1.008664547413082</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-0.98357268328236</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-0.3747815308582382</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-0.6828353031950062</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>rX720WuH</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.5433678598024729</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.4951170185374512</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.601344323308319</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.3848737850720292</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.250719339467145</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-0.2942859991667932</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.8876061204998762</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.9513170810054635</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.266585410099734</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.651747893514101</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.648141638865388</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.684562038779547</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.924308986029744</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.393250603600472</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.507909773406535</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.8954974136261342</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>bqYbtBlo</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.603101164269612</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.6936071339782097</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.5021935076316714</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0.884945125711188</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1875531303090652</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.3806959942641707</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.05976488207139166</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.08695142355816238</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-0.8869824316378117</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-0.00245949352663638</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>-0.9369561756496314</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-0.2243688266550934</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.4381689846953519</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-0.6030456099693067</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.2035568440527765</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>0ljCkFRb</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.218539354588758</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.1827935300620635</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.253463599803697</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0.7918011211836632</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.008331616252221603</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.109308416465419</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.8522561207213173</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.3071202497330769</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.202890826403577</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.100322227779814</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.021580789735214</v>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="n">
+        <v>2.206276820505477</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.820914585087503</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.6378194136649263</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.202012642351314</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>AsQgyP6l</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>-0.7507345088329139</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-1.874826632999356</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-1.471643549630181</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.033284429728883</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-0.6269860051245043</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.5247676554602924</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-1.766589696206862</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-2.04044483317947</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-1.133046289567404</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-3.402417605601842</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-1.414284710009279</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-2.461122026001213</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-1.077262254503851</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-1.183409545188885</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-1.488559307598337</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-0.8807330454127904</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>h2acepbK</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>-0.6109850871102163</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.2193259963670536</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.1957071329082872</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.009800496737416892</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.1255322082784411</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.1008254116220643</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.01625680487256738</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-0.02358782855846227</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.1372462828890724</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-0.1695909090626171</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-0.2625805324535515</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-0.258994474578882</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.2755311555540689</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.1448457167102834</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-0.3395012770987078</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-0.5413787754566416</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>KdJMr7EE</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.263300929276904</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.4721991211238389</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-1.208659136630746</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.5660493154974203</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.2858524575199713</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.870490139900542</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.4952792116738851</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-0.4454908876610637</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.3090028609170081</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-0.3019550975135488</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-0.266264141037631</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.3766384538013625</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-0.5417874700315402</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-0.1887981374870764</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0.01750063558862808</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.1091665210264807</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>vNHAXt6D</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>-0.3857175195591681</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-1.466605598207953</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-1.300387020122653</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.662399930309539</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.1423454511811978</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.03497350982392103</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.1662629262189674</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-0.3157925603453741</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.2325585089029517</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.2437345070734987</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="n">
+        <v>0.1194017023107173</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-0.1554283953663032</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-0.1554232218040645</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.6347664650342542</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.8345654538450723</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>WdE2Z2y1</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>-1.152986450172703</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.1701182531711391</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.3440078977021602</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.119453041540151</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.5412064762332385</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.3313070679155636</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.7836469477346508</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-0.6966730516108254</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.861454432719523</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.9117749842962335</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="n">
+        <v>1.558800801661705</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.542347511409603</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.220932602123338</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.260952756009219</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>vaZNtoqR</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>-0.09688731981536636</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.3705372905628339</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.1523089944820085</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.096515268335277</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-0.4882573513985071</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-0.8375641890014703</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-1.377516785968514</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-1.261327095480674</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-0.004246653601562149</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.003455803395791651</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.08727784835743263</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-0.01402990383184144</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-0.3787930551242762</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-0.2421899625231038</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-0.4171329329664175</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.2362014523025413</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>hQspntL6</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>-0.6280750401054379</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.6498937493313093</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.4620138914331788</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.8447771676272915</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-0.1820861284423223</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.870490139900542</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.6898368293887136</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-0.3331710304088537</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-0.1828861274006979</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.2428824725269</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.02824090209003846</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-0.09047440413878563</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.2911615499644572</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.5304862334178647</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-0.1015095878434702</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.1518542782765817</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>p0vxl2jf</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>-1.61479495777691</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.1351548566898307</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.2004825710024291</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.45729950854992</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-0.3661434322484087</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.5617887242090636</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.3746524164525119</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-0.5479871674267475</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-0.6707418532681887</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-0.05564288079151049</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-0.04507283443975256</v>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="n">
+        <v>-0.4317430079142955</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-0.3378279083861607</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-0.01551159329894776</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-0.2695064684518005</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>lYpTkOLs</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.8188743134899813</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7622659642597908</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.6189942839123077</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.04211622760254817</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.1407498860355079</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.3642330188146352</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.1964752499889473</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.1533862229118311</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.491821372111932</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.9660283053238979</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.7234473878074728</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.7708117649154913</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.571980865612529</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.514509872031375</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.7598263425779767</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.847612130540327</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_selected.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,975 +513,488 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>UTsToXQN</t>
+          <t>AsQgyP6l</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-1.089104005994074</v>
+        <v>-0.7507345088329139</v>
       </c>
       <c r="C2" t="n">
-        <v>-2.119044338745529</v>
+        <v>-1.874826632999356</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.979962415025062</v>
+        <v>-1.471643549630181</v>
       </c>
       <c r="E2" t="n">
-        <v>1.054080412946867</v>
+        <v>1.033284429728883</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.183285528860827</v>
+        <v>-0.6269860051245043</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.6564714590565774</v>
+        <v>-0.5247676554602924</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.657317338973111</v>
+        <v>-1.766589696206862</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.541940539902537</v>
+        <v>-2.04044483317947</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.068585671627444</v>
+        <v>-1.133046289567404</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.8001539872911598</v>
+        <v>-3.402417605601842</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.4572391945066741</v>
+        <v>-1.414284710009279</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.5094268879828273</v>
+        <v>-2.461122026001213</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.9567348314201104</v>
+        <v>-1.077262254503851</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.7677086706682111</v>
+        <v>-1.183409545188885</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4097641509537051</v>
+        <v>-1.488559307598337</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.7892909646907847</v>
+        <v>-0.8807330454127904</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Y1lKmgdB</t>
+          <t>h2acepbK</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8749413522637783</v>
+        <v>-0.6109850871102163</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.5883840703364156</v>
+        <v>-0.2193259963670536</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.047888760187941</v>
+        <v>-0.1957071329082872</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2041862634844467</v>
+        <v>0.009800496737416892</v>
       </c>
       <c r="F3" t="n">
-        <v>1.033202657524469</v>
+        <v>-0.1255322082784411</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.9528050171482207</v>
+        <v>0.1008254116220643</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1243384133909171</v>
+        <v>-0.01625680487256738</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3717225996320591</v>
+        <v>-0.02358782855846227</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.6702640728706372</v>
+        <v>0.1079602946888284</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.4488601885245642</v>
+        <v>-0.1757556294550804</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.3345956744599414</v>
+        <v>-0.2774299132742701</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2958967051057916</v>
+        <v>-0.2687746093738468</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8805604131422201</v>
+        <v>0.2950057651617009</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.7231280416971764</v>
+        <v>0.14513221617239</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.6657896516321498</v>
+        <v>-0.3448620560676817</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.472103788600626</v>
+        <v>-0.5502758859252697</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>EuWhpKkJ</t>
+          <t>vNHAXt6D</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.08929178515082328</v>
+        <v>-0.3857175195591681</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5649224108178401</v>
+        <v>-1.466605598207953</v>
       </c>
       <c r="D4" t="n">
-        <v>1.082565308011193</v>
+        <v>-1.300387020122653</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2637945906450659</v>
+        <v>1.662399930309539</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1406205722589951</v>
+        <v>0.1423454511811978</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.4918417045612208</v>
+        <v>0.03497350982392103</v>
       </c>
       <c r="H4" t="n">
-        <v>0.304762841104986</v>
+        <v>-0.1662629262189674</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2889037020777884</v>
+        <v>-0.3157925603453741</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.661003630797847</v>
+        <v>0.2380145599279786</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.9911791101728817</v>
-      </c>
-      <c r="L4" t="n">
-        <v>-0.7547387141448741</v>
-      </c>
-      <c r="M4" t="inlineStr"/>
+        <v>0.2425313773642625</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>0.1194017023107173</v>
+      </c>
       <c r="N4" t="n">
-        <v>-1.692819827955905</v>
+        <v>-0.1393292321987324</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.081418477291888</v>
+        <v>-0.1701193348583589</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.7908495291758721</v>
+        <v>0.6459606100133861</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.455733035542072</v>
+        <v>0.8411045321330348</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>4Md3iycn</t>
+          <t>KdJMr7EE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.3816199284901388</v>
+        <v>0.263300929276904</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.7114034283262028</v>
+        <v>-0.4721991211238389</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.9058584889746654</v>
+        <v>-1.208659136630746</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5607658645393837</v>
+        <v>0.5660493154974203</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2639275152827336</v>
+        <v>0.2858524575199713</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2613600482677215</v>
+        <v>-0.870490139900542</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.236280079356351</v>
+        <v>-0.4952792116738851</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1595426378963365</v>
+        <v>-0.4454908876610637</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.3780587537936612</v>
+        <v>0.3122000286408453</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.223421286671909</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
+        <v>-0.2981132819214219</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-0.2506514296572501</v>
+      </c>
       <c r="M5" t="n">
-        <v>-0.1417370357195767</v>
+        <v>0.408538249394976</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3814590297612275</v>
+        <v>-0.5223794580892224</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.04816084630145995</v>
+        <v>-0.1917464665577576</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2215856258693287</v>
+        <v>-0.00528884106593901</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.8997061238694745</v>
+        <v>0.1300664428846242</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>vuBo4Eth</t>
+          <t>WdE2Z2y1</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.02213126811697107</v>
+        <v>-1.152986450172703</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.03803431090841986</v>
+        <v>-0.1701182531711391</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5219195005903686</v>
+        <v>0.3440078977021602</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8727478669138413</v>
+        <v>2.119453041540151</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3779572376946718</v>
+        <v>-0.5412064762332385</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.6893974099556495</v>
+        <v>0.3313070679155636</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2137918965918375</v>
+        <v>-0.7836469477346508</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1655782564498114</v>
+        <v>-0.6966730516108254</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6492546164461913</v>
+        <v>2.869405344527601</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.2116020972123646</v>
-      </c>
-      <c r="L6" t="n">
-        <v>-0.2081936083390243</v>
-      </c>
-      <c r="M6" t="n">
-        <v>-0.301106616747537</v>
-      </c>
+        <v>0.9115658298785337</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>-0.7489636071862401</v>
+        <v>1.56494749386429</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9331287283426219</v>
+        <v>1.539129526317081</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4144601452423908</v>
+        <v>1.220932602123338</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1769060157715691</v>
+        <v>1.263056045588113</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>n5Eg2hB4</t>
+          <t>vaZNtoqR</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4381581325543281</v>
+        <v>-0.09688731981536636</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3352862759035707</v>
+        <v>-0.3705372905628339</v>
       </c>
       <c r="D7" t="n">
-        <v>0.813496849768266</v>
+        <v>-0.1523089944820085</v>
       </c>
       <c r="E7" t="n">
-        <v>0.357578704672834</v>
+        <v>1.096515268335277</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8091143970631965</v>
+        <v>-0.4882573513985071</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.06380434287329315</v>
+        <v>-0.8375641890014703</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4024629266998628</v>
+        <v>-1.377516785968514</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4734535241602817</v>
+        <v>-1.261327095480674</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5180763954717099</v>
+        <v>0.02480275227016124</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.659927723724715</v>
+        <v>-0.005681951667185078</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.4660113210531162</v>
+        <v>0.08609448527953208</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5536849897265729</v>
+        <v>0.005065118779700396</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.008664547413082</v>
+        <v>-0.3669991980679015</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.98357268328236</v>
+        <v>-0.2447634177198886</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3747815308582382</v>
+        <v>-0.4241108369405399</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.6828353031950062</v>
+        <v>0.2300076376349349</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>rX720WuH</t>
+          <t>hQspntL6</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5433678598024729</v>
+        <v>-0.6280750401054379</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4951170185374512</v>
+        <v>-0.6498937493313093</v>
       </c>
       <c r="D8" t="n">
-        <v>0.601344323308319</v>
+        <v>-0.4620138914331788</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3848737850720292</v>
+        <v>0.8447771676272915</v>
       </c>
       <c r="F8" t="n">
-        <v>1.250719339467145</v>
+        <v>-0.1820861284423223</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2942859991667932</v>
+        <v>-0.870490139900542</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8876061204998762</v>
+        <v>-0.6898368293887136</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9513170810054635</v>
+        <v>-0.3331710304088537</v>
       </c>
       <c r="J8" t="n">
-        <v>1.266585410099734</v>
+        <v>-0.1915864428418993</v>
       </c>
       <c r="K8" t="n">
-        <v>3.651747893514101</v>
+        <v>0.2433688443626213</v>
       </c>
       <c r="L8" t="n">
-        <v>1.648141638865388</v>
+        <v>0.02855155430301946</v>
       </c>
       <c r="M8" t="n">
-        <v>2.684562038779547</v>
+        <v>-0.09279282648450032</v>
       </c>
       <c r="N8" t="n">
-        <v>1.924308986029744</v>
+        <v>0.2910440825345039</v>
       </c>
       <c r="O8" t="n">
-        <v>1.393250603600472</v>
+        <v>0.5316318495603307</v>
       </c>
       <c r="P8" t="n">
-        <v>1.507909773406535</v>
+        <v>-0.1012254389449448</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.8954974136261342</v>
+        <v>0.1548839813201179</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bqYbtBlo</t>
+          <t>p0vxl2jf</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.603101164269612</v>
+        <v>-1.61479495777691</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6936071339782097</v>
+        <v>-0.1351548566898307</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5021935076316714</v>
+        <v>0.2004825710024291</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.884945125711188</v>
+        <v>1.45729950854992</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1875531303090652</v>
+        <v>-0.3661434322484087</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3806959942641707</v>
+        <v>0.5617887242090636</v>
       </c>
       <c r="H9" t="n">
-        <v>0.05976488207139166</v>
+        <v>-0.3746524164525119</v>
       </c>
       <c r="I9" t="n">
-        <v>0.08695142355816238</v>
+        <v>-0.5479871674267475</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.8869824316378117</v>
+        <v>-0.6885914638417949</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.00245949352663638</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="n">
-        <v>-0.9369561756496314</v>
-      </c>
+        <v>-0.0565998893170734</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-0.04614421298215181</v>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>-0.2243688266550934</v>
+        <v>-0.441503343952501</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4381689846953519</v>
+        <v>-0.3426781922940413</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6030456099693067</v>
+        <v>-0.01551159329894776</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.2035568440527765</v>
+        <v>-0.2788846655153502</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>0ljCkFRb</t>
+          <t>lYpTkOLs</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.218539354588758</v>
+        <v>0.8188743134899813</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1827935300620635</v>
+        <v>0.7622659642597908</v>
       </c>
       <c r="D10" t="n">
-        <v>0.253463599803697</v>
+        <v>0.6189942839123077</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7918011211836632</v>
+        <v>0.04211622760254817</v>
       </c>
       <c r="F10" t="n">
-        <v>0.008331616252221603</v>
+        <v>0.1407498860355079</v>
       </c>
       <c r="G10" t="n">
-        <v>2.109308416465419</v>
+        <v>0.3642330188146352</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8522561207213173</v>
+        <v>0.1964752499889473</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3071202497330769</v>
+        <v>0.1533862229118311</v>
       </c>
       <c r="J10" t="n">
-        <v>1.202890826403577</v>
+        <v>1.480210611744344</v>
       </c>
       <c r="K10" t="n">
-        <v>1.100322227779814</v>
+        <v>0.9648512641107475</v>
       </c>
       <c r="L10" t="n">
-        <v>1.021580789735214</v>
-      </c>
-      <c r="M10" t="inlineStr"/>
+        <v>0.7234473878074728</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.7595428153851388</v>
+      </c>
       <c r="N10" t="n">
-        <v>2.206276820505477</v>
+        <v>1.58090285862383</v>
       </c>
       <c r="O10" t="n">
-        <v>1.820914585087503</v>
+        <v>1.507509788740819</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6378194136649263</v>
+        <v>0.7581381289778182</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.202012642351314</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>AsQgyP6l</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>-0.7507345088329139</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-1.874826632999356</v>
-      </c>
-      <c r="D11" t="n">
-        <v>-1.471643549630181</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1.033284429728883</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-0.6269860051245043</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-0.5247676554602924</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-1.766589696206862</v>
-      </c>
-      <c r="I11" t="n">
-        <v>-2.04044483317947</v>
-      </c>
-      <c r="J11" t="n">
-        <v>-1.133046289567404</v>
-      </c>
-      <c r="K11" t="n">
-        <v>-3.402417605601842</v>
-      </c>
-      <c r="L11" t="n">
-        <v>-1.414284710009279</v>
-      </c>
-      <c r="M11" t="n">
-        <v>-2.461122026001213</v>
-      </c>
-      <c r="N11" t="n">
-        <v>-1.077262254503851</v>
-      </c>
-      <c r="O11" t="n">
-        <v>-1.183409545188885</v>
-      </c>
-      <c r="P11" t="n">
-        <v>-1.488559307598337</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>-0.8807330454127904</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>h2acepbK</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>-0.6109850871102163</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-0.2193259963670536</v>
-      </c>
-      <c r="D12" t="n">
-        <v>-0.1957071329082872</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.009800496737416892</v>
-      </c>
-      <c r="F12" t="n">
-        <v>-0.1255322082784411</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.1008254116220643</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-0.01625680487256738</v>
-      </c>
-      <c r="I12" t="n">
-        <v>-0.02358782855846227</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.1372462828890724</v>
-      </c>
-      <c r="K12" t="n">
-        <v>-0.1695909090626171</v>
-      </c>
-      <c r="L12" t="n">
-        <v>-0.2625805324535515</v>
-      </c>
-      <c r="M12" t="n">
-        <v>-0.258994474578882</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.2755311555540689</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.1448457167102834</v>
-      </c>
-      <c r="P12" t="n">
-        <v>-0.3395012770987078</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>-0.5413787754566416</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>KdJMr7EE</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0.263300929276904</v>
-      </c>
-      <c r="C13" t="n">
-        <v>-0.4721991211238389</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-1.208659136630746</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.5660493154974203</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.2858524575199713</v>
-      </c>
-      <c r="G13" t="n">
-        <v>-0.870490139900542</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-0.4952792116738851</v>
-      </c>
-      <c r="I13" t="n">
-        <v>-0.4454908876610637</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.3090028609170081</v>
-      </c>
-      <c r="K13" t="n">
-        <v>-0.3019550975135488</v>
-      </c>
-      <c r="L13" t="n">
-        <v>-0.266264141037631</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.3766384538013625</v>
-      </c>
-      <c r="N13" t="n">
-        <v>-0.5417874700315402</v>
-      </c>
-      <c r="O13" t="n">
-        <v>-0.1887981374870764</v>
-      </c>
-      <c r="P13" t="n">
-        <v>-0.01750063558862808</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0.1091665210264807</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>vNHAXt6D</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>-0.3857175195591681</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-1.466605598207953</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-1.300387020122653</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1.662399930309539</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.1423454511811978</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.03497350982392103</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-0.1662629262189674</v>
-      </c>
-      <c r="I14" t="n">
-        <v>-0.3157925603453741</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.2325585089029517</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.2437345070734987</v>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="n">
-        <v>0.1194017023107173</v>
-      </c>
-      <c r="N14" t="n">
-        <v>-0.1554283953663032</v>
-      </c>
-      <c r="O14" t="n">
-        <v>-0.1554232218040645</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0.6347664650342542</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.8345654538450723</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>WdE2Z2y1</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>-1.152986450172703</v>
-      </c>
-      <c r="C15" t="n">
-        <v>-0.1701182531711391</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.3440078977021602</v>
-      </c>
-      <c r="E15" t="n">
-        <v>2.119453041540151</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-0.5412064762332385</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.3313070679155636</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-0.7836469477346508</v>
-      </c>
-      <c r="I15" t="n">
-        <v>-0.6966730516108254</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2.861454432719523</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.9117749842962335</v>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="n">
-        <v>1.558800801661705</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.542347511409603</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.220932602123338</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.260952756009219</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>vaZNtoqR</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>-0.09688731981536636</v>
-      </c>
-      <c r="C16" t="n">
-        <v>-0.3705372905628339</v>
-      </c>
-      <c r="D16" t="n">
-        <v>-0.1523089944820085</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1.096515268335277</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-0.4882573513985071</v>
-      </c>
-      <c r="G16" t="n">
-        <v>-0.8375641890014703</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-1.377516785968514</v>
-      </c>
-      <c r="I16" t="n">
-        <v>-1.261327095480674</v>
-      </c>
-      <c r="J16" t="n">
-        <v>-0.004246653601562149</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.003455803395791651</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.08727784835743263</v>
-      </c>
-      <c r="M16" t="n">
-        <v>-0.01402990383184144</v>
-      </c>
-      <c r="N16" t="n">
-        <v>-0.3787930551242762</v>
-      </c>
-      <c r="O16" t="n">
-        <v>-0.2421899625231038</v>
-      </c>
-      <c r="P16" t="n">
-        <v>-0.4171329329664175</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.2362014523025413</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>hQspntL6</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>-0.6280750401054379</v>
-      </c>
-      <c r="C17" t="n">
-        <v>-0.6498937493313093</v>
-      </c>
-      <c r="D17" t="n">
-        <v>-0.4620138914331788</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.8447771676272915</v>
-      </c>
-      <c r="F17" t="n">
-        <v>-0.1820861284423223</v>
-      </c>
-      <c r="G17" t="n">
-        <v>-0.870490139900542</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-0.6898368293887136</v>
-      </c>
-      <c r="I17" t="n">
-        <v>-0.3331710304088537</v>
-      </c>
-      <c r="J17" t="n">
-        <v>-0.1828861274006979</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.2428824725269</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.02824090209003846</v>
-      </c>
-      <c r="M17" t="n">
-        <v>-0.09047440413878563</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.2911615499644572</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.5304862334178647</v>
-      </c>
-      <c r="P17" t="n">
-        <v>-0.1015095878434702</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.1518542782765817</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>p0vxl2jf</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>-1.61479495777691</v>
-      </c>
-      <c r="C18" t="n">
-        <v>-0.1351548566898307</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.2004825710024291</v>
-      </c>
-      <c r="E18" t="n">
-        <v>1.45729950854992</v>
-      </c>
-      <c r="F18" t="n">
-        <v>-0.3661434322484087</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.5617887242090636</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-0.3746524164525119</v>
-      </c>
-      <c r="I18" t="n">
-        <v>-0.5479871674267475</v>
-      </c>
-      <c r="J18" t="n">
-        <v>-0.6707418532681887</v>
-      </c>
-      <c r="K18" t="n">
-        <v>-0.05564288079151049</v>
-      </c>
-      <c r="L18" t="n">
-        <v>-0.04507283443975256</v>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="n">
-        <v>-0.4317430079142955</v>
-      </c>
-      <c r="O18" t="n">
-        <v>-0.3378279083861607</v>
-      </c>
-      <c r="P18" t="n">
-        <v>-0.01551159329894776</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>-0.2695064684518005</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>lYpTkOLs</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>0.8188743134899813</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.7622659642597908</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.6189942839123077</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.04211622760254817</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.1407498860355079</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.3642330188146352</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.1964752499889473</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.1533862229118311</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1.491821372111932</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.9660283053238979</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.7234473878074728</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.7708117649154913</v>
-      </c>
-      <c r="N19" t="n">
-        <v>1.571980865612529</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.514509872031375</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0.7598263425779767</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1.847612130540327</v>
+        <v>1.849485369928158</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_selected.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,488 +513,975 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AsQgyP6l</t>
+          <t>b59ZhlYj</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.7507345088329139</v>
+        <v>-1.494145886105382</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.874826632999356</v>
+        <v>0.05277339939719972</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.471643549630181</v>
+        <v>0.3567158693370323</v>
       </c>
       <c r="E2" t="n">
-        <v>1.033284429728883</v>
+        <v>2.553549223492907</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6269860051245043</v>
+        <v>-0.8157340618883102</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.5247676554602924</v>
+        <v>1.41786344758492</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.766589696206862</v>
+        <v>-0.40887825914999</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.04044483317947</v>
+        <v>-0.5307943825439924</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.133046289567404</v>
+        <v>2.182674188153003</v>
       </c>
       <c r="K2" t="n">
-        <v>-3.402417605601842</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-1.414284710009279</v>
-      </c>
+        <v>0.8643699789188671</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>-2.461122026001213</v>
+        <v>1.715249234299654</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.077262254503851</v>
+        <v>1.214497137172322</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.183409545188885</v>
+        <v>1.03275254840236</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.488559307598337</v>
+        <v>1.220932602123338</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.8807330454127904</v>
+        <v>0.8557618500321539</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>h2acepbK</t>
+          <t>nRkUEVfA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.6109850871102163</v>
+        <v>-0.9141068849728293</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.2193259963670536</v>
+        <v>-0.8690219807506178</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1957071329082872</v>
+        <v>-0.7874999296302688</v>
       </c>
       <c r="E3" t="n">
-        <v>0.009800496737416892</v>
+        <v>1.5737572027343</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1255322082784411</v>
+        <v>-0.2740152279901214</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1008254116220643</v>
+        <v>-1.940583544120362</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.01625680487256738</v>
+        <v>-0.8986659372759538</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.02358782855846227</v>
+        <v>-0.9892394537870582</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1079602946888284</v>
+        <v>-0.7673994594561081</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.1757556294550804</v>
+        <v>-0.4121842807692509</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.2774299132742701</v>
+        <v>-0.341911498832105</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2687746093738468</v>
+        <v>-0.2977463543715418</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2950057651617009</v>
+        <v>-0.6644233727811136</v>
       </c>
       <c r="O3" t="n">
-        <v>0.14513221617239</v>
+        <v>-0.8977962524670838</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.3448620560676817</v>
+        <v>-0.2215856258693287</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.5502758859252697</v>
+        <v>-1.489825122073882</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>vNHAXt6D</t>
+          <t>WWnG5RHd</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.3857175195591681</v>
+        <v>0.1715548658288728</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.466605598207953</v>
+        <v>-0.1116840581259897</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.300387020122653</v>
+        <v>-0.3022298363182437</v>
       </c>
       <c r="E4" t="n">
-        <v>1.662399930309539</v>
+        <v>0.8708301420648954</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1423454511811978</v>
+        <v>-0.03901712037883563</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03497350982392103</v>
+        <v>0.08436243617252812</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1662629262189674</v>
+        <v>0.08892976056047015</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3157925603453741</v>
+        <v>0.142298323344011</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2380145599279786</v>
+        <v>1.089658972692287</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2425313773642625</v>
+        <v>0.774397310817702</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>0.1194017023107173</v>
+        <v>0.6035334967331737</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1393292321987324</v>
+        <v>0.5478551809739014</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1701193348583589</v>
+        <v>0.6490794358106857</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6459606100133861</v>
+        <v>0.7581381289778182</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.8411045321330348</v>
+        <v>1.262229914180223</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>KdJMr7EE</t>
+          <t>QB1LGiQc</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.263300929276904</v>
+        <v>-0.5746064737168792</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.4721991211238389</v>
+        <v>-1.763902380016605</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.208659136630746</v>
+        <v>-1.71858726313952</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5660493154974203</v>
+        <v>1.317242776260429</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2858524575199713</v>
+        <v>-0.01916119856581175</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.870490139900542</v>
+        <v>-0.2613600482677215</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4952792116738851</v>
+        <v>-0.6877459649382098</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4454908876610637</v>
+        <v>-0.7517966075006308</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3122000286408453</v>
+        <v>-0.2869951620556818</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.2981132819214219</v>
+        <v>0.281142368462486</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.2506514296572501</v>
+        <v>0.02876962369808287</v>
       </c>
       <c r="M5" t="n">
-        <v>0.408538249394976</v>
+        <v>-0.09464247575025052</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5223794580892224</v>
+        <v>0.5116177067110346</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1917464665577576</v>
+        <v>0.3436860146384036</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.00528884106593901</v>
+        <v>0.3681654130209227</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1300664428846242</v>
+        <v>0.1454326034677159</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WdE2Z2y1</t>
+          <t>l8H0Dwy3</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1.152986450172703</v>
+        <v>-0.4672695759574186</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.1701182531711391</v>
+        <v>0.1014640656132596</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3440078977021602</v>
+        <v>-0.1355415319082189</v>
       </c>
       <c r="E6" t="n">
-        <v>2.119453041540151</v>
+        <v>0.9649445394627079</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5412064762332385</v>
+        <v>-0.5378589714660428</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3313070679155636</v>
+        <v>-1.545472133331506</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7836469477346508</v>
+        <v>-1.273616906351171</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6966730516108254</v>
+        <v>-1.1037532491048</v>
       </c>
       <c r="J6" t="n">
-        <v>2.869405344527601</v>
+        <v>-0.4387012164251973</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9115658298785337</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+        <v>-0.1280680207290674</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.1477002956929472</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.07641052251886059</v>
+      </c>
       <c r="N6" t="n">
-        <v>1.56494749386429</v>
+        <v>0.2224209599728264</v>
       </c>
       <c r="O6" t="n">
-        <v>1.539129526317081</v>
+        <v>-0.1794266531830861</v>
       </c>
       <c r="P6" t="n">
-        <v>1.220932602123338</v>
+        <v>-0.01676052682967693</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.263056045588113</v>
+        <v>-0.02935623008596802</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vaZNtoqR</t>
+          <t>dYK8BH5F</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.09688731981536636</v>
+        <v>-2.222269408842512</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.3705372905628339</v>
+        <v>-2.666763750058612</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1523089944820085</v>
+        <v>-1.959872606925816</v>
       </c>
       <c r="E7" t="n">
-        <v>1.096515268335277</v>
+        <v>1.868178949662952</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4882573513985071</v>
+        <v>-0.6320354995267445</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.8375641890014703</v>
+        <v>-2.82958421839529</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.377516785968514</v>
+        <v>-2.45903829100711</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.261327095480674</v>
+        <v>-2.48662137967578</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02480275227016124</v>
+        <v>-3.318955279715238</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.005681951667185078</v>
+        <v>-4.60709406644122</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08609448527953208</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.005065118779700396</v>
-      </c>
+        <v>-2.365203359987869</v>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>-0.3669991980679015</v>
+        <v>-2.960363101851597</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2447634177198886</v>
+        <v>-3.020031170003769</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.4241108369405399</v>
+        <v>-1.786221799088887</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2300076376349349</v>
+        <v>-2.581283759360275</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hQspntL6</t>
+          <t>bJl87mmp</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.6280750401054379</v>
+        <v>0.4162110350236226</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.6498937493313093</v>
+        <v>-0.2077929315555111</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4620138914331788</v>
+        <v>-0.3199836202199033</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8447771676272915</v>
+        <v>-0.2190046004076241</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1820861284423223</v>
+        <v>0.9212676257653331</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.870490139900542</v>
+        <v>0.7264184787044203</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6898368293887136</v>
+        <v>0.9420024563660192</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3331710304088537</v>
+        <v>0.7210042033069118</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1915864428418993</v>
+        <v>0.8773392577975514</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2433688443626213</v>
+        <v>0.5132252900695891</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02855155430301946</v>
+        <v>0.1872134253033116</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.09279282648450032</v>
+        <v>0.2595521475069723</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2910440825345039</v>
+        <v>0.1433290034381357</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5316318495603307</v>
+        <v>0.5029364957676546</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1012254389449448</v>
+        <v>-0.4989939838729616</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1548839813201179</v>
+        <v>0.6738577128512974</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>p0vxl2jf</t>
+          <t>figxD9PM</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-1.61479495777691</v>
+        <v>-0.3107615853696001</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.1351548566898307</v>
+        <v>-1.152222794456274</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2004825710024291</v>
+        <v>-1.260934167007854</v>
       </c>
       <c r="E9" t="n">
-        <v>1.45729950854992</v>
+        <v>0.6076175639302568</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3661434322484087</v>
+        <v>-0.4373765517526328</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5617887242090636</v>
+        <v>-1.109203283918809</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3746524164525119</v>
+        <v>-1.182691108708749</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5479871674267475</v>
+        <v>-0.9746146672395217</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6885914638417949</v>
+        <v>-0.01608332695440042</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.0565998893170734</v>
+        <v>-0.8647081323842092</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.04614421298215181</v>
-      </c>
-      <c r="M9" t="inlineStr"/>
+        <v>-0.7769005786482469</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-0.2134800542680593</v>
+      </c>
       <c r="N9" t="n">
-        <v>-0.441503343952501</v>
+        <v>-0.9504345228074812</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3426781922940413</v>
+        <v>-0.6148875106898247</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.01551159329894776</v>
+        <v>-0.258507223371522</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2788846655153502</v>
+        <v>-0.8347032881710398</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>lYpTkOLs</t>
+          <t>Gp6AbAAT</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8188743134899813</v>
+        <v>-0.5522196347055954</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7622659642597908</v>
+        <v>0.1305103029164039</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6189942839123077</v>
+        <v>0.4043707629678023</v>
       </c>
       <c r="E10" t="n">
-        <v>0.04211622760254817</v>
+        <v>1.081359898532039</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1407498860355079</v>
+        <v>-0.2667929091768128</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3642330188146352</v>
+        <v>0.265455166117421</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1964752499889473</v>
+        <v>-0.2929478671559027</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1533862229118311</v>
+        <v>-0.6221481657558822</v>
       </c>
       <c r="J10" t="n">
-        <v>1.480210611744344</v>
+        <v>2.171035602332605</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9648512641107475</v>
+        <v>1.195454333336072</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7234473878074728</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.7595428153851388</v>
-      </c>
+        <v>0.9641717492931782</v>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>1.58090285862383</v>
+        <v>1.784725145125058</v>
       </c>
       <c r="O10" t="n">
-        <v>1.507509788740819</v>
+        <v>2.003375722925192</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7581381289778182</v>
+        <v>0.2821508981916026</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.849485369928158</v>
+        <v>1.825359038080488</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>UTsToXQN</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>-1.089104005994074</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-2.119044338745529</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-1.979962415025062</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.054080412946867</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-1.183285528860827</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.6564714590565774</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-1.657317338973111</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-1.541940539902537</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-1.081813726358947</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-0.7967365903916459</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-0.4444212369977332</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-0.5196579909025872</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-0.9551463180551236</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-0.7721446887195067</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.4142999603478467</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-0.7855582330211027</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Y1lKmgdB</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.8749413522637783</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.5883840703364156</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-1.047888760187941</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.2041862634844467</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.033202657524469</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0.9528050171482207</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.1243384133909171</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-0.3717225996320591</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-0.6719907402423255</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-0.4499578048691156</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-0.3421295682271684</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-0.2958967051057916</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-0.8849969969576442</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-0.7098504175451567</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-0.6909764778351962</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-1.480373744221479</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>EuWhpKkJ</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>-0.08929178515082328</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.5649224108178401</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.082565308011193</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.2637945906450659</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.1406205722589951</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.4918417045612208</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.304762841104986</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.2889037020777884</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-1.657833262242505</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-0.9906294455107092</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-0.7566702575452863</v>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="n">
+        <v>-1.711352044775649</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-2.071794810261851</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0.7891613155757138</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-1.472651219330218</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>4Md3iycn</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>-0.3816199284901388</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.7114034283262028</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.9058584889746654</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.5607658645393837</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.2639275152827336</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0.2613600482677215</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.236280079356351</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-0.1595426378963365</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-0.3768478204040515</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-0.2217303274762055</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="n">
+        <v>-0.1417370357195767</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.3686243048688147</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-0.03936589953695014</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-0.2215856258693287</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-0.9025696663259467</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>vuBo4Eth</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>-0.02213126811697107</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.03803431090841986</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.5219195005903686</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.8727478669138413</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.3779572376946718</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0.6893974099556495</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.2137918965918375</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.1655782564498114</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-0.5716498983447856</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-0.2076551062684487</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-0.2039503067461642</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-0.2588671608494623</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-0.7579773334570864</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-0.9272235857815471</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-0.4136351756675585</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-0.1641277418590291</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>n5Eg2hB4</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.4381581325543281</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.3352862759035707</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.813496849768266</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.357578704672834</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.8091143970631965</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-0.06380434287329315</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.4024629266998628</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.4734535241602817</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-0.5093760800305086</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-0.6604140955604363</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-0.4663219732660971</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-0.5513665673808581</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-1.008547079983129</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-0.9847182994248261</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-0.3750656797567636</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-0.6858650062385424</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>rX720WuH</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.5433678598024729</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.4951170185374512</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.601344323308319</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.3848737850720292</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.250719339467145</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.2942859991667932</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.8876061204998762</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.9513170810054635</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.266057024253387</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.653203531216452</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.649325001943288</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2.680256501110609</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.914055785204459</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.394786023469503</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.511206957927661</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.8975948924803029</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>bqYbtBlo</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.603101164269612</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.6936071339782097</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.5021935076316714</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.884945125711188</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.1875531303090652</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.3806959942641707</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.05976488207139166</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.08695142355816238</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-0.9155034516631874</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.005222623833988855</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="n">
+        <v>-0.9517456605922356</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-0.2259094828861832</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.4392070200231062</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-0.5993648905163104</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.2076531798662143</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>0ljCkFRb</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1.218539354588758</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.1827935300620635</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.253463599803697</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-0.7918011211836632</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.008331616252221603</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.109308416465419</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.8522561207213173</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.3071202497330769</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.205730524250235</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.09689237337686</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.005968078354834</v>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="n">
+        <v>2.183083148860708</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.824496662957592</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.6256076191422373</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.199419883172152</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_selected.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,975 +513,488 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>b59ZhlYj</t>
+          <t>UTsToXQN</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-1.494145886105382</v>
+        <v>-1.089104005994074</v>
       </c>
       <c r="C2" t="n">
-        <v>0.05277339939719972</v>
+        <v>-2.119044338745529</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3567158693370323</v>
+        <v>-1.979962415025062</v>
       </c>
       <c r="E2" t="n">
-        <v>2.553549223492907</v>
+        <v>1.054080412946867</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.8157340618883102</v>
+        <v>-1.183285528860827</v>
       </c>
       <c r="G2" t="n">
-        <v>1.41786344758492</v>
+        <v>-0.6564714590565774</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.40887825914999</v>
+        <v>-1.657317338973111</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5307943825439924</v>
+        <v>-1.541940539902537</v>
       </c>
       <c r="J2" t="n">
-        <v>2.182674188153003</v>
+        <v>-1.069208416812551</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8643699789188671</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
+        <v>-0.7996380630715636</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-0.4454343712539092</v>
+      </c>
       <c r="M2" t="n">
-        <v>1.715249234299654</v>
+        <v>-0.5196579909025872</v>
       </c>
       <c r="N2" t="n">
-        <v>1.214497137172322</v>
+        <v>-0.9639975089393359</v>
       </c>
       <c r="O2" t="n">
-        <v>1.03275254840236</v>
+        <v>-0.778049669596425</v>
       </c>
       <c r="P2" t="n">
-        <v>1.220932602123338</v>
+        <v>0.4227039563037084</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.8557618500321539</v>
+        <v>-0.7927019427234161</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>nRkUEVfA</t>
+          <t>EuWhpKkJ</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.9141068849728293</v>
+        <v>-0.08929178515082328</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.8690219807506178</v>
+        <v>0.5649224108178401</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.7874999296302688</v>
+        <v>1.082565308011193</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5737572027343</v>
+        <v>0.2637945906450659</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2740152279901214</v>
+        <v>0.1406205722589951</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.940583544120362</v>
+        <v>-0.4918417045612208</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.8986659372759538</v>
+        <v>0.304762841104986</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9892394537870582</v>
+        <v>0.2889037020777884</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.7673994594561081</v>
+        <v>-1.658028621727407</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.4121842807692509</v>
+        <v>-0.980392476285019</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.341911498832105</v>
-      </c>
-      <c r="M3" t="n">
-        <v>-0.2977463543715418</v>
-      </c>
+        <v>-0.755883102900614</v>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>-0.6644233727811136</v>
+        <v>-1.700256940444126</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.8977962524670838</v>
+        <v>-2.07185556017178</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2215856258693287</v>
+        <v>-0.7814646857878187</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.489825122073882</v>
+        <v>-1.465042233576137</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>WWnG5RHd</t>
+          <t>Y1lKmgdB</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1715548658288728</v>
+        <v>0.8749413522637783</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.1116840581259897</v>
+        <v>-0.5883840703364156</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.3022298363182437</v>
+        <v>-1.047888760187941</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8708301420648954</v>
+        <v>0.2041862634844467</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.03901712037883563</v>
+        <v>1.033202657524469</v>
       </c>
       <c r="G4" t="n">
-        <v>0.08436243617252812</v>
+        <v>-0.9528050171482207</v>
       </c>
       <c r="H4" t="n">
-        <v>0.08892976056047015</v>
+        <v>-0.1243384133909171</v>
       </c>
       <c r="I4" t="n">
-        <v>0.142298323344011</v>
+        <v>-0.3717225996320591</v>
       </c>
       <c r="J4" t="n">
-        <v>1.089658972692287</v>
+        <v>-0.6586923625832538</v>
       </c>
       <c r="K4" t="n">
-        <v>0.774397310817702</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
+        <v>-0.452622909940144</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-0.3478130293700226</v>
+      </c>
       <c r="M4" t="n">
-        <v>0.6035334967331737</v>
+        <v>-0.2958967051057916</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5478551809739014</v>
+        <v>-0.8751940264142155</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6490794358106857</v>
+        <v>-0.7076410926370029</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7581381289778182</v>
+        <v>-0.6909764778351962</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.262229914180223</v>
+        <v>-1.503254472940154</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>QB1LGiQc</t>
+          <t>4Md3iycn</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.5746064737168792</v>
+        <v>-0.3816199284901388</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.763902380016605</v>
+        <v>-0.7114034283262028</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.71858726313952</v>
+        <v>-0.9058584889746654</v>
       </c>
       <c r="E5" t="n">
-        <v>1.317242776260429</v>
+        <v>0.5607658645393837</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.01916119856581175</v>
+        <v>0.2639275152827336</v>
       </c>
       <c r="G5" t="n">
         <v>-0.2613600482677215</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6877459649382098</v>
+        <v>-0.236280079356351</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7517966075006308</v>
+        <v>-0.1595426378963365</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2869951620556818</v>
+        <v>-0.37546389653021</v>
       </c>
       <c r="K5" t="n">
-        <v>0.281142368462486</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.02876962369808287</v>
-      </c>
+        <v>-0.2196793118104066</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>-0.09464247575025052</v>
+        <v>-0.1292631754317479</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5116177067110346</v>
+        <v>0.3742039191717288</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3436860146384036</v>
+        <v>-0.03125956058097643</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3681654130209227</v>
+        <v>-0.2215856258693287</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1454326034677159</v>
+        <v>-0.9127998501494116</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>l8H0Dwy3</t>
+          <t>vuBo4Eth</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.4672695759574186</v>
+        <v>-0.02213126811697107</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1014640656132596</v>
+        <v>-0.03803431090841986</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1355415319082189</v>
+        <v>0.5219195005903686</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9649445394627079</v>
+        <v>0.8727478669138413</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5378589714660428</v>
+        <v>0.3779572376946718</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.545472133331506</v>
+        <v>-0.6893974099556495</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.273616906351171</v>
+        <v>0.2137918965918375</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.1037532491048</v>
+        <v>0.1655782564498114</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.4387012164251973</v>
+        <v>-0.5648144117841412</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1280680207290674</v>
+        <v>-0.203350971926636</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1477002956929472</v>
+        <v>-0.1997755377872052</v>
       </c>
       <c r="M6" t="n">
-        <v>0.07641052251886059</v>
+        <v>-0.2497989399709813</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2224209599728264</v>
+        <v>-0.7756911210483911</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1794266531830861</v>
+        <v>-0.9263076427250702</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01676052682967693</v>
+        <v>-0.4157531587800876</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.02935623008596802</v>
+        <v>-0.1511862458309207</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>dYK8BH5F</t>
+          <t>n5Eg2hB4</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-2.222269408842512</v>
+        <v>0.4381581325543281</v>
       </c>
       <c r="C7" t="n">
-        <v>-2.666763750058612</v>
+        <v>0.3352862759035707</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.959872606925816</v>
+        <v>0.813496849768266</v>
       </c>
       <c r="E7" t="n">
-        <v>1.868178949662952</v>
+        <v>0.357578704672834</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6320354995267445</v>
+        <v>0.8091143970631965</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.82958421839529</v>
+        <v>-0.06380434287329315</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.45903829100711</v>
+        <v>0.4024629266998628</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.48662137967578</v>
+        <v>0.4734535241602817</v>
       </c>
       <c r="J7" t="n">
-        <v>-3.318955279715238</v>
+        <v>-0.5070988666716786</v>
       </c>
       <c r="K7" t="n">
-        <v>-4.60709406644122</v>
+        <v>-0.6537926046466033</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.365203359987869</v>
-      </c>
-      <c r="M7" t="inlineStr"/>
+        <v>-0.4666026368424547</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-0.5462253685990638</v>
+      </c>
       <c r="N7" t="n">
-        <v>-2.960363101851597</v>
+        <v>-1.006590448238864</v>
       </c>
       <c r="O7" t="n">
-        <v>-3.020031170003769</v>
+        <v>-0.9798510859088047</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.786221799088887</v>
+        <v>-0.3750603424339831</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.581283759360275</v>
+        <v>-0.6811442896281282</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bJl87mmp</t>
+          <t>rX720WuH</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4162110350236226</v>
+        <v>0.5433678598024729</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.2077929315555111</v>
+        <v>0.4951170185374512</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3199836202199033</v>
+        <v>0.601344323308319</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2190046004076241</v>
+        <v>0.3848737850720292</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9212676257653331</v>
+        <v>1.250719339467145</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7264184787044203</v>
+        <v>-0.2942859991667932</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9420024563660192</v>
+        <v>0.8876061204998762</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7210042033069118</v>
+        <v>0.9513170810054635</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8773392577975514</v>
+        <v>1.280350356419517</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5132252900695891</v>
+        <v>3.649419275280097</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1872134253033116</v>
+        <v>1.647092669159903</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2595521475069723</v>
+        <v>2.687143715828145</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1433290034381357</v>
+        <v>1.936693623900217</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5029364957676546</v>
+        <v>1.381396687399485</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4989939838729616</v>
+        <v>1.508673010564203</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.6738577128512974</v>
+        <v>0.894058501933861</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>figxD9PM</t>
+          <t>bqYbtBlo</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.3107615853696001</v>
+        <v>0.603101164269612</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.152222794456274</v>
+        <v>0.6936071339782097</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.260934167007854</v>
+        <v>-0.5021935076316714</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6076175639302568</v>
+        <v>-0.884945125711188</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4373765517526328</v>
+        <v>0.1875531303090652</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.109203283918809</v>
+        <v>0.3806959942641707</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.182691108708749</v>
+        <v>0.05976488207139166</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9746146672395217</v>
+        <v>0.08695142355816238</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.01608332695440042</v>
+        <v>-0.9437807744578713</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.8647081323842092</v>
-      </c>
-      <c r="L9" t="n">
-        <v>-0.7769005786482469</v>
-      </c>
+        <v>0.07015212162968831</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>-0.2134800542680593</v>
+        <v>-0.9680480742461458</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9504345228074812</v>
+        <v>-0.213584760437518</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6148875106898247</v>
+        <v>0.4807421887656042</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.258507223371522</v>
+        <v>-0.5980430135742417</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.8347032881710398</v>
+        <v>0.2518240204578585</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Gp6AbAAT</t>
+          <t>0ljCkFRb</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.5522196347055954</v>
+        <v>1.218539354588758</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1305103029164039</v>
+        <v>0.1827935300620635</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4043707629678023</v>
+        <v>0.253463599803697</v>
       </c>
       <c r="E10" t="n">
-        <v>1.081359898532039</v>
+        <v>-0.7918011211836632</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2667929091768128</v>
+        <v>0.008331616252221603</v>
       </c>
       <c r="G10" t="n">
-        <v>0.265455166117421</v>
+        <v>2.109308416465419</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2929478671559027</v>
+        <v>0.8522561207213173</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6221481657558822</v>
+        <v>0.3071202497330769</v>
       </c>
       <c r="J10" t="n">
-        <v>2.171035602332605</v>
+        <v>1.189350781256033</v>
       </c>
       <c r="K10" t="n">
-        <v>1.195454333336072</v>
+        <v>1.11533875177473</v>
       </c>
       <c r="L10" t="n">
-        <v>0.9641717492931782</v>
+        <v>1.021109330593651</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>1.784725145125058</v>
+        <v>2.186904148929176</v>
       </c>
       <c r="O10" t="n">
-        <v>2.003375722925192</v>
+        <v>1.831202459405711</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2821508981916026</v>
+        <v>0.6273689356599329</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.825359038080488</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>UTsToXQN</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>-1.089104005994074</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-2.119044338745529</v>
-      </c>
-      <c r="D11" t="n">
-        <v>-1.979962415025062</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1.054080412946867</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-1.183285528860827</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-0.6564714590565774</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-1.657317338973111</v>
-      </c>
-      <c r="I11" t="n">
-        <v>-1.541940539902537</v>
-      </c>
-      <c r="J11" t="n">
-        <v>-1.081813726358947</v>
-      </c>
-      <c r="K11" t="n">
-        <v>-0.7967365903916459</v>
-      </c>
-      <c r="L11" t="n">
-        <v>-0.4444212369977332</v>
-      </c>
-      <c r="M11" t="n">
-        <v>-0.5196579909025872</v>
-      </c>
-      <c r="N11" t="n">
-        <v>-0.9551463180551236</v>
-      </c>
-      <c r="O11" t="n">
-        <v>-0.7721446887195067</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0.4142999603478467</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>-0.7855582330211027</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Y1lKmgdB</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0.8749413522637783</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-0.5883840703364156</v>
-      </c>
-      <c r="D12" t="n">
-        <v>-1.047888760187941</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.2041862634844467</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1.033202657524469</v>
-      </c>
-      <c r="G12" t="n">
-        <v>-0.9528050171482207</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-0.1243384133909171</v>
-      </c>
-      <c r="I12" t="n">
-        <v>-0.3717225996320591</v>
-      </c>
-      <c r="J12" t="n">
-        <v>-0.6719907402423255</v>
-      </c>
-      <c r="K12" t="n">
-        <v>-0.4499578048691156</v>
-      </c>
-      <c r="L12" t="n">
-        <v>-0.3421295682271684</v>
-      </c>
-      <c r="M12" t="n">
-        <v>-0.2958967051057916</v>
-      </c>
-      <c r="N12" t="n">
-        <v>-0.8849969969576442</v>
-      </c>
-      <c r="O12" t="n">
-        <v>-0.7098504175451567</v>
-      </c>
-      <c r="P12" t="n">
-        <v>-0.6909764778351962</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>-1.480373744221479</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>EuWhpKkJ</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>-0.08929178515082328</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.5649224108178401</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1.082565308011193</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.2637945906450659</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.1406205722589951</v>
-      </c>
-      <c r="G13" t="n">
-        <v>-0.4918417045612208</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.304762841104986</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.2889037020777884</v>
-      </c>
-      <c r="J13" t="n">
-        <v>-1.657833262242505</v>
-      </c>
-      <c r="K13" t="n">
-        <v>-0.9906294455107092</v>
-      </c>
-      <c r="L13" t="n">
-        <v>-0.7566702575452863</v>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="n">
-        <v>-1.711352044775649</v>
-      </c>
-      <c r="O13" t="n">
-        <v>-2.071794810261851</v>
-      </c>
-      <c r="P13" t="n">
-        <v>-0.7891613155757138</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>-1.472651219330218</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>4Md3iycn</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>-0.3816199284901388</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-0.7114034283262028</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.9058584889746654</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.5607658645393837</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.2639275152827336</v>
-      </c>
-      <c r="G14" t="n">
-        <v>-0.2613600482677215</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-0.236280079356351</v>
-      </c>
-      <c r="I14" t="n">
-        <v>-0.1595426378963365</v>
-      </c>
-      <c r="J14" t="n">
-        <v>-0.3768478204040515</v>
-      </c>
-      <c r="K14" t="n">
-        <v>-0.2217303274762055</v>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="n">
-        <v>-0.1417370357195767</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.3686243048688147</v>
-      </c>
-      <c r="O14" t="n">
-        <v>-0.03936589953695014</v>
-      </c>
-      <c r="P14" t="n">
-        <v>-0.2215856258693287</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>-0.9025696663259467</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>vuBo4Eth</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>-0.02213126811697107</v>
-      </c>
-      <c r="C15" t="n">
-        <v>-0.03803431090841986</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.5219195005903686</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.8727478669138413</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.3779572376946718</v>
-      </c>
-      <c r="G15" t="n">
-        <v>-0.6893974099556495</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.2137918965918375</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.1655782564498114</v>
-      </c>
-      <c r="J15" t="n">
-        <v>-0.5716498983447856</v>
-      </c>
-      <c r="K15" t="n">
-        <v>-0.2076551062684487</v>
-      </c>
-      <c r="L15" t="n">
-        <v>-0.2039503067461642</v>
-      </c>
-      <c r="M15" t="n">
-        <v>-0.2588671608494623</v>
-      </c>
-      <c r="N15" t="n">
-        <v>-0.7579773334570864</v>
-      </c>
-      <c r="O15" t="n">
-        <v>-0.9272235857815471</v>
-      </c>
-      <c r="P15" t="n">
-        <v>-0.4136351756675585</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>-0.1641277418590291</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>n5Eg2hB4</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0.4381581325543281</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.3352862759035707</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.813496849768266</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.357578704672834</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.8091143970631965</v>
-      </c>
-      <c r="G16" t="n">
-        <v>-0.06380434287329315</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.4024629266998628</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.4734535241602817</v>
-      </c>
-      <c r="J16" t="n">
-        <v>-0.5093760800305086</v>
-      </c>
-      <c r="K16" t="n">
-        <v>-0.6604140955604363</v>
-      </c>
-      <c r="L16" t="n">
-        <v>-0.4663219732660971</v>
-      </c>
-      <c r="M16" t="n">
-        <v>-0.5513665673808581</v>
-      </c>
-      <c r="N16" t="n">
-        <v>-1.008547079983129</v>
-      </c>
-      <c r="O16" t="n">
-        <v>-0.9847182994248261</v>
-      </c>
-      <c r="P16" t="n">
-        <v>-0.3750656797567636</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>-0.6858650062385424</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>rX720WuH</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0.5433678598024729</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.4951170185374512</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.601344323308319</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.3848737850720292</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1.250719339467145</v>
-      </c>
-      <c r="G17" t="n">
-        <v>-0.2942859991667932</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.8876061204998762</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.9513170810054635</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1.266057024253387</v>
-      </c>
-      <c r="K17" t="n">
-        <v>3.653203531216452</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1.649325001943288</v>
-      </c>
-      <c r="M17" t="n">
-        <v>2.680256501110609</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1.914055785204459</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.394786023469503</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.511206957927661</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.8975948924803029</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>bqYbtBlo</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>0.603101164269612</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.6936071339782097</v>
-      </c>
-      <c r="D18" t="n">
-        <v>-0.5021935076316714</v>
-      </c>
-      <c r="E18" t="n">
-        <v>-0.884945125711188</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.1875531303090652</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.3806959942641707</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.05976488207139166</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.08695142355816238</v>
-      </c>
-      <c r="J18" t="n">
-        <v>-0.9155034516631874</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.005222623833988855</v>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="n">
-        <v>-0.9517456605922356</v>
-      </c>
-      <c r="N18" t="n">
-        <v>-0.2259094828861832</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0.4392070200231062</v>
-      </c>
-      <c r="P18" t="n">
-        <v>-0.5993648905163104</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0.2076531798662143</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>0ljCkFRb</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1.218539354588758</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.1827935300620635</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.253463599803697</v>
-      </c>
-      <c r="E19" t="n">
-        <v>-0.7918011211836632</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.008331616252221603</v>
-      </c>
-      <c r="G19" t="n">
-        <v>2.109308416465419</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.8522561207213173</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.3071202497330769</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1.205730524250235</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1.09689237337686</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1.005968078354834</v>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="n">
-        <v>2.183083148860708</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.824496662957592</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0.6256076191422373</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1.199419883172152</v>
+        <v>1.224875229520009</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_selected.xlsx
@@ -425,86 +425,121 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:X10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_goal_attempts</t>
+          <t>is_cup</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_goals</t>
+          <t>dif_mean_last_120_matches_shots_on_goal</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_points</t>
+          <t>dif_mean_last_480_matches_shots_on_goal</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_goal_ratio</t>
+          <t>dif_mean_last_120_matches_goal_attempts</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_dangerous_attacks</t>
+          <t>dif_mean_last_120_matches_goals</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_ball_possession</t>
+          <t>dif_mean_last_480_matches_goals</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_ball_possession</t>
+          <t>dif_mean_last_480_matches_PPS</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_total_passes</t>
+          <t>dif_mean_last_480_matches_attacks</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_480_matches_dangerous_attacks</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_120_matches_dead_balls</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_480_matches_dead_balls</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_120_matches_ball_possession</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_480_matches_ball_possession</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_120_matches_yellow_cards</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_120_matches_red_cards</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_120_matches_KGP</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_120_matches_clean_sheet</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_480_matches_clean_sheet</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_start</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_sub</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_start</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_wage_player_miss</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_sub</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_start</t>
         </is>
@@ -513,488 +548,679 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>UTsToXQN</t>
+          <t>b59ZhlYj</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-1.089104005994074</v>
+        <v>-0.3599058830750308</v>
       </c>
       <c r="C2" t="n">
-        <v>-2.119044338745529</v>
+        <v>1.710743631542281</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.979962415025062</v>
+        <v>-0.6773641867586002</v>
       </c>
       <c r="E2" t="n">
-        <v>1.054080412946867</v>
+        <v>0.7265620854536937</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.183285528860827</v>
+        <v>1.837436302316097</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.6564714590565774</v>
+        <v>-0.4272217269101021</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.657317338973111</v>
+        <v>0.6207914482129464</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.541940539902537</v>
+        <v>-0.2755902281668369</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.069208416812551</v>
+        <v>-0.03925801139859179</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.7996380630715636</v>
+        <v>0.1753497759828859</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.4454343712539092</v>
+        <v>-0.1725821533118382</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.5196579909025872</v>
+        <v>0.5965235065968808</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.9639975089393359</v>
+        <v>-0.304129511942855</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.778049669596425</v>
+        <v>-1.60909346297759</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4227039563037084</v>
+        <v>0.1858363880754785</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.7927019427234161</v>
+        <v>0.304093406053983</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.030522106773776</v>
+      </c>
+      <c r="S2" t="n">
+        <v>-0.4616991107641448</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.171055587595844</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.216496786772881</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.3635307622098762</v>
+      </c>
+      <c r="W2" t="n">
+        <v>2.157730019592718</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.8260432361707218</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>EuWhpKkJ</t>
+          <t>nRkUEVfA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.08929178515082328</v>
+        <v>-0.3599058830750308</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5649224108178401</v>
+        <v>-0.6681812538398224</v>
       </c>
       <c r="D3" t="n">
-        <v>1.082565308011193</v>
+        <v>-0.4210583437337042</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2637945906450659</v>
+        <v>-1.468783363430817</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1406205722589951</v>
+        <v>-1.670085124702939</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.4918417045612208</v>
+        <v>-0.8440749626503906</v>
       </c>
       <c r="H3" t="n">
-        <v>0.304762841104986</v>
+        <v>0.9106740810342397</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2889037020777884</v>
+        <v>-0.9360067805215497</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.658028621727407</v>
+        <v>-0.4277378079154586</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.980392476285019</v>
+        <v>-0.7674681719576234</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.755883102900614</v>
-      </c>
-      <c r="M3" t="inlineStr"/>
+        <v>-0.3510913091945683</v>
+      </c>
+      <c r="M3" t="n">
+        <v>-1.40608358243841</v>
+      </c>
       <c r="N3" t="n">
-        <v>-1.700256940444126</v>
+        <v>-1.098391914476162</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.07185556017178</v>
-      </c>
-      <c r="P3" t="n">
-        <v>-0.7814646857878187</v>
-      </c>
+        <v>-0.3633822570342667</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>-1.465042233576137</v>
+        <v>-0.2286007813493715</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-0.3533793952129379</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-1.283475637688978</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-0.7539775774508379</v>
+      </c>
+      <c r="U3" t="n">
+        <v>-0.6551466635501546</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.02266541421508649</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-0.2359843669629579</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-1.473660996952944</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Y1lKmgdB</t>
+          <t>QB1LGiQc</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8749413522637783</v>
+        <v>-0.3599058830750308</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.5883840703364156</v>
+        <v>0.03806207150798988</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.047888760187941</v>
+        <v>-0.8373445608177252</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2041862634844467</v>
+        <v>0.2131345207952197</v>
       </c>
       <c r="F4" t="n">
-        <v>1.033202657524469</v>
+        <v>-0.6788290692410376</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.9528050171482207</v>
+        <v>-1.423168040422333</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1243384133909171</v>
+        <v>0.3860125499191102</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3717225996320591</v>
+        <v>-1.040104681936619</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.6586923625832538</v>
+        <v>-0.3269752693718961</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.452622909940144</v>
+        <v>2.258673306109492</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.3478130293700226</v>
+        <v>0.8451362643452778</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2958967051057916</v>
+        <v>0.06211992946667702</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8751940264142155</v>
+        <v>-0.7837682007987712</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7076410926370029</v>
+        <v>0.2149836600108486</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.6909764778351962</v>
+        <v>1.84010583430354</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.503254472940154</v>
+        <v>1.568034655021711</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-0.122729144881819</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-0.4424512545707199</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-0.302714068112666</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.5131771543204815</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.1882951621165427</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.08963326487390609</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.1656993028602143</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>4Md3iycn</t>
+          <t>WWnG5RHd</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.3816199284901388</v>
+        <v>-0.3599058830750308</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.7114034283262028</v>
+        <v>0.8744028515251354</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.9058584889746654</v>
+        <v>0.5074180037372389</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5607658645393837</v>
+        <v>-0.2206232493472842</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2639275152827336</v>
+        <v>0.4649279178303873</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2613600482677215</v>
+        <v>0.08856967839284208</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.236280079356351</v>
+        <v>0.1326018504579238</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1595426378963365</v>
+        <v>0.3881884719292334</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.37546389653021</v>
+        <v>0.2565774503912245</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.2196793118104066</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
+        <v>0.5479149328303442</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.632656468484712</v>
+      </c>
       <c r="M5" t="n">
-        <v>-0.1292631754317479</v>
+        <v>0.1464994416451303</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3742039191717288</v>
+        <v>0.1907914279966741</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.03125956058097643</v>
+        <v>-0.274402885181172</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2215856258693287</v>
+        <v>0.1858363880754785</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9127998501494116</v>
+        <v>-0.64293249634725</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.030522106773776</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.537585423277828</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.084728551915876</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.5386538928636554</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.04931113158429624</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.201722361028002</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.267614463603137</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>vuBo4Eth</t>
+          <t>l8H0Dwy3</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.02213126811697107</v>
+        <v>-0.3599058830750308</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.03803431090841986</v>
+        <v>-0.2778888898318207</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5219195005903686</v>
+        <v>0.04537543241254807</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8727478669138413</v>
+        <v>-1.71664494636939</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3779572376946718</v>
+        <v>0.3505522191232447</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.6893974099556495</v>
+        <v>0.1897955178247477</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2137918965918375</v>
+        <v>1.398702134377405</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1655782564498114</v>
+        <v>-1.063735498000458</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5648144117841412</v>
+        <v>-0.8167239328583649</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.203350971926636</v>
+        <v>0.2209699992703295</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.1997755377872052</v>
+        <v>-0.6142200016618612</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2497989399709813</v>
+        <v>-1.721100427904635</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7756911210483911</v>
+        <v>-1.292040719869342</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9263076427250702</v>
+        <v>-0.6748100585200976</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4157531587800876</v>
+        <v>0.1858363880754785</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1511862458309207</v>
+        <v>-0.39273213587782</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-0.6993547707096163</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.3353857218519511</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-0.4197940018615448</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.1880653108585775</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.3395631681187184</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.128407145567272</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-0.03908366629462074</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>n5Eg2hB4</t>
+          <t>dYK8BH5F</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4381581325543281</v>
+        <v>-0.3599058830750308</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3352862759035707</v>
+        <v>-3.418813152562878</v>
       </c>
       <c r="D7" t="n">
-        <v>0.813496849768266</v>
+        <v>-2.492252652473787</v>
       </c>
       <c r="E7" t="n">
-        <v>0.357578704672834</v>
+        <v>-3.062179253750219</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8091143970631965</v>
+        <v>-2.280088851141033</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.06380434287329315</v>
+        <v>-2.280469624189132</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4024629266998628</v>
+        <v>2.788403327719391</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4734535241602817</v>
+        <v>-1.319154710853845</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5070988666716786</v>
+        <v>-0.5465963408424968</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6537926046466033</v>
+        <v>-1.193256922640433</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.4666026368424547</v>
+        <v>-0.965116127397697</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5462253685990638</v>
+        <v>-2.801158183788836</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.006590448238864</v>
+        <v>-2.393552840652452</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9798510859088047</v>
+        <v>0.5264114614966795</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3750603424339831</v>
+        <v>0.1858363880754785</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.6811442896281282</v>
+        <v>2.919120377707291</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-1.275980396537413</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-0.8778377616659899</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-3.323208730386712</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-2.963949383959041</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-1.344141053571661</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-7.662065598525417</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-2.58994778056852</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>rX720WuH</t>
+          <t>bJl87mmp</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5433678598024729</v>
+        <v>-0.3599058830750308</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4951170185374512</v>
+        <v>0.6513786435205632</v>
       </c>
       <c r="D8" t="n">
-        <v>0.601344323308319</v>
+        <v>0.6655013773134499</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3848737850720292</v>
+        <v>0.3636219104364969</v>
       </c>
       <c r="F8" t="n">
-        <v>1.250719339467145</v>
+        <v>-0.1450758086077061</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2942859991667932</v>
+        <v>0.3013656036219576</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8876061204998762</v>
+        <v>-0.1943849885931757</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9513170810054635</v>
+        <v>1.453825521200317</v>
       </c>
       <c r="J8" t="n">
-        <v>1.280350356419517</v>
+        <v>1.305156483962819</v>
       </c>
       <c r="K8" t="n">
-        <v>3.649419275280097</v>
+        <v>0.7075857143363976</v>
       </c>
       <c r="L8" t="n">
-        <v>1.647092669159903</v>
+        <v>2.208034995176337</v>
       </c>
       <c r="M8" t="n">
-        <v>2.687143715828145</v>
+        <v>1.01279576667725</v>
       </c>
       <c r="N8" t="n">
-        <v>1.936693623900217</v>
+        <v>0.8397862300860824</v>
       </c>
       <c r="O8" t="n">
-        <v>1.381396687399485</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.508673010564203</v>
-      </c>
+        <v>-0.7192997444466447</v>
+      </c>
+      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="n">
-        <v>0.894058501933861</v>
+        <v>0.5953844676759615</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.1079211054493</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.5887672227012535</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.8508470740940742</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.129320062391939</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.08289588674841238</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.3223628884612232</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.6846860000724546</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bqYbtBlo</t>
+          <t>figxD9PM</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.603101164269612</v>
+        <v>-0.3599058830750308</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6936071339782097</v>
+        <v>-0.5938398511716313</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5021935076316714</v>
+        <v>-0.7339755993181695</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.884945125711188</v>
+        <v>-1.150104185366936</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1875531303090652</v>
+        <v>-0.6407038363386568</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3806959942641707</v>
+        <v>-1.144796981984592</v>
       </c>
       <c r="H9" t="n">
-        <v>0.05976488207139166</v>
+        <v>1.324819454501377</v>
       </c>
       <c r="I9" t="n">
-        <v>0.08695142355816238</v>
+        <v>-1.375684334621603</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.9437807744578713</v>
+        <v>-0.8762886536485475</v>
       </c>
       <c r="K9" t="n">
-        <v>0.07015212162968831</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
+        <v>-0.2960591979873696</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-1.001185891308536</v>
+      </c>
       <c r="M9" t="n">
-        <v>-0.9680480742461458</v>
+        <v>-1.344205273507544</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.213584760437518</v>
+        <v>-1.505881660689372</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4807421887656042</v>
-      </c>
-      <c r="P9" t="n">
-        <v>-0.5980430135742417</v>
-      </c>
+        <v>-0.3188925711077193</v>
+      </c>
+      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="n">
-        <v>0.2518240204578585</v>
+        <v>-1.473129313223233</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-1.045330146206294</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-1.248722564006405</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-0.004455347483578663</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-0.9352162523214952</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-0.7133899210125512</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-0.9635201553991795</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-0.8643414714171572</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>0ljCkFRb</t>
+          <t>Gp6AbAAT</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.218539354588758</v>
+        <v>-0.3599058830750308</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1827935300620635</v>
+        <v>0.558451890185325</v>
       </c>
       <c r="D10" t="n">
-        <v>0.253463599803697</v>
+        <v>0.2556007248179482</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7918011211836632</v>
+        <v>-0.6366766207084615</v>
       </c>
       <c r="F10" t="n">
-        <v>0.008331616252221603</v>
+        <v>0.4268026849280065</v>
       </c>
       <c r="G10" t="n">
-        <v>2.109308416465419</v>
+        <v>-0.02573307112672131</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8522561207213173</v>
+        <v>0.6875721375104134</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3071202497330769</v>
+        <v>-0.7267120921890499</v>
       </c>
       <c r="J10" t="n">
-        <v>1.189350781256033</v>
+        <v>-0.3757972306546511</v>
       </c>
       <c r="K10" t="n">
-        <v>1.11533875177473</v>
+        <v>0.7912227903633788</v>
       </c>
       <c r="L10" t="n">
-        <v>1.021109330593651</v>
-      </c>
-      <c r="M10" t="inlineStr"/>
+        <v>0.5136263428977412</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.2758813603187584</v>
+      </c>
       <c r="N10" t="n">
-        <v>2.186904148929176</v>
+        <v>-0.3920321324530076</v>
       </c>
       <c r="O10" t="n">
-        <v>1.831202459405711</v>
+        <v>1.238246436321436</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6273689356599329</v>
+        <v>-0.08987518629586511</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.224875229520009</v>
+        <v>-2.427379819099291</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.1079211054493</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.1215414840493157</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.160255081679961</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.783540879030881</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.572492121949167</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.518315842342165</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.824293200876743</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_selected.xlsx
@@ -606,19 +606,19 @@
         <v>-0.4616991107641448</v>
       </c>
       <c r="T2" t="n">
-        <v>2.171055587595844</v>
+        <v>2.172818065581398</v>
       </c>
       <c r="U2" t="n">
-        <v>1.216496786772881</v>
+        <v>1.204841275109347</v>
       </c>
       <c r="V2" t="n">
         <v>0.3635307622098762</v>
       </c>
       <c r="W2" t="n">
-        <v>2.157730019592718</v>
+        <v>2.155544702065573</v>
       </c>
       <c r="X2" t="n">
-        <v>0.8260432361707218</v>
+        <v>0.8265398387273903</v>
       </c>
     </row>
     <row r="3">
@@ -680,19 +680,19 @@
         <v>-1.283475637688978</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7539775774508379</v>
+        <v>-0.7663830724071415</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6551466635501546</v>
+        <v>-0.645770694607388</v>
       </c>
       <c r="V3" t="n">
-        <v>0.02266541421508649</v>
+        <v>0.02672651624789316</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.2359843669629579</v>
+        <v>-0.2346544817984842</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.473660996952944</v>
+        <v>-1.47545565928826</v>
       </c>
     </row>
     <row r="4">
@@ -984,19 +984,19 @@
         <v>-0.8778377616659899</v>
       </c>
       <c r="T7" t="n">
-        <v>-3.323208730386712</v>
+        <v>-3.325149252890543</v>
       </c>
       <c r="U7" t="n">
-        <v>-2.963949383959041</v>
+        <v>-2.965972302982025</v>
       </c>
       <c r="V7" t="n">
         <v>-1.344141053571661</v>
       </c>
       <c r="W7" t="n">
-        <v>-7.662065598525417</v>
+        <v>-7.662388986932908</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.58994778056852</v>
+        <v>-2.599183116598204</v>
       </c>
     </row>
     <row r="8">
@@ -1132,19 +1132,19 @@
         <v>-1.248722564006405</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.004455347483578663</v>
+        <v>0.006483885733290086</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.9352162523214952</v>
+        <v>-0.9343305761122164</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.7133899210125512</v>
+        <v>-0.7224419469796113</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.9635201553991795</v>
+        <v>-0.9604228198121816</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.8643414714171572</v>
+        <v>-0.8661969877799832</v>
       </c>
     </row>
     <row r="10">
@@ -1208,19 +1208,19 @@
         <v>0.1215414840493157</v>
       </c>
       <c r="T10" t="n">
-        <v>2.160255081679961</v>
+        <v>2.147729125229747</v>
       </c>
       <c r="U10" t="n">
-        <v>1.783540879030881</v>
+        <v>1.780295538759672</v>
       </c>
       <c r="V10" t="n">
         <v>0.572492121949167</v>
       </c>
       <c r="W10" t="n">
-        <v>1.518315842342165</v>
+        <v>1.517342904345922</v>
       </c>
       <c r="X10" t="n">
-        <v>1.824293200876743</v>
+        <v>1.828277735598424</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_selected.xlsx
@@ -425,802 +425,756 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X10"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>is_cup</t>
+          <t>dif_mean_last_360_matches_shots_on_goal</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_shots_on_goal</t>
+          <t>dif_mean_last_360_matches_goal_attempts</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_shots_on_goal</t>
+          <t>dif_mean_last_360_matches_goals</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_goal_attempts</t>
+          <t>dif_mean_last_360_matches_points</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_goals</t>
+          <t>dif_mean_last_360_matches_goal_ratio</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_goals</t>
+          <t>dif_mean_last_360_matches_attacks</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_PPS</t>
+          <t>dif_mean_last_360_matches_dangerous_attacks</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_attacks</t>
+          <t>dif_mean_last_360_matches_ball_possession</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_dangerous_attacks</t>
+          <t>dif_mean_last_60_matches_total_passes</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_dead_balls</t>
+          <t>dif_mean_last_360_matches_total_passes</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_dead_balls</t>
+          <t>dif_mean_last_360_matches_PPDA</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_ball_possession</t>
+          <t>dif_mean_last_360_matches_clean_sheet</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_ball_possession</t>
+          <t>dif_mean_rat_player_start</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_yellow_cards</t>
+          <t>dif_mean_pot_player_start</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_red_cards</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_120_matches_KGP</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_120_matches_clean_sheet</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_480_matches_clean_sheet</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_wage_player_miss</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
           <t>dif_mean_value_player_sub</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>b59ZhlYj</t>
+          <t>GryrQGK8</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.3599058830750308</v>
+        <v>1.113390232161491</v>
       </c>
       <c r="C2" t="n">
-        <v>1.710743631542281</v>
+        <v>1.373961530470889</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.6773641867586002</v>
+        <v>0.8168511407303304</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7265620854536937</v>
+        <v>0.7322303789239926</v>
       </c>
       <c r="F2" t="n">
-        <v>1.837436302316097</v>
+        <v>0.4728042676232283</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.4272217269101021</v>
+        <v>0.5341626840143012</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6207914482129464</v>
+        <v>0.872873975011928</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2755902281668369</v>
+        <v>0.4382308434191302</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.03925801139859179</v>
+        <v>-1.753073318970458</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1753497759828859</v>
+        <v>0.2173343583651602</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.1725821533118382</v>
+        <v>-0.2136067523764347</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5965235065968808</v>
+        <v>0.5518596207730274</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.304129511942855</v>
+        <v>-0.8086897192528119</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.60909346297759</v>
+        <v>-0.8464354295814858</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1858363880754785</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.304093406053983</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.030522106773776</v>
-      </c>
-      <c r="S2" t="n">
-        <v>-0.4616991107641448</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.172818065581398</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.204841275109347</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.3635307622098762</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2.155544702065573</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.8265398387273903</v>
+        <v>-0.2655281024215103</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>nRkUEVfA</t>
+          <t>SMfm4Zck</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.3599058830750308</v>
+        <v>1.001966388316364</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.6681812538398224</v>
+        <v>-0.2029697942398856</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.4210583437337042</v>
+        <v>-0.8425507892379399</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.468783363430817</v>
+        <v>-0.3727769696545887</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.670085124702939</v>
+        <v>1.045597171335448</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.8440749626503906</v>
+        <v>-0.5783521813473671</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9106740810342397</v>
+        <v>-0.6846908700995495</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9360067805215497</v>
+        <v>-1.078229128277048</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.4277378079154586</v>
+        <v>-1.536819133502709</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.7674681719576234</v>
+        <v>-1.156588771386546</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.3510913091945683</v>
+        <v>1.175832129041914</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.40608358243841</v>
+        <v>0.7938967494071046</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.098391914476162</v>
+        <v>-0.09888386592737583</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3633822570342667</v>
-      </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="n">
-        <v>-0.2286007813493715</v>
-      </c>
-      <c r="R3" t="n">
-        <v>-0.3533793952129379</v>
-      </c>
-      <c r="S3" t="n">
-        <v>-1.283475637688978</v>
-      </c>
-      <c r="T3" t="n">
-        <v>-0.7663830724071415</v>
-      </c>
-      <c r="U3" t="n">
-        <v>-0.645770694607388</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0.02672651624789316</v>
-      </c>
-      <c r="W3" t="n">
-        <v>-0.2346544817984842</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-1.47545565928826</v>
+        <v>-0.2826341978557363</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-0.6679683798339506</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>QB1LGiQc</t>
+          <t>Im9H9ezS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.3599058830750308</v>
+        <v>1.03799795537913</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03806207150798988</v>
+        <v>1.207702562565047</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.8373445608177252</v>
+        <v>0.6717709266945991</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2131345207952197</v>
+        <v>0.675171817651935</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6788290692410376</v>
+        <v>0.1319469406310609</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.423168040422333</v>
+        <v>2.803179346297943</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3860125499191102</v>
+        <v>1.997686827177754</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.040104681936619</v>
+        <v>2.282238421189783</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.3269752693718961</v>
+        <v>1.25158777558733</v>
       </c>
       <c r="K4" t="n">
-        <v>2.258673306109492</v>
+        <v>2.559833501755135</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8451362643452778</v>
+        <v>-1.348722491556425</v>
       </c>
       <c r="M4" t="n">
-        <v>0.06211992946667702</v>
+        <v>0.3609254589735233</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7837682007987712</v>
+        <v>3.134825269100369</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2149836600108486</v>
+        <v>2.154149852830441</v>
       </c>
       <c r="P4" t="n">
-        <v>1.84010583430354</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.568034655021711</v>
-      </c>
-      <c r="R4" t="n">
-        <v>-0.122729144881819</v>
-      </c>
-      <c r="S4" t="n">
-        <v>-0.4424512545707199</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-0.302714068112666</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0.5131771543204815</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.1882951621165427</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0.08963326487390609</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.1656993028602143</v>
+        <v>7.788209858319497</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>WWnG5RHd</t>
+          <t>xdpX3Q36</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.3599058830750308</v>
+        <v>0.1349039877398754</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8744028515251354</v>
+        <v>1.236679994757237</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5074180037372389</v>
+        <v>0.1265593939117396</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2206232493472842</v>
+        <v>-0.113200697952129</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4649279178303873</v>
+        <v>-0.4582388529017811</v>
       </c>
       <c r="G5" t="n">
-        <v>0.08856967839284208</v>
+        <v>0.9624055318700538</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1326018504579238</v>
+        <v>0.44121823788374</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3881884719292334</v>
+        <v>0.6268416393513023</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2565774503912245</v>
+        <v>0.7249452298011638</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5479149328303442</v>
+        <v>0.5885529784683046</v>
       </c>
       <c r="L5" t="n">
-        <v>1.632656468484712</v>
+        <v>-0.5888916586917855</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1464994416451303</v>
+        <v>-0.1343802195769549</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1907914279966741</v>
+        <v>0.6291165741928454</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.274402885181172</v>
+        <v>1.396789221136621</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1858363880754785</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-0.64293249634725</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.030522106773776</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.537585423277828</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.084728551915876</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.5386538928636554</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.04931113158429624</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.201722361028002</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.267614463603137</v>
+        <v>1.15210042122999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>l8H0Dwy3</t>
+          <t>b59ZhlYj</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.3599058830750308</v>
+        <v>-0.5590378729235299</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.2778888898318207</v>
+        <v>-1.38058044138358</v>
       </c>
       <c r="D6" t="n">
-        <v>0.04537543241254807</v>
+        <v>0.2807308886563236</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.71664494636939</v>
+        <v>0.5587241341544539</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3505522191232447</v>
+        <v>2.319578495964357</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1897955178247477</v>
+        <v>-0.8270838920265664</v>
       </c>
       <c r="H6" t="n">
-        <v>1.398702134377405</v>
+        <v>-0.8581925894637333</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.063735498000458</v>
+        <v>-0.3641448400253376</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.8167239328583649</v>
+        <v>0.2008468509028535</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2209699992703295</v>
+        <v>-0.5589172337427125</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6142200016618612</v>
+        <v>1.145160968189009</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.721100427904635</v>
-      </c>
-      <c r="N6" t="n">
-        <v>-1.292040719869342</v>
-      </c>
-      <c r="O6" t="n">
-        <v>-0.6748100585200976</v>
-      </c>
+        <v>0.3265573098496126</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>0.1858363880754785</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>-0.39273213587782</v>
-      </c>
-      <c r="R6" t="n">
-        <v>-0.6993547707096163</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.3353857218519511</v>
-      </c>
-      <c r="T6" t="n">
-        <v>-0.4197940018615448</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.1880653108585775</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0.3395631681187184</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.128407145567272</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-0.03908366629462074</v>
+        <v>2.279186116952506</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>dYK8BH5F</t>
+          <t>nRkUEVfA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.3599058830750308</v>
+        <v>0.01009955129325991</v>
       </c>
       <c r="C7" t="n">
-        <v>-3.418813152562878</v>
+        <v>-0.8550570888797364</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.492252652473787</v>
+        <v>-0.4909490452863656</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.062179253750219</v>
+        <v>-0.2811618149360732</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.280088851141033</v>
+        <v>1.564083421593441</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.280469624189132</v>
+        <v>-0.7743897032183537</v>
       </c>
       <c r="H7" t="n">
-        <v>2.788403327719391</v>
+        <v>-0.2896953014049846</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.319154710853845</v>
+        <v>-0.8545553497578419</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5465963408424968</v>
+        <v>-1.305299946707824</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.193256922640433</v>
+        <v>-1.053161634473345</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.965116127397697</v>
+        <v>0.3480153688300152</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.801158183788836</v>
+        <v>-0.9239491357243156</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.393552840652452</v>
+        <v>-1.807012920030738</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5264114614966795</v>
+        <v>-1.088288851849469</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1858363880754785</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.919120377707291</v>
-      </c>
-      <c r="R7" t="n">
-        <v>-1.275980396537413</v>
-      </c>
-      <c r="S7" t="n">
-        <v>-0.8778377616659899</v>
-      </c>
-      <c r="T7" t="n">
-        <v>-3.325149252890543</v>
-      </c>
-      <c r="U7" t="n">
-        <v>-2.965972302982025</v>
-      </c>
-      <c r="V7" t="n">
-        <v>-1.344141053571661</v>
-      </c>
-      <c r="W7" t="n">
-        <v>-7.662388986932908</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-2.599183116598204</v>
+        <v>-0.2564477632333106</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bJl87mmp</t>
+          <t>QB1LGiQc</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.3599058830750308</v>
+        <v>-0.8056300303938805</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6513786435205632</v>
+        <v>-0.4572617617094734</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6655013773134499</v>
+        <v>-1.505847269165701</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3636219104364969</v>
+        <v>-1.44925503759714</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1450758086077061</v>
+        <v>1.196061802161643</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3013656036219576</v>
+        <v>-0.9630362787708663</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1943849885931757</v>
+        <v>-0.02224322938454943</v>
       </c>
       <c r="I8" t="n">
-        <v>1.453825521200317</v>
+        <v>-0.6559586163848824</v>
       </c>
       <c r="J8" t="n">
-        <v>1.305156483962819</v>
+        <v>0.2059351846785653</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7075857143363976</v>
+        <v>-0.8195286371847378</v>
       </c>
       <c r="L8" t="n">
-        <v>2.208034995176337</v>
+        <v>0.9427595114920474</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01279576667725</v>
+        <v>-0.8919395850696932</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8397862300860824</v>
+        <v>0.2100076232501994</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7192997444466447</v>
-      </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="n">
-        <v>0.5953844676759615</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.1079211054493</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.5887672227012535</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.8508470740940742</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0.129320062391939</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0.08289588674841238</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0.3223628884612232</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0.6846860000724546</v>
+        <v>0.3979931193516148</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.08757168206761069</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>figxD9PM</t>
+          <t>WWnG5RHd</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.3599058830750308</v>
+        <v>0.5377814667956179</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.5938398511716313</v>
+        <v>0.2919662687277572</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7339755993181695</v>
+        <v>0.1189980660848241</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.150104185366936</v>
+        <v>-0.07884501493268578</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6407038363386568</v>
+        <v>0.7903759400795747</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.144796981984592</v>
+        <v>0.2842592047366539</v>
       </c>
       <c r="H9" t="n">
-        <v>1.324819454501377</v>
+        <v>-0.04308067677655226</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.375684334621603</v>
+        <v>0.1567732695964923</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.8762886536485475</v>
+        <v>0.4476310390248734</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.2960591979873696</v>
+        <v>0.23481067900785</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.001185891308536</v>
+        <v>0.08958009316591797</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.344205273507544</v>
+        <v>0.885924207539145</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.505881660689372</v>
+        <v>1.58609515831017</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3188925711077193</v>
-      </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="n">
-        <v>-1.473129313223233</v>
-      </c>
-      <c r="R9" t="n">
-        <v>-1.045330146206294</v>
-      </c>
-      <c r="S9" t="n">
-        <v>-1.248722564006405</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0.006483885733290086</v>
-      </c>
-      <c r="U9" t="n">
-        <v>-0.9343305761122164</v>
-      </c>
-      <c r="V9" t="n">
-        <v>-0.7224419469796113</v>
-      </c>
-      <c r="W9" t="n">
-        <v>-0.9604228198121816</v>
-      </c>
-      <c r="X9" t="n">
-        <v>-0.8661969877799832</v>
+        <v>0.7899283853403383</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.259328784947405</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
+          <t>l8H0Dwy3</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.641176955079851</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.3494837139342817</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.3286148763976501</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.08243583035303341</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.8759041655776509</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0.76667472793811</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.5665814704864155</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-1.269027854322651</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-1.447773292427753</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-1.23456479502071</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.8090633338766853</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.3764388596197331</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0.04055606412101758</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-0.2192040654391647</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.09909481565559561</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>dYK8BH5F</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>-2.971723895665359</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-2.111696520363853</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-2.393750560185963</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-1.682712953787743</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.696735392777583</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-1.46824564876615</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.6654133689752167</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-2.509480885110352</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-4.083530188246439</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-2.865277808675043</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.631287053769862</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-1.337265438913831</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-3.188102103392056</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-3.633547906734635</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-8.136132180912893</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>bJl87mmp</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.5377814667956179</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.5376279642153464</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.02448146824837932</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-0.09602285644240748</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.2000318422263683</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.440348250481136</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.9646732350059287</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.049448755876304</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.373850199277053</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.9172352635878234</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-0.2684426750405142</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.6698597406204414</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.8543318621549012</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.6377905571631129</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.3188214558055723</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>figxD9PM</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>-0.1341675653009762</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.1923324822620733</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.9043016331577505</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-1.006448456457651</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.5511765682611169</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-1.147804150501237</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.461131965078615</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-1.173880944774476</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-0.903321578426596</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-1.082281318847444</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.034417461233949</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-1.233374792052336</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-1.058218756805907</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-0.7532995530697074</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-1.02637639489598</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
           <t>Gp6AbAAT</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>-0.3599058830750308</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.558451890185325</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.2556007248179482</v>
-      </c>
-      <c r="E10" t="n">
-        <v>-0.6366766207084615</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.4268026849280065</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-0.02573307112672131</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.6875721375104134</v>
-      </c>
-      <c r="I10" t="n">
-        <v>-0.7267120921890499</v>
-      </c>
-      <c r="J10" t="n">
-        <v>-0.3757972306546511</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.7912227903633788</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.5136263428977412</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.2758813603187584</v>
-      </c>
-      <c r="N10" t="n">
-        <v>-0.3920321324530076</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.238246436321436</v>
-      </c>
-      <c r="P10" t="n">
-        <v>-0.08987518629586511</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>-2.427379819099291</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.1079211054493</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.1215414840493157</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.147729125229747</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.780295538759672</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0.572492121949167</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.517342904345922</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.828277735598424</v>
+      <c r="B14" t="n">
+        <v>0.8148813753973633</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.4347829137563611</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.3571798926326645</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.6048330771542327</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.9816988086632867</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0.9343520006789207</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.2821159661448166</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-0.2428325303514146</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-0.2087640180419423</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-0.666643921368868</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.05859779758910933</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2449329556803246</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.253358148333284</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.43035262832514</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.602152122623487</v>
       </c>
     </row>
   </sheetData>
